--- a/branches/develop/StructureDefinition-mii-pr-diagnose-condition.xlsx
+++ b/branches/develop/StructureDefinition-mii-pr-diagnose-condition.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2026.0.1</t>
+    <t>2027.0.0-dev</t>
   </si>
   <si>
     <t>Name</t>

--- a/branches/develop/StructureDefinition-mii-pr-diagnose-condition.xlsx
+++ b/branches/develop/StructureDefinition-mii-pr-diagnose-condition.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9492" uniqueCount="874">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9506" uniqueCount="875">
   <si>
     <t>Property</t>
   </si>
@@ -1269,6 +1269,9 @@
   </si>
   <si>
     <t>Condition.code.coding.extension.value[x].code</t>
+  </si>
+  <si>
+    <t>Note that FHIR strings SHALL NOT exceed 1MB in size</t>
   </si>
   <si>
     <t>Condition.code.coding:icd10-gm.extension:Mehrfachcodierungs-Kennzeichen.value[x].display</t>
@@ -11352,7 +11355,7 @@
         <v>82</v>
       </c>
       <c r="AI69" t="s" s="2">
-        <v>80</v>
+        <v>198</v>
       </c>
       <c r="AJ69" t="s" s="2">
         <v>119</v>
@@ -11710,7 +11713,7 @@
         <v>82</v>
       </c>
       <c r="AI72" t="s" s="2">
-        <v>80</v>
+        <v>198</v>
       </c>
       <c r="AJ72" t="s" s="2">
         <v>119</v>
@@ -11946,7 +11949,7 @@
         <v>91</v>
       </c>
       <c r="AI74" t="s" s="2">
-        <v>80</v>
+        <v>198</v>
       </c>
       <c r="AJ74" t="s" s="2">
         <v>103</v>
@@ -12184,7 +12187,7 @@
         <v>82</v>
       </c>
       <c r="AI76" t="s" s="2">
-        <v>80</v>
+        <v>198</v>
       </c>
       <c r="AJ76" t="s" s="2">
         <v>119</v>
@@ -12306,7 +12309,7 @@
         <v>91</v>
       </c>
       <c r="AI77" t="s" s="2">
-        <v>80</v>
+        <v>198</v>
       </c>
       <c r="AJ77" t="s" s="2">
         <v>103</v>
@@ -12426,7 +12429,7 @@
         <v>91</v>
       </c>
       <c r="AI78" t="s" s="2">
-        <v>80</v>
+        <v>198</v>
       </c>
       <c r="AJ78" t="s" s="2">
         <v>103</v>
@@ -12486,7 +12489,9 @@
       <c r="M79" t="s" s="2">
         <v>280</v>
       </c>
-      <c r="N79" s="2"/>
+      <c r="N79" t="s" s="2">
+        <v>402</v>
+      </c>
       <c r="O79" t="s" s="2">
         <v>281</v>
       </c>
@@ -12546,7 +12551,7 @@
         <v>91</v>
       </c>
       <c r="AI79" t="s" s="2">
-        <v>80</v>
+        <v>198</v>
       </c>
       <c r="AJ79" t="s" s="2">
         <v>103</v>
@@ -12572,10 +12577,10 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -12606,7 +12611,9 @@
       <c r="M80" t="s" s="2">
         <v>286</v>
       </c>
-      <c r="N80" s="2"/>
+      <c r="N80" t="s" s="2">
+        <v>402</v>
+      </c>
       <c r="O80" t="s" s="2">
         <v>287</v>
       </c>
@@ -12666,7 +12673,7 @@
         <v>91</v>
       </c>
       <c r="AI80" t="s" s="2">
-        <v>80</v>
+        <v>198</v>
       </c>
       <c r="AJ80" t="s" s="2">
         <v>103</v>
@@ -12692,10 +12699,10 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -12788,7 +12795,7 @@
         <v>91</v>
       </c>
       <c r="AI81" t="s" s="2">
-        <v>80</v>
+        <v>198</v>
       </c>
       <c r="AJ81" t="s" s="2">
         <v>103</v>
@@ -12814,13 +12821,13 @@
     </row>
     <row r="82">
       <c r="A82" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="B82" t="s" s="2">
         <v>360</v>
       </c>
       <c r="C82" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="D82" t="s" s="2">
         <v>80</v>
@@ -12842,7 +12849,7 @@
         <v>80</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="L82" t="s" s="2">
         <v>380</v>
@@ -12934,7 +12941,7 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="B83" t="s" s="2">
         <v>383</v>
@@ -13052,7 +13059,7 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="B84" t="s" s="2">
         <v>385</v>
@@ -13146,7 +13153,7 @@
         <v>82</v>
       </c>
       <c r="AI84" t="s" s="2">
-        <v>80</v>
+        <v>198</v>
       </c>
       <c r="AJ84" t="s" s="2">
         <v>119</v>
@@ -13172,7 +13179,7 @@
     </row>
     <row r="85">
       <c r="A85" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="B85" t="s" s="2">
         <v>387</v>
@@ -13215,7 +13222,7 @@
       </c>
       <c r="Q85" s="2"/>
       <c r="R85" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="S85" t="s" s="2">
         <v>80</v>
@@ -13292,7 +13299,7 @@
     </row>
     <row r="86">
       <c r="A86" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="B86" t="s" s="2">
         <v>390</v>
@@ -13355,7 +13362,7 @@
       </c>
       <c r="Y86" s="2"/>
       <c r="Z86" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="AA86" t="s" s="2">
         <v>80</v>
@@ -13382,7 +13389,7 @@
         <v>91</v>
       </c>
       <c r="AI86" t="s" s="2">
-        <v>80</v>
+        <v>198</v>
       </c>
       <c r="AJ86" t="s" s="2">
         <v>103</v>
@@ -13408,7 +13415,7 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="B87" t="s" s="2">
         <v>393</v>
@@ -13526,7 +13533,7 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="B88" t="s" s="2">
         <v>395</v>
@@ -13620,7 +13627,7 @@
         <v>82</v>
       </c>
       <c r="AI88" t="s" s="2">
-        <v>80</v>
+        <v>198</v>
       </c>
       <c r="AJ88" t="s" s="2">
         <v>119</v>
@@ -13646,7 +13653,7 @@
     </row>
     <row r="89">
       <c r="A89" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="B89" t="s" s="2">
         <v>397</v>
@@ -13742,7 +13749,7 @@
         <v>91</v>
       </c>
       <c r="AI89" t="s" s="2">
-        <v>80</v>
+        <v>198</v>
       </c>
       <c r="AJ89" t="s" s="2">
         <v>103</v>
@@ -13768,7 +13775,7 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="B90" t="s" s="2">
         <v>399</v>
@@ -13862,7 +13869,7 @@
         <v>91</v>
       </c>
       <c r="AI90" t="s" s="2">
-        <v>80</v>
+        <v>198</v>
       </c>
       <c r="AJ90" t="s" s="2">
         <v>103</v>
@@ -13888,7 +13895,7 @@
     </row>
     <row r="91">
       <c r="A91" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="B91" t="s" s="2">
         <v>401</v>
@@ -13922,7 +13929,9 @@
       <c r="M91" t="s" s="2">
         <v>280</v>
       </c>
-      <c r="N91" s="2"/>
+      <c r="N91" t="s" s="2">
+        <v>402</v>
+      </c>
       <c r="O91" t="s" s="2">
         <v>281</v>
       </c>
@@ -13982,7 +13991,7 @@
         <v>91</v>
       </c>
       <c r="AI91" t="s" s="2">
-        <v>80</v>
+        <v>198</v>
       </c>
       <c r="AJ91" t="s" s="2">
         <v>103</v>
@@ -14008,10 +14017,10 @@
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -14042,7 +14051,9 @@
       <c r="M92" t="s" s="2">
         <v>286</v>
       </c>
-      <c r="N92" s="2"/>
+      <c r="N92" t="s" s="2">
+        <v>402</v>
+      </c>
       <c r="O92" t="s" s="2">
         <v>287</v>
       </c>
@@ -14102,7 +14113,7 @@
         <v>91</v>
       </c>
       <c r="AI92" t="s" s="2">
-        <v>80</v>
+        <v>198</v>
       </c>
       <c r="AJ92" t="s" s="2">
         <v>103</v>
@@ -14128,10 +14139,10 @@
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -14224,7 +14235,7 @@
         <v>91</v>
       </c>
       <c r="AI93" t="s" s="2">
-        <v>80</v>
+        <v>198</v>
       </c>
       <c r="AJ93" t="s" s="2">
         <v>103</v>
@@ -14250,13 +14261,13 @@
     </row>
     <row r="94">
       <c r="A94" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="B94" t="s" s="2">
         <v>360</v>
       </c>
       <c r="C94" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="D94" t="s" s="2">
         <v>80</v>
@@ -14278,7 +14289,7 @@
         <v>80</v>
       </c>
       <c r="K94" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="L94" t="s" s="2">
         <v>380</v>
@@ -14370,7 +14381,7 @@
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="B95" t="s" s="2">
         <v>383</v>
@@ -14488,7 +14499,7 @@
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="B96" t="s" s="2">
         <v>385</v>
@@ -14582,7 +14593,7 @@
         <v>82</v>
       </c>
       <c r="AI96" t="s" s="2">
-        <v>80</v>
+        <v>198</v>
       </c>
       <c r="AJ96" t="s" s="2">
         <v>119</v>
@@ -14608,7 +14619,7 @@
     </row>
     <row r="97">
       <c r="A97" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="B97" t="s" s="2">
         <v>387</v>
@@ -14651,7 +14662,7 @@
       </c>
       <c r="Q97" s="2"/>
       <c r="R97" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="S97" t="s" s="2">
         <v>80</v>
@@ -14728,7 +14739,7 @@
     </row>
     <row r="98">
       <c r="A98" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="B98" t="s" s="2">
         <v>390</v>
@@ -14791,7 +14802,7 @@
       </c>
       <c r="Y98" s="2"/>
       <c r="Z98" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="AA98" t="s" s="2">
         <v>80</v>
@@ -14818,10 +14829,10 @@
         <v>91</v>
       </c>
       <c r="AI98" t="s" s="2">
-        <v>80</v>
+        <v>198</v>
       </c>
       <c r="AJ98" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="AK98" t="s" s="2">
         <v>80</v>
@@ -14844,7 +14855,7 @@
     </row>
     <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="B99" t="s" s="2">
         <v>393</v>
@@ -14962,7 +14973,7 @@
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="B100" t="s" s="2">
         <v>395</v>
@@ -15082,7 +15093,7 @@
     </row>
     <row r="101">
       <c r="A101" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="B101" t="s" s="2">
         <v>397</v>
@@ -15204,7 +15215,7 @@
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="B102" t="s" s="2">
         <v>399</v>
@@ -15324,7 +15335,7 @@
     </row>
     <row r="103">
       <c r="A103" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="B103" t="s" s="2">
         <v>401</v>
@@ -15444,10 +15455,10 @@
     </row>
     <row r="104" hidden="true">
       <c r="A104" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -15564,10 +15575,10 @@
     </row>
     <row r="105" hidden="true">
       <c r="A105" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -15686,7 +15697,7 @@
     </row>
     <row r="106">
       <c r="A106" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="B106" t="s" s="2">
         <v>361</v>
@@ -15715,7 +15726,7 @@
         <v>132</v>
       </c>
       <c r="L106" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="M106" t="s" s="2">
         <v>267</v>
@@ -15731,7 +15742,7 @@
       </c>
       <c r="Q106" s="2"/>
       <c r="R106" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="S106" t="s" s="2">
         <v>80</v>
@@ -15782,7 +15793,7 @@
         <v>91</v>
       </c>
       <c r="AI106" t="s" s="2">
-        <v>80</v>
+        <v>198</v>
       </c>
       <c r="AJ106" t="s" s="2">
         <v>103</v>
@@ -15808,7 +15819,7 @@
     </row>
     <row r="107">
       <c r="A107" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="B107" t="s" s="2">
         <v>362</v>
@@ -15837,10 +15848,10 @@
         <v>105</v>
       </c>
       <c r="L107" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="M107" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="N107" t="s" s="2">
         <v>275</v>
@@ -15902,7 +15913,7 @@
         <v>91</v>
       </c>
       <c r="AI107" t="s" s="2">
-        <v>80</v>
+        <v>198</v>
       </c>
       <c r="AJ107" t="s" s="2">
         <v>103</v>
@@ -15928,7 +15939,7 @@
     </row>
     <row r="108">
       <c r="A108" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="B108" t="s" s="2">
         <v>363</v>
@@ -15957,12 +15968,14 @@
         <v>166</v>
       </c>
       <c r="L108" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="M108" t="s" s="2">
         <v>280</v>
       </c>
-      <c r="N108" s="2"/>
+      <c r="N108" t="s" s="2">
+        <v>402</v>
+      </c>
       <c r="O108" t="s" s="2">
         <v>281</v>
       </c>
@@ -15977,7 +15990,7 @@
         <v>80</v>
       </c>
       <c r="T108" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="U108" t="s" s="2">
         <v>80</v>
@@ -16022,13 +16035,13 @@
         <v>91</v>
       </c>
       <c r="AI108" t="s" s="2">
-        <v>80</v>
+        <v>198</v>
       </c>
       <c r="AJ108" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="AK108" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="AL108" t="s" s="2">
         <v>80</v>
@@ -16048,7 +16061,7 @@
     </row>
     <row r="109" hidden="true">
       <c r="A109" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="B109" t="s" s="2">
         <v>365</v>
@@ -16082,7 +16095,9 @@
       <c r="M109" t="s" s="2">
         <v>286</v>
       </c>
-      <c r="N109" s="2"/>
+      <c r="N109" t="s" s="2">
+        <v>402</v>
+      </c>
       <c r="O109" t="s" s="2">
         <v>287</v>
       </c>
@@ -16142,7 +16157,7 @@
         <v>91</v>
       </c>
       <c r="AI109" t="s" s="2">
-        <v>80</v>
+        <v>198</v>
       </c>
       <c r="AJ109" t="s" s="2">
         <v>103</v>
@@ -16168,7 +16183,7 @@
     </row>
     <row r="110" hidden="true">
       <c r="A110" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="B110" t="s" s="2">
         <v>366</v>
@@ -16264,7 +16279,7 @@
         <v>91</v>
       </c>
       <c r="AI110" t="s" s="2">
-        <v>80</v>
+        <v>198</v>
       </c>
       <c r="AJ110" t="s" s="2">
         <v>103</v>
@@ -16290,13 +16305,13 @@
     </row>
     <row r="111">
       <c r="A111" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="B111" t="s" s="2">
         <v>356</v>
       </c>
       <c r="C111" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="D111" t="s" s="2">
         <v>80</v>
@@ -16318,13 +16333,13 @@
         <v>92</v>
       </c>
       <c r="K111" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="L111" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="M111" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="N111" t="s" s="2">
         <v>259</v>
@@ -16340,7 +16355,7 @@
         <v>80</v>
       </c>
       <c r="S111" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="T111" t="s" s="2">
         <v>80</v>
@@ -16359,7 +16374,7 @@
       </c>
       <c r="Y111" s="2"/>
       <c r="Z111" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="AA111" t="s" s="2">
         <v>80</v>
@@ -16392,7 +16407,7 @@
         <v>103</v>
       </c>
       <c r="AK111" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="AL111" t="s" s="2">
         <v>80</v>
@@ -16412,7 +16427,7 @@
     </row>
     <row r="112" hidden="true">
       <c r="A112" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="B112" t="s" s="2">
         <v>359</v>
@@ -16530,7 +16545,7 @@
     </row>
     <row r="113" hidden="true">
       <c r="A113" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="B113" t="s" s="2">
         <v>360</v>
@@ -16624,7 +16639,7 @@
         <v>82</v>
       </c>
       <c r="AI113" t="s" s="2">
-        <v>80</v>
+        <v>198</v>
       </c>
       <c r="AJ113" t="s" s="2">
         <v>119</v>
@@ -16650,7 +16665,7 @@
     </row>
     <row r="114">
       <c r="A114" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="B114" t="s" s="2">
         <v>361</v>
@@ -16679,7 +16694,7 @@
         <v>132</v>
       </c>
       <c r="L114" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="M114" t="s" s="2">
         <v>267</v>
@@ -16695,7 +16710,7 @@
       </c>
       <c r="Q114" s="2"/>
       <c r="R114" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="S114" t="s" s="2">
         <v>80</v>
@@ -16746,7 +16761,7 @@
         <v>91</v>
       </c>
       <c r="AI114" t="s" s="2">
-        <v>80</v>
+        <v>198</v>
       </c>
       <c r="AJ114" t="s" s="2">
         <v>103</v>
@@ -16772,7 +16787,7 @@
     </row>
     <row r="115">
       <c r="A115" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="B115" t="s" s="2">
         <v>362</v>
@@ -16801,10 +16816,10 @@
         <v>105</v>
       </c>
       <c r="L115" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="M115" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="N115" t="s" s="2">
         <v>275</v>
@@ -16866,7 +16881,7 @@
         <v>91</v>
       </c>
       <c r="AI115" t="s" s="2">
-        <v>80</v>
+        <v>198</v>
       </c>
       <c r="AJ115" t="s" s="2">
         <v>103</v>
@@ -16892,7 +16907,7 @@
     </row>
     <row r="116">
       <c r="A116" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="B116" t="s" s="2">
         <v>363</v>
@@ -16921,12 +16936,14 @@
         <v>166</v>
       </c>
       <c r="L116" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="M116" t="s" s="2">
         <v>280</v>
       </c>
-      <c r="N116" s="2"/>
+      <c r="N116" t="s" s="2">
+        <v>402</v>
+      </c>
       <c r="O116" t="s" s="2">
         <v>281</v>
       </c>
@@ -16986,13 +17003,13 @@
         <v>91</v>
       </c>
       <c r="AI116" t="s" s="2">
-        <v>80</v>
+        <v>198</v>
       </c>
       <c r="AJ116" t="s" s="2">
         <v>103</v>
       </c>
       <c r="AK116" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="AL116" t="s" s="2">
         <v>80</v>
@@ -17012,7 +17029,7 @@
     </row>
     <row r="117" hidden="true">
       <c r="A117" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="B117" t="s" s="2">
         <v>365</v>
@@ -17046,7 +17063,9 @@
       <c r="M117" t="s" s="2">
         <v>286</v>
       </c>
-      <c r="N117" s="2"/>
+      <c r="N117" t="s" s="2">
+        <v>402</v>
+      </c>
       <c r="O117" t="s" s="2">
         <v>287</v>
       </c>
@@ -17106,7 +17125,7 @@
         <v>91</v>
       </c>
       <c r="AI117" t="s" s="2">
-        <v>80</v>
+        <v>198</v>
       </c>
       <c r="AJ117" t="s" s="2">
         <v>103</v>
@@ -17132,7 +17151,7 @@
     </row>
     <row r="118" hidden="true">
       <c r="A118" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="B118" t="s" s="2">
         <v>366</v>
@@ -17228,7 +17247,7 @@
         <v>91</v>
       </c>
       <c r="AI118" t="s" s="2">
-        <v>80</v>
+        <v>198</v>
       </c>
       <c r="AJ118" t="s" s="2">
         <v>103</v>
@@ -17254,13 +17273,13 @@
     </row>
     <row r="119">
       <c r="A119" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="B119" t="s" s="2">
         <v>356</v>
       </c>
       <c r="C119" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="D119" t="s" s="2">
         <v>80</v>
@@ -17285,10 +17304,10 @@
         <v>144</v>
       </c>
       <c r="L119" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="M119" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="N119" t="s" s="2">
         <v>259</v>
@@ -17304,7 +17323,7 @@
         <v>80</v>
       </c>
       <c r="S119" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="T119" t="s" s="2">
         <v>80</v>
@@ -17323,7 +17342,7 @@
       </c>
       <c r="Y119" s="2"/>
       <c r="Z119" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="AA119" t="s" s="2">
         <v>80</v>
@@ -17356,7 +17375,7 @@
         <v>103</v>
       </c>
       <c r="AK119" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="AL119" t="s" s="2">
         <v>80</v>
@@ -17376,7 +17395,7 @@
     </row>
     <row r="120" hidden="true">
       <c r="A120" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="B120" t="s" s="2">
         <v>359</v>
@@ -17494,7 +17513,7 @@
     </row>
     <row r="121" hidden="true">
       <c r="A121" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="B121" t="s" s="2">
         <v>360</v>
@@ -17614,7 +17633,7 @@
     </row>
     <row r="122">
       <c r="A122" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="B122" t="s" s="2">
         <v>361</v>
@@ -17736,7 +17755,7 @@
     </row>
     <row r="123">
       <c r="A123" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="B123" t="s" s="2">
         <v>362</v>
@@ -17856,7 +17875,7 @@
     </row>
     <row r="124">
       <c r="A124" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="B124" t="s" s="2">
         <v>363</v>
@@ -17956,7 +17975,7 @@
         <v>103</v>
       </c>
       <c r="AK124" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="AL124" t="s" s="2">
         <v>80</v>
@@ -17976,7 +17995,7 @@
     </row>
     <row r="125" hidden="true">
       <c r="A125" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="B125" t="s" s="2">
         <v>365</v>
@@ -18096,7 +18115,7 @@
     </row>
     <row r="126" hidden="true">
       <c r="A126" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="B126" t="s" s="2">
         <v>366</v>
@@ -18218,13 +18237,13 @@
     </row>
     <row r="127">
       <c r="A127" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="B127" t="s" s="2">
         <v>356</v>
       </c>
       <c r="C127" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="D127" t="s" s="2">
         <v>80</v>
@@ -18249,10 +18268,10 @@
         <v>144</v>
       </c>
       <c r="L127" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="M127" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="N127" t="s" s="2">
         <v>259</v>
@@ -18268,7 +18287,7 @@
         <v>80</v>
       </c>
       <c r="S127" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="T127" t="s" s="2">
         <v>80</v>
@@ -18287,7 +18306,7 @@
       </c>
       <c r="Y127" s="2"/>
       <c r="Z127" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="AA127" t="s" s="2">
         <v>80</v>
@@ -18320,7 +18339,7 @@
         <v>103</v>
       </c>
       <c r="AK127" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="AL127" t="s" s="2">
         <v>80</v>
@@ -18340,7 +18359,7 @@
     </row>
     <row r="128" hidden="true">
       <c r="A128" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="B128" t="s" s="2">
         <v>359</v>
@@ -18458,7 +18477,7 @@
     </row>
     <row r="129" hidden="true">
       <c r="A129" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="B129" t="s" s="2">
         <v>360</v>
@@ -18578,7 +18597,7 @@
     </row>
     <row r="130">
       <c r="A130" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="B130" t="s" s="2">
         <v>361</v>
@@ -18700,7 +18719,7 @@
     </row>
     <row r="131" hidden="true">
       <c r="A131" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="B131" t="s" s="2">
         <v>362</v>
@@ -18820,7 +18839,7 @@
     </row>
     <row r="132">
       <c r="A132" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="B132" t="s" s="2">
         <v>363</v>
@@ -18920,7 +18939,7 @@
         <v>103</v>
       </c>
       <c r="AK132" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="AL132" t="s" s="2">
         <v>80</v>
@@ -18940,7 +18959,7 @@
     </row>
     <row r="133" hidden="true">
       <c r="A133" t="s" s="2">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="B133" t="s" s="2">
         <v>365</v>
@@ -19060,7 +19079,7 @@
     </row>
     <row r="134" hidden="true">
       <c r="A134" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="B134" t="s" s="2">
         <v>366</v>
@@ -19182,10 +19201,10 @@
     </row>
     <row r="135" hidden="true">
       <c r="A135" t="s" s="2">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="B135" t="s" s="2">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="C135" s="2"/>
       <c r="D135" t="s" s="2">
@@ -19284,7 +19303,7 @@
         <v>103</v>
       </c>
       <c r="AK135" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="AL135" t="s" s="2">
         <v>80</v>
@@ -19304,10 +19323,10 @@
     </row>
     <row r="136">
       <c r="A136" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="B136" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="C136" s="2"/>
       <c r="D136" t="s" s="2">
@@ -19333,13 +19352,13 @@
         <v>241</v>
       </c>
       <c r="L136" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="M136" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="N136" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="O136" s="2"/>
       <c r="P136" t="s" s="2">
@@ -19368,10 +19387,10 @@
         <v>156</v>
       </c>
       <c r="Y136" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="Z136" t="s" s="2">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="AA136" t="s" s="2">
         <v>80</v>
@@ -19389,7 +19408,7 @@
         <v>80</v>
       </c>
       <c r="AF136" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="AG136" t="s" s="2">
         <v>81</v>
@@ -19404,13 +19423,13 @@
         <v>103</v>
       </c>
       <c r="AK136" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="AL136" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AM136" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="AN136" t="s" s="2">
         <v>80</v>
@@ -19419,15 +19438,15 @@
         <v>80</v>
       </c>
       <c r="AP136" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
     </row>
     <row r="137" hidden="true">
       <c r="A137" t="s" s="2">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="B137" t="s" s="2">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="C137" s="2"/>
       <c r="D137" t="s" s="2">
@@ -19542,10 +19561,10 @@
     </row>
     <row r="138" hidden="true">
       <c r="A138" t="s" s="2">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="B138" t="s" s="2">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="C138" s="2"/>
       <c r="D138" t="s" s="2">
@@ -19662,10 +19681,10 @@
     </row>
     <row r="139" hidden="true">
       <c r="A139" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="B139" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="C139" s="2"/>
       <c r="D139" t="s" s="2">
@@ -19737,7 +19756,7 @@
         <v>80</v>
       </c>
       <c r="AB139" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="AC139" s="2"/>
       <c r="AD139" t="s" s="2">
@@ -19782,13 +19801,13 @@
     </row>
     <row r="140">
       <c r="A140" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="B140" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="C140" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="D140" t="s" s="2">
         <v>80</v>
@@ -19813,10 +19832,10 @@
         <v>144</v>
       </c>
       <c r="L140" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="M140" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="N140" t="s" s="2">
         <v>259</v>
@@ -19851,7 +19870,7 @@
       </c>
       <c r="Y140" s="2"/>
       <c r="Z140" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="AA140" t="s" s="2">
         <v>80</v>
@@ -19904,10 +19923,10 @@
     </row>
     <row r="141" hidden="true">
       <c r="A141" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="B141" t="s" s="2">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="C141" s="2"/>
       <c r="D141" t="s" s="2">
@@ -20022,10 +20041,10 @@
     </row>
     <row r="142" hidden="true">
       <c r="A142" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="B142" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="C142" s="2"/>
       <c r="D142" t="s" s="2">
@@ -20142,10 +20161,10 @@
     </row>
     <row r="143">
       <c r="A143" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="B143" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="C143" s="2"/>
       <c r="D143" t="s" s="2">
@@ -20190,7 +20209,7 @@
         <v>80</v>
       </c>
       <c r="S143" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="T143" t="s" s="2">
         <v>80</v>
@@ -20264,10 +20283,10 @@
     </row>
     <row r="144">
       <c r="A144" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="B144" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="C144" s="2"/>
       <c r="D144" t="s" s="2">
@@ -20384,10 +20403,10 @@
     </row>
     <row r="145">
       <c r="A145" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="B145" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="C145" s="2"/>
       <c r="D145" t="s" s="2">
@@ -20504,10 +20523,10 @@
     </row>
     <row r="146" hidden="true">
       <c r="A146" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="B146" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="C146" s="2"/>
       <c r="D146" t="s" s="2">
@@ -20624,10 +20643,10 @@
     </row>
     <row r="147" hidden="true">
       <c r="A147" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="B147" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="C147" s="2"/>
       <c r="D147" t="s" s="2">
@@ -20746,10 +20765,10 @@
     </row>
     <row r="148" hidden="true">
       <c r="A148" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="B148" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="C148" s="2"/>
       <c r="D148" t="s" s="2">
@@ -20868,14 +20887,14 @@
     </row>
     <row r="149">
       <c r="A149" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="B149" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="C149" s="2"/>
       <c r="D149" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="E149" s="2"/>
       <c r="F149" t="s" s="2">
@@ -20894,17 +20913,17 @@
         <v>92</v>
       </c>
       <c r="K149" t="s" s="2">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="L149" t="s" s="2">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="M149" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="N149" s="2"/>
       <c r="O149" t="s" s="2">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="P149" t="s" s="2">
         <v>80</v>
@@ -20953,7 +20972,7 @@
         <v>80</v>
       </c>
       <c r="AF149" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="AG149" t="s" s="2">
         <v>91</v>
@@ -20971,16 +20990,16 @@
         <v>80</v>
       </c>
       <c r="AL149" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="AM149" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN149" t="s" s="2">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="AO149" t="s" s="2">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="AP149" t="s" s="2">
         <v>80</v>
@@ -20988,10 +21007,10 @@
     </row>
     <row r="150" hidden="true">
       <c r="A150" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="B150" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="C150" s="2"/>
       <c r="D150" t="s" s="2">
@@ -21106,10 +21125,10 @@
     </row>
     <row r="151" hidden="true">
       <c r="A151" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="B151" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="C151" s="2"/>
       <c r="D151" t="s" s="2">
@@ -21226,10 +21245,10 @@
     </row>
     <row r="152">
       <c r="A152" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="B152" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="C152" s="2"/>
       <c r="D152" t="s" s="2">
@@ -21255,13 +21274,13 @@
         <v>105</v>
       </c>
       <c r="L152" t="s" s="2">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="M152" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="N152" t="s" s="2">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="O152" s="2"/>
       <c r="P152" t="s" s="2">
@@ -21311,7 +21330,7 @@
         <v>80</v>
       </c>
       <c r="AF152" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="AG152" t="s" s="2">
         <v>81</v>
@@ -21320,7 +21339,7 @@
         <v>91</v>
       </c>
       <c r="AI152" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="AJ152" t="s" s="2">
         <v>103</v>
@@ -21346,10 +21365,10 @@
     </row>
     <row r="153" hidden="true">
       <c r="A153" t="s" s="2">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="B153" t="s" s="2">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="C153" s="2"/>
       <c r="D153" t="s" s="2">
@@ -21375,13 +21394,13 @@
         <v>132</v>
       </c>
       <c r="L153" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="M153" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="N153" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="O153" s="2"/>
       <c r="P153" t="s" s="2">
@@ -21410,10 +21429,10 @@
         <v>148</v>
       </c>
       <c r="Y153" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="Z153" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="AA153" t="s" s="2">
         <v>80</v>
@@ -21431,7 +21450,7 @@
         <v>80</v>
       </c>
       <c r="AF153" t="s" s="2">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="AG153" t="s" s="2">
         <v>81</v>
@@ -21466,10 +21485,10 @@
     </row>
     <row r="154" hidden="true">
       <c r="A154" t="s" s="2">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="B154" t="s" s="2">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="C154" s="2"/>
       <c r="D154" t="s" s="2">
@@ -21495,13 +21514,13 @@
         <v>233</v>
       </c>
       <c r="L154" t="s" s="2">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="M154" t="s" s="2">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="N154" t="s" s="2">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="O154" s="2"/>
       <c r="P154" t="s" s="2">
@@ -21551,7 +21570,7 @@
         <v>80</v>
       </c>
       <c r="AF154" t="s" s="2">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="AG154" t="s" s="2">
         <v>81</v>
@@ -21586,10 +21605,10 @@
     </row>
     <row r="155" hidden="true">
       <c r="A155" t="s" s="2">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="B155" t="s" s="2">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="C155" s="2"/>
       <c r="D155" t="s" s="2">
@@ -21615,13 +21634,13 @@
         <v>105</v>
       </c>
       <c r="L155" t="s" s="2">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="M155" t="s" s="2">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="N155" t="s" s="2">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="O155" s="2"/>
       <c r="P155" t="s" s="2">
@@ -21671,7 +21690,7 @@
         <v>80</v>
       </c>
       <c r="AF155" t="s" s="2">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="AG155" t="s" s="2">
         <v>81</v>
@@ -21706,10 +21725,10 @@
     </row>
     <row r="156">
       <c r="A156" t="s" s="2">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="B156" t="s" s="2">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="C156" s="2"/>
       <c r="D156" t="s" s="2">
@@ -21732,16 +21751,16 @@
         <v>92</v>
       </c>
       <c r="K156" t="s" s="2">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="L156" t="s" s="2">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="M156" t="s" s="2">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="N156" t="s" s="2">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="O156" s="2"/>
       <c r="P156" t="s" s="2">
@@ -21791,7 +21810,7 @@
         <v>80</v>
       </c>
       <c r="AF156" t="s" s="2">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="AG156" t="s" s="2">
         <v>81</v>
@@ -21809,16 +21828,16 @@
         <v>80</v>
       </c>
       <c r="AL156" t="s" s="2">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="AM156" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN156" t="s" s="2">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="AO156" t="s" s="2">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="AP156" t="s" s="2">
         <v>80</v>
@@ -21826,10 +21845,10 @@
     </row>
     <row r="157" hidden="true">
       <c r="A157" t="s" s="2">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="B157" t="s" s="2">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="C157" s="2"/>
       <c r="D157" t="s" s="2">
@@ -21944,10 +21963,10 @@
     </row>
     <row r="158" hidden="true">
       <c r="A158" t="s" s="2">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="B158" t="s" s="2">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="C158" s="2"/>
       <c r="D158" t="s" s="2">
@@ -22064,10 +22083,10 @@
     </row>
     <row r="159">
       <c r="A159" t="s" s="2">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="B159" t="s" s="2">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="C159" s="2"/>
       <c r="D159" t="s" s="2">
@@ -22093,13 +22112,13 @@
         <v>105</v>
       </c>
       <c r="L159" t="s" s="2">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="M159" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="N159" t="s" s="2">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="O159" s="2"/>
       <c r="P159" t="s" s="2">
@@ -22149,7 +22168,7 @@
         <v>80</v>
       </c>
       <c r="AF159" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="AG159" t="s" s="2">
         <v>81</v>
@@ -22158,7 +22177,7 @@
         <v>91</v>
       </c>
       <c r="AI159" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="AJ159" t="s" s="2">
         <v>103</v>
@@ -22184,10 +22203,10 @@
     </row>
     <row r="160" hidden="true">
       <c r="A160" t="s" s="2">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="B160" t="s" s="2">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="C160" s="2"/>
       <c r="D160" t="s" s="2">
@@ -22213,13 +22232,13 @@
         <v>132</v>
       </c>
       <c r="L160" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="M160" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="N160" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="O160" s="2"/>
       <c r="P160" t="s" s="2">
@@ -22248,10 +22267,10 @@
         <v>148</v>
       </c>
       <c r="Y160" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="Z160" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="AA160" t="s" s="2">
         <v>80</v>
@@ -22269,7 +22288,7 @@
         <v>80</v>
       </c>
       <c r="AF160" t="s" s="2">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="AG160" t="s" s="2">
         <v>81</v>
@@ -22304,10 +22323,10 @@
     </row>
     <row r="161" hidden="true">
       <c r="A161" t="s" s="2">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="B161" t="s" s="2">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="C161" s="2"/>
       <c r="D161" t="s" s="2">
@@ -22333,13 +22352,13 @@
         <v>233</v>
       </c>
       <c r="L161" t="s" s="2">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="M161" t="s" s="2">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="N161" t="s" s="2">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="O161" s="2"/>
       <c r="P161" t="s" s="2">
@@ -22389,7 +22408,7 @@
         <v>80</v>
       </c>
       <c r="AF161" t="s" s="2">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="AG161" t="s" s="2">
         <v>81</v>
@@ -22424,10 +22443,10 @@
     </row>
     <row r="162" hidden="true">
       <c r="A162" t="s" s="2">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="B162" t="s" s="2">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="C162" s="2"/>
       <c r="D162" t="s" s="2">
@@ -22453,13 +22472,13 @@
         <v>105</v>
       </c>
       <c r="L162" t="s" s="2">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="M162" t="s" s="2">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="N162" t="s" s="2">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="O162" s="2"/>
       <c r="P162" t="s" s="2">
@@ -22509,7 +22528,7 @@
         <v>80</v>
       </c>
       <c r="AF162" t="s" s="2">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="AG162" t="s" s="2">
         <v>81</v>
@@ -22544,10 +22563,10 @@
     </row>
     <row r="163" hidden="true">
       <c r="A163" t="s" s="2">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="B163" t="s" s="2">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="C163" s="2"/>
       <c r="D163" t="s" s="2">
@@ -22570,16 +22589,16 @@
         <v>92</v>
       </c>
       <c r="K163" t="s" s="2">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="L163" t="s" s="2">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="M163" t="s" s="2">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="N163" t="s" s="2">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="O163" s="2"/>
       <c r="P163" t="s" s="2">
@@ -22617,17 +22636,17 @@
         <v>80</v>
       </c>
       <c r="AB163" t="s" s="2">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="AC163" s="2"/>
       <c r="AD163" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE163" t="s" s="2">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="AF163" t="s" s="2">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="AG163" t="s" s="2">
         <v>81</v>
@@ -22642,19 +22661,19 @@
         <v>103</v>
       </c>
       <c r="AK163" t="s" s="2">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="AL163" t="s" s="2">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="AM163" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN163" t="s" s="2">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="AO163" t="s" s="2">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="AP163" t="s" s="2">
         <v>80</v>
@@ -22662,13 +22681,13 @@
     </row>
     <row r="164">
       <c r="A164" t="s" s="2">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="B164" t="s" s="2">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="C164" t="s" s="2">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="D164" t="s" s="2">
         <v>80</v>
@@ -22690,16 +22709,16 @@
         <v>92</v>
       </c>
       <c r="K164" t="s" s="2">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="L164" t="s" s="2">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="M164" t="s" s="2">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="N164" t="s" s="2">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="O164" s="2"/>
       <c r="P164" t="s" s="2">
@@ -22749,7 +22768,7 @@
         <v>80</v>
       </c>
       <c r="AF164" t="s" s="2">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="AG164" t="s" s="2">
         <v>81</v>
@@ -22764,19 +22783,19 @@
         <v>103</v>
       </c>
       <c r="AK164" t="s" s="2">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="AL164" t="s" s="2">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="AM164" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN164" t="s" s="2">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="AO164" t="s" s="2">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="AP164" t="s" s="2">
         <v>80</v>
@@ -22784,10 +22803,10 @@
     </row>
     <row r="165" hidden="true">
       <c r="A165" t="s" s="2">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="B165" t="s" s="2">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="C165" s="2"/>
       <c r="D165" t="s" s="2">
@@ -22902,10 +22921,10 @@
     </row>
     <row r="166" hidden="true">
       <c r="A166" t="s" s="2">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="B166" t="s" s="2">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="C166" s="2"/>
       <c r="D166" t="s" s="2">
@@ -23022,10 +23041,10 @@
     </row>
     <row r="167">
       <c r="A167" t="s" s="2">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="B167" t="s" s="2">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="C167" s="2"/>
       <c r="D167" t="s" s="2">
@@ -23051,13 +23070,13 @@
         <v>226</v>
       </c>
       <c r="L167" t="s" s="2">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="M167" t="s" s="2">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="N167" t="s" s="2">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="O167" s="2"/>
       <c r="P167" t="s" s="2">
@@ -23107,7 +23126,7 @@
         <v>80</v>
       </c>
       <c r="AF167" t="s" s="2">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="AG167" t="s" s="2">
         <v>81</v>
@@ -23116,13 +23135,13 @@
         <v>91</v>
       </c>
       <c r="AI167" t="s" s="2">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="AJ167" t="s" s="2">
         <v>103</v>
       </c>
       <c r="AK167" t="s" s="2">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="AL167" t="s" s="2">
         <v>80</v>
@@ -23131,7 +23150,7 @@
         <v>80</v>
       </c>
       <c r="AN167" t="s" s="2">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="AO167" t="s" s="2">
         <v>80</v>
@@ -23142,10 +23161,10 @@
     </row>
     <row r="168" hidden="true">
       <c r="A168" t="s" s="2">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="B168" t="s" s="2">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="C168" s="2"/>
       <c r="D168" t="s" s="2">
@@ -23171,10 +23190,10 @@
         <v>105</v>
       </c>
       <c r="L168" t="s" s="2">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="M168" t="s" s="2">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="N168" s="2"/>
       <c r="O168" s="2"/>
@@ -23260,10 +23279,10 @@
     </row>
     <row r="169" hidden="true">
       <c r="A169" t="s" s="2">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="B169" t="s" s="2">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="C169" s="2"/>
       <c r="D169" t="s" s="2">
@@ -23376,13 +23395,13 @@
     </row>
     <row r="170">
       <c r="A170" t="s" s="2">
+        <v>622</v>
+      </c>
+      <c r="B170" t="s" s="2">
         <v>621</v>
       </c>
-      <c r="B170" t="s" s="2">
-        <v>620</v>
-      </c>
       <c r="C170" t="s" s="2">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="D170" t="s" s="2">
         <v>80</v>
@@ -23404,7 +23423,7 @@
         <v>80</v>
       </c>
       <c r="K170" t="s" s="2">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="L170" t="s" s="2">
         <v>380</v>
@@ -23496,10 +23515,10 @@
     </row>
     <row r="171" hidden="true">
       <c r="A171" t="s" s="2">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="B171" t="s" s="2">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="C171" s="2"/>
       <c r="D171" t="s" s="2">
@@ -23614,10 +23633,10 @@
     </row>
     <row r="172" hidden="true">
       <c r="A172" t="s" s="2">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="B172" t="s" s="2">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="C172" s="2"/>
       <c r="D172" t="s" s="2">
@@ -23708,7 +23727,7 @@
         <v>82</v>
       </c>
       <c r="AI172" t="s" s="2">
-        <v>80</v>
+        <v>198</v>
       </c>
       <c r="AJ172" t="s" s="2">
         <v>119</v>
@@ -23734,10 +23753,10 @@
     </row>
     <row r="173">
       <c r="A173" t="s" s="2">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="B173" t="s" s="2">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="C173" s="2"/>
       <c r="D173" t="s" s="2">
@@ -23777,7 +23796,7 @@
       </c>
       <c r="Q173" s="2"/>
       <c r="R173" t="s" s="2">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="S173" t="s" s="2">
         <v>80</v>
@@ -23854,10 +23873,10 @@
     </row>
     <row r="174">
       <c r="A174" t="s" s="2">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="B174" t="s" s="2">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="C174" s="2"/>
       <c r="D174" t="s" s="2">
@@ -23946,13 +23965,13 @@
         <v>91</v>
       </c>
       <c r="AI174" t="s" s="2">
-        <v>80</v>
+        <v>198</v>
       </c>
       <c r="AJ174" t="s" s="2">
         <v>103</v>
       </c>
       <c r="AK174" t="s" s="2">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="AL174" t="s" s="2">
         <v>80</v>
@@ -23972,10 +23991,10 @@
     </row>
     <row r="175" hidden="true">
       <c r="A175" t="s" s="2">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="B175" t="s" s="2">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="C175" s="2"/>
       <c r="D175" t="s" s="2">
@@ -24090,10 +24109,10 @@
     </row>
     <row r="176" hidden="true">
       <c r="A176" t="s" s="2">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="B176" t="s" s="2">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="C176" s="2"/>
       <c r="D176" t="s" s="2">
@@ -24184,7 +24203,7 @@
         <v>82</v>
       </c>
       <c r="AI176" t="s" s="2">
-        <v>80</v>
+        <v>198</v>
       </c>
       <c r="AJ176" t="s" s="2">
         <v>119</v>
@@ -24210,10 +24229,10 @@
     </row>
     <row r="177">
       <c r="A177" t="s" s="2">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="B177" t="s" s="2">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="C177" s="2"/>
       <c r="D177" t="s" s="2">
@@ -24276,10 +24295,10 @@
         <v>245</v>
       </c>
       <c r="Y177" t="s" s="2">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="Z177" t="s" s="2">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="AA177" t="s" s="2">
         <v>80</v>
@@ -24306,7 +24325,7 @@
         <v>82</v>
       </c>
       <c r="AI177" t="s" s="2">
-        <v>80</v>
+        <v>198</v>
       </c>
       <c r="AJ177" t="s" s="2">
         <v>103</v>
@@ -24332,10 +24351,10 @@
     </row>
     <row r="178" hidden="true">
       <c r="A178" t="s" s="2">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="B178" t="s" s="2">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="C178" s="2"/>
       <c r="D178" t="s" s="2">
@@ -24450,10 +24469,10 @@
     </row>
     <row r="179" hidden="true">
       <c r="A179" t="s" s="2">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="B179" t="s" s="2">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="C179" s="2"/>
       <c r="D179" t="s" s="2">
@@ -24544,7 +24563,7 @@
         <v>82</v>
       </c>
       <c r="AI179" t="s" s="2">
-        <v>80</v>
+        <v>198</v>
       </c>
       <c r="AJ179" t="s" s="2">
         <v>119</v>
@@ -24570,10 +24589,10 @@
     </row>
     <row r="180">
       <c r="A180" t="s" s="2">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="B180" t="s" s="2">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="C180" s="2"/>
       <c r="D180" t="s" s="2">
@@ -24666,7 +24685,7 @@
         <v>91</v>
       </c>
       <c r="AI180" t="s" s="2">
-        <v>80</v>
+        <v>198</v>
       </c>
       <c r="AJ180" t="s" s="2">
         <v>103</v>
@@ -24692,10 +24711,10 @@
     </row>
     <row r="181" hidden="true">
       <c r="A181" t="s" s="2">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="B181" t="s" s="2">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="C181" s="2"/>
       <c r="D181" t="s" s="2">
@@ -24786,7 +24805,7 @@
         <v>91</v>
       </c>
       <c r="AI181" t="s" s="2">
-        <v>80</v>
+        <v>198</v>
       </c>
       <c r="AJ181" t="s" s="2">
         <v>103</v>
@@ -24812,10 +24831,10 @@
     </row>
     <row r="182">
       <c r="A182" t="s" s="2">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="B182" t="s" s="2">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="C182" s="2"/>
       <c r="D182" t="s" s="2">
@@ -24846,7 +24865,9 @@
       <c r="M182" t="s" s="2">
         <v>280</v>
       </c>
-      <c r="N182" s="2"/>
+      <c r="N182" t="s" s="2">
+        <v>402</v>
+      </c>
       <c r="O182" t="s" s="2">
         <v>281</v>
       </c>
@@ -24906,7 +24927,7 @@
         <v>91</v>
       </c>
       <c r="AI182" t="s" s="2">
-        <v>80</v>
+        <v>198</v>
       </c>
       <c r="AJ182" t="s" s="2">
         <v>103</v>
@@ -24932,10 +24953,10 @@
     </row>
     <row r="183" hidden="true">
       <c r="A183" t="s" s="2">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="B183" t="s" s="2">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="C183" s="2"/>
       <c r="D183" t="s" s="2">
@@ -24966,7 +24987,9 @@
       <c r="M183" t="s" s="2">
         <v>286</v>
       </c>
-      <c r="N183" s="2"/>
+      <c r="N183" t="s" s="2">
+        <v>402</v>
+      </c>
       <c r="O183" t="s" s="2">
         <v>287</v>
       </c>
@@ -25026,7 +25049,7 @@
         <v>91</v>
       </c>
       <c r="AI183" t="s" s="2">
-        <v>80</v>
+        <v>198</v>
       </c>
       <c r="AJ183" t="s" s="2">
         <v>103</v>
@@ -25052,10 +25075,10 @@
     </row>
     <row r="184" hidden="true">
       <c r="A184" t="s" s="2">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="B184" t="s" s="2">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="C184" s="2"/>
       <c r="D184" t="s" s="2">
@@ -25148,7 +25171,7 @@
         <v>91</v>
       </c>
       <c r="AI184" t="s" s="2">
-        <v>80</v>
+        <v>198</v>
       </c>
       <c r="AJ184" t="s" s="2">
         <v>103</v>
@@ -25174,10 +25197,10 @@
     </row>
     <row r="185" hidden="true">
       <c r="A185" t="s" s="2">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="B185" t="s" s="2">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="C185" s="2"/>
       <c r="D185" t="s" s="2">
@@ -25270,7 +25293,7 @@
         <v>91</v>
       </c>
       <c r="AI185" t="s" s="2">
-        <v>80</v>
+        <v>198</v>
       </c>
       <c r="AJ185" t="s" s="2">
         <v>103</v>
@@ -25296,10 +25319,10 @@
     </row>
     <row r="186" hidden="true">
       <c r="A186" t="s" s="2">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="B186" t="s" s="2">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="C186" s="2"/>
       <c r="D186" t="s" s="2">
@@ -25325,10 +25348,10 @@
         <v>226</v>
       </c>
       <c r="L186" t="s" s="2">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="M186" t="s" s="2">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="N186" s="2"/>
       <c r="O186" s="2"/>
@@ -25379,7 +25402,7 @@
         <v>80</v>
       </c>
       <c r="AF186" t="s" s="2">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="AG186" t="s" s="2">
         <v>81</v>
@@ -25414,10 +25437,10 @@
     </row>
     <row r="187">
       <c r="A187" t="s" s="2">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="B187" t="s" s="2">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="C187" s="2"/>
       <c r="D187" t="s" s="2">
@@ -25443,20 +25466,20 @@
         <v>226</v>
       </c>
       <c r="L187" t="s" s="2">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="M187" t="s" s="2">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="N187" t="s" s="2">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="O187" s="2"/>
       <c r="P187" t="s" s="2">
         <v>80</v>
       </c>
       <c r="Q187" t="s" s="2">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="R187" t="s" s="2">
         <v>80</v>
@@ -25501,7 +25524,7 @@
         <v>80</v>
       </c>
       <c r="AF187" t="s" s="2">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="AG187" t="s" s="2">
         <v>81</v>
@@ -25510,13 +25533,13 @@
         <v>91</v>
       </c>
       <c r="AI187" t="s" s="2">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="AJ187" t="s" s="2">
         <v>103</v>
       </c>
       <c r="AK187" t="s" s="2">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="AL187" t="s" s="2">
         <v>80</v>
@@ -25525,7 +25548,7 @@
         <v>80</v>
       </c>
       <c r="AN187" t="s" s="2">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="AO187" t="s" s="2">
         <v>80</v>
@@ -25536,10 +25559,10 @@
     </row>
     <row r="188" hidden="true">
       <c r="A188" t="s" s="2">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="B188" t="s" s="2">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="C188" s="2"/>
       <c r="D188" t="s" s="2">
@@ -25565,10 +25588,10 @@
         <v>105</v>
       </c>
       <c r="L188" t="s" s="2">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="M188" t="s" s="2">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="N188" s="2"/>
       <c r="O188" s="2"/>
@@ -25654,10 +25677,10 @@
     </row>
     <row r="189" hidden="true">
       <c r="A189" t="s" s="2">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="B189" t="s" s="2">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="C189" s="2"/>
       <c r="D189" t="s" s="2">
@@ -25770,13 +25793,13 @@
     </row>
     <row r="190">
       <c r="A190" t="s" s="2">
+        <v>677</v>
+      </c>
+      <c r="B190" t="s" s="2">
         <v>676</v>
       </c>
-      <c r="B190" t="s" s="2">
-        <v>675</v>
-      </c>
       <c r="C190" t="s" s="2">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="D190" t="s" s="2">
         <v>80</v>
@@ -25798,7 +25821,7 @@
         <v>80</v>
       </c>
       <c r="K190" t="s" s="2">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="L190" t="s" s="2">
         <v>380</v>
@@ -25890,10 +25913,10 @@
     </row>
     <row r="191" hidden="true">
       <c r="A191" t="s" s="2">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="B191" t="s" s="2">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="C191" s="2"/>
       <c r="D191" t="s" s="2">
@@ -26008,10 +26031,10 @@
     </row>
     <row r="192" hidden="true">
       <c r="A192" t="s" s="2">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="B192" t="s" s="2">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="C192" s="2"/>
       <c r="D192" t="s" s="2">
@@ -26102,7 +26125,7 @@
         <v>82</v>
       </c>
       <c r="AI192" t="s" s="2">
-        <v>80</v>
+        <v>198</v>
       </c>
       <c r="AJ192" t="s" s="2">
         <v>119</v>
@@ -26128,10 +26151,10 @@
     </row>
     <row r="193">
       <c r="A193" t="s" s="2">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="B193" t="s" s="2">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="C193" s="2"/>
       <c r="D193" t="s" s="2">
@@ -26171,7 +26194,7 @@
       </c>
       <c r="Q193" s="2"/>
       <c r="R193" t="s" s="2">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="S193" t="s" s="2">
         <v>80</v>
@@ -26248,10 +26271,10 @@
     </row>
     <row r="194">
       <c r="A194" t="s" s="2">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="B194" t="s" s="2">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="C194" s="2"/>
       <c r="D194" t="s" s="2">
@@ -26340,13 +26363,13 @@
         <v>91</v>
       </c>
       <c r="AI194" t="s" s="2">
-        <v>80</v>
+        <v>198</v>
       </c>
       <c r="AJ194" t="s" s="2">
         <v>103</v>
       </c>
       <c r="AK194" t="s" s="2">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="AL194" t="s" s="2">
         <v>80</v>
@@ -26366,10 +26389,10 @@
     </row>
     <row r="195" hidden="true">
       <c r="A195" t="s" s="2">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="B195" t="s" s="2">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="C195" s="2"/>
       <c r="D195" t="s" s="2">
@@ -26484,10 +26507,10 @@
     </row>
     <row r="196" hidden="true">
       <c r="A196" t="s" s="2">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="B196" t="s" s="2">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="C196" s="2"/>
       <c r="D196" t="s" s="2">
@@ -26578,7 +26601,7 @@
         <v>82</v>
       </c>
       <c r="AI196" t="s" s="2">
-        <v>80</v>
+        <v>198</v>
       </c>
       <c r="AJ196" t="s" s="2">
         <v>119</v>
@@ -26604,10 +26627,10 @@
     </row>
     <row r="197">
       <c r="A197" t="s" s="2">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="B197" t="s" s="2">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="C197" s="2"/>
       <c r="D197" t="s" s="2">
@@ -26670,10 +26693,10 @@
         <v>245</v>
       </c>
       <c r="Y197" t="s" s="2">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="Z197" t="s" s="2">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="AA197" t="s" s="2">
         <v>80</v>
@@ -26700,7 +26723,7 @@
         <v>82</v>
       </c>
       <c r="AI197" t="s" s="2">
-        <v>80</v>
+        <v>198</v>
       </c>
       <c r="AJ197" t="s" s="2">
         <v>103</v>
@@ -26726,10 +26749,10 @@
     </row>
     <row r="198" hidden="true">
       <c r="A198" t="s" s="2">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="B198" t="s" s="2">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="C198" s="2"/>
       <c r="D198" t="s" s="2">
@@ -26844,10 +26867,10 @@
     </row>
     <row r="199" hidden="true">
       <c r="A199" t="s" s="2">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="B199" t="s" s="2">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="C199" s="2"/>
       <c r="D199" t="s" s="2">
@@ -26938,7 +26961,7 @@
         <v>82</v>
       </c>
       <c r="AI199" t="s" s="2">
-        <v>80</v>
+        <v>198</v>
       </c>
       <c r="AJ199" t="s" s="2">
         <v>119</v>
@@ -26964,10 +26987,10 @@
     </row>
     <row r="200">
       <c r="A200" t="s" s="2">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="B200" t="s" s="2">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="C200" s="2"/>
       <c r="D200" t="s" s="2">
@@ -27060,7 +27083,7 @@
         <v>91</v>
       </c>
       <c r="AI200" t="s" s="2">
-        <v>80</v>
+        <v>198</v>
       </c>
       <c r="AJ200" t="s" s="2">
         <v>103</v>
@@ -27086,10 +27109,10 @@
     </row>
     <row r="201" hidden="true">
       <c r="A201" t="s" s="2">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="B201" t="s" s="2">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="C201" s="2"/>
       <c r="D201" t="s" s="2">
@@ -27180,7 +27203,7 @@
         <v>91</v>
       </c>
       <c r="AI201" t="s" s="2">
-        <v>80</v>
+        <v>198</v>
       </c>
       <c r="AJ201" t="s" s="2">
         <v>103</v>
@@ -27206,10 +27229,10 @@
     </row>
     <row r="202">
       <c r="A202" t="s" s="2">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="B202" t="s" s="2">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="C202" s="2"/>
       <c r="D202" t="s" s="2">
@@ -27240,7 +27263,9 @@
       <c r="M202" t="s" s="2">
         <v>280</v>
       </c>
-      <c r="N202" s="2"/>
+      <c r="N202" t="s" s="2">
+        <v>402</v>
+      </c>
       <c r="O202" t="s" s="2">
         <v>281</v>
       </c>
@@ -27300,7 +27325,7 @@
         <v>91</v>
       </c>
       <c r="AI202" t="s" s="2">
-        <v>80</v>
+        <v>198</v>
       </c>
       <c r="AJ202" t="s" s="2">
         <v>103</v>
@@ -27326,10 +27351,10 @@
     </row>
     <row r="203" hidden="true">
       <c r="A203" t="s" s="2">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="B203" t="s" s="2">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="C203" s="2"/>
       <c r="D203" t="s" s="2">
@@ -27360,7 +27385,9 @@
       <c r="M203" t="s" s="2">
         <v>286</v>
       </c>
-      <c r="N203" s="2"/>
+      <c r="N203" t="s" s="2">
+        <v>402</v>
+      </c>
       <c r="O203" t="s" s="2">
         <v>287</v>
       </c>
@@ -27420,7 +27447,7 @@
         <v>91</v>
       </c>
       <c r="AI203" t="s" s="2">
-        <v>80</v>
+        <v>198</v>
       </c>
       <c r="AJ203" t="s" s="2">
         <v>103</v>
@@ -27446,10 +27473,10 @@
     </row>
     <row r="204" hidden="true">
       <c r="A204" t="s" s="2">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="B204" t="s" s="2">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="C204" s="2"/>
       <c r="D204" t="s" s="2">
@@ -27542,7 +27569,7 @@
         <v>91</v>
       </c>
       <c r="AI204" t="s" s="2">
-        <v>80</v>
+        <v>198</v>
       </c>
       <c r="AJ204" t="s" s="2">
         <v>103</v>
@@ -27568,10 +27595,10 @@
     </row>
     <row r="205" hidden="true">
       <c r="A205" t="s" s="2">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="B205" t="s" s="2">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="C205" s="2"/>
       <c r="D205" t="s" s="2">
@@ -27664,7 +27691,7 @@
         <v>91</v>
       </c>
       <c r="AI205" t="s" s="2">
-        <v>80</v>
+        <v>198</v>
       </c>
       <c r="AJ205" t="s" s="2">
         <v>103</v>
@@ -27690,10 +27717,10 @@
     </row>
     <row r="206" hidden="true">
       <c r="A206" t="s" s="2">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="B206" t="s" s="2">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="C206" s="2"/>
       <c r="D206" t="s" s="2">
@@ -27719,10 +27746,10 @@
         <v>226</v>
       </c>
       <c r="L206" t="s" s="2">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="M206" t="s" s="2">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="N206" s="2"/>
       <c r="O206" s="2"/>
@@ -27773,7 +27800,7 @@
         <v>80</v>
       </c>
       <c r="AF206" t="s" s="2">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="AG206" t="s" s="2">
         <v>81</v>
@@ -27808,13 +27835,13 @@
     </row>
     <row r="207">
       <c r="A207" t="s" s="2">
-        <v>711</v>
+        <v>712</v>
       </c>
       <c r="B207" t="s" s="2">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="C207" t="s" s="2">
-        <v>712</v>
+        <v>713</v>
       </c>
       <c r="D207" t="s" s="2">
         <v>80</v>
@@ -27839,13 +27866,13 @@
         <v>226</v>
       </c>
       <c r="L207" t="s" s="2">
-        <v>713</v>
+        <v>714</v>
       </c>
       <c r="M207" t="s" s="2">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="N207" t="s" s="2">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="O207" s="2"/>
       <c r="P207" t="s" s="2">
@@ -27895,7 +27922,7 @@
         <v>80</v>
       </c>
       <c r="AF207" t="s" s="2">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="AG207" t="s" s="2">
         <v>81</v>
@@ -27913,16 +27940,16 @@
         <v>80</v>
       </c>
       <c r="AL207" t="s" s="2">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="AM207" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN207" t="s" s="2">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="AO207" t="s" s="2">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="AP207" t="s" s="2">
         <v>80</v>
@@ -27930,13 +27957,13 @@
     </row>
     <row r="208">
       <c r="A208" t="s" s="2">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="B208" t="s" s="2">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="C208" t="s" s="2">
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="D208" t="s" s="2">
         <v>80</v>
@@ -27958,16 +27985,16 @@
         <v>92</v>
       </c>
       <c r="K208" t="s" s="2">
-        <v>717</v>
+        <v>718</v>
       </c>
       <c r="L208" t="s" s="2">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="M208" t="s" s="2">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="N208" t="s" s="2">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="O208" s="2"/>
       <c r="P208" t="s" s="2">
@@ -28017,7 +28044,7 @@
         <v>80</v>
       </c>
       <c r="AF208" t="s" s="2">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="AG208" t="s" s="2">
         <v>81</v>
@@ -28035,16 +28062,16 @@
         <v>80</v>
       </c>
       <c r="AL208" t="s" s="2">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="AM208" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN208" t="s" s="2">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="AO208" t="s" s="2">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="AP208" t="s" s="2">
         <v>80</v>
@@ -28052,10 +28079,10 @@
     </row>
     <row r="209" hidden="true">
       <c r="A209" t="s" s="2">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="B209" t="s" s="2">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="C209" s="2"/>
       <c r="D209" t="s" s="2">
@@ -28170,10 +28197,10 @@
     </row>
     <row r="210" hidden="true">
       <c r="A210" t="s" s="2">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="B210" t="s" s="2">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="C210" s="2"/>
       <c r="D210" t="s" s="2">
@@ -28290,13 +28317,13 @@
     </row>
     <row r="211" hidden="true">
       <c r="A211" t="s" s="2">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="B211" t="s" s="2">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="C211" t="s" s="2">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="D211" t="s" s="2">
         <v>80</v>
@@ -28318,16 +28345,16 @@
         <v>80</v>
       </c>
       <c r="K211" t="s" s="2">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="L211" t="s" s="2">
-        <v>724</v>
+        <v>725</v>
       </c>
       <c r="M211" t="s" s="2">
         <v>381</v>
       </c>
       <c r="N211" t="s" s="2">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="O211" s="2"/>
       <c r="P211" t="s" s="2">
@@ -28412,10 +28439,10 @@
     </row>
     <row r="212" hidden="true">
       <c r="A212" t="s" s="2">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="B212" t="s" s="2">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="C212" s="2"/>
       <c r="D212" t="s" s="2">
@@ -28530,10 +28557,10 @@
     </row>
     <row r="213" hidden="true">
       <c r="A213" t="s" s="2">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="B213" t="s" s="2">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="C213" s="2"/>
       <c r="D213" t="s" s="2">
@@ -28624,7 +28651,7 @@
         <v>82</v>
       </c>
       <c r="AI213" t="s" s="2">
-        <v>80</v>
+        <v>198</v>
       </c>
       <c r="AJ213" t="s" s="2">
         <v>119</v>
@@ -28650,10 +28677,10 @@
     </row>
     <row r="214">
       <c r="A214" t="s" s="2">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="B214" t="s" s="2">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="C214" s="2"/>
       <c r="D214" t="s" s="2">
@@ -28693,7 +28720,7 @@
       </c>
       <c r="Q214" s="2"/>
       <c r="R214" t="s" s="2">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="S214" t="s" s="2">
         <v>80</v>
@@ -28770,10 +28797,10 @@
     </row>
     <row r="215">
       <c r="A215" t="s" s="2">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="B215" t="s" s="2">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="C215" s="2"/>
       <c r="D215" t="s" s="2">
@@ -28862,7 +28889,7 @@
         <v>91</v>
       </c>
       <c r="AI215" t="s" s="2">
-        <v>80</v>
+        <v>198</v>
       </c>
       <c r="AJ215" t="s" s="2">
         <v>103</v>
@@ -28888,10 +28915,10 @@
     </row>
     <row r="216" hidden="true">
       <c r="A216" t="s" s="2">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="B216" t="s" s="2">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="C216" s="2"/>
       <c r="D216" t="s" s="2">
@@ -29006,10 +29033,10 @@
     </row>
     <row r="217" hidden="true">
       <c r="A217" t="s" s="2">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="B217" t="s" s="2">
-        <v>737</v>
+        <v>738</v>
       </c>
       <c r="C217" s="2"/>
       <c r="D217" t="s" s="2">
@@ -29100,7 +29127,7 @@
         <v>82</v>
       </c>
       <c r="AI217" t="s" s="2">
-        <v>80</v>
+        <v>198</v>
       </c>
       <c r="AJ217" t="s" s="2">
         <v>119</v>
@@ -29126,10 +29153,10 @@
     </row>
     <row r="218">
       <c r="A218" t="s" s="2">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="B218" t="s" s="2">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="C218" s="2"/>
       <c r="D218" t="s" s="2">
@@ -29192,10 +29219,10 @@
         <v>245</v>
       </c>
       <c r="Y218" t="s" s="2">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="Z218" t="s" s="2">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="AA218" t="s" s="2">
         <v>80</v>
@@ -29222,7 +29249,7 @@
         <v>82</v>
       </c>
       <c r="AI218" t="s" s="2">
-        <v>80</v>
+        <v>198</v>
       </c>
       <c r="AJ218" t="s" s="2">
         <v>103</v>
@@ -29248,10 +29275,10 @@
     </row>
     <row r="219" hidden="true">
       <c r="A219" t="s" s="2">
-        <v>740</v>
+        <v>741</v>
       </c>
       <c r="B219" t="s" s="2">
-        <v>741</v>
+        <v>742</v>
       </c>
       <c r="C219" s="2"/>
       <c r="D219" t="s" s="2">
@@ -29366,10 +29393,10 @@
     </row>
     <row r="220" hidden="true">
       <c r="A220" t="s" s="2">
-        <v>742</v>
+        <v>743</v>
       </c>
       <c r="B220" t="s" s="2">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="C220" s="2"/>
       <c r="D220" t="s" s="2">
@@ -29460,7 +29487,7 @@
         <v>82</v>
       </c>
       <c r="AI220" t="s" s="2">
-        <v>80</v>
+        <v>198</v>
       </c>
       <c r="AJ220" t="s" s="2">
         <v>119</v>
@@ -29486,10 +29513,10 @@
     </row>
     <row r="221">
       <c r="A221" t="s" s="2">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="B221" t="s" s="2">
-        <v>745</v>
+        <v>746</v>
       </c>
       <c r="C221" s="2"/>
       <c r="D221" t="s" s="2">
@@ -29582,7 +29609,7 @@
         <v>91</v>
       </c>
       <c r="AI221" t="s" s="2">
-        <v>80</v>
+        <v>198</v>
       </c>
       <c r="AJ221" t="s" s="2">
         <v>103</v>
@@ -29608,10 +29635,10 @@
     </row>
     <row r="222" hidden="true">
       <c r="A222" t="s" s="2">
-        <v>746</v>
+        <v>747</v>
       </c>
       <c r="B222" t="s" s="2">
-        <v>747</v>
+        <v>748</v>
       </c>
       <c r="C222" s="2"/>
       <c r="D222" t="s" s="2">
@@ -29702,7 +29729,7 @@
         <v>91</v>
       </c>
       <c r="AI222" t="s" s="2">
-        <v>80</v>
+        <v>198</v>
       </c>
       <c r="AJ222" t="s" s="2">
         <v>103</v>
@@ -29728,10 +29755,10 @@
     </row>
     <row r="223">
       <c r="A223" t="s" s="2">
-        <v>748</v>
+        <v>749</v>
       </c>
       <c r="B223" t="s" s="2">
-        <v>749</v>
+        <v>750</v>
       </c>
       <c r="C223" s="2"/>
       <c r="D223" t="s" s="2">
@@ -29762,7 +29789,9 @@
       <c r="M223" t="s" s="2">
         <v>280</v>
       </c>
-      <c r="N223" s="2"/>
+      <c r="N223" t="s" s="2">
+        <v>402</v>
+      </c>
       <c r="O223" t="s" s="2">
         <v>281</v>
       </c>
@@ -29822,7 +29851,7 @@
         <v>91</v>
       </c>
       <c r="AI223" t="s" s="2">
-        <v>80</v>
+        <v>198</v>
       </c>
       <c r="AJ223" t="s" s="2">
         <v>103</v>
@@ -29848,10 +29877,10 @@
     </row>
     <row r="224" hidden="true">
       <c r="A224" t="s" s="2">
-        <v>750</v>
+        <v>751</v>
       </c>
       <c r="B224" t="s" s="2">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="C224" s="2"/>
       <c r="D224" t="s" s="2">
@@ -29882,7 +29911,9 @@
       <c r="M224" t="s" s="2">
         <v>286</v>
       </c>
-      <c r="N224" s="2"/>
+      <c r="N224" t="s" s="2">
+        <v>402</v>
+      </c>
       <c r="O224" t="s" s="2">
         <v>287</v>
       </c>
@@ -29942,7 +29973,7 @@
         <v>91</v>
       </c>
       <c r="AI224" t="s" s="2">
-        <v>80</v>
+        <v>198</v>
       </c>
       <c r="AJ224" t="s" s="2">
         <v>103</v>
@@ -29968,10 +29999,10 @@
     </row>
     <row r="225" hidden="true">
       <c r="A225" t="s" s="2">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="B225" t="s" s="2">
-        <v>753</v>
+        <v>754</v>
       </c>
       <c r="C225" s="2"/>
       <c r="D225" t="s" s="2">
@@ -30064,7 +30095,7 @@
         <v>91</v>
       </c>
       <c r="AI225" t="s" s="2">
-        <v>80</v>
+        <v>198</v>
       </c>
       <c r="AJ225" t="s" s="2">
         <v>103</v>
@@ -30090,10 +30121,10 @@
     </row>
     <row r="226" hidden="true">
       <c r="A226" t="s" s="2">
-        <v>754</v>
+        <v>755</v>
       </c>
       <c r="B226" t="s" s="2">
-        <v>755</v>
+        <v>756</v>
       </c>
       <c r="C226" s="2"/>
       <c r="D226" t="s" s="2">
@@ -30186,7 +30217,7 @@
         <v>91</v>
       </c>
       <c r="AI226" t="s" s="2">
-        <v>80</v>
+        <v>198</v>
       </c>
       <c r="AJ226" t="s" s="2">
         <v>103</v>
@@ -30212,10 +30243,10 @@
     </row>
     <row r="227" hidden="true">
       <c r="A227" t="s" s="2">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="B227" t="s" s="2">
-        <v>757</v>
+        <v>758</v>
       </c>
       <c r="C227" s="2"/>
       <c r="D227" t="s" s="2">
@@ -30238,19 +30269,19 @@
         <v>92</v>
       </c>
       <c r="K227" t="s" s="2">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="L227" t="s" s="2">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="M227" t="s" s="2">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="N227" t="s" s="2">
-        <v>761</v>
+        <v>762</v>
       </c>
       <c r="O227" t="s" s="2">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="P227" t="s" s="2">
         <v>80</v>
@@ -30299,7 +30330,7 @@
         <v>80</v>
       </c>
       <c r="AF227" t="s" s="2">
-        <v>763</v>
+        <v>764</v>
       </c>
       <c r="AG227" t="s" s="2">
         <v>81</v>
@@ -30323,7 +30354,7 @@
         <v>80</v>
       </c>
       <c r="AN227" t="s" s="2">
-        <v>764</v>
+        <v>765</v>
       </c>
       <c r="AO227" t="s" s="2">
         <v>80</v>
@@ -30334,10 +30365,10 @@
     </row>
     <row r="228" hidden="true">
       <c r="A228" t="s" s="2">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="B228" t="s" s="2">
-        <v>766</v>
+        <v>767</v>
       </c>
       <c r="C228" s="2"/>
       <c r="D228" t="s" s="2">
@@ -30363,20 +30394,20 @@
         <v>166</v>
       </c>
       <c r="L228" t="s" s="2">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="M228" t="s" s="2">
-        <v>768</v>
+        <v>769</v>
       </c>
       <c r="N228" s="2"/>
       <c r="O228" t="s" s="2">
-        <v>769</v>
+        <v>770</v>
       </c>
       <c r="P228" t="s" s="2">
         <v>80</v>
       </c>
       <c r="Q228" t="s" s="2">
-        <v>770</v>
+        <v>771</v>
       </c>
       <c r="R228" t="s" s="2">
         <v>80</v>
@@ -30400,10 +30431,10 @@
         <v>245</v>
       </c>
       <c r="Y228" t="s" s="2">
-        <v>771</v>
+        <v>772</v>
       </c>
       <c r="Z228" t="s" s="2">
-        <v>772</v>
+        <v>773</v>
       </c>
       <c r="AA228" t="s" s="2">
         <v>80</v>
@@ -30421,7 +30452,7 @@
         <v>80</v>
       </c>
       <c r="AF228" t="s" s="2">
-        <v>773</v>
+        <v>774</v>
       </c>
       <c r="AG228" t="s" s="2">
         <v>81</v>
@@ -30445,7 +30476,7 @@
         <v>80</v>
       </c>
       <c r="AN228" t="s" s="2">
-        <v>774</v>
+        <v>775</v>
       </c>
       <c r="AO228" t="s" s="2">
         <v>80</v>
@@ -30456,10 +30487,10 @@
     </row>
     <row r="229" hidden="true">
       <c r="A229" t="s" s="2">
-        <v>775</v>
+        <v>776</v>
       </c>
       <c r="B229" t="s" s="2">
-        <v>776</v>
+        <v>777</v>
       </c>
       <c r="C229" s="2"/>
       <c r="D229" t="s" s="2">
@@ -30485,14 +30516,14 @@
         <v>105</v>
       </c>
       <c r="L229" t="s" s="2">
-        <v>777</v>
+        <v>778</v>
       </c>
       <c r="M229" t="s" s="2">
-        <v>778</v>
+        <v>779</v>
       </c>
       <c r="N229" s="2"/>
       <c r="O229" t="s" s="2">
-        <v>779</v>
+        <v>780</v>
       </c>
       <c r="P229" t="s" s="2">
         <v>80</v>
@@ -30541,7 +30572,7 @@
         <v>80</v>
       </c>
       <c r="AF229" t="s" s="2">
-        <v>780</v>
+        <v>781</v>
       </c>
       <c r="AG229" t="s" s="2">
         <v>81</v>
@@ -30565,7 +30596,7 @@
         <v>80</v>
       </c>
       <c r="AN229" t="s" s="2">
-        <v>781</v>
+        <v>782</v>
       </c>
       <c r="AO229" t="s" s="2">
         <v>80</v>
@@ -30576,10 +30607,10 @@
     </row>
     <row r="230" hidden="true">
       <c r="A230" t="s" s="2">
-        <v>782</v>
+        <v>783</v>
       </c>
       <c r="B230" t="s" s="2">
-        <v>783</v>
+        <v>784</v>
       </c>
       <c r="C230" s="2"/>
       <c r="D230" t="s" s="2">
@@ -30605,14 +30636,14 @@
         <v>132</v>
       </c>
       <c r="L230" t="s" s="2">
-        <v>784</v>
+        <v>785</v>
       </c>
       <c r="M230" t="s" s="2">
-        <v>785</v>
+        <v>786</v>
       </c>
       <c r="N230" s="2"/>
       <c r="O230" t="s" s="2">
-        <v>786</v>
+        <v>787</v>
       </c>
       <c r="P230" t="s" s="2">
         <v>80</v>
@@ -30661,7 +30692,7 @@
         <v>80</v>
       </c>
       <c r="AF230" t="s" s="2">
-        <v>787</v>
+        <v>788</v>
       </c>
       <c r="AG230" t="s" s="2">
         <v>81</v>
@@ -30670,7 +30701,7 @@
         <v>91</v>
       </c>
       <c r="AI230" t="s" s="2">
-        <v>788</v>
+        <v>789</v>
       </c>
       <c r="AJ230" t="s" s="2">
         <v>103</v>
@@ -30685,7 +30716,7 @@
         <v>80</v>
       </c>
       <c r="AN230" t="s" s="2">
-        <v>781</v>
+        <v>782</v>
       </c>
       <c r="AO230" t="s" s="2">
         <v>80</v>
@@ -30696,10 +30727,10 @@
     </row>
     <row r="231" hidden="true">
       <c r="A231" t="s" s="2">
-        <v>789</v>
+        <v>790</v>
       </c>
       <c r="B231" t="s" s="2">
-        <v>790</v>
+        <v>791</v>
       </c>
       <c r="C231" s="2"/>
       <c r="D231" t="s" s="2">
@@ -30725,16 +30756,16 @@
         <v>166</v>
       </c>
       <c r="L231" t="s" s="2">
-        <v>791</v>
+        <v>792</v>
       </c>
       <c r="M231" t="s" s="2">
-        <v>792</v>
+        <v>793</v>
       </c>
       <c r="N231" t="s" s="2">
-        <v>793</v>
+        <v>794</v>
       </c>
       <c r="O231" t="s" s="2">
-        <v>794</v>
+        <v>795</v>
       </c>
       <c r="P231" t="s" s="2">
         <v>80</v>
@@ -30783,7 +30814,7 @@
         <v>80</v>
       </c>
       <c r="AF231" t="s" s="2">
-        <v>795</v>
+        <v>796</v>
       </c>
       <c r="AG231" t="s" s="2">
         <v>81</v>
@@ -30807,7 +30838,7 @@
         <v>80</v>
       </c>
       <c r="AN231" t="s" s="2">
-        <v>781</v>
+        <v>782</v>
       </c>
       <c r="AO231" t="s" s="2">
         <v>80</v>
@@ -30818,10 +30849,10 @@
     </row>
     <row r="232" hidden="true">
       <c r="A232" t="s" s="2">
-        <v>796</v>
+        <v>797</v>
       </c>
       <c r="B232" t="s" s="2">
-        <v>796</v>
+        <v>797</v>
       </c>
       <c r="C232" s="2"/>
       <c r="D232" t="s" s="2">
@@ -30844,16 +30875,16 @@
         <v>80</v>
       </c>
       <c r="K232" t="s" s="2">
-        <v>797</v>
+        <v>798</v>
       </c>
       <c r="L232" t="s" s="2">
-        <v>798</v>
+        <v>799</v>
       </c>
       <c r="M232" t="s" s="2">
-        <v>799</v>
+        <v>800</v>
       </c>
       <c r="N232" t="s" s="2">
-        <v>800</v>
+        <v>801</v>
       </c>
       <c r="O232" s="2"/>
       <c r="P232" t="s" s="2">
@@ -30903,7 +30934,7 @@
         <v>80</v>
       </c>
       <c r="AF232" t="s" s="2">
-        <v>796</v>
+        <v>797</v>
       </c>
       <c r="AG232" t="s" s="2">
         <v>81</v>
@@ -30912,7 +30943,7 @@
         <v>91</v>
       </c>
       <c r="AI232" t="s" s="2">
-        <v>801</v>
+        <v>802</v>
       </c>
       <c r="AJ232" t="s" s="2">
         <v>103</v>
@@ -30930,7 +30961,7 @@
         <v>80</v>
       </c>
       <c r="AO232" t="s" s="2">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="AP232" t="s" s="2">
         <v>80</v>
@@ -30938,10 +30969,10 @@
     </row>
     <row r="233">
       <c r="A233" t="s" s="2">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="B233" t="s" s="2">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="C233" s="2"/>
       <c r="D233" t="s" s="2">
@@ -30967,10 +30998,10 @@
         <v>226</v>
       </c>
       <c r="L233" t="s" s="2">
-        <v>804</v>
+        <v>805</v>
       </c>
       <c r="M233" t="s" s="2">
-        <v>805</v>
+        <v>806</v>
       </c>
       <c r="N233" s="2"/>
       <c r="O233" s="2"/>
@@ -31021,7 +31052,7 @@
         <v>80</v>
       </c>
       <c r="AF233" t="s" s="2">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="AG233" t="s" s="2">
         <v>81</v>
@@ -31036,7 +31067,7 @@
         <v>103</v>
       </c>
       <c r="AK233" t="s" s="2">
-        <v>806</v>
+        <v>807</v>
       </c>
       <c r="AL233" t="s" s="2">
         <v>80</v>
@@ -31045,10 +31076,10 @@
         <v>80</v>
       </c>
       <c r="AN233" t="s" s="2">
-        <v>807</v>
+        <v>808</v>
       </c>
       <c r="AO233" t="s" s="2">
-        <v>808</v>
+        <v>809</v>
       </c>
       <c r="AP233" t="s" s="2">
         <v>80</v>
@@ -31056,10 +31087,10 @@
     </row>
     <row r="234" hidden="true">
       <c r="A234" t="s" s="2">
-        <v>809</v>
+        <v>810</v>
       </c>
       <c r="B234" t="s" s="2">
-        <v>809</v>
+        <v>810</v>
       </c>
       <c r="C234" s="2"/>
       <c r="D234" t="s" s="2">
@@ -31082,13 +31113,13 @@
         <v>92</v>
       </c>
       <c r="K234" t="s" s="2">
-        <v>810</v>
+        <v>811</v>
       </c>
       <c r="L234" t="s" s="2">
-        <v>811</v>
+        <v>812</v>
       </c>
       <c r="M234" t="s" s="2">
-        <v>812</v>
+        <v>813</v>
       </c>
       <c r="N234" s="2"/>
       <c r="O234" s="2"/>
@@ -31139,7 +31170,7 @@
         <v>80</v>
       </c>
       <c r="AF234" t="s" s="2">
-        <v>809</v>
+        <v>810</v>
       </c>
       <c r="AG234" t="s" s="2">
         <v>81</v>
@@ -31166,7 +31197,7 @@
         <v>80</v>
       </c>
       <c r="AO234" t="s" s="2">
-        <v>813</v>
+        <v>814</v>
       </c>
       <c r="AP234" t="s" s="2">
         <v>80</v>
@@ -31174,10 +31205,10 @@
     </row>
     <row r="235" hidden="true">
       <c r="A235" t="s" s="2">
-        <v>814</v>
+        <v>815</v>
       </c>
       <c r="B235" t="s" s="2">
-        <v>814</v>
+        <v>815</v>
       </c>
       <c r="C235" s="2"/>
       <c r="D235" t="s" s="2">
@@ -31200,13 +31231,13 @@
         <v>92</v>
       </c>
       <c r="K235" t="s" s="2">
-        <v>810</v>
+        <v>811</v>
       </c>
       <c r="L235" t="s" s="2">
-        <v>815</v>
+        <v>816</v>
       </c>
       <c r="M235" t="s" s="2">
-        <v>816</v>
+        <v>817</v>
       </c>
       <c r="N235" s="2"/>
       <c r="O235" s="2"/>
@@ -31257,7 +31288,7 @@
         <v>80</v>
       </c>
       <c r="AF235" t="s" s="2">
-        <v>814</v>
+        <v>815</v>
       </c>
       <c r="AG235" t="s" s="2">
         <v>81</v>
@@ -31281,10 +31312,10 @@
         <v>80</v>
       </c>
       <c r="AN235" t="s" s="2">
-        <v>817</v>
+        <v>818</v>
       </c>
       <c r="AO235" t="s" s="2">
-        <v>818</v>
+        <v>819</v>
       </c>
       <c r="AP235" t="s" s="2">
         <v>80</v>
@@ -31292,10 +31323,10 @@
     </row>
     <row r="236" hidden="true">
       <c r="A236" t="s" s="2">
-        <v>819</v>
+        <v>820</v>
       </c>
       <c r="B236" t="s" s="2">
-        <v>819</v>
+        <v>820</v>
       </c>
       <c r="C236" s="2"/>
       <c r="D236" t="s" s="2">
@@ -31318,13 +31349,13 @@
         <v>80</v>
       </c>
       <c r="K236" t="s" s="2">
-        <v>820</v>
+        <v>821</v>
       </c>
       <c r="L236" t="s" s="2">
-        <v>821</v>
+        <v>822</v>
       </c>
       <c r="M236" t="s" s="2">
-        <v>822</v>
+        <v>823</v>
       </c>
       <c r="N236" s="2"/>
       <c r="O236" s="2"/>
@@ -31375,7 +31406,7 @@
         <v>80</v>
       </c>
       <c r="AF236" t="s" s="2">
-        <v>819</v>
+        <v>820</v>
       </c>
       <c r="AG236" t="s" s="2">
         <v>81</v>
@@ -31387,7 +31418,7 @@
         <v>80</v>
       </c>
       <c r="AJ236" t="s" s="2">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="AK236" t="s" s="2">
         <v>80</v>
@@ -31410,10 +31441,10 @@
     </row>
     <row r="237" hidden="true">
       <c r="A237" t="s" s="2">
-        <v>824</v>
+        <v>825</v>
       </c>
       <c r="B237" t="s" s="2">
-        <v>824</v>
+        <v>825</v>
       </c>
       <c r="C237" s="2"/>
       <c r="D237" t="s" s="2">
@@ -31528,10 +31559,10 @@
     </row>
     <row r="238" hidden="true">
       <c r="A238" t="s" s="2">
-        <v>825</v>
+        <v>826</v>
       </c>
       <c r="B238" t="s" s="2">
-        <v>825</v>
+        <v>826</v>
       </c>
       <c r="C238" s="2"/>
       <c r="D238" t="s" s="2">
@@ -31648,14 +31679,14 @@
     </row>
     <row r="239" hidden="true">
       <c r="A239" t="s" s="2">
-        <v>826</v>
+        <v>827</v>
       </c>
       <c r="B239" t="s" s="2">
-        <v>826</v>
+        <v>827</v>
       </c>
       <c r="C239" s="2"/>
       <c r="D239" t="s" s="2">
-        <v>827</v>
+        <v>828</v>
       </c>
       <c r="E239" s="2"/>
       <c r="F239" t="s" s="2">
@@ -31677,10 +31708,10 @@
         <v>111</v>
       </c>
       <c r="L239" t="s" s="2">
-        <v>828</v>
+        <v>829</v>
       </c>
       <c r="M239" t="s" s="2">
-        <v>829</v>
+        <v>830</v>
       </c>
       <c r="N239" t="s" s="2">
         <v>114</v>
@@ -31735,7 +31766,7 @@
         <v>80</v>
       </c>
       <c r="AF239" t="s" s="2">
-        <v>830</v>
+        <v>831</v>
       </c>
       <c r="AG239" t="s" s="2">
         <v>81</v>
@@ -31770,10 +31801,10 @@
     </row>
     <row r="240" hidden="true">
       <c r="A240" t="s" s="2">
-        <v>831</v>
+        <v>832</v>
       </c>
       <c r="B240" t="s" s="2">
-        <v>831</v>
+        <v>832</v>
       </c>
       <c r="C240" s="2"/>
       <c r="D240" t="s" s="2">
@@ -31799,10 +31830,10 @@
         <v>241</v>
       </c>
       <c r="L240" t="s" s="2">
-        <v>832</v>
+        <v>833</v>
       </c>
       <c r="M240" t="s" s="2">
-        <v>833</v>
+        <v>834</v>
       </c>
       <c r="N240" s="2"/>
       <c r="O240" s="2"/>
@@ -31832,10 +31863,10 @@
         <v>156</v>
       </c>
       <c r="Y240" t="s" s="2">
-        <v>834</v>
+        <v>835</v>
       </c>
       <c r="Z240" t="s" s="2">
-        <v>835</v>
+        <v>836</v>
       </c>
       <c r="AA240" t="s" s="2">
         <v>80</v>
@@ -31853,7 +31884,7 @@
         <v>80</v>
       </c>
       <c r="AF240" t="s" s="2">
-        <v>831</v>
+        <v>832</v>
       </c>
       <c r="AG240" t="s" s="2">
         <v>81</v>
@@ -31862,7 +31893,7 @@
         <v>91</v>
       </c>
       <c r="AI240" t="s" s="2">
-        <v>836</v>
+        <v>837</v>
       </c>
       <c r="AJ240" t="s" s="2">
         <v>103</v>
@@ -31874,7 +31905,7 @@
         <v>80</v>
       </c>
       <c r="AM240" t="s" s="2">
-        <v>837</v>
+        <v>838</v>
       </c>
       <c r="AN240" t="s" s="2">
         <v>252</v>
@@ -31888,10 +31919,10 @@
     </row>
     <row r="241" hidden="true">
       <c r="A241" t="s" s="2">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="B241" t="s" s="2">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="C241" s="2"/>
       <c r="D241" t="s" s="2">
@@ -31914,13 +31945,13 @@
         <v>80</v>
       </c>
       <c r="K241" t="s" s="2">
-        <v>839</v>
+        <v>840</v>
       </c>
       <c r="L241" t="s" s="2">
-        <v>840</v>
+        <v>841</v>
       </c>
       <c r="M241" t="s" s="2">
-        <v>841</v>
+        <v>842</v>
       </c>
       <c r="N241" s="2"/>
       <c r="O241" s="2"/>
@@ -31971,7 +32002,7 @@
         <v>80</v>
       </c>
       <c r="AF241" t="s" s="2">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="AG241" t="s" s="2">
         <v>81</v>
@@ -31980,7 +32011,7 @@
         <v>82</v>
       </c>
       <c r="AI241" t="s" s="2">
-        <v>836</v>
+        <v>837</v>
       </c>
       <c r="AJ241" t="s" s="2">
         <v>103</v>
@@ -32006,10 +32037,10 @@
     </row>
     <row r="242" hidden="true">
       <c r="A242" t="s" s="2">
-        <v>842</v>
+        <v>843</v>
       </c>
       <c r="B242" t="s" s="2">
-        <v>842</v>
+        <v>843</v>
       </c>
       <c r="C242" s="2"/>
       <c r="D242" t="s" s="2">
@@ -32035,10 +32066,10 @@
         <v>241</v>
       </c>
       <c r="L242" t="s" s="2">
-        <v>843</v>
+        <v>844</v>
       </c>
       <c r="M242" t="s" s="2">
-        <v>844</v>
+        <v>845</v>
       </c>
       <c r="N242" s="2"/>
       <c r="O242" s="2"/>
@@ -32068,10 +32099,10 @@
         <v>156</v>
       </c>
       <c r="Y242" t="s" s="2">
-        <v>845</v>
+        <v>846</v>
       </c>
       <c r="Z242" t="s" s="2">
-        <v>846</v>
+        <v>847</v>
       </c>
       <c r="AA242" t="s" s="2">
         <v>80</v>
@@ -32089,7 +32120,7 @@
         <v>80</v>
       </c>
       <c r="AF242" t="s" s="2">
-        <v>842</v>
+        <v>843</v>
       </c>
       <c r="AG242" t="s" s="2">
         <v>81</v>
@@ -32124,10 +32155,10 @@
     </row>
     <row r="243" hidden="true">
       <c r="A243" t="s" s="2">
-        <v>847</v>
+        <v>848</v>
       </c>
       <c r="B243" t="s" s="2">
-        <v>847</v>
+        <v>848</v>
       </c>
       <c r="C243" s="2"/>
       <c r="D243" t="s" s="2">
@@ -32150,16 +32181,16 @@
         <v>80</v>
       </c>
       <c r="K243" t="s" s="2">
-        <v>820</v>
+        <v>821</v>
       </c>
       <c r="L243" t="s" s="2">
-        <v>848</v>
+        <v>849</v>
       </c>
       <c r="M243" t="s" s="2">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="N243" t="s" s="2">
-        <v>850</v>
+        <v>851</v>
       </c>
       <c r="O243" s="2"/>
       <c r="P243" t="s" s="2">
@@ -32209,7 +32240,7 @@
         <v>80</v>
       </c>
       <c r="AF243" t="s" s="2">
-        <v>847</v>
+        <v>848</v>
       </c>
       <c r="AG243" t="s" s="2">
         <v>81</v>
@@ -32221,7 +32252,7 @@
         <v>80</v>
       </c>
       <c r="AJ243" t="s" s="2">
-        <v>851</v>
+        <v>852</v>
       </c>
       <c r="AK243" t="s" s="2">
         <v>80</v>
@@ -32244,10 +32275,10 @@
     </row>
     <row r="244" hidden="true">
       <c r="A244" t="s" s="2">
-        <v>852</v>
+        <v>853</v>
       </c>
       <c r="B244" t="s" s="2">
-        <v>852</v>
+        <v>853</v>
       </c>
       <c r="C244" s="2"/>
       <c r="D244" t="s" s="2">
@@ -32362,10 +32393,10 @@
     </row>
     <row r="245" hidden="true">
       <c r="A245" t="s" s="2">
-        <v>853</v>
+        <v>854</v>
       </c>
       <c r="B245" t="s" s="2">
-        <v>853</v>
+        <v>854</v>
       </c>
       <c r="C245" s="2"/>
       <c r="D245" t="s" s="2">
@@ -32482,14 +32513,14 @@
     </row>
     <row r="246" hidden="true">
       <c r="A246" t="s" s="2">
-        <v>854</v>
+        <v>855</v>
       </c>
       <c r="B246" t="s" s="2">
-        <v>854</v>
+        <v>855</v>
       </c>
       <c r="C246" s="2"/>
       <c r="D246" t="s" s="2">
-        <v>827</v>
+        <v>828</v>
       </c>
       <c r="E246" s="2"/>
       <c r="F246" t="s" s="2">
@@ -32511,10 +32542,10 @@
         <v>111</v>
       </c>
       <c r="L246" t="s" s="2">
-        <v>828</v>
+        <v>829</v>
       </c>
       <c r="M246" t="s" s="2">
-        <v>829</v>
+        <v>830</v>
       </c>
       <c r="N246" t="s" s="2">
         <v>114</v>
@@ -32569,7 +32600,7 @@
         <v>80</v>
       </c>
       <c r="AF246" t="s" s="2">
-        <v>830</v>
+        <v>831</v>
       </c>
       <c r="AG246" t="s" s="2">
         <v>81</v>
@@ -32604,10 +32635,10 @@
     </row>
     <row r="247" hidden="true">
       <c r="A247" t="s" s="2">
-        <v>855</v>
+        <v>856</v>
       </c>
       <c r="B247" t="s" s="2">
-        <v>855</v>
+        <v>856</v>
       </c>
       <c r="C247" s="2"/>
       <c r="D247" t="s" s="2">
@@ -32633,10 +32664,10 @@
         <v>241</v>
       </c>
       <c r="L247" t="s" s="2">
-        <v>856</v>
+        <v>857</v>
       </c>
       <c r="M247" t="s" s="2">
-        <v>857</v>
+        <v>858</v>
       </c>
       <c r="N247" s="2"/>
       <c r="O247" s="2"/>
@@ -32666,10 +32697,10 @@
         <v>156</v>
       </c>
       <c r="Y247" t="s" s="2">
-        <v>858</v>
+        <v>859</v>
       </c>
       <c r="Z247" t="s" s="2">
-        <v>859</v>
+        <v>860</v>
       </c>
       <c r="AA247" t="s" s="2">
         <v>80</v>
@@ -32687,7 +32718,7 @@
         <v>80</v>
       </c>
       <c r="AF247" t="s" s="2">
-        <v>855</v>
+        <v>856</v>
       </c>
       <c r="AG247" t="s" s="2">
         <v>81</v>
@@ -32696,7 +32727,7 @@
         <v>82</v>
       </c>
       <c r="AI247" t="s" s="2">
-        <v>860</v>
+        <v>861</v>
       </c>
       <c r="AJ247" t="s" s="2">
         <v>103</v>
@@ -32705,7 +32736,7 @@
         <v>80</v>
       </c>
       <c r="AL247" t="s" s="2">
-        <v>861</v>
+        <v>862</v>
       </c>
       <c r="AM247" t="s" s="2">
         <v>331</v>
@@ -32714,7 +32745,7 @@
         <v>80</v>
       </c>
       <c r="AO247" t="s" s="2">
-        <v>862</v>
+        <v>863</v>
       </c>
       <c r="AP247" t="s" s="2">
         <v>80</v>
@@ -32722,10 +32753,10 @@
     </row>
     <row r="248" hidden="true">
       <c r="A248" t="s" s="2">
-        <v>863</v>
+        <v>864</v>
       </c>
       <c r="B248" t="s" s="2">
-        <v>863</v>
+        <v>864</v>
       </c>
       <c r="C248" s="2"/>
       <c r="D248" t="s" s="2">
@@ -32748,13 +32779,13 @@
         <v>92</v>
       </c>
       <c r="K248" t="s" s="2">
-        <v>864</v>
+        <v>865</v>
       </c>
       <c r="L248" t="s" s="2">
-        <v>865</v>
+        <v>866</v>
       </c>
       <c r="M248" t="s" s="2">
-        <v>866</v>
+        <v>867</v>
       </c>
       <c r="N248" s="2"/>
       <c r="O248" s="2"/>
@@ -32805,7 +32836,7 @@
         <v>80</v>
       </c>
       <c r="AF248" t="s" s="2">
-        <v>863</v>
+        <v>864</v>
       </c>
       <c r="AG248" t="s" s="2">
         <v>81</v>
@@ -32814,7 +32845,7 @@
         <v>82</v>
       </c>
       <c r="AI248" t="s" s="2">
-        <v>860</v>
+        <v>861</v>
       </c>
       <c r="AJ248" t="s" s="2">
         <v>103</v>
@@ -32832,7 +32863,7 @@
         <v>80</v>
       </c>
       <c r="AO248" t="s" s="2">
-        <v>862</v>
+        <v>863</v>
       </c>
       <c r="AP248" t="s" s="2">
         <v>80</v>
@@ -32840,10 +32871,10 @@
     </row>
     <row r="249">
       <c r="A249" t="s" s="2">
-        <v>867</v>
+        <v>868</v>
       </c>
       <c r="B249" t="s" s="2">
-        <v>867</v>
+        <v>868</v>
       </c>
       <c r="C249" s="2"/>
       <c r="D249" t="s" s="2">
@@ -32866,13 +32897,13 @@
         <v>80</v>
       </c>
       <c r="K249" t="s" s="2">
-        <v>868</v>
+        <v>869</v>
       </c>
       <c r="L249" t="s" s="2">
-        <v>869</v>
+        <v>870</v>
       </c>
       <c r="M249" t="s" s="2">
-        <v>870</v>
+        <v>871</v>
       </c>
       <c r="N249" s="2"/>
       <c r="O249" s="2"/>
@@ -32923,7 +32954,7 @@
         <v>80</v>
       </c>
       <c r="AF249" t="s" s="2">
-        <v>867</v>
+        <v>868</v>
       </c>
       <c r="AG249" t="s" s="2">
         <v>81</v>
@@ -32938,16 +32969,16 @@
         <v>103</v>
       </c>
       <c r="AK249" t="s" s="2">
-        <v>871</v>
+        <v>872</v>
       </c>
       <c r="AL249" t="s" s="2">
-        <v>872</v>
+        <v>873</v>
       </c>
       <c r="AM249" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN249" t="s" s="2">
-        <v>873</v>
+        <v>874</v>
       </c>
       <c r="AO249" t="s" s="2">
         <v>80</v>

--- a/branches/develop/StructureDefinition-mii-pr-diagnose-condition.xlsx
+++ b/branches/develop/StructureDefinition-mii-pr-diagnose-condition.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AP$249</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AP$250</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9506" uniqueCount="875">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9544" uniqueCount="880">
   <si>
     <t>Property</t>
   </si>
@@ -1627,6 +1627,22 @@
   </si>
   <si>
     <t>Condition.bodySite.extension</t>
+  </si>
+  <si>
+    <t>Condition.bodySite.extension:bodySite</t>
+  </si>
+  <si>
+    <t>bodySite</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {bodySite}
+</t>
+  </si>
+  <si>
+    <t>Target anatomic location or structure</t>
+  </si>
+  <si>
+    <t>Record details about the anatomical location of a specimen or body part. This resource may be used when a coded concept does not provide the necessary detail needed for the use case.</t>
   </si>
   <si>
     <t>Condition.bodySite.coding</t>
@@ -3051,7 +3067,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AP249"/>
+  <dimension ref="A1:AP250"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="79.40625" customWidth="true" bestFit="true"/>
@@ -19684,9 +19700,11 @@
         <v>517</v>
       </c>
       <c r="B139" t="s" s="2">
-        <v>517</v>
-      </c>
-      <c r="C139" s="2"/>
+        <v>516</v>
+      </c>
+      <c r="C139" t="s" s="2">
+        <v>518</v>
+      </c>
       <c r="D139" t="s" s="2">
         <v>80</v>
       </c>
@@ -19695,32 +19713,28 @@
         <v>81</v>
       </c>
       <c r="G139" t="s" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="H139" t="s" s="2">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="I139" t="s" s="2">
         <v>80</v>
       </c>
       <c r="J139" t="s" s="2">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="K139" t="s" s="2">
-        <v>144</v>
+        <v>519</v>
       </c>
       <c r="L139" t="s" s="2">
-        <v>257</v>
+        <v>520</v>
       </c>
       <c r="M139" t="s" s="2">
-        <v>258</v>
-      </c>
-      <c r="N139" t="s" s="2">
-        <v>259</v>
-      </c>
-      <c r="O139" t="s" s="2">
-        <v>260</v>
-      </c>
+        <v>521</v>
+      </c>
+      <c r="N139" s="2"/>
+      <c r="O139" s="2"/>
       <c r="P139" t="s" s="2">
         <v>80</v>
       </c>
@@ -19756,17 +19770,19 @@
         <v>80</v>
       </c>
       <c r="AB139" t="s" s="2">
-        <v>518</v>
-      </c>
-      <c r="AC139" s="2"/>
+        <v>80</v>
+      </c>
+      <c r="AC139" t="s" s="2">
+        <v>80</v>
+      </c>
       <c r="AD139" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE139" t="s" s="2">
-        <v>117</v>
+        <v>80</v>
       </c>
       <c r="AF139" t="s" s="2">
-        <v>261</v>
+        <v>118</v>
       </c>
       <c r="AG139" t="s" s="2">
         <v>81</v>
@@ -19778,7 +19794,7 @@
         <v>80</v>
       </c>
       <c r="AJ139" t="s" s="2">
-        <v>103</v>
+        <v>119</v>
       </c>
       <c r="AK139" t="s" s="2">
         <v>80</v>
@@ -19790,7 +19806,7 @@
         <v>80</v>
       </c>
       <c r="AN139" t="s" s="2">
-        <v>262</v>
+        <v>80</v>
       </c>
       <c r="AO139" t="s" s="2">
         <v>80</v>
@@ -19799,16 +19815,14 @@
         <v>80</v>
       </c>
     </row>
-    <row r="140">
+    <row r="140" hidden="true">
       <c r="A140" t="s" s="2">
-        <v>519</v>
+        <v>522</v>
       </c>
       <c r="B140" t="s" s="2">
-        <v>517</v>
-      </c>
-      <c r="C140" t="s" s="2">
-        <v>520</v>
-      </c>
+        <v>522</v>
+      </c>
+      <c r="C140" s="2"/>
       <c r="D140" t="s" s="2">
         <v>80</v>
       </c>
@@ -19817,7 +19831,7 @@
         <v>81</v>
       </c>
       <c r="G140" t="s" s="2">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="H140" t="s" s="2">
         <v>92</v>
@@ -19832,10 +19846,10 @@
         <v>144</v>
       </c>
       <c r="L140" t="s" s="2">
-        <v>476</v>
+        <v>257</v>
       </c>
       <c r="M140" t="s" s="2">
-        <v>477</v>
+        <v>258</v>
       </c>
       <c r="N140" t="s" s="2">
         <v>259</v>
@@ -19866,26 +19880,26 @@
         <v>80</v>
       </c>
       <c r="X140" t="s" s="2">
-        <v>245</v>
-      </c>
-      <c r="Y140" s="2"/>
+        <v>80</v>
+      </c>
+      <c r="Y140" t="s" s="2">
+        <v>80</v>
+      </c>
       <c r="Z140" t="s" s="2">
-        <v>521</v>
+        <v>80</v>
       </c>
       <c r="AA140" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AB140" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC140" t="s" s="2">
-        <v>80</v>
-      </c>
+        <v>523</v>
+      </c>
+      <c r="AC140" s="2"/>
       <c r="AD140" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE140" t="s" s="2">
-        <v>80</v>
+        <v>117</v>
       </c>
       <c r="AF140" t="s" s="2">
         <v>261</v>
@@ -19921,14 +19935,16 @@
         <v>80</v>
       </c>
     </row>
-    <row r="141" hidden="true">
+    <row r="141">
       <c r="A141" t="s" s="2">
+        <v>524</v>
+      </c>
+      <c r="B141" t="s" s="2">
         <v>522</v>
       </c>
-      <c r="B141" t="s" s="2">
-        <v>523</v>
-      </c>
-      <c r="C141" s="2"/>
+      <c r="C141" t="s" s="2">
+        <v>525</v>
+      </c>
       <c r="D141" t="s" s="2">
         <v>80</v>
       </c>
@@ -19940,25 +19956,29 @@
         <v>91</v>
       </c>
       <c r="H141" t="s" s="2">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="I141" t="s" s="2">
         <v>80</v>
       </c>
       <c r="J141" t="s" s="2">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="K141" t="s" s="2">
-        <v>105</v>
+        <v>144</v>
       </c>
       <c r="L141" t="s" s="2">
-        <v>106</v>
+        <v>476</v>
       </c>
       <c r="M141" t="s" s="2">
-        <v>107</v>
-      </c>
-      <c r="N141" s="2"/>
-      <c r="O141" s="2"/>
+        <v>477</v>
+      </c>
+      <c r="N141" t="s" s="2">
+        <v>259</v>
+      </c>
+      <c r="O141" t="s" s="2">
+        <v>260</v>
+      </c>
       <c r="P141" t="s" s="2">
         <v>80</v>
       </c>
@@ -19982,13 +20002,11 @@
         <v>80</v>
       </c>
       <c r="X141" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Y141" t="s" s="2">
-        <v>80</v>
-      </c>
+        <v>245</v>
+      </c>
+      <c r="Y141" s="2"/>
       <c r="Z141" t="s" s="2">
-        <v>80</v>
+        <v>526</v>
       </c>
       <c r="AA141" t="s" s="2">
         <v>80</v>
@@ -20006,19 +20024,19 @@
         <v>80</v>
       </c>
       <c r="AF141" t="s" s="2">
-        <v>108</v>
+        <v>261</v>
       </c>
       <c r="AG141" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH141" t="s" s="2">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="AI141" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ141" t="s" s="2">
-        <v>80</v>
+        <v>103</v>
       </c>
       <c r="AK141" t="s" s="2">
         <v>80</v>
@@ -20030,7 +20048,7 @@
         <v>80</v>
       </c>
       <c r="AN141" t="s" s="2">
-        <v>80</v>
+        <v>262</v>
       </c>
       <c r="AO141" t="s" s="2">
         <v>80</v>
@@ -20041,21 +20059,21 @@
     </row>
     <row r="142" hidden="true">
       <c r="A142" t="s" s="2">
-        <v>524</v>
+        <v>527</v>
       </c>
       <c r="B142" t="s" s="2">
-        <v>525</v>
+        <v>528</v>
       </c>
       <c r="C142" s="2"/>
       <c r="D142" t="s" s="2">
-        <v>110</v>
+        <v>80</v>
       </c>
       <c r="E142" s="2"/>
       <c r="F142" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G142" t="s" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="H142" t="s" s="2">
         <v>80</v>
@@ -20067,17 +20085,15 @@
         <v>80</v>
       </c>
       <c r="K142" t="s" s="2">
-        <v>111</v>
+        <v>105</v>
       </c>
       <c r="L142" t="s" s="2">
-        <v>112</v>
+        <v>106</v>
       </c>
       <c r="M142" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="N142" t="s" s="2">
-        <v>114</v>
-      </c>
+        <v>107</v>
+      </c>
+      <c r="N142" s="2"/>
       <c r="O142" s="2"/>
       <c r="P142" t="s" s="2">
         <v>80</v>
@@ -20114,31 +20130,31 @@
         <v>80</v>
       </c>
       <c r="AB142" t="s" s="2">
-        <v>115</v>
+        <v>80</v>
       </c>
       <c r="AC142" t="s" s="2">
-        <v>116</v>
+        <v>80</v>
       </c>
       <c r="AD142" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE142" t="s" s="2">
-        <v>117</v>
+        <v>80</v>
       </c>
       <c r="AF142" t="s" s="2">
-        <v>118</v>
+        <v>108</v>
       </c>
       <c r="AG142" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH142" t="s" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="AI142" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ142" t="s" s="2">
-        <v>119</v>
+        <v>80</v>
       </c>
       <c r="AK142" t="s" s="2">
         <v>80</v>
@@ -20159,48 +20175,46 @@
         <v>80</v>
       </c>
     </row>
-    <row r="143">
+    <row r="143" hidden="true">
       <c r="A143" t="s" s="2">
-        <v>526</v>
+        <v>529</v>
       </c>
       <c r="B143" t="s" s="2">
-        <v>527</v>
+        <v>530</v>
       </c>
       <c r="C143" s="2"/>
       <c r="D143" t="s" s="2">
-        <v>80</v>
+        <v>110</v>
       </c>
       <c r="E143" s="2"/>
       <c r="F143" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="G143" t="s" s="2">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="H143" t="s" s="2">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="I143" t="s" s="2">
         <v>80</v>
       </c>
       <c r="J143" t="s" s="2">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="K143" t="s" s="2">
-        <v>132</v>
+        <v>111</v>
       </c>
       <c r="L143" t="s" s="2">
-        <v>266</v>
+        <v>112</v>
       </c>
       <c r="M143" t="s" s="2">
-        <v>267</v>
+        <v>113</v>
       </c>
       <c r="N143" t="s" s="2">
-        <v>268</v>
-      </c>
-      <c r="O143" t="s" s="2">
-        <v>269</v>
-      </c>
+        <v>114</v>
+      </c>
+      <c r="O143" s="2"/>
       <c r="P143" t="s" s="2">
         <v>80</v>
       </c>
@@ -20209,7 +20223,7 @@
         <v>80</v>
       </c>
       <c r="S143" t="s" s="2">
-        <v>528</v>
+        <v>80</v>
       </c>
       <c r="T143" t="s" s="2">
         <v>80</v>
@@ -20236,31 +20250,31 @@
         <v>80</v>
       </c>
       <c r="AB143" t="s" s="2">
-        <v>80</v>
+        <v>115</v>
       </c>
       <c r="AC143" t="s" s="2">
-        <v>80</v>
+        <v>116</v>
       </c>
       <c r="AD143" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE143" t="s" s="2">
-        <v>80</v>
+        <v>117</v>
       </c>
       <c r="AF143" t="s" s="2">
-        <v>270</v>
+        <v>118</v>
       </c>
       <c r="AG143" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH143" t="s" s="2">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="AI143" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ143" t="s" s="2">
-        <v>103</v>
+        <v>119</v>
       </c>
       <c r="AK143" t="s" s="2">
         <v>80</v>
@@ -20272,7 +20286,7 @@
         <v>80</v>
       </c>
       <c r="AN143" t="s" s="2">
-        <v>271</v>
+        <v>80</v>
       </c>
       <c r="AO143" t="s" s="2">
         <v>80</v>
@@ -20283,10 +20297,10 @@
     </row>
     <row r="144">
       <c r="A144" t="s" s="2">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="B144" t="s" s="2">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="C144" s="2"/>
       <c r="D144" t="s" s="2">
@@ -20294,7 +20308,7 @@
       </c>
       <c r="E144" s="2"/>
       <c r="F144" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="G144" t="s" s="2">
         <v>91</v>
@@ -20309,18 +20323,20 @@
         <v>92</v>
       </c>
       <c r="K144" t="s" s="2">
-        <v>105</v>
+        <v>132</v>
       </c>
       <c r="L144" t="s" s="2">
-        <v>273</v>
+        <v>266</v>
       </c>
       <c r="M144" t="s" s="2">
-        <v>274</v>
+        <v>267</v>
       </c>
       <c r="N144" t="s" s="2">
-        <v>275</v>
-      </c>
-      <c r="O144" s="2"/>
+        <v>268</v>
+      </c>
+      <c r="O144" t="s" s="2">
+        <v>269</v>
+      </c>
       <c r="P144" t="s" s="2">
         <v>80</v>
       </c>
@@ -20329,7 +20345,7 @@
         <v>80</v>
       </c>
       <c r="S144" t="s" s="2">
-        <v>80</v>
+        <v>533</v>
       </c>
       <c r="T144" t="s" s="2">
         <v>80</v>
@@ -20368,7 +20384,7 @@
         <v>80</v>
       </c>
       <c r="AF144" t="s" s="2">
-        <v>276</v>
+        <v>270</v>
       </c>
       <c r="AG144" t="s" s="2">
         <v>81</v>
@@ -20392,7 +20408,7 @@
         <v>80</v>
       </c>
       <c r="AN144" t="s" s="2">
-        <v>277</v>
+        <v>271</v>
       </c>
       <c r="AO144" t="s" s="2">
         <v>80</v>
@@ -20403,10 +20419,10 @@
     </row>
     <row r="145">
       <c r="A145" t="s" s="2">
-        <v>531</v>
+        <v>534</v>
       </c>
       <c r="B145" t="s" s="2">
-        <v>532</v>
+        <v>535</v>
       </c>
       <c r="C145" s="2"/>
       <c r="D145" t="s" s="2">
@@ -20414,7 +20430,7 @@
       </c>
       <c r="E145" s="2"/>
       <c r="F145" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="G145" t="s" s="2">
         <v>91</v>
@@ -20429,18 +20445,18 @@
         <v>92</v>
       </c>
       <c r="K145" t="s" s="2">
-        <v>166</v>
+        <v>105</v>
       </c>
       <c r="L145" t="s" s="2">
-        <v>279</v>
+        <v>273</v>
       </c>
       <c r="M145" t="s" s="2">
-        <v>280</v>
-      </c>
-      <c r="N145" s="2"/>
-      <c r="O145" t="s" s="2">
-        <v>281</v>
-      </c>
+        <v>274</v>
+      </c>
+      <c r="N145" t="s" s="2">
+        <v>275</v>
+      </c>
+      <c r="O145" s="2"/>
       <c r="P145" t="s" s="2">
         <v>80</v>
       </c>
@@ -20488,7 +20504,7 @@
         <v>80</v>
       </c>
       <c r="AF145" t="s" s="2">
-        <v>282</v>
+        <v>276</v>
       </c>
       <c r="AG145" t="s" s="2">
         <v>81</v>
@@ -20512,7 +20528,7 @@
         <v>80</v>
       </c>
       <c r="AN145" t="s" s="2">
-        <v>283</v>
+        <v>277</v>
       </c>
       <c r="AO145" t="s" s="2">
         <v>80</v>
@@ -20521,12 +20537,12 @@
         <v>80</v>
       </c>
     </row>
-    <row r="146" hidden="true">
+    <row r="146">
       <c r="A146" t="s" s="2">
-        <v>533</v>
+        <v>536</v>
       </c>
       <c r="B146" t="s" s="2">
-        <v>534</v>
+        <v>537</v>
       </c>
       <c r="C146" s="2"/>
       <c r="D146" t="s" s="2">
@@ -20534,13 +20550,13 @@
       </c>
       <c r="E146" s="2"/>
       <c r="F146" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="G146" t="s" s="2">
         <v>91</v>
       </c>
       <c r="H146" t="s" s="2">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="I146" t="s" s="2">
         <v>80</v>
@@ -20549,17 +20565,17 @@
         <v>92</v>
       </c>
       <c r="K146" t="s" s="2">
-        <v>105</v>
+        <v>166</v>
       </c>
       <c r="L146" t="s" s="2">
-        <v>285</v>
+        <v>279</v>
       </c>
       <c r="M146" t="s" s="2">
-        <v>286</v>
+        <v>280</v>
       </c>
       <c r="N146" s="2"/>
       <c r="O146" t="s" s="2">
-        <v>287</v>
+        <v>281</v>
       </c>
       <c r="P146" t="s" s="2">
         <v>80</v>
@@ -20608,7 +20624,7 @@
         <v>80</v>
       </c>
       <c r="AF146" t="s" s="2">
-        <v>288</v>
+        <v>282</v>
       </c>
       <c r="AG146" t="s" s="2">
         <v>81</v>
@@ -20632,7 +20648,7 @@
         <v>80</v>
       </c>
       <c r="AN146" t="s" s="2">
-        <v>289</v>
+        <v>283</v>
       </c>
       <c r="AO146" t="s" s="2">
         <v>80</v>
@@ -20643,10 +20659,10 @@
     </row>
     <row r="147" hidden="true">
       <c r="A147" t="s" s="2">
-        <v>535</v>
+        <v>538</v>
       </c>
       <c r="B147" t="s" s="2">
-        <v>536</v>
+        <v>539</v>
       </c>
       <c r="C147" s="2"/>
       <c r="D147" t="s" s="2">
@@ -20669,19 +20685,17 @@
         <v>92</v>
       </c>
       <c r="K147" t="s" s="2">
-        <v>291</v>
+        <v>105</v>
       </c>
       <c r="L147" t="s" s="2">
-        <v>292</v>
+        <v>285</v>
       </c>
       <c r="M147" t="s" s="2">
-        <v>293</v>
-      </c>
-      <c r="N147" t="s" s="2">
-        <v>294</v>
-      </c>
+        <v>286</v>
+      </c>
+      <c r="N147" s="2"/>
       <c r="O147" t="s" s="2">
-        <v>295</v>
+        <v>287</v>
       </c>
       <c r="P147" t="s" s="2">
         <v>80</v>
@@ -20730,7 +20744,7 @@
         <v>80</v>
       </c>
       <c r="AF147" t="s" s="2">
-        <v>296</v>
+        <v>288</v>
       </c>
       <c r="AG147" t="s" s="2">
         <v>81</v>
@@ -20754,7 +20768,7 @@
         <v>80</v>
       </c>
       <c r="AN147" t="s" s="2">
-        <v>297</v>
+        <v>289</v>
       </c>
       <c r="AO147" t="s" s="2">
         <v>80</v>
@@ -20765,10 +20779,10 @@
     </row>
     <row r="148" hidden="true">
       <c r="A148" t="s" s="2">
-        <v>537</v>
+        <v>540</v>
       </c>
       <c r="B148" t="s" s="2">
-        <v>537</v>
+        <v>541</v>
       </c>
       <c r="C148" s="2"/>
       <c r="D148" t="s" s="2">
@@ -20791,19 +20805,19 @@
         <v>92</v>
       </c>
       <c r="K148" t="s" s="2">
-        <v>105</v>
+        <v>291</v>
       </c>
       <c r="L148" t="s" s="2">
-        <v>299</v>
+        <v>292</v>
       </c>
       <c r="M148" t="s" s="2">
-        <v>300</v>
+        <v>293</v>
       </c>
       <c r="N148" t="s" s="2">
-        <v>301</v>
+        <v>294</v>
       </c>
       <c r="O148" t="s" s="2">
-        <v>302</v>
+        <v>295</v>
       </c>
       <c r="P148" t="s" s="2">
         <v>80</v>
@@ -20852,7 +20866,7 @@
         <v>80</v>
       </c>
       <c r="AF148" t="s" s="2">
-        <v>303</v>
+        <v>296</v>
       </c>
       <c r="AG148" t="s" s="2">
         <v>81</v>
@@ -20876,7 +20890,7 @@
         <v>80</v>
       </c>
       <c r="AN148" t="s" s="2">
-        <v>304</v>
+        <v>297</v>
       </c>
       <c r="AO148" t="s" s="2">
         <v>80</v>
@@ -20885,26 +20899,26 @@
         <v>80</v>
       </c>
     </row>
-    <row r="149">
+    <row r="149" hidden="true">
       <c r="A149" t="s" s="2">
-        <v>538</v>
+        <v>542</v>
       </c>
       <c r="B149" t="s" s="2">
-        <v>538</v>
+        <v>542</v>
       </c>
       <c r="C149" s="2"/>
       <c r="D149" t="s" s="2">
-        <v>539</v>
+        <v>80</v>
       </c>
       <c r="E149" s="2"/>
       <c r="F149" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="G149" t="s" s="2">
         <v>91</v>
       </c>
       <c r="H149" t="s" s="2">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="I149" t="s" s="2">
         <v>80</v>
@@ -20913,17 +20927,19 @@
         <v>92</v>
       </c>
       <c r="K149" t="s" s="2">
-        <v>540</v>
+        <v>105</v>
       </c>
       <c r="L149" t="s" s="2">
-        <v>541</v>
+        <v>299</v>
       </c>
       <c r="M149" t="s" s="2">
-        <v>542</v>
-      </c>
-      <c r="N149" s="2"/>
+        <v>300</v>
+      </c>
+      <c r="N149" t="s" s="2">
+        <v>301</v>
+      </c>
       <c r="O149" t="s" s="2">
-        <v>543</v>
+        <v>302</v>
       </c>
       <c r="P149" t="s" s="2">
         <v>80</v>
@@ -20972,10 +20988,10 @@
         <v>80</v>
       </c>
       <c r="AF149" t="s" s="2">
-        <v>538</v>
+        <v>303</v>
       </c>
       <c r="AG149" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AH149" t="s" s="2">
         <v>91</v>
@@ -20990,59 +21006,61 @@
         <v>80</v>
       </c>
       <c r="AL149" t="s" s="2">
-        <v>544</v>
+        <v>80</v>
       </c>
       <c r="AM149" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN149" t="s" s="2">
-        <v>545</v>
+        <v>304</v>
       </c>
       <c r="AO149" t="s" s="2">
-        <v>546</v>
+        <v>80</v>
       </c>
       <c r="AP149" t="s" s="2">
         <v>80</v>
       </c>
     </row>
-    <row r="150" hidden="true">
+    <row r="150">
       <c r="A150" t="s" s="2">
-        <v>547</v>
+        <v>543</v>
       </c>
       <c r="B150" t="s" s="2">
-        <v>547</v>
+        <v>543</v>
       </c>
       <c r="C150" s="2"/>
       <c r="D150" t="s" s="2">
-        <v>80</v>
+        <v>544</v>
       </c>
       <c r="E150" s="2"/>
       <c r="F150" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="G150" t="s" s="2">
         <v>91</v>
       </c>
       <c r="H150" t="s" s="2">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="I150" t="s" s="2">
         <v>80</v>
       </c>
       <c r="J150" t="s" s="2">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="K150" t="s" s="2">
-        <v>105</v>
+        <v>545</v>
       </c>
       <c r="L150" t="s" s="2">
-        <v>106</v>
+        <v>546</v>
       </c>
       <c r="M150" t="s" s="2">
-        <v>107</v>
+        <v>547</v>
       </c>
       <c r="N150" s="2"/>
-      <c r="O150" s="2"/>
+      <c r="O150" t="s" s="2">
+        <v>548</v>
+      </c>
       <c r="P150" t="s" s="2">
         <v>80</v>
       </c>
@@ -21090,10 +21108,10 @@
         <v>80</v>
       </c>
       <c r="AF150" t="s" s="2">
-        <v>108</v>
+        <v>543</v>
       </c>
       <c r="AG150" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AH150" t="s" s="2">
         <v>91</v>
@@ -21102,22 +21120,22 @@
         <v>80</v>
       </c>
       <c r="AJ150" t="s" s="2">
-        <v>80</v>
+        <v>103</v>
       </c>
       <c r="AK150" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL150" t="s" s="2">
-        <v>80</v>
+        <v>549</v>
       </c>
       <c r="AM150" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN150" t="s" s="2">
-        <v>80</v>
+        <v>550</v>
       </c>
       <c r="AO150" t="s" s="2">
-        <v>80</v>
+        <v>551</v>
       </c>
       <c r="AP150" t="s" s="2">
         <v>80</v>
@@ -21125,21 +21143,21 @@
     </row>
     <row r="151" hidden="true">
       <c r="A151" t="s" s="2">
-        <v>548</v>
+        <v>552</v>
       </c>
       <c r="B151" t="s" s="2">
-        <v>548</v>
+        <v>552</v>
       </c>
       <c r="C151" s="2"/>
       <c r="D151" t="s" s="2">
-        <v>110</v>
+        <v>80</v>
       </c>
       <c r="E151" s="2"/>
       <c r="F151" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G151" t="s" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="H151" t="s" s="2">
         <v>80</v>
@@ -21151,17 +21169,15 @@
         <v>80</v>
       </c>
       <c r="K151" t="s" s="2">
-        <v>111</v>
+        <v>105</v>
       </c>
       <c r="L151" t="s" s="2">
-        <v>112</v>
+        <v>106</v>
       </c>
       <c r="M151" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="N151" t="s" s="2">
-        <v>114</v>
-      </c>
+        <v>107</v>
+      </c>
+      <c r="N151" s="2"/>
       <c r="O151" s="2"/>
       <c r="P151" t="s" s="2">
         <v>80</v>
@@ -21198,31 +21214,31 @@
         <v>80</v>
       </c>
       <c r="AB151" t="s" s="2">
-        <v>115</v>
+        <v>80</v>
       </c>
       <c r="AC151" t="s" s="2">
-        <v>116</v>
+        <v>80</v>
       </c>
       <c r="AD151" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE151" t="s" s="2">
-        <v>117</v>
+        <v>80</v>
       </c>
       <c r="AF151" t="s" s="2">
-        <v>118</v>
+        <v>108</v>
       </c>
       <c r="AG151" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH151" t="s" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="AI151" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ151" t="s" s="2">
-        <v>119</v>
+        <v>80</v>
       </c>
       <c r="AK151" t="s" s="2">
         <v>80</v>
@@ -21243,44 +21259,44 @@
         <v>80</v>
       </c>
     </row>
-    <row r="152">
+    <row r="152" hidden="true">
       <c r="A152" t="s" s="2">
-        <v>549</v>
+        <v>553</v>
       </c>
       <c r="B152" t="s" s="2">
-        <v>549</v>
+        <v>553</v>
       </c>
       <c r="C152" s="2"/>
       <c r="D152" t="s" s="2">
-        <v>80</v>
+        <v>110</v>
       </c>
       <c r="E152" s="2"/>
       <c r="F152" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G152" t="s" s="2">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="H152" t="s" s="2">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="I152" t="s" s="2">
         <v>80</v>
       </c>
       <c r="J152" t="s" s="2">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="K152" t="s" s="2">
-        <v>105</v>
+        <v>111</v>
       </c>
       <c r="L152" t="s" s="2">
-        <v>550</v>
+        <v>112</v>
       </c>
       <c r="M152" t="s" s="2">
-        <v>551</v>
+        <v>113</v>
       </c>
       <c r="N152" t="s" s="2">
-        <v>552</v>
+        <v>114</v>
       </c>
       <c r="O152" s="2"/>
       <c r="P152" t="s" s="2">
@@ -21318,57 +21334,57 @@
         <v>80</v>
       </c>
       <c r="AB152" t="s" s="2">
-        <v>80</v>
+        <v>115</v>
       </c>
       <c r="AC152" t="s" s="2">
-        <v>80</v>
+        <v>116</v>
       </c>
       <c r="AD152" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE152" t="s" s="2">
-        <v>80</v>
+        <v>117</v>
       </c>
       <c r="AF152" t="s" s="2">
-        <v>553</v>
+        <v>118</v>
       </c>
       <c r="AG152" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH152" t="s" s="2">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="AI152" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ152" t="s" s="2">
+        <v>119</v>
+      </c>
+      <c r="AK152" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL152" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM152" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN152" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AO152" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AP152" t="s" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="s" s="2">
         <v>554</v>
       </c>
-      <c r="AJ152" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="AK152" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AL152" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AM152" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN152" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AO152" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AP152" t="s" s="2">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="153" hidden="true">
-      <c r="A153" t="s" s="2">
-        <v>555</v>
-      </c>
       <c r="B153" t="s" s="2">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="C153" s="2"/>
       <c r="D153" t="s" s="2">
@@ -21382,7 +21398,7 @@
         <v>91</v>
       </c>
       <c r="H153" t="s" s="2">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="I153" t="s" s="2">
         <v>80</v>
@@ -21391,16 +21407,16 @@
         <v>92</v>
       </c>
       <c r="K153" t="s" s="2">
-        <v>132</v>
+        <v>105</v>
       </c>
       <c r="L153" t="s" s="2">
+        <v>555</v>
+      </c>
+      <c r="M153" t="s" s="2">
         <v>556</v>
       </c>
-      <c r="M153" t="s" s="2">
+      <c r="N153" t="s" s="2">
         <v>557</v>
-      </c>
-      <c r="N153" t="s" s="2">
-        <v>558</v>
       </c>
       <c r="O153" s="2"/>
       <c r="P153" t="s" s="2">
@@ -21426,40 +21442,40 @@
         <v>80</v>
       </c>
       <c r="X153" t="s" s="2">
-        <v>148</v>
+        <v>80</v>
       </c>
       <c r="Y153" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z153" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA153" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB153" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC153" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD153" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE153" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF153" t="s" s="2">
+        <v>558</v>
+      </c>
+      <c r="AG153" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH153" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="AI153" t="s" s="2">
         <v>559</v>
-      </c>
-      <c r="Z153" t="s" s="2">
-        <v>560</v>
-      </c>
-      <c r="AA153" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB153" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC153" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AD153" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE153" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AF153" t="s" s="2">
-        <v>561</v>
-      </c>
-      <c r="AG153" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH153" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="AI153" t="s" s="2">
-        <v>80</v>
       </c>
       <c r="AJ153" t="s" s="2">
         <v>103</v>
@@ -21485,10 +21501,10 @@
     </row>
     <row r="154" hidden="true">
       <c r="A154" t="s" s="2">
-        <v>562</v>
+        <v>560</v>
       </c>
       <c r="B154" t="s" s="2">
-        <v>562</v>
+        <v>560</v>
       </c>
       <c r="C154" s="2"/>
       <c r="D154" t="s" s="2">
@@ -21511,16 +21527,16 @@
         <v>92</v>
       </c>
       <c r="K154" t="s" s="2">
-        <v>233</v>
+        <v>132</v>
       </c>
       <c r="L154" t="s" s="2">
+        <v>561</v>
+      </c>
+      <c r="M154" t="s" s="2">
+        <v>562</v>
+      </c>
+      <c r="N154" t="s" s="2">
         <v>563</v>
-      </c>
-      <c r="M154" t="s" s="2">
-        <v>564</v>
-      </c>
-      <c r="N154" t="s" s="2">
-        <v>565</v>
       </c>
       <c r="O154" s="2"/>
       <c r="P154" t="s" s="2">
@@ -21546,13 +21562,13 @@
         <v>80</v>
       </c>
       <c r="X154" t="s" s="2">
-        <v>80</v>
+        <v>148</v>
       </c>
       <c r="Y154" t="s" s="2">
-        <v>80</v>
+        <v>564</v>
       </c>
       <c r="Z154" t="s" s="2">
-        <v>80</v>
+        <v>565</v>
       </c>
       <c r="AA154" t="s" s="2">
         <v>80</v>
@@ -21631,7 +21647,7 @@
         <v>92</v>
       </c>
       <c r="K155" t="s" s="2">
-        <v>105</v>
+        <v>233</v>
       </c>
       <c r="L155" t="s" s="2">
         <v>568</v>
@@ -21723,7 +21739,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="156">
+    <row r="156" hidden="true">
       <c r="A156" t="s" s="2">
         <v>572</v>
       </c>
@@ -21742,7 +21758,7 @@
         <v>91</v>
       </c>
       <c r="H156" t="s" s="2">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="I156" t="s" s="2">
         <v>80</v>
@@ -21751,16 +21767,16 @@
         <v>92</v>
       </c>
       <c r="K156" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="L156" t="s" s="2">
         <v>573</v>
       </c>
-      <c r="L156" t="s" s="2">
+      <c r="M156" t="s" s="2">
         <v>574</v>
       </c>
-      <c r="M156" t="s" s="2">
+      <c r="N156" t="s" s="2">
         <v>575</v>
-      </c>
-      <c r="N156" t="s" s="2">
-        <v>576</v>
       </c>
       <c r="O156" s="2"/>
       <c r="P156" t="s" s="2">
@@ -21810,7 +21826,7 @@
         <v>80</v>
       </c>
       <c r="AF156" t="s" s="2">
-        <v>572</v>
+        <v>576</v>
       </c>
       <c r="AG156" t="s" s="2">
         <v>81</v>
@@ -21828,27 +21844,27 @@
         <v>80</v>
       </c>
       <c r="AL156" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM156" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN156" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AO156" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AP156" t="s" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="s" s="2">
         <v>577</v>
       </c>
-      <c r="AM156" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN156" t="s" s="2">
-        <v>578</v>
-      </c>
-      <c r="AO156" t="s" s="2">
-        <v>579</v>
-      </c>
-      <c r="AP156" t="s" s="2">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="157" hidden="true">
-      <c r="A157" t="s" s="2">
-        <v>580</v>
-      </c>
       <c r="B157" t="s" s="2">
-        <v>580</v>
+        <v>577</v>
       </c>
       <c r="C157" s="2"/>
       <c r="D157" t="s" s="2">
@@ -21862,24 +21878,26 @@
         <v>91</v>
       </c>
       <c r="H157" t="s" s="2">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="I157" t="s" s="2">
         <v>80</v>
       </c>
       <c r="J157" t="s" s="2">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="K157" t="s" s="2">
-        <v>105</v>
+        <v>578</v>
       </c>
       <c r="L157" t="s" s="2">
-        <v>106</v>
+        <v>579</v>
       </c>
       <c r="M157" t="s" s="2">
-        <v>107</v>
-      </c>
-      <c r="N157" s="2"/>
+        <v>580</v>
+      </c>
+      <c r="N157" t="s" s="2">
+        <v>581</v>
+      </c>
       <c r="O157" s="2"/>
       <c r="P157" t="s" s="2">
         <v>80</v>
@@ -21928,7 +21946,7 @@
         <v>80</v>
       </c>
       <c r="AF157" t="s" s="2">
-        <v>108</v>
+        <v>577</v>
       </c>
       <c r="AG157" t="s" s="2">
         <v>81</v>
@@ -21940,22 +21958,22 @@
         <v>80</v>
       </c>
       <c r="AJ157" t="s" s="2">
-        <v>80</v>
+        <v>103</v>
       </c>
       <c r="AK157" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL157" t="s" s="2">
-        <v>80</v>
+        <v>582</v>
       </c>
       <c r="AM157" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN157" t="s" s="2">
-        <v>80</v>
+        <v>583</v>
       </c>
       <c r="AO157" t="s" s="2">
-        <v>80</v>
+        <v>584</v>
       </c>
       <c r="AP157" t="s" s="2">
         <v>80</v>
@@ -21963,21 +21981,21 @@
     </row>
     <row r="158" hidden="true">
       <c r="A158" t="s" s="2">
-        <v>581</v>
+        <v>585</v>
       </c>
       <c r="B158" t="s" s="2">
-        <v>581</v>
+        <v>585</v>
       </c>
       <c r="C158" s="2"/>
       <c r="D158" t="s" s="2">
-        <v>110</v>
+        <v>80</v>
       </c>
       <c r="E158" s="2"/>
       <c r="F158" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G158" t="s" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="H158" t="s" s="2">
         <v>80</v>
@@ -21989,17 +22007,15 @@
         <v>80</v>
       </c>
       <c r="K158" t="s" s="2">
-        <v>111</v>
+        <v>105</v>
       </c>
       <c r="L158" t="s" s="2">
-        <v>112</v>
+        <v>106</v>
       </c>
       <c r="M158" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="N158" t="s" s="2">
-        <v>114</v>
-      </c>
+        <v>107</v>
+      </c>
+      <c r="N158" s="2"/>
       <c r="O158" s="2"/>
       <c r="P158" t="s" s="2">
         <v>80</v>
@@ -22036,31 +22052,31 @@
         <v>80</v>
       </c>
       <c r="AB158" t="s" s="2">
-        <v>115</v>
+        <v>80</v>
       </c>
       <c r="AC158" t="s" s="2">
-        <v>116</v>
+        <v>80</v>
       </c>
       <c r="AD158" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE158" t="s" s="2">
-        <v>117</v>
+        <v>80</v>
       </c>
       <c r="AF158" t="s" s="2">
-        <v>118</v>
+        <v>108</v>
       </c>
       <c r="AG158" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH158" t="s" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="AI158" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ158" t="s" s="2">
-        <v>119</v>
+        <v>80</v>
       </c>
       <c r="AK158" t="s" s="2">
         <v>80</v>
@@ -22081,44 +22097,44 @@
         <v>80</v>
       </c>
     </row>
-    <row r="159">
+    <row r="159" hidden="true">
       <c r="A159" t="s" s="2">
-        <v>582</v>
+        <v>586</v>
       </c>
       <c r="B159" t="s" s="2">
-        <v>582</v>
+        <v>586</v>
       </c>
       <c r="C159" s="2"/>
       <c r="D159" t="s" s="2">
-        <v>80</v>
+        <v>110</v>
       </c>
       <c r="E159" s="2"/>
       <c r="F159" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G159" t="s" s="2">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="H159" t="s" s="2">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="I159" t="s" s="2">
         <v>80</v>
       </c>
       <c r="J159" t="s" s="2">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="K159" t="s" s="2">
-        <v>105</v>
+        <v>111</v>
       </c>
       <c r="L159" t="s" s="2">
-        <v>550</v>
+        <v>112</v>
       </c>
       <c r="M159" t="s" s="2">
-        <v>551</v>
+        <v>113</v>
       </c>
       <c r="N159" t="s" s="2">
-        <v>552</v>
+        <v>114</v>
       </c>
       <c r="O159" s="2"/>
       <c r="P159" t="s" s="2">
@@ -22156,31 +22172,31 @@
         <v>80</v>
       </c>
       <c r="AB159" t="s" s="2">
-        <v>80</v>
+        <v>115</v>
       </c>
       <c r="AC159" t="s" s="2">
-        <v>80</v>
+        <v>116</v>
       </c>
       <c r="AD159" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE159" t="s" s="2">
-        <v>80</v>
+        <v>117</v>
       </c>
       <c r="AF159" t="s" s="2">
-        <v>553</v>
+        <v>118</v>
       </c>
       <c r="AG159" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH159" t="s" s="2">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="AI159" t="s" s="2">
-        <v>554</v>
+        <v>80</v>
       </c>
       <c r="AJ159" t="s" s="2">
-        <v>103</v>
+        <v>119</v>
       </c>
       <c r="AK159" t="s" s="2">
         <v>80</v>
@@ -22201,12 +22217,12 @@
         <v>80</v>
       </c>
     </row>
-    <row r="160" hidden="true">
+    <row r="160">
       <c r="A160" t="s" s="2">
-        <v>583</v>
+        <v>587</v>
       </c>
       <c r="B160" t="s" s="2">
-        <v>583</v>
+        <v>587</v>
       </c>
       <c r="C160" s="2"/>
       <c r="D160" t="s" s="2">
@@ -22220,7 +22236,7 @@
         <v>91</v>
       </c>
       <c r="H160" t="s" s="2">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="I160" t="s" s="2">
         <v>80</v>
@@ -22229,16 +22245,16 @@
         <v>92</v>
       </c>
       <c r="K160" t="s" s="2">
-        <v>132</v>
+        <v>105</v>
       </c>
       <c r="L160" t="s" s="2">
+        <v>555</v>
+      </c>
+      <c r="M160" t="s" s="2">
         <v>556</v>
       </c>
-      <c r="M160" t="s" s="2">
+      <c r="N160" t="s" s="2">
         <v>557</v>
-      </c>
-      <c r="N160" t="s" s="2">
-        <v>558</v>
       </c>
       <c r="O160" s="2"/>
       <c r="P160" t="s" s="2">
@@ -22264,40 +22280,40 @@
         <v>80</v>
       </c>
       <c r="X160" t="s" s="2">
-        <v>148</v>
+        <v>80</v>
       </c>
       <c r="Y160" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z160" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA160" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB160" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC160" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD160" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE160" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF160" t="s" s="2">
+        <v>558</v>
+      </c>
+      <c r="AG160" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH160" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="AI160" t="s" s="2">
         <v>559</v>
-      </c>
-      <c r="Z160" t="s" s="2">
-        <v>560</v>
-      </c>
-      <c r="AA160" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB160" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC160" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AD160" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE160" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AF160" t="s" s="2">
-        <v>561</v>
-      </c>
-      <c r="AG160" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH160" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="AI160" t="s" s="2">
-        <v>80</v>
       </c>
       <c r="AJ160" t="s" s="2">
         <v>103</v>
@@ -22323,10 +22339,10 @@
     </row>
     <row r="161" hidden="true">
       <c r="A161" t="s" s="2">
-        <v>584</v>
+        <v>588</v>
       </c>
       <c r="B161" t="s" s="2">
-        <v>584</v>
+        <v>588</v>
       </c>
       <c r="C161" s="2"/>
       <c r="D161" t="s" s="2">
@@ -22349,16 +22365,16 @@
         <v>92</v>
       </c>
       <c r="K161" t="s" s="2">
-        <v>233</v>
+        <v>132</v>
       </c>
       <c r="L161" t="s" s="2">
+        <v>561</v>
+      </c>
+      <c r="M161" t="s" s="2">
+        <v>562</v>
+      </c>
+      <c r="N161" t="s" s="2">
         <v>563</v>
-      </c>
-      <c r="M161" t="s" s="2">
-        <v>564</v>
-      </c>
-      <c r="N161" t="s" s="2">
-        <v>565</v>
       </c>
       <c r="O161" s="2"/>
       <c r="P161" t="s" s="2">
@@ -22384,13 +22400,13 @@
         <v>80</v>
       </c>
       <c r="X161" t="s" s="2">
-        <v>80</v>
+        <v>148</v>
       </c>
       <c r="Y161" t="s" s="2">
-        <v>80</v>
+        <v>564</v>
       </c>
       <c r="Z161" t="s" s="2">
-        <v>80</v>
+        <v>565</v>
       </c>
       <c r="AA161" t="s" s="2">
         <v>80</v>
@@ -22443,10 +22459,10 @@
     </row>
     <row r="162" hidden="true">
       <c r="A162" t="s" s="2">
-        <v>585</v>
+        <v>589</v>
       </c>
       <c r="B162" t="s" s="2">
-        <v>585</v>
+        <v>589</v>
       </c>
       <c r="C162" s="2"/>
       <c r="D162" t="s" s="2">
@@ -22469,7 +22485,7 @@
         <v>92</v>
       </c>
       <c r="K162" t="s" s="2">
-        <v>105</v>
+        <v>233</v>
       </c>
       <c r="L162" t="s" s="2">
         <v>568</v>
@@ -22563,10 +22579,10 @@
     </row>
     <row r="163" hidden="true">
       <c r="A163" t="s" s="2">
-        <v>586</v>
+        <v>590</v>
       </c>
       <c r="B163" t="s" s="2">
-        <v>586</v>
+        <v>590</v>
       </c>
       <c r="C163" s="2"/>
       <c r="D163" t="s" s="2">
@@ -22580,7 +22596,7 @@
         <v>91</v>
       </c>
       <c r="H163" t="s" s="2">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="I163" t="s" s="2">
         <v>80</v>
@@ -22589,16 +22605,16 @@
         <v>92</v>
       </c>
       <c r="K163" t="s" s="2">
-        <v>587</v>
+        <v>105</v>
       </c>
       <c r="L163" t="s" s="2">
-        <v>588</v>
+        <v>573</v>
       </c>
       <c r="M163" t="s" s="2">
-        <v>589</v>
+        <v>574</v>
       </c>
       <c r="N163" t="s" s="2">
-        <v>590</v>
+        <v>575</v>
       </c>
       <c r="O163" s="2"/>
       <c r="P163" t="s" s="2">
@@ -22636,17 +22652,19 @@
         <v>80</v>
       </c>
       <c r="AB163" t="s" s="2">
-        <v>591</v>
-      </c>
-      <c r="AC163" s="2"/>
+        <v>80</v>
+      </c>
+      <c r="AC163" t="s" s="2">
+        <v>80</v>
+      </c>
       <c r="AD163" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE163" t="s" s="2">
-        <v>592</v>
+        <v>80</v>
       </c>
       <c r="AF163" t="s" s="2">
-        <v>586</v>
+        <v>576</v>
       </c>
       <c r="AG163" t="s" s="2">
         <v>81</v>
@@ -22661,34 +22679,32 @@
         <v>103</v>
       </c>
       <c r="AK163" t="s" s="2">
-        <v>593</v>
+        <v>80</v>
       </c>
       <c r="AL163" t="s" s="2">
-        <v>594</v>
+        <v>80</v>
       </c>
       <c r="AM163" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN163" t="s" s="2">
-        <v>595</v>
+        <v>80</v>
       </c>
       <c r="AO163" t="s" s="2">
-        <v>596</v>
+        <v>80</v>
       </c>
       <c r="AP163" t="s" s="2">
         <v>80</v>
       </c>
     </row>
-    <row r="164">
+    <row r="164" hidden="true">
       <c r="A164" t="s" s="2">
-        <v>597</v>
+        <v>591</v>
       </c>
       <c r="B164" t="s" s="2">
-        <v>586</v>
-      </c>
-      <c r="C164" t="s" s="2">
-        <v>598</v>
-      </c>
+        <v>591</v>
+      </c>
+      <c r="C164" s="2"/>
       <c r="D164" t="s" s="2">
         <v>80</v>
       </c>
@@ -22709,16 +22725,16 @@
         <v>92</v>
       </c>
       <c r="K164" t="s" s="2">
-        <v>599</v>
+        <v>592</v>
       </c>
       <c r="L164" t="s" s="2">
-        <v>600</v>
+        <v>593</v>
       </c>
       <c r="M164" t="s" s="2">
-        <v>601</v>
+        <v>594</v>
       </c>
       <c r="N164" t="s" s="2">
-        <v>590</v>
+        <v>595</v>
       </c>
       <c r="O164" s="2"/>
       <c r="P164" t="s" s="2">
@@ -22756,19 +22772,17 @@
         <v>80</v>
       </c>
       <c r="AB164" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC164" t="s" s="2">
-        <v>80</v>
-      </c>
+        <v>596</v>
+      </c>
+      <c r="AC164" s="2"/>
       <c r="AD164" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE164" t="s" s="2">
-        <v>80</v>
+        <v>597</v>
       </c>
       <c r="AF164" t="s" s="2">
-        <v>586</v>
+        <v>591</v>
       </c>
       <c r="AG164" t="s" s="2">
         <v>81</v>
@@ -22783,32 +22797,34 @@
         <v>103</v>
       </c>
       <c r="AK164" t="s" s="2">
+        <v>598</v>
+      </c>
+      <c r="AL164" t="s" s="2">
+        <v>599</v>
+      </c>
+      <c r="AM164" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN164" t="s" s="2">
+        <v>600</v>
+      </c>
+      <c r="AO164" t="s" s="2">
+        <v>601</v>
+      </c>
+      <c r="AP164" t="s" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="s" s="2">
         <v>602</v>
       </c>
-      <c r="AL164" t="s" s="2">
-        <v>594</v>
-      </c>
-      <c r="AM164" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN164" t="s" s="2">
-        <v>595</v>
-      </c>
-      <c r="AO164" t="s" s="2">
-        <v>596</v>
-      </c>
-      <c r="AP164" t="s" s="2">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="165" hidden="true">
-      <c r="A165" t="s" s="2">
+      <c r="B165" t="s" s="2">
+        <v>591</v>
+      </c>
+      <c r="C165" t="s" s="2">
         <v>603</v>
       </c>
-      <c r="B165" t="s" s="2">
-        <v>604</v>
-      </c>
-      <c r="C165" s="2"/>
       <c r="D165" t="s" s="2">
         <v>80</v>
       </c>
@@ -22820,24 +22836,26 @@
         <v>91</v>
       </c>
       <c r="H165" t="s" s="2">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="I165" t="s" s="2">
         <v>80</v>
       </c>
       <c r="J165" t="s" s="2">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="K165" t="s" s="2">
-        <v>105</v>
+        <v>604</v>
       </c>
       <c r="L165" t="s" s="2">
-        <v>106</v>
+        <v>605</v>
       </c>
       <c r="M165" t="s" s="2">
-        <v>107</v>
-      </c>
-      <c r="N165" s="2"/>
+        <v>606</v>
+      </c>
+      <c r="N165" t="s" s="2">
+        <v>595</v>
+      </c>
       <c r="O165" s="2"/>
       <c r="P165" t="s" s="2">
         <v>80</v>
@@ -22886,7 +22904,7 @@
         <v>80</v>
       </c>
       <c r="AF165" t="s" s="2">
-        <v>108</v>
+        <v>591</v>
       </c>
       <c r="AG165" t="s" s="2">
         <v>81</v>
@@ -22898,22 +22916,22 @@
         <v>80</v>
       </c>
       <c r="AJ165" t="s" s="2">
-        <v>80</v>
+        <v>103</v>
       </c>
       <c r="AK165" t="s" s="2">
-        <v>80</v>
+        <v>607</v>
       </c>
       <c r="AL165" t="s" s="2">
-        <v>80</v>
+        <v>599</v>
       </c>
       <c r="AM165" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN165" t="s" s="2">
-        <v>80</v>
+        <v>600</v>
       </c>
       <c r="AO165" t="s" s="2">
-        <v>80</v>
+        <v>601</v>
       </c>
       <c r="AP165" t="s" s="2">
         <v>80</v>
@@ -22921,21 +22939,21 @@
     </row>
     <row r="166" hidden="true">
       <c r="A166" t="s" s="2">
-        <v>605</v>
+        <v>608</v>
       </c>
       <c r="B166" t="s" s="2">
-        <v>606</v>
+        <v>609</v>
       </c>
       <c r="C166" s="2"/>
       <c r="D166" t="s" s="2">
-        <v>110</v>
+        <v>80</v>
       </c>
       <c r="E166" s="2"/>
       <c r="F166" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G166" t="s" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="H166" t="s" s="2">
         <v>80</v>
@@ -22947,17 +22965,15 @@
         <v>80</v>
       </c>
       <c r="K166" t="s" s="2">
-        <v>111</v>
+        <v>105</v>
       </c>
       <c r="L166" t="s" s="2">
-        <v>112</v>
+        <v>106</v>
       </c>
       <c r="M166" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="N166" t="s" s="2">
-        <v>114</v>
-      </c>
+        <v>107</v>
+      </c>
+      <c r="N166" s="2"/>
       <c r="O166" s="2"/>
       <c r="P166" t="s" s="2">
         <v>80</v>
@@ -22994,31 +23010,31 @@
         <v>80</v>
       </c>
       <c r="AB166" t="s" s="2">
-        <v>115</v>
+        <v>80</v>
       </c>
       <c r="AC166" t="s" s="2">
-        <v>116</v>
+        <v>80</v>
       </c>
       <c r="AD166" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE166" t="s" s="2">
-        <v>117</v>
+        <v>80</v>
       </c>
       <c r="AF166" t="s" s="2">
-        <v>118</v>
+        <v>108</v>
       </c>
       <c r="AG166" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH166" t="s" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="AI166" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ166" t="s" s="2">
-        <v>119</v>
+        <v>80</v>
       </c>
       <c r="AK166" t="s" s="2">
         <v>80</v>
@@ -23039,44 +23055,44 @@
         <v>80</v>
       </c>
     </row>
-    <row r="167">
+    <row r="167" hidden="true">
       <c r="A167" t="s" s="2">
-        <v>607</v>
+        <v>610</v>
       </c>
       <c r="B167" t="s" s="2">
-        <v>608</v>
+        <v>611</v>
       </c>
       <c r="C167" s="2"/>
       <c r="D167" t="s" s="2">
-        <v>80</v>
+        <v>110</v>
       </c>
       <c r="E167" s="2"/>
       <c r="F167" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G167" t="s" s="2">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="H167" t="s" s="2">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="I167" t="s" s="2">
         <v>80</v>
       </c>
       <c r="J167" t="s" s="2">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="K167" t="s" s="2">
-        <v>226</v>
+        <v>111</v>
       </c>
       <c r="L167" t="s" s="2">
-        <v>609</v>
+        <v>112</v>
       </c>
       <c r="M167" t="s" s="2">
-        <v>610</v>
+        <v>113</v>
       </c>
       <c r="N167" t="s" s="2">
-        <v>611</v>
+        <v>114</v>
       </c>
       <c r="O167" s="2"/>
       <c r="P167" t="s" s="2">
@@ -23114,57 +23130,57 @@
         <v>80</v>
       </c>
       <c r="AB167" t="s" s="2">
-        <v>80</v>
+        <v>115</v>
       </c>
       <c r="AC167" t="s" s="2">
-        <v>80</v>
+        <v>116</v>
       </c>
       <c r="AD167" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE167" t="s" s="2">
-        <v>80</v>
+        <v>117</v>
       </c>
       <c r="AF167" t="s" s="2">
+        <v>118</v>
+      </c>
+      <c r="AG167" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH167" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AI167" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ167" t="s" s="2">
+        <v>119</v>
+      </c>
+      <c r="AK167" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL167" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM167" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN167" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AO167" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AP167" t="s" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="s" s="2">
         <v>612</v>
       </c>
-      <c r="AG167" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH167" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="AI167" t="s" s="2">
+      <c r="B168" t="s" s="2">
         <v>613</v>
-      </c>
-      <c r="AJ167" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="AK167" t="s" s="2">
-        <v>614</v>
-      </c>
-      <c r="AL167" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AM167" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN167" t="s" s="2">
-        <v>615</v>
-      </c>
-      <c r="AO167" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AP167" t="s" s="2">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="168" hidden="true">
-      <c r="A168" t="s" s="2">
-        <v>616</v>
-      </c>
-      <c r="B168" t="s" s="2">
-        <v>617</v>
       </c>
       <c r="C168" s="2"/>
       <c r="D168" t="s" s="2">
@@ -23178,24 +23194,26 @@
         <v>91</v>
       </c>
       <c r="H168" t="s" s="2">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="I168" t="s" s="2">
         <v>80</v>
       </c>
       <c r="J168" t="s" s="2">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="K168" t="s" s="2">
-        <v>105</v>
+        <v>226</v>
       </c>
       <c r="L168" t="s" s="2">
-        <v>618</v>
+        <v>614</v>
       </c>
       <c r="M168" t="s" s="2">
-        <v>619</v>
-      </c>
-      <c r="N168" s="2"/>
+        <v>615</v>
+      </c>
+      <c r="N168" t="s" s="2">
+        <v>616</v>
+      </c>
       <c r="O168" s="2"/>
       <c r="P168" t="s" s="2">
         <v>80</v>
@@ -23244,7 +23262,7 @@
         <v>80</v>
       </c>
       <c r="AF168" t="s" s="2">
-        <v>108</v>
+        <v>617</v>
       </c>
       <c r="AG168" t="s" s="2">
         <v>81</v>
@@ -23253,13 +23271,13 @@
         <v>91</v>
       </c>
       <c r="AI168" t="s" s="2">
-        <v>80</v>
+        <v>618</v>
       </c>
       <c r="AJ168" t="s" s="2">
-        <v>80</v>
+        <v>103</v>
       </c>
       <c r="AK168" t="s" s="2">
-        <v>80</v>
+        <v>619</v>
       </c>
       <c r="AL168" t="s" s="2">
         <v>80</v>
@@ -23268,7 +23286,7 @@
         <v>80</v>
       </c>
       <c r="AN168" t="s" s="2">
-        <v>80</v>
+        <v>620</v>
       </c>
       <c r="AO168" t="s" s="2">
         <v>80</v>
@@ -23279,10 +23297,10 @@
     </row>
     <row r="169" hidden="true">
       <c r="A169" t="s" s="2">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="B169" t="s" s="2">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="C169" s="2"/>
       <c r="D169" t="s" s="2">
@@ -23293,7 +23311,7 @@
         <v>81</v>
       </c>
       <c r="G169" t="s" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="H169" t="s" s="2">
         <v>80</v>
@@ -23305,13 +23323,13 @@
         <v>80</v>
       </c>
       <c r="K169" t="s" s="2">
-        <v>111</v>
+        <v>105</v>
       </c>
       <c r="L169" t="s" s="2">
-        <v>189</v>
+        <v>623</v>
       </c>
       <c r="M169" t="s" s="2">
-        <v>190</v>
+        <v>624</v>
       </c>
       <c r="N169" s="2"/>
       <c r="O169" s="2"/>
@@ -23350,29 +23368,31 @@
         <v>80</v>
       </c>
       <c r="AB169" t="s" s="2">
-        <v>115</v>
-      </c>
-      <c r="AC169" s="2"/>
+        <v>80</v>
+      </c>
+      <c r="AC169" t="s" s="2">
+        <v>80</v>
+      </c>
       <c r="AD169" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE169" t="s" s="2">
-        <v>117</v>
+        <v>80</v>
       </c>
       <c r="AF169" t="s" s="2">
-        <v>118</v>
+        <v>108</v>
       </c>
       <c r="AG169" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH169" t="s" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="AI169" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ169" t="s" s="2">
-        <v>119</v>
+        <v>80</v>
       </c>
       <c r="AK169" t="s" s="2">
         <v>80</v>
@@ -23393,16 +23413,14 @@
         <v>80</v>
       </c>
     </row>
-    <row r="170">
+    <row r="170" hidden="true">
       <c r="A170" t="s" s="2">
-        <v>622</v>
+        <v>625</v>
       </c>
       <c r="B170" t="s" s="2">
-        <v>621</v>
-      </c>
-      <c r="C170" t="s" s="2">
-        <v>623</v>
-      </c>
+        <v>626</v>
+      </c>
+      <c r="C170" s="2"/>
       <c r="D170" t="s" s="2">
         <v>80</v>
       </c>
@@ -23411,10 +23429,10 @@
         <v>81</v>
       </c>
       <c r="G170" t="s" s="2">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="H170" t="s" s="2">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="I170" t="s" s="2">
         <v>80</v>
@@ -23423,13 +23441,13 @@
         <v>80</v>
       </c>
       <c r="K170" t="s" s="2">
-        <v>624</v>
+        <v>111</v>
       </c>
       <c r="L170" t="s" s="2">
-        <v>380</v>
+        <v>189</v>
       </c>
       <c r="M170" t="s" s="2">
-        <v>381</v>
+        <v>190</v>
       </c>
       <c r="N170" s="2"/>
       <c r="O170" s="2"/>
@@ -23468,16 +23486,14 @@
         <v>80</v>
       </c>
       <c r="AB170" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC170" t="s" s="2">
-        <v>80</v>
-      </c>
+        <v>115</v>
+      </c>
+      <c r="AC170" s="2"/>
       <c r="AD170" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE170" t="s" s="2">
-        <v>80</v>
+        <v>117</v>
       </c>
       <c r="AF170" t="s" s="2">
         <v>118</v>
@@ -23489,7 +23505,7 @@
         <v>82</v>
       </c>
       <c r="AI170" t="s" s="2">
-        <v>198</v>
+        <v>80</v>
       </c>
       <c r="AJ170" t="s" s="2">
         <v>119</v>
@@ -23513,14 +23529,16 @@
         <v>80</v>
       </c>
     </row>
-    <row r="171" hidden="true">
+    <row r="171">
       <c r="A171" t="s" s="2">
-        <v>625</v>
+        <v>627</v>
       </c>
       <c r="B171" t="s" s="2">
         <v>626</v>
       </c>
-      <c r="C171" s="2"/>
+      <c r="C171" t="s" s="2">
+        <v>628</v>
+      </c>
       <c r="D171" t="s" s="2">
         <v>80</v>
       </c>
@@ -23532,7 +23550,7 @@
         <v>91</v>
       </c>
       <c r="H171" t="s" s="2">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="I171" t="s" s="2">
         <v>80</v>
@@ -23541,13 +23559,13 @@
         <v>80</v>
       </c>
       <c r="K171" t="s" s="2">
-        <v>105</v>
+        <v>629</v>
       </c>
       <c r="L171" t="s" s="2">
-        <v>106</v>
+        <v>380</v>
       </c>
       <c r="M171" t="s" s="2">
-        <v>107</v>
+        <v>381</v>
       </c>
       <c r="N171" s="2"/>
       <c r="O171" s="2"/>
@@ -23598,19 +23616,19 @@
         <v>80</v>
       </c>
       <c r="AF171" t="s" s="2">
-        <v>108</v>
+        <v>118</v>
       </c>
       <c r="AG171" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH171" t="s" s="2">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="AI171" t="s" s="2">
-        <v>80</v>
+        <v>198</v>
       </c>
       <c r="AJ171" t="s" s="2">
-        <v>80</v>
+        <v>119</v>
       </c>
       <c r="AK171" t="s" s="2">
         <v>80</v>
@@ -23633,21 +23651,21 @@
     </row>
     <row r="172" hidden="true">
       <c r="A172" t="s" s="2">
-        <v>627</v>
+        <v>630</v>
       </c>
       <c r="B172" t="s" s="2">
-        <v>628</v>
+        <v>631</v>
       </c>
       <c r="C172" s="2"/>
       <c r="D172" t="s" s="2">
-        <v>110</v>
+        <v>80</v>
       </c>
       <c r="E172" s="2"/>
       <c r="F172" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G172" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H172" t="s" s="2">
         <v>80</v>
@@ -23659,17 +23677,15 @@
         <v>80</v>
       </c>
       <c r="K172" t="s" s="2">
-        <v>111</v>
+        <v>105</v>
       </c>
       <c r="L172" t="s" s="2">
-        <v>112</v>
+        <v>106</v>
       </c>
       <c r="M172" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="N172" t="s" s="2">
-        <v>114</v>
-      </c>
+        <v>107</v>
+      </c>
+      <c r="N172" s="2"/>
       <c r="O172" s="2"/>
       <c r="P172" t="s" s="2">
         <v>80</v>
@@ -23706,31 +23722,31 @@
         <v>80</v>
       </c>
       <c r="AB172" t="s" s="2">
-        <v>115</v>
+        <v>80</v>
       </c>
       <c r="AC172" t="s" s="2">
-        <v>116</v>
+        <v>80</v>
       </c>
       <c r="AD172" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE172" t="s" s="2">
-        <v>117</v>
+        <v>80</v>
       </c>
       <c r="AF172" t="s" s="2">
-        <v>118</v>
+        <v>108</v>
       </c>
       <c r="AG172" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH172" t="s" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="AI172" t="s" s="2">
-        <v>198</v>
+        <v>80</v>
       </c>
       <c r="AJ172" t="s" s="2">
-        <v>119</v>
+        <v>80</v>
       </c>
       <c r="AK172" t="s" s="2">
         <v>80</v>
@@ -23751,26 +23767,26 @@
         <v>80</v>
       </c>
     </row>
-    <row r="173">
+    <row r="173" hidden="true">
       <c r="A173" t="s" s="2">
-        <v>629</v>
+        <v>632</v>
       </c>
       <c r="B173" t="s" s="2">
-        <v>630</v>
+        <v>633</v>
       </c>
       <c r="C173" s="2"/>
       <c r="D173" t="s" s="2">
-        <v>80</v>
+        <v>110</v>
       </c>
       <c r="E173" s="2"/>
       <c r="F173" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="G173" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H173" t="s" s="2">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="I173" t="s" s="2">
         <v>80</v>
@@ -23779,16 +23795,16 @@
         <v>80</v>
       </c>
       <c r="K173" t="s" s="2">
-        <v>132</v>
+        <v>111</v>
       </c>
       <c r="L173" t="s" s="2">
-        <v>205</v>
+        <v>112</v>
       </c>
       <c r="M173" t="s" s="2">
-        <v>206</v>
+        <v>113</v>
       </c>
       <c r="N173" t="s" s="2">
-        <v>207</v>
+        <v>114</v>
       </c>
       <c r="O173" s="2"/>
       <c r="P173" t="s" s="2">
@@ -23796,7 +23812,7 @@
       </c>
       <c r="Q173" s="2"/>
       <c r="R173" t="s" s="2">
-        <v>631</v>
+        <v>80</v>
       </c>
       <c r="S173" t="s" s="2">
         <v>80</v>
@@ -23826,31 +23842,31 @@
         <v>80</v>
       </c>
       <c r="AB173" t="s" s="2">
-        <v>80</v>
+        <v>115</v>
       </c>
       <c r="AC173" t="s" s="2">
-        <v>80</v>
+        <v>116</v>
       </c>
       <c r="AD173" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE173" t="s" s="2">
-        <v>80</v>
+        <v>117</v>
       </c>
       <c r="AF173" t="s" s="2">
-        <v>209</v>
+        <v>118</v>
       </c>
       <c r="AG173" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AH173" t="s" s="2">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="AI173" t="s" s="2">
-        <v>80</v>
+        <v>198</v>
       </c>
       <c r="AJ173" t="s" s="2">
-        <v>80</v>
+        <v>119</v>
       </c>
       <c r="AK173" t="s" s="2">
         <v>80</v>
@@ -23873,10 +23889,10 @@
     </row>
     <row r="174">
       <c r="A174" t="s" s="2">
-        <v>632</v>
+        <v>634</v>
       </c>
       <c r="B174" t="s" s="2">
-        <v>633</v>
+        <v>635</v>
       </c>
       <c r="C174" s="2"/>
       <c r="D174" t="s" s="2">
@@ -23899,22 +23915,24 @@
         <v>80</v>
       </c>
       <c r="K174" t="s" s="2">
-        <v>241</v>
+        <v>132</v>
       </c>
       <c r="L174" t="s" s="2">
-        <v>213</v>
+        <v>205</v>
       </c>
       <c r="M174" t="s" s="2">
-        <v>214</v>
-      </c>
-      <c r="N174" s="2"/>
+        <v>206</v>
+      </c>
+      <c r="N174" t="s" s="2">
+        <v>207</v>
+      </c>
       <c r="O174" s="2"/>
       <c r="P174" t="s" s="2">
         <v>80</v>
       </c>
       <c r="Q174" s="2"/>
       <c r="R174" t="s" s="2">
-        <v>80</v>
+        <v>636</v>
       </c>
       <c r="S174" t="s" s="2">
         <v>80</v>
@@ -23956,22 +23974,22 @@
         <v>80</v>
       </c>
       <c r="AF174" t="s" s="2">
-        <v>215</v>
+        <v>209</v>
       </c>
       <c r="AG174" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AH174" t="s" s="2">
         <v>91</v>
       </c>
       <c r="AI174" t="s" s="2">
-        <v>198</v>
+        <v>80</v>
       </c>
       <c r="AJ174" t="s" s="2">
-        <v>103</v>
+        <v>80</v>
       </c>
       <c r="AK174" t="s" s="2">
-        <v>634</v>
+        <v>80</v>
       </c>
       <c r="AL174" t="s" s="2">
         <v>80</v>
@@ -23989,12 +24007,12 @@
         <v>80</v>
       </c>
     </row>
-    <row r="175" hidden="true">
+    <row r="175">
       <c r="A175" t="s" s="2">
-        <v>635</v>
+        <v>637</v>
       </c>
       <c r="B175" t="s" s="2">
-        <v>636</v>
+        <v>638</v>
       </c>
       <c r="C175" s="2"/>
       <c r="D175" t="s" s="2">
@@ -24002,13 +24020,13 @@
       </c>
       <c r="E175" s="2"/>
       <c r="F175" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="G175" t="s" s="2">
         <v>91</v>
       </c>
       <c r="H175" t="s" s="2">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="I175" t="s" s="2">
         <v>80</v>
@@ -24017,13 +24035,13 @@
         <v>80</v>
       </c>
       <c r="K175" t="s" s="2">
-        <v>105</v>
+        <v>241</v>
       </c>
       <c r="L175" t="s" s="2">
-        <v>106</v>
+        <v>213</v>
       </c>
       <c r="M175" t="s" s="2">
-        <v>107</v>
+        <v>214</v>
       </c>
       <c r="N175" s="2"/>
       <c r="O175" s="2"/>
@@ -24074,7 +24092,7 @@
         <v>80</v>
       </c>
       <c r="AF175" t="s" s="2">
-        <v>108</v>
+        <v>215</v>
       </c>
       <c r="AG175" t="s" s="2">
         <v>81</v>
@@ -24083,13 +24101,13 @@
         <v>91</v>
       </c>
       <c r="AI175" t="s" s="2">
-        <v>80</v>
+        <v>198</v>
       </c>
       <c r="AJ175" t="s" s="2">
-        <v>80</v>
+        <v>103</v>
       </c>
       <c r="AK175" t="s" s="2">
-        <v>80</v>
+        <v>639</v>
       </c>
       <c r="AL175" t="s" s="2">
         <v>80</v>
@@ -24109,21 +24127,21 @@
     </row>
     <row r="176" hidden="true">
       <c r="A176" t="s" s="2">
-        <v>637</v>
+        <v>640</v>
       </c>
       <c r="B176" t="s" s="2">
-        <v>638</v>
+        <v>641</v>
       </c>
       <c r="C176" s="2"/>
       <c r="D176" t="s" s="2">
-        <v>110</v>
+        <v>80</v>
       </c>
       <c r="E176" s="2"/>
       <c r="F176" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G176" t="s" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="H176" t="s" s="2">
         <v>80</v>
@@ -24135,17 +24153,15 @@
         <v>80</v>
       </c>
       <c r="K176" t="s" s="2">
-        <v>111</v>
+        <v>105</v>
       </c>
       <c r="L176" t="s" s="2">
-        <v>112</v>
+        <v>106</v>
       </c>
       <c r="M176" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="N176" t="s" s="2">
-        <v>114</v>
-      </c>
+        <v>107</v>
+      </c>
+      <c r="N176" s="2"/>
       <c r="O176" s="2"/>
       <c r="P176" t="s" s="2">
         <v>80</v>
@@ -24182,31 +24198,31 @@
         <v>80</v>
       </c>
       <c r="AB176" t="s" s="2">
-        <v>115</v>
+        <v>80</v>
       </c>
       <c r="AC176" t="s" s="2">
-        <v>116</v>
+        <v>80</v>
       </c>
       <c r="AD176" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE176" t="s" s="2">
-        <v>117</v>
+        <v>80</v>
       </c>
       <c r="AF176" t="s" s="2">
-        <v>118</v>
+        <v>108</v>
       </c>
       <c r="AG176" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH176" t="s" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="AI176" t="s" s="2">
-        <v>198</v>
+        <v>80</v>
       </c>
       <c r="AJ176" t="s" s="2">
-        <v>119</v>
+        <v>80</v>
       </c>
       <c r="AK176" t="s" s="2">
         <v>80</v>
@@ -24227,48 +24243,46 @@
         <v>80</v>
       </c>
     </row>
-    <row r="177">
+    <row r="177" hidden="true">
       <c r="A177" t="s" s="2">
-        <v>639</v>
+        <v>642</v>
       </c>
       <c r="B177" t="s" s="2">
-        <v>640</v>
+        <v>643</v>
       </c>
       <c r="C177" s="2"/>
       <c r="D177" t="s" s="2">
-        <v>80</v>
+        <v>110</v>
       </c>
       <c r="E177" s="2"/>
       <c r="F177" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="G177" t="s" s="2">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="H177" t="s" s="2">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="I177" t="s" s="2">
         <v>80</v>
       </c>
       <c r="J177" t="s" s="2">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="K177" t="s" s="2">
-        <v>144</v>
+        <v>111</v>
       </c>
       <c r="L177" t="s" s="2">
-        <v>257</v>
+        <v>112</v>
       </c>
       <c r="M177" t="s" s="2">
-        <v>258</v>
+        <v>113</v>
       </c>
       <c r="N177" t="s" s="2">
-        <v>259</v>
-      </c>
-      <c r="O177" t="s" s="2">
-        <v>260</v>
-      </c>
+        <v>114</v>
+      </c>
+      <c r="O177" s="2"/>
       <c r="P177" t="s" s="2">
         <v>80</v>
       </c>
@@ -24292,31 +24306,31 @@
         <v>80</v>
       </c>
       <c r="X177" t="s" s="2">
-        <v>245</v>
+        <v>80</v>
       </c>
       <c r="Y177" t="s" s="2">
-        <v>641</v>
+        <v>80</v>
       </c>
       <c r="Z177" t="s" s="2">
-        <v>642</v>
+        <v>80</v>
       </c>
       <c r="AA177" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AB177" t="s" s="2">
-        <v>80</v>
+        <v>115</v>
       </c>
       <c r="AC177" t="s" s="2">
-        <v>80</v>
+        <v>116</v>
       </c>
       <c r="AD177" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE177" t="s" s="2">
-        <v>80</v>
+        <v>117</v>
       </c>
       <c r="AF177" t="s" s="2">
-        <v>261</v>
+        <v>118</v>
       </c>
       <c r="AG177" t="s" s="2">
         <v>81</v>
@@ -24328,7 +24342,7 @@
         <v>198</v>
       </c>
       <c r="AJ177" t="s" s="2">
-        <v>103</v>
+        <v>119</v>
       </c>
       <c r="AK177" t="s" s="2">
         <v>80</v>
@@ -24340,7 +24354,7 @@
         <v>80</v>
       </c>
       <c r="AN177" t="s" s="2">
-        <v>262</v>
+        <v>80</v>
       </c>
       <c r="AO177" t="s" s="2">
         <v>80</v>
@@ -24349,12 +24363,12 @@
         <v>80</v>
       </c>
     </row>
-    <row r="178" hidden="true">
+    <row r="178">
       <c r="A178" t="s" s="2">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="B178" t="s" s="2">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="C178" s="2"/>
       <c r="D178" t="s" s="2">
@@ -24362,31 +24376,35 @@
       </c>
       <c r="E178" s="2"/>
       <c r="F178" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="G178" t="s" s="2">
         <v>91</v>
       </c>
       <c r="H178" t="s" s="2">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="I178" t="s" s="2">
         <v>80</v>
       </c>
       <c r="J178" t="s" s="2">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="K178" t="s" s="2">
-        <v>105</v>
+        <v>144</v>
       </c>
       <c r="L178" t="s" s="2">
-        <v>106</v>
+        <v>257</v>
       </c>
       <c r="M178" t="s" s="2">
-        <v>107</v>
-      </c>
-      <c r="N178" s="2"/>
-      <c r="O178" s="2"/>
+        <v>258</v>
+      </c>
+      <c r="N178" t="s" s="2">
+        <v>259</v>
+      </c>
+      <c r="O178" t="s" s="2">
+        <v>260</v>
+      </c>
       <c r="P178" t="s" s="2">
         <v>80</v>
       </c>
@@ -24410,13 +24428,13 @@
         <v>80</v>
       </c>
       <c r="X178" t="s" s="2">
-        <v>80</v>
+        <v>245</v>
       </c>
       <c r="Y178" t="s" s="2">
-        <v>80</v>
+        <v>646</v>
       </c>
       <c r="Z178" t="s" s="2">
-        <v>80</v>
+        <v>647</v>
       </c>
       <c r="AA178" t="s" s="2">
         <v>80</v>
@@ -24434,19 +24452,19 @@
         <v>80</v>
       </c>
       <c r="AF178" t="s" s="2">
-        <v>108</v>
+        <v>261</v>
       </c>
       <c r="AG178" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH178" t="s" s="2">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="AI178" t="s" s="2">
-        <v>80</v>
+        <v>198</v>
       </c>
       <c r="AJ178" t="s" s="2">
-        <v>80</v>
+        <v>103</v>
       </c>
       <c r="AK178" t="s" s="2">
         <v>80</v>
@@ -24458,7 +24476,7 @@
         <v>80</v>
       </c>
       <c r="AN178" t="s" s="2">
-        <v>80</v>
+        <v>262</v>
       </c>
       <c r="AO178" t="s" s="2">
         <v>80</v>
@@ -24469,21 +24487,21 @@
     </row>
     <row r="179" hidden="true">
       <c r="A179" t="s" s="2">
-        <v>645</v>
+        <v>648</v>
       </c>
       <c r="B179" t="s" s="2">
-        <v>646</v>
+        <v>649</v>
       </c>
       <c r="C179" s="2"/>
       <c r="D179" t="s" s="2">
-        <v>110</v>
+        <v>80</v>
       </c>
       <c r="E179" s="2"/>
       <c r="F179" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G179" t="s" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="H179" t="s" s="2">
         <v>80</v>
@@ -24495,17 +24513,15 @@
         <v>80</v>
       </c>
       <c r="K179" t="s" s="2">
-        <v>111</v>
+        <v>105</v>
       </c>
       <c r="L179" t="s" s="2">
-        <v>112</v>
+        <v>106</v>
       </c>
       <c r="M179" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="N179" t="s" s="2">
-        <v>114</v>
-      </c>
+        <v>107</v>
+      </c>
+      <c r="N179" s="2"/>
       <c r="O179" s="2"/>
       <c r="P179" t="s" s="2">
         <v>80</v>
@@ -24542,31 +24558,31 @@
         <v>80</v>
       </c>
       <c r="AB179" t="s" s="2">
-        <v>115</v>
+        <v>80</v>
       </c>
       <c r="AC179" t="s" s="2">
-        <v>116</v>
+        <v>80</v>
       </c>
       <c r="AD179" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE179" t="s" s="2">
-        <v>117</v>
+        <v>80</v>
       </c>
       <c r="AF179" t="s" s="2">
-        <v>118</v>
+        <v>108</v>
       </c>
       <c r="AG179" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH179" t="s" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="AI179" t="s" s="2">
-        <v>198</v>
+        <v>80</v>
       </c>
       <c r="AJ179" t="s" s="2">
-        <v>119</v>
+        <v>80</v>
       </c>
       <c r="AK179" t="s" s="2">
         <v>80</v>
@@ -24587,48 +24603,46 @@
         <v>80</v>
       </c>
     </row>
-    <row r="180">
+    <row r="180" hidden="true">
       <c r="A180" t="s" s="2">
-        <v>647</v>
+        <v>650</v>
       </c>
       <c r="B180" t="s" s="2">
-        <v>648</v>
+        <v>651</v>
       </c>
       <c r="C180" s="2"/>
       <c r="D180" t="s" s="2">
-        <v>80</v>
+        <v>110</v>
       </c>
       <c r="E180" s="2"/>
       <c r="F180" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="G180" t="s" s="2">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="H180" t="s" s="2">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="I180" t="s" s="2">
         <v>80</v>
       </c>
       <c r="J180" t="s" s="2">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="K180" t="s" s="2">
-        <v>132</v>
+        <v>111</v>
       </c>
       <c r="L180" t="s" s="2">
-        <v>266</v>
+        <v>112</v>
       </c>
       <c r="M180" t="s" s="2">
-        <v>267</v>
+        <v>113</v>
       </c>
       <c r="N180" t="s" s="2">
-        <v>268</v>
-      </c>
-      <c r="O180" t="s" s="2">
-        <v>269</v>
-      </c>
+        <v>114</v>
+      </c>
+      <c r="O180" s="2"/>
       <c r="P180" t="s" s="2">
         <v>80</v>
       </c>
@@ -24664,31 +24678,31 @@
         <v>80</v>
       </c>
       <c r="AB180" t="s" s="2">
-        <v>80</v>
+        <v>115</v>
       </c>
       <c r="AC180" t="s" s="2">
-        <v>80</v>
+        <v>116</v>
       </c>
       <c r="AD180" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE180" t="s" s="2">
-        <v>80</v>
+        <v>117</v>
       </c>
       <c r="AF180" t="s" s="2">
-        <v>270</v>
+        <v>118</v>
       </c>
       <c r="AG180" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH180" t="s" s="2">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="AI180" t="s" s="2">
         <v>198</v>
       </c>
       <c r="AJ180" t="s" s="2">
-        <v>103</v>
+        <v>119</v>
       </c>
       <c r="AK180" t="s" s="2">
         <v>80</v>
@@ -24700,7 +24714,7 @@
         <v>80</v>
       </c>
       <c r="AN180" t="s" s="2">
-        <v>271</v>
+        <v>80</v>
       </c>
       <c r="AO180" t="s" s="2">
         <v>80</v>
@@ -24709,12 +24723,12 @@
         <v>80</v>
       </c>
     </row>
-    <row r="181" hidden="true">
+    <row r="181">
       <c r="A181" t="s" s="2">
-        <v>649</v>
+        <v>652</v>
       </c>
       <c r="B181" t="s" s="2">
-        <v>650</v>
+        <v>653</v>
       </c>
       <c r="C181" s="2"/>
       <c r="D181" t="s" s="2">
@@ -24722,13 +24736,13 @@
       </c>
       <c r="E181" s="2"/>
       <c r="F181" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="G181" t="s" s="2">
         <v>91</v>
       </c>
       <c r="H181" t="s" s="2">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="I181" t="s" s="2">
         <v>80</v>
@@ -24737,18 +24751,20 @@
         <v>92</v>
       </c>
       <c r="K181" t="s" s="2">
-        <v>105</v>
+        <v>132</v>
       </c>
       <c r="L181" t="s" s="2">
-        <v>273</v>
+        <v>266</v>
       </c>
       <c r="M181" t="s" s="2">
-        <v>274</v>
+        <v>267</v>
       </c>
       <c r="N181" t="s" s="2">
-        <v>275</v>
-      </c>
-      <c r="O181" s="2"/>
+        <v>268</v>
+      </c>
+      <c r="O181" t="s" s="2">
+        <v>269</v>
+      </c>
       <c r="P181" t="s" s="2">
         <v>80</v>
       </c>
@@ -24796,7 +24812,7 @@
         <v>80</v>
       </c>
       <c r="AF181" t="s" s="2">
-        <v>276</v>
+        <v>270</v>
       </c>
       <c r="AG181" t="s" s="2">
         <v>81</v>
@@ -24820,7 +24836,7 @@
         <v>80</v>
       </c>
       <c r="AN181" t="s" s="2">
-        <v>277</v>
+        <v>271</v>
       </c>
       <c r="AO181" t="s" s="2">
         <v>80</v>
@@ -24829,12 +24845,12 @@
         <v>80</v>
       </c>
     </row>
-    <row r="182">
+    <row r="182" hidden="true">
       <c r="A182" t="s" s="2">
-        <v>651</v>
+        <v>654</v>
       </c>
       <c r="B182" t="s" s="2">
-        <v>652</v>
+        <v>655</v>
       </c>
       <c r="C182" s="2"/>
       <c r="D182" t="s" s="2">
@@ -24842,13 +24858,13 @@
       </c>
       <c r="E182" s="2"/>
       <c r="F182" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="G182" t="s" s="2">
         <v>91</v>
       </c>
       <c r="H182" t="s" s="2">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="I182" t="s" s="2">
         <v>80</v>
@@ -24857,20 +24873,18 @@
         <v>92</v>
       </c>
       <c r="K182" t="s" s="2">
-        <v>166</v>
+        <v>105</v>
       </c>
       <c r="L182" t="s" s="2">
-        <v>279</v>
+        <v>273</v>
       </c>
       <c r="M182" t="s" s="2">
-        <v>280</v>
+        <v>274</v>
       </c>
       <c r="N182" t="s" s="2">
-        <v>402</v>
-      </c>
-      <c r="O182" t="s" s="2">
-        <v>281</v>
-      </c>
+        <v>275</v>
+      </c>
+      <c r="O182" s="2"/>
       <c r="P182" t="s" s="2">
         <v>80</v>
       </c>
@@ -24918,7 +24932,7 @@
         <v>80</v>
       </c>
       <c r="AF182" t="s" s="2">
-        <v>282</v>
+        <v>276</v>
       </c>
       <c r="AG182" t="s" s="2">
         <v>81</v>
@@ -24942,7 +24956,7 @@
         <v>80</v>
       </c>
       <c r="AN182" t="s" s="2">
-        <v>283</v>
+        <v>277</v>
       </c>
       <c r="AO182" t="s" s="2">
         <v>80</v>
@@ -24951,12 +24965,12 @@
         <v>80</v>
       </c>
     </row>
-    <row r="183" hidden="true">
+    <row r="183">
       <c r="A183" t="s" s="2">
-        <v>653</v>
+        <v>656</v>
       </c>
       <c r="B183" t="s" s="2">
-        <v>654</v>
+        <v>657</v>
       </c>
       <c r="C183" s="2"/>
       <c r="D183" t="s" s="2">
@@ -24964,13 +24978,13 @@
       </c>
       <c r="E183" s="2"/>
       <c r="F183" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="G183" t="s" s="2">
         <v>91</v>
       </c>
       <c r="H183" t="s" s="2">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="I183" t="s" s="2">
         <v>80</v>
@@ -24979,19 +24993,19 @@
         <v>92</v>
       </c>
       <c r="K183" t="s" s="2">
-        <v>105</v>
+        <v>166</v>
       </c>
       <c r="L183" t="s" s="2">
-        <v>285</v>
+        <v>279</v>
       </c>
       <c r="M183" t="s" s="2">
-        <v>286</v>
+        <v>280</v>
       </c>
       <c r="N183" t="s" s="2">
         <v>402</v>
       </c>
       <c r="O183" t="s" s="2">
-        <v>287</v>
+        <v>281</v>
       </c>
       <c r="P183" t="s" s="2">
         <v>80</v>
@@ -25040,7 +25054,7 @@
         <v>80</v>
       </c>
       <c r="AF183" t="s" s="2">
-        <v>288</v>
+        <v>282</v>
       </c>
       <c r="AG183" t="s" s="2">
         <v>81</v>
@@ -25064,7 +25078,7 @@
         <v>80</v>
       </c>
       <c r="AN183" t="s" s="2">
-        <v>289</v>
+        <v>283</v>
       </c>
       <c r="AO183" t="s" s="2">
         <v>80</v>
@@ -25075,10 +25089,10 @@
     </row>
     <row r="184" hidden="true">
       <c r="A184" t="s" s="2">
-        <v>655</v>
+        <v>658</v>
       </c>
       <c r="B184" t="s" s="2">
-        <v>656</v>
+        <v>659</v>
       </c>
       <c r="C184" s="2"/>
       <c r="D184" t="s" s="2">
@@ -25101,19 +25115,19 @@
         <v>92</v>
       </c>
       <c r="K184" t="s" s="2">
-        <v>291</v>
+        <v>105</v>
       </c>
       <c r="L184" t="s" s="2">
-        <v>292</v>
+        <v>285</v>
       </c>
       <c r="M184" t="s" s="2">
-        <v>293</v>
+        <v>286</v>
       </c>
       <c r="N184" t="s" s="2">
-        <v>294</v>
+        <v>402</v>
       </c>
       <c r="O184" t="s" s="2">
-        <v>295</v>
+        <v>287</v>
       </c>
       <c r="P184" t="s" s="2">
         <v>80</v>
@@ -25162,7 +25176,7 @@
         <v>80</v>
       </c>
       <c r="AF184" t="s" s="2">
-        <v>296</v>
+        <v>288</v>
       </c>
       <c r="AG184" t="s" s="2">
         <v>81</v>
@@ -25186,7 +25200,7 @@
         <v>80</v>
       </c>
       <c r="AN184" t="s" s="2">
-        <v>297</v>
+        <v>289</v>
       </c>
       <c r="AO184" t="s" s="2">
         <v>80</v>
@@ -25197,10 +25211,10 @@
     </row>
     <row r="185" hidden="true">
       <c r="A185" t="s" s="2">
-        <v>657</v>
+        <v>660</v>
       </c>
       <c r="B185" t="s" s="2">
-        <v>658</v>
+        <v>661</v>
       </c>
       <c r="C185" s="2"/>
       <c r="D185" t="s" s="2">
@@ -25223,19 +25237,19 @@
         <v>92</v>
       </c>
       <c r="K185" t="s" s="2">
-        <v>105</v>
+        <v>291</v>
       </c>
       <c r="L185" t="s" s="2">
-        <v>299</v>
+        <v>292</v>
       </c>
       <c r="M185" t="s" s="2">
-        <v>300</v>
+        <v>293</v>
       </c>
       <c r="N185" t="s" s="2">
-        <v>301</v>
+        <v>294</v>
       </c>
       <c r="O185" t="s" s="2">
-        <v>302</v>
+        <v>295</v>
       </c>
       <c r="P185" t="s" s="2">
         <v>80</v>
@@ -25284,7 +25298,7 @@
         <v>80</v>
       </c>
       <c r="AF185" t="s" s="2">
-        <v>303</v>
+        <v>296</v>
       </c>
       <c r="AG185" t="s" s="2">
         <v>81</v>
@@ -25308,7 +25322,7 @@
         <v>80</v>
       </c>
       <c r="AN185" t="s" s="2">
-        <v>304</v>
+        <v>297</v>
       </c>
       <c r="AO185" t="s" s="2">
         <v>80</v>
@@ -25319,10 +25333,10 @@
     </row>
     <row r="186" hidden="true">
       <c r="A186" t="s" s="2">
-        <v>659</v>
+        <v>662</v>
       </c>
       <c r="B186" t="s" s="2">
-        <v>660</v>
+        <v>663</v>
       </c>
       <c r="C186" s="2"/>
       <c r="D186" t="s" s="2">
@@ -25342,19 +25356,23 @@
         <v>80</v>
       </c>
       <c r="J186" t="s" s="2">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="K186" t="s" s="2">
-        <v>226</v>
+        <v>105</v>
       </c>
       <c r="L186" t="s" s="2">
-        <v>661</v>
+        <v>299</v>
       </c>
       <c r="M186" t="s" s="2">
-        <v>662</v>
-      </c>
-      <c r="N186" s="2"/>
-      <c r="O186" s="2"/>
+        <v>300</v>
+      </c>
+      <c r="N186" t="s" s="2">
+        <v>301</v>
+      </c>
+      <c r="O186" t="s" s="2">
+        <v>302</v>
+      </c>
       <c r="P186" t="s" s="2">
         <v>80</v>
       </c>
@@ -25402,7 +25420,7 @@
         <v>80</v>
       </c>
       <c r="AF186" t="s" s="2">
-        <v>663</v>
+        <v>303</v>
       </c>
       <c r="AG186" t="s" s="2">
         <v>81</v>
@@ -25411,10 +25429,10 @@
         <v>91</v>
       </c>
       <c r="AI186" t="s" s="2">
-        <v>80</v>
+        <v>198</v>
       </c>
       <c r="AJ186" t="s" s="2">
-        <v>80</v>
+        <v>103</v>
       </c>
       <c r="AK186" t="s" s="2">
         <v>80</v>
@@ -25426,7 +25444,7 @@
         <v>80</v>
       </c>
       <c r="AN186" t="s" s="2">
-        <v>80</v>
+        <v>304</v>
       </c>
       <c r="AO186" t="s" s="2">
         <v>80</v>
@@ -25435,7 +25453,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="187">
+    <row r="187" hidden="true">
       <c r="A187" t="s" s="2">
         <v>664</v>
       </c>
@@ -25454,13 +25472,13 @@
         <v>91</v>
       </c>
       <c r="H187" t="s" s="2">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="I187" t="s" s="2">
         <v>80</v>
       </c>
       <c r="J187" t="s" s="2">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="K187" t="s" s="2">
         <v>226</v>
@@ -25471,98 +25489,94 @@
       <c r="M187" t="s" s="2">
         <v>667</v>
       </c>
-      <c r="N187" t="s" s="2">
-        <v>668</v>
-      </c>
+      <c r="N187" s="2"/>
       <c r="O187" s="2"/>
       <c r="P187" t="s" s="2">
         <v>80</v>
       </c>
-      <c r="Q187" t="s" s="2">
+      <c r="Q187" s="2"/>
+      <c r="R187" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S187" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T187" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U187" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V187" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W187" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X187" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y187" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z187" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA187" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB187" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC187" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD187" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE187" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF187" t="s" s="2">
+        <v>668</v>
+      </c>
+      <c r="AG187" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH187" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="AI187" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ187" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AK187" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL187" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM187" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN187" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AO187" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AP187" t="s" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="s" s="2">
         <v>669</v>
       </c>
-      <c r="R187" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="S187" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="T187" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="U187" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="V187" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="W187" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="X187" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Y187" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Z187" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AA187" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB187" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC187" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AD187" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE187" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AF187" t="s" s="2">
+      <c r="B188" t="s" s="2">
         <v>670</v>
-      </c>
-      <c r="AG187" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH187" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="AI187" t="s" s="2">
-        <v>613</v>
-      </c>
-      <c r="AJ187" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="AK187" t="s" s="2">
-        <v>671</v>
-      </c>
-      <c r="AL187" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AM187" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN187" t="s" s="2">
-        <v>672</v>
-      </c>
-      <c r="AO187" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AP187" t="s" s="2">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="188" hidden="true">
-      <c r="A188" t="s" s="2">
-        <v>673</v>
-      </c>
-      <c r="B188" t="s" s="2">
-        <v>674</v>
       </c>
       <c r="C188" s="2"/>
       <c r="D188" t="s" s="2">
@@ -25576,29 +25590,33 @@
         <v>91</v>
       </c>
       <c r="H188" t="s" s="2">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="I188" t="s" s="2">
         <v>80</v>
       </c>
       <c r="J188" t="s" s="2">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="K188" t="s" s="2">
-        <v>105</v>
+        <v>226</v>
       </c>
       <c r="L188" t="s" s="2">
-        <v>618</v>
+        <v>671</v>
       </c>
       <c r="M188" t="s" s="2">
-        <v>619</v>
-      </c>
-      <c r="N188" s="2"/>
+        <v>672</v>
+      </c>
+      <c r="N188" t="s" s="2">
+        <v>673</v>
+      </c>
       <c r="O188" s="2"/>
       <c r="P188" t="s" s="2">
         <v>80</v>
       </c>
-      <c r="Q188" s="2"/>
+      <c r="Q188" t="s" s="2">
+        <v>674</v>
+      </c>
       <c r="R188" t="s" s="2">
         <v>80</v>
       </c>
@@ -25642,7 +25660,7 @@
         <v>80</v>
       </c>
       <c r="AF188" t="s" s="2">
-        <v>108</v>
+        <v>675</v>
       </c>
       <c r="AG188" t="s" s="2">
         <v>81</v>
@@ -25651,13 +25669,13 @@
         <v>91</v>
       </c>
       <c r="AI188" t="s" s="2">
-        <v>80</v>
+        <v>618</v>
       </c>
       <c r="AJ188" t="s" s="2">
-        <v>80</v>
+        <v>103</v>
       </c>
       <c r="AK188" t="s" s="2">
-        <v>80</v>
+        <v>676</v>
       </c>
       <c r="AL188" t="s" s="2">
         <v>80</v>
@@ -25666,7 +25684,7 @@
         <v>80</v>
       </c>
       <c r="AN188" t="s" s="2">
-        <v>80</v>
+        <v>677</v>
       </c>
       <c r="AO188" t="s" s="2">
         <v>80</v>
@@ -25677,10 +25695,10 @@
     </row>
     <row r="189" hidden="true">
       <c r="A189" t="s" s="2">
-        <v>675</v>
+        <v>678</v>
       </c>
       <c r="B189" t="s" s="2">
-        <v>676</v>
+        <v>679</v>
       </c>
       <c r="C189" s="2"/>
       <c r="D189" t="s" s="2">
@@ -25691,7 +25709,7 @@
         <v>81</v>
       </c>
       <c r="G189" t="s" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="H189" t="s" s="2">
         <v>80</v>
@@ -25703,13 +25721,13 @@
         <v>80</v>
       </c>
       <c r="K189" t="s" s="2">
-        <v>111</v>
+        <v>105</v>
       </c>
       <c r="L189" t="s" s="2">
-        <v>189</v>
+        <v>623</v>
       </c>
       <c r="M189" t="s" s="2">
-        <v>190</v>
+        <v>624</v>
       </c>
       <c r="N189" s="2"/>
       <c r="O189" s="2"/>
@@ -25748,29 +25766,31 @@
         <v>80</v>
       </c>
       <c r="AB189" t="s" s="2">
-        <v>115</v>
-      </c>
-      <c r="AC189" s="2"/>
+        <v>80</v>
+      </c>
+      <c r="AC189" t="s" s="2">
+        <v>80</v>
+      </c>
       <c r="AD189" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE189" t="s" s="2">
-        <v>117</v>
+        <v>80</v>
       </c>
       <c r="AF189" t="s" s="2">
-        <v>118</v>
+        <v>108</v>
       </c>
       <c r="AG189" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH189" t="s" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="AI189" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ189" t="s" s="2">
-        <v>119</v>
+        <v>80</v>
       </c>
       <c r="AK189" t="s" s="2">
         <v>80</v>
@@ -25791,16 +25811,14 @@
         <v>80</v>
       </c>
     </row>
-    <row r="190">
+    <row r="190" hidden="true">
       <c r="A190" t="s" s="2">
-        <v>677</v>
+        <v>680</v>
       </c>
       <c r="B190" t="s" s="2">
-        <v>676</v>
-      </c>
-      <c r="C190" t="s" s="2">
-        <v>678</v>
-      </c>
+        <v>681</v>
+      </c>
+      <c r="C190" s="2"/>
       <c r="D190" t="s" s="2">
         <v>80</v>
       </c>
@@ -25809,10 +25827,10 @@
         <v>81</v>
       </c>
       <c r="G190" t="s" s="2">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="H190" t="s" s="2">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="I190" t="s" s="2">
         <v>80</v>
@@ -25821,13 +25839,13 @@
         <v>80</v>
       </c>
       <c r="K190" t="s" s="2">
-        <v>624</v>
+        <v>111</v>
       </c>
       <c r="L190" t="s" s="2">
-        <v>380</v>
+        <v>189</v>
       </c>
       <c r="M190" t="s" s="2">
-        <v>381</v>
+        <v>190</v>
       </c>
       <c r="N190" s="2"/>
       <c r="O190" s="2"/>
@@ -25866,16 +25884,14 @@
         <v>80</v>
       </c>
       <c r="AB190" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC190" t="s" s="2">
-        <v>80</v>
-      </c>
+        <v>115</v>
+      </c>
+      <c r="AC190" s="2"/>
       <c r="AD190" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE190" t="s" s="2">
-        <v>80</v>
+        <v>117</v>
       </c>
       <c r="AF190" t="s" s="2">
         <v>118</v>
@@ -25887,7 +25903,7 @@
         <v>82</v>
       </c>
       <c r="AI190" t="s" s="2">
-        <v>198</v>
+        <v>80</v>
       </c>
       <c r="AJ190" t="s" s="2">
         <v>119</v>
@@ -25911,14 +25927,16 @@
         <v>80</v>
       </c>
     </row>
-    <row r="191" hidden="true">
+    <row r="191">
       <c r="A191" t="s" s="2">
-        <v>679</v>
+        <v>682</v>
       </c>
       <c r="B191" t="s" s="2">
-        <v>680</v>
-      </c>
-      <c r="C191" s="2"/>
+        <v>681</v>
+      </c>
+      <c r="C191" t="s" s="2">
+        <v>683</v>
+      </c>
       <c r="D191" t="s" s="2">
         <v>80</v>
       </c>
@@ -25930,7 +25948,7 @@
         <v>91</v>
       </c>
       <c r="H191" t="s" s="2">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="I191" t="s" s="2">
         <v>80</v>
@@ -25939,13 +25957,13 @@
         <v>80</v>
       </c>
       <c r="K191" t="s" s="2">
-        <v>105</v>
+        <v>629</v>
       </c>
       <c r="L191" t="s" s="2">
-        <v>106</v>
+        <v>380</v>
       </c>
       <c r="M191" t="s" s="2">
-        <v>107</v>
+        <v>381</v>
       </c>
       <c r="N191" s="2"/>
       <c r="O191" s="2"/>
@@ -25996,19 +26014,19 @@
         <v>80</v>
       </c>
       <c r="AF191" t="s" s="2">
-        <v>108</v>
+        <v>118</v>
       </c>
       <c r="AG191" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH191" t="s" s="2">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="AI191" t="s" s="2">
-        <v>80</v>
+        <v>198</v>
       </c>
       <c r="AJ191" t="s" s="2">
-        <v>80</v>
+        <v>119</v>
       </c>
       <c r="AK191" t="s" s="2">
         <v>80</v>
@@ -26031,21 +26049,21 @@
     </row>
     <row r="192" hidden="true">
       <c r="A192" t="s" s="2">
-        <v>681</v>
+        <v>684</v>
       </c>
       <c r="B192" t="s" s="2">
-        <v>682</v>
+        <v>685</v>
       </c>
       <c r="C192" s="2"/>
       <c r="D192" t="s" s="2">
-        <v>110</v>
+        <v>80</v>
       </c>
       <c r="E192" s="2"/>
       <c r="F192" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G192" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H192" t="s" s="2">
         <v>80</v>
@@ -26057,17 +26075,15 @@
         <v>80</v>
       </c>
       <c r="K192" t="s" s="2">
-        <v>111</v>
+        <v>105</v>
       </c>
       <c r="L192" t="s" s="2">
-        <v>112</v>
+        <v>106</v>
       </c>
       <c r="M192" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="N192" t="s" s="2">
-        <v>114</v>
-      </c>
+        <v>107</v>
+      </c>
+      <c r="N192" s="2"/>
       <c r="O192" s="2"/>
       <c r="P192" t="s" s="2">
         <v>80</v>
@@ -26104,31 +26120,31 @@
         <v>80</v>
       </c>
       <c r="AB192" t="s" s="2">
-        <v>115</v>
+        <v>80</v>
       </c>
       <c r="AC192" t="s" s="2">
-        <v>116</v>
+        <v>80</v>
       </c>
       <c r="AD192" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE192" t="s" s="2">
-        <v>117</v>
+        <v>80</v>
       </c>
       <c r="AF192" t="s" s="2">
-        <v>118</v>
+        <v>108</v>
       </c>
       <c r="AG192" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH192" t="s" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="AI192" t="s" s="2">
-        <v>198</v>
+        <v>80</v>
       </c>
       <c r="AJ192" t="s" s="2">
-        <v>119</v>
+        <v>80</v>
       </c>
       <c r="AK192" t="s" s="2">
         <v>80</v>
@@ -26149,26 +26165,26 @@
         <v>80</v>
       </c>
     </row>
-    <row r="193">
+    <row r="193" hidden="true">
       <c r="A193" t="s" s="2">
-        <v>683</v>
+        <v>686</v>
       </c>
       <c r="B193" t="s" s="2">
-        <v>684</v>
+        <v>687</v>
       </c>
       <c r="C193" s="2"/>
       <c r="D193" t="s" s="2">
-        <v>80</v>
+        <v>110</v>
       </c>
       <c r="E193" s="2"/>
       <c r="F193" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="G193" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H193" t="s" s="2">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="I193" t="s" s="2">
         <v>80</v>
@@ -26177,16 +26193,16 @@
         <v>80</v>
       </c>
       <c r="K193" t="s" s="2">
-        <v>132</v>
+        <v>111</v>
       </c>
       <c r="L193" t="s" s="2">
-        <v>205</v>
+        <v>112</v>
       </c>
       <c r="M193" t="s" s="2">
-        <v>206</v>
+        <v>113</v>
       </c>
       <c r="N193" t="s" s="2">
-        <v>207</v>
+        <v>114</v>
       </c>
       <c r="O193" s="2"/>
       <c r="P193" t="s" s="2">
@@ -26194,7 +26210,7 @@
       </c>
       <c r="Q193" s="2"/>
       <c r="R193" t="s" s="2">
-        <v>631</v>
+        <v>80</v>
       </c>
       <c r="S193" t="s" s="2">
         <v>80</v>
@@ -26224,31 +26240,31 @@
         <v>80</v>
       </c>
       <c r="AB193" t="s" s="2">
-        <v>80</v>
+        <v>115</v>
       </c>
       <c r="AC193" t="s" s="2">
-        <v>80</v>
+        <v>116</v>
       </c>
       <c r="AD193" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE193" t="s" s="2">
-        <v>80</v>
+        <v>117</v>
       </c>
       <c r="AF193" t="s" s="2">
-        <v>209</v>
+        <v>118</v>
       </c>
       <c r="AG193" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AH193" t="s" s="2">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="AI193" t="s" s="2">
-        <v>80</v>
+        <v>198</v>
       </c>
       <c r="AJ193" t="s" s="2">
-        <v>80</v>
+        <v>119</v>
       </c>
       <c r="AK193" t="s" s="2">
         <v>80</v>
@@ -26271,10 +26287,10 @@
     </row>
     <row r="194">
       <c r="A194" t="s" s="2">
-        <v>685</v>
+        <v>688</v>
       </c>
       <c r="B194" t="s" s="2">
-        <v>686</v>
+        <v>689</v>
       </c>
       <c r="C194" s="2"/>
       <c r="D194" t="s" s="2">
@@ -26297,22 +26313,24 @@
         <v>80</v>
       </c>
       <c r="K194" t="s" s="2">
-        <v>241</v>
+        <v>132</v>
       </c>
       <c r="L194" t="s" s="2">
-        <v>213</v>
+        <v>205</v>
       </c>
       <c r="M194" t="s" s="2">
-        <v>214</v>
-      </c>
-      <c r="N194" s="2"/>
+        <v>206</v>
+      </c>
+      <c r="N194" t="s" s="2">
+        <v>207</v>
+      </c>
       <c r="O194" s="2"/>
       <c r="P194" t="s" s="2">
         <v>80</v>
       </c>
       <c r="Q194" s="2"/>
       <c r="R194" t="s" s="2">
-        <v>80</v>
+        <v>636</v>
       </c>
       <c r="S194" t="s" s="2">
         <v>80</v>
@@ -26354,22 +26372,22 @@
         <v>80</v>
       </c>
       <c r="AF194" t="s" s="2">
-        <v>215</v>
+        <v>209</v>
       </c>
       <c r="AG194" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AH194" t="s" s="2">
         <v>91</v>
       </c>
       <c r="AI194" t="s" s="2">
-        <v>198</v>
+        <v>80</v>
       </c>
       <c r="AJ194" t="s" s="2">
-        <v>103</v>
+        <v>80</v>
       </c>
       <c r="AK194" t="s" s="2">
-        <v>687</v>
+        <v>80</v>
       </c>
       <c r="AL194" t="s" s="2">
         <v>80</v>
@@ -26387,12 +26405,12 @@
         <v>80</v>
       </c>
     </row>
-    <row r="195" hidden="true">
+    <row r="195">
       <c r="A195" t="s" s="2">
-        <v>688</v>
+        <v>690</v>
       </c>
       <c r="B195" t="s" s="2">
-        <v>689</v>
+        <v>691</v>
       </c>
       <c r="C195" s="2"/>
       <c r="D195" t="s" s="2">
@@ -26400,13 +26418,13 @@
       </c>
       <c r="E195" s="2"/>
       <c r="F195" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="G195" t="s" s="2">
         <v>91</v>
       </c>
       <c r="H195" t="s" s="2">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="I195" t="s" s="2">
         <v>80</v>
@@ -26415,13 +26433,13 @@
         <v>80</v>
       </c>
       <c r="K195" t="s" s="2">
-        <v>105</v>
+        <v>241</v>
       </c>
       <c r="L195" t="s" s="2">
-        <v>106</v>
+        <v>213</v>
       </c>
       <c r="M195" t="s" s="2">
-        <v>107</v>
+        <v>214</v>
       </c>
       <c r="N195" s="2"/>
       <c r="O195" s="2"/>
@@ -26472,7 +26490,7 @@
         <v>80</v>
       </c>
       <c r="AF195" t="s" s="2">
-        <v>108</v>
+        <v>215</v>
       </c>
       <c r="AG195" t="s" s="2">
         <v>81</v>
@@ -26481,13 +26499,13 @@
         <v>91</v>
       </c>
       <c r="AI195" t="s" s="2">
-        <v>80</v>
+        <v>198</v>
       </c>
       <c r="AJ195" t="s" s="2">
-        <v>80</v>
+        <v>103</v>
       </c>
       <c r="AK195" t="s" s="2">
-        <v>80</v>
+        <v>692</v>
       </c>
       <c r="AL195" t="s" s="2">
         <v>80</v>
@@ -26507,21 +26525,21 @@
     </row>
     <row r="196" hidden="true">
       <c r="A196" t="s" s="2">
-        <v>690</v>
+        <v>693</v>
       </c>
       <c r="B196" t="s" s="2">
-        <v>691</v>
+        <v>694</v>
       </c>
       <c r="C196" s="2"/>
       <c r="D196" t="s" s="2">
-        <v>110</v>
+        <v>80</v>
       </c>
       <c r="E196" s="2"/>
       <c r="F196" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G196" t="s" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="H196" t="s" s="2">
         <v>80</v>
@@ -26533,17 +26551,15 @@
         <v>80</v>
       </c>
       <c r="K196" t="s" s="2">
-        <v>111</v>
+        <v>105</v>
       </c>
       <c r="L196" t="s" s="2">
-        <v>112</v>
+        <v>106</v>
       </c>
       <c r="M196" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="N196" t="s" s="2">
-        <v>114</v>
-      </c>
+        <v>107</v>
+      </c>
+      <c r="N196" s="2"/>
       <c r="O196" s="2"/>
       <c r="P196" t="s" s="2">
         <v>80</v>
@@ -26580,31 +26596,31 @@
         <v>80</v>
       </c>
       <c r="AB196" t="s" s="2">
-        <v>115</v>
+        <v>80</v>
       </c>
       <c r="AC196" t="s" s="2">
-        <v>116</v>
+        <v>80</v>
       </c>
       <c r="AD196" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE196" t="s" s="2">
-        <v>117</v>
+        <v>80</v>
       </c>
       <c r="AF196" t="s" s="2">
-        <v>118</v>
+        <v>108</v>
       </c>
       <c r="AG196" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH196" t="s" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="AI196" t="s" s="2">
-        <v>198</v>
+        <v>80</v>
       </c>
       <c r="AJ196" t="s" s="2">
-        <v>119</v>
+        <v>80</v>
       </c>
       <c r="AK196" t="s" s="2">
         <v>80</v>
@@ -26625,48 +26641,46 @@
         <v>80</v>
       </c>
     </row>
-    <row r="197">
+    <row r="197" hidden="true">
       <c r="A197" t="s" s="2">
-        <v>692</v>
+        <v>695</v>
       </c>
       <c r="B197" t="s" s="2">
-        <v>693</v>
+        <v>696</v>
       </c>
       <c r="C197" s="2"/>
       <c r="D197" t="s" s="2">
-        <v>80</v>
+        <v>110</v>
       </c>
       <c r="E197" s="2"/>
       <c r="F197" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="G197" t="s" s="2">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="H197" t="s" s="2">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="I197" t="s" s="2">
         <v>80</v>
       </c>
       <c r="J197" t="s" s="2">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="K197" t="s" s="2">
-        <v>144</v>
+        <v>111</v>
       </c>
       <c r="L197" t="s" s="2">
-        <v>257</v>
+        <v>112</v>
       </c>
       <c r="M197" t="s" s="2">
-        <v>258</v>
+        <v>113</v>
       </c>
       <c r="N197" t="s" s="2">
-        <v>259</v>
-      </c>
-      <c r="O197" t="s" s="2">
-        <v>260</v>
-      </c>
+        <v>114</v>
+      </c>
+      <c r="O197" s="2"/>
       <c r="P197" t="s" s="2">
         <v>80</v>
       </c>
@@ -26690,31 +26704,31 @@
         <v>80</v>
       </c>
       <c r="X197" t="s" s="2">
-        <v>245</v>
+        <v>80</v>
       </c>
       <c r="Y197" t="s" s="2">
-        <v>641</v>
+        <v>80</v>
       </c>
       <c r="Z197" t="s" s="2">
-        <v>642</v>
+        <v>80</v>
       </c>
       <c r="AA197" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AB197" t="s" s="2">
-        <v>80</v>
+        <v>115</v>
       </c>
       <c r="AC197" t="s" s="2">
-        <v>80</v>
+        <v>116</v>
       </c>
       <c r="AD197" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE197" t="s" s="2">
-        <v>80</v>
+        <v>117</v>
       </c>
       <c r="AF197" t="s" s="2">
-        <v>261</v>
+        <v>118</v>
       </c>
       <c r="AG197" t="s" s="2">
         <v>81</v>
@@ -26726,7 +26740,7 @@
         <v>198</v>
       </c>
       <c r="AJ197" t="s" s="2">
-        <v>103</v>
+        <v>119</v>
       </c>
       <c r="AK197" t="s" s="2">
         <v>80</v>
@@ -26738,7 +26752,7 @@
         <v>80</v>
       </c>
       <c r="AN197" t="s" s="2">
-        <v>262</v>
+        <v>80</v>
       </c>
       <c r="AO197" t="s" s="2">
         <v>80</v>
@@ -26747,12 +26761,12 @@
         <v>80</v>
       </c>
     </row>
-    <row r="198" hidden="true">
+    <row r="198">
       <c r="A198" t="s" s="2">
-        <v>694</v>
+        <v>697</v>
       </c>
       <c r="B198" t="s" s="2">
-        <v>695</v>
+        <v>698</v>
       </c>
       <c r="C198" s="2"/>
       <c r="D198" t="s" s="2">
@@ -26760,31 +26774,35 @@
       </c>
       <c r="E198" s="2"/>
       <c r="F198" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="G198" t="s" s="2">
         <v>91</v>
       </c>
       <c r="H198" t="s" s="2">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="I198" t="s" s="2">
         <v>80</v>
       </c>
       <c r="J198" t="s" s="2">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="K198" t="s" s="2">
-        <v>105</v>
+        <v>144</v>
       </c>
       <c r="L198" t="s" s="2">
-        <v>106</v>
+        <v>257</v>
       </c>
       <c r="M198" t="s" s="2">
-        <v>107</v>
-      </c>
-      <c r="N198" s="2"/>
-      <c r="O198" s="2"/>
+        <v>258</v>
+      </c>
+      <c r="N198" t="s" s="2">
+        <v>259</v>
+      </c>
+      <c r="O198" t="s" s="2">
+        <v>260</v>
+      </c>
       <c r="P198" t="s" s="2">
         <v>80</v>
       </c>
@@ -26808,13 +26826,13 @@
         <v>80</v>
       </c>
       <c r="X198" t="s" s="2">
-        <v>80</v>
+        <v>245</v>
       </c>
       <c r="Y198" t="s" s="2">
-        <v>80</v>
+        <v>646</v>
       </c>
       <c r="Z198" t="s" s="2">
-        <v>80</v>
+        <v>647</v>
       </c>
       <c r="AA198" t="s" s="2">
         <v>80</v>
@@ -26832,19 +26850,19 @@
         <v>80</v>
       </c>
       <c r="AF198" t="s" s="2">
-        <v>108</v>
+        <v>261</v>
       </c>
       <c r="AG198" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH198" t="s" s="2">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="AI198" t="s" s="2">
-        <v>80</v>
+        <v>198</v>
       </c>
       <c r="AJ198" t="s" s="2">
-        <v>80</v>
+        <v>103</v>
       </c>
       <c r="AK198" t="s" s="2">
         <v>80</v>
@@ -26856,7 +26874,7 @@
         <v>80</v>
       </c>
       <c r="AN198" t="s" s="2">
-        <v>80</v>
+        <v>262</v>
       </c>
       <c r="AO198" t="s" s="2">
         <v>80</v>
@@ -26867,21 +26885,21 @@
     </row>
     <row r="199" hidden="true">
       <c r="A199" t="s" s="2">
-        <v>696</v>
+        <v>699</v>
       </c>
       <c r="B199" t="s" s="2">
-        <v>697</v>
+        <v>700</v>
       </c>
       <c r="C199" s="2"/>
       <c r="D199" t="s" s="2">
-        <v>110</v>
+        <v>80</v>
       </c>
       <c r="E199" s="2"/>
       <c r="F199" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G199" t="s" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="H199" t="s" s="2">
         <v>80</v>
@@ -26893,17 +26911,15 @@
         <v>80</v>
       </c>
       <c r="K199" t="s" s="2">
-        <v>111</v>
+        <v>105</v>
       </c>
       <c r="L199" t="s" s="2">
-        <v>112</v>
+        <v>106</v>
       </c>
       <c r="M199" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="N199" t="s" s="2">
-        <v>114</v>
-      </c>
+        <v>107</v>
+      </c>
+      <c r="N199" s="2"/>
       <c r="O199" s="2"/>
       <c r="P199" t="s" s="2">
         <v>80</v>
@@ -26940,31 +26956,31 @@
         <v>80</v>
       </c>
       <c r="AB199" t="s" s="2">
-        <v>115</v>
+        <v>80</v>
       </c>
       <c r="AC199" t="s" s="2">
-        <v>116</v>
+        <v>80</v>
       </c>
       <c r="AD199" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE199" t="s" s="2">
-        <v>117</v>
+        <v>80</v>
       </c>
       <c r="AF199" t="s" s="2">
-        <v>118</v>
+        <v>108</v>
       </c>
       <c r="AG199" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH199" t="s" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="AI199" t="s" s="2">
-        <v>198</v>
+        <v>80</v>
       </c>
       <c r="AJ199" t="s" s="2">
-        <v>119</v>
+        <v>80</v>
       </c>
       <c r="AK199" t="s" s="2">
         <v>80</v>
@@ -26985,48 +27001,46 @@
         <v>80</v>
       </c>
     </row>
-    <row r="200">
+    <row r="200" hidden="true">
       <c r="A200" t="s" s="2">
-        <v>698</v>
+        <v>701</v>
       </c>
       <c r="B200" t="s" s="2">
-        <v>699</v>
+        <v>702</v>
       </c>
       <c r="C200" s="2"/>
       <c r="D200" t="s" s="2">
-        <v>80</v>
+        <v>110</v>
       </c>
       <c r="E200" s="2"/>
       <c r="F200" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="G200" t="s" s="2">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="H200" t="s" s="2">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="I200" t="s" s="2">
         <v>80</v>
       </c>
       <c r="J200" t="s" s="2">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="K200" t="s" s="2">
-        <v>132</v>
+        <v>111</v>
       </c>
       <c r="L200" t="s" s="2">
-        <v>266</v>
+        <v>112</v>
       </c>
       <c r="M200" t="s" s="2">
-        <v>267</v>
+        <v>113</v>
       </c>
       <c r="N200" t="s" s="2">
-        <v>268</v>
-      </c>
-      <c r="O200" t="s" s="2">
-        <v>269</v>
-      </c>
+        <v>114</v>
+      </c>
+      <c r="O200" s="2"/>
       <c r="P200" t="s" s="2">
         <v>80</v>
       </c>
@@ -27062,31 +27076,31 @@
         <v>80</v>
       </c>
       <c r="AB200" t="s" s="2">
-        <v>80</v>
+        <v>115</v>
       </c>
       <c r="AC200" t="s" s="2">
-        <v>80</v>
+        <v>116</v>
       </c>
       <c r="AD200" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE200" t="s" s="2">
-        <v>80</v>
+        <v>117</v>
       </c>
       <c r="AF200" t="s" s="2">
-        <v>270</v>
+        <v>118</v>
       </c>
       <c r="AG200" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH200" t="s" s="2">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="AI200" t="s" s="2">
         <v>198</v>
       </c>
       <c r="AJ200" t="s" s="2">
-        <v>103</v>
+        <v>119</v>
       </c>
       <c r="AK200" t="s" s="2">
         <v>80</v>
@@ -27098,7 +27112,7 @@
         <v>80</v>
       </c>
       <c r="AN200" t="s" s="2">
-        <v>271</v>
+        <v>80</v>
       </c>
       <c r="AO200" t="s" s="2">
         <v>80</v>
@@ -27107,12 +27121,12 @@
         <v>80</v>
       </c>
     </row>
-    <row r="201" hidden="true">
+    <row r="201">
       <c r="A201" t="s" s="2">
-        <v>700</v>
+        <v>703</v>
       </c>
       <c r="B201" t="s" s="2">
-        <v>701</v>
+        <v>704</v>
       </c>
       <c r="C201" s="2"/>
       <c r="D201" t="s" s="2">
@@ -27120,13 +27134,13 @@
       </c>
       <c r="E201" s="2"/>
       <c r="F201" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="G201" t="s" s="2">
         <v>91</v>
       </c>
       <c r="H201" t="s" s="2">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="I201" t="s" s="2">
         <v>80</v>
@@ -27135,18 +27149,20 @@
         <v>92</v>
       </c>
       <c r="K201" t="s" s="2">
-        <v>105</v>
+        <v>132</v>
       </c>
       <c r="L201" t="s" s="2">
-        <v>273</v>
+        <v>266</v>
       </c>
       <c r="M201" t="s" s="2">
-        <v>274</v>
+        <v>267</v>
       </c>
       <c r="N201" t="s" s="2">
-        <v>275</v>
-      </c>
-      <c r="O201" s="2"/>
+        <v>268</v>
+      </c>
+      <c r="O201" t="s" s="2">
+        <v>269</v>
+      </c>
       <c r="P201" t="s" s="2">
         <v>80</v>
       </c>
@@ -27194,7 +27210,7 @@
         <v>80</v>
       </c>
       <c r="AF201" t="s" s="2">
-        <v>276</v>
+        <v>270</v>
       </c>
       <c r="AG201" t="s" s="2">
         <v>81</v>
@@ -27218,7 +27234,7 @@
         <v>80</v>
       </c>
       <c r="AN201" t="s" s="2">
-        <v>277</v>
+        <v>271</v>
       </c>
       <c r="AO201" t="s" s="2">
         <v>80</v>
@@ -27227,12 +27243,12 @@
         <v>80</v>
       </c>
     </row>
-    <row r="202">
+    <row r="202" hidden="true">
       <c r="A202" t="s" s="2">
-        <v>702</v>
+        <v>705</v>
       </c>
       <c r="B202" t="s" s="2">
-        <v>703</v>
+        <v>706</v>
       </c>
       <c r="C202" s="2"/>
       <c r="D202" t="s" s="2">
@@ -27240,13 +27256,13 @@
       </c>
       <c r="E202" s="2"/>
       <c r="F202" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="G202" t="s" s="2">
         <v>91</v>
       </c>
       <c r="H202" t="s" s="2">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="I202" t="s" s="2">
         <v>80</v>
@@ -27255,20 +27271,18 @@
         <v>92</v>
       </c>
       <c r="K202" t="s" s="2">
-        <v>166</v>
+        <v>105</v>
       </c>
       <c r="L202" t="s" s="2">
-        <v>279</v>
+        <v>273</v>
       </c>
       <c r="M202" t="s" s="2">
-        <v>280</v>
+        <v>274</v>
       </c>
       <c r="N202" t="s" s="2">
-        <v>402</v>
-      </c>
-      <c r="O202" t="s" s="2">
-        <v>281</v>
-      </c>
+        <v>275</v>
+      </c>
+      <c r="O202" s="2"/>
       <c r="P202" t="s" s="2">
         <v>80</v>
       </c>
@@ -27316,7 +27330,7 @@
         <v>80</v>
       </c>
       <c r="AF202" t="s" s="2">
-        <v>282</v>
+        <v>276</v>
       </c>
       <c r="AG202" t="s" s="2">
         <v>81</v>
@@ -27340,7 +27354,7 @@
         <v>80</v>
       </c>
       <c r="AN202" t="s" s="2">
-        <v>283</v>
+        <v>277</v>
       </c>
       <c r="AO202" t="s" s="2">
         <v>80</v>
@@ -27349,12 +27363,12 @@
         <v>80</v>
       </c>
     </row>
-    <row r="203" hidden="true">
+    <row r="203">
       <c r="A203" t="s" s="2">
-        <v>704</v>
+        <v>707</v>
       </c>
       <c r="B203" t="s" s="2">
-        <v>705</v>
+        <v>708</v>
       </c>
       <c r="C203" s="2"/>
       <c r="D203" t="s" s="2">
@@ -27362,13 +27376,13 @@
       </c>
       <c r="E203" s="2"/>
       <c r="F203" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="G203" t="s" s="2">
         <v>91</v>
       </c>
       <c r="H203" t="s" s="2">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="I203" t="s" s="2">
         <v>80</v>
@@ -27377,19 +27391,19 @@
         <v>92</v>
       </c>
       <c r="K203" t="s" s="2">
-        <v>105</v>
+        <v>166</v>
       </c>
       <c r="L203" t="s" s="2">
-        <v>285</v>
+        <v>279</v>
       </c>
       <c r="M203" t="s" s="2">
-        <v>286</v>
+        <v>280</v>
       </c>
       <c r="N203" t="s" s="2">
         <v>402</v>
       </c>
       <c r="O203" t="s" s="2">
-        <v>287</v>
+        <v>281</v>
       </c>
       <c r="P203" t="s" s="2">
         <v>80</v>
@@ -27438,7 +27452,7 @@
         <v>80</v>
       </c>
       <c r="AF203" t="s" s="2">
-        <v>288</v>
+        <v>282</v>
       </c>
       <c r="AG203" t="s" s="2">
         <v>81</v>
@@ -27462,7 +27476,7 @@
         <v>80</v>
       </c>
       <c r="AN203" t="s" s="2">
-        <v>289</v>
+        <v>283</v>
       </c>
       <c r="AO203" t="s" s="2">
         <v>80</v>
@@ -27473,10 +27487,10 @@
     </row>
     <row r="204" hidden="true">
       <c r="A204" t="s" s="2">
-        <v>706</v>
+        <v>709</v>
       </c>
       <c r="B204" t="s" s="2">
-        <v>707</v>
+        <v>710</v>
       </c>
       <c r="C204" s="2"/>
       <c r="D204" t="s" s="2">
@@ -27499,19 +27513,19 @@
         <v>92</v>
       </c>
       <c r="K204" t="s" s="2">
-        <v>291</v>
+        <v>105</v>
       </c>
       <c r="L204" t="s" s="2">
-        <v>292</v>
+        <v>285</v>
       </c>
       <c r="M204" t="s" s="2">
-        <v>293</v>
+        <v>286</v>
       </c>
       <c r="N204" t="s" s="2">
-        <v>294</v>
+        <v>402</v>
       </c>
       <c r="O204" t="s" s="2">
-        <v>295</v>
+        <v>287</v>
       </c>
       <c r="P204" t="s" s="2">
         <v>80</v>
@@ -27560,7 +27574,7 @@
         <v>80</v>
       </c>
       <c r="AF204" t="s" s="2">
-        <v>296</v>
+        <v>288</v>
       </c>
       <c r="AG204" t="s" s="2">
         <v>81</v>
@@ -27584,7 +27598,7 @@
         <v>80</v>
       </c>
       <c r="AN204" t="s" s="2">
-        <v>297</v>
+        <v>289</v>
       </c>
       <c r="AO204" t="s" s="2">
         <v>80</v>
@@ -27595,10 +27609,10 @@
     </row>
     <row r="205" hidden="true">
       <c r="A205" t="s" s="2">
-        <v>708</v>
+        <v>711</v>
       </c>
       <c r="B205" t="s" s="2">
-        <v>709</v>
+        <v>712</v>
       </c>
       <c r="C205" s="2"/>
       <c r="D205" t="s" s="2">
@@ -27621,19 +27635,19 @@
         <v>92</v>
       </c>
       <c r="K205" t="s" s="2">
-        <v>105</v>
+        <v>291</v>
       </c>
       <c r="L205" t="s" s="2">
-        <v>299</v>
+        <v>292</v>
       </c>
       <c r="M205" t="s" s="2">
-        <v>300</v>
+        <v>293</v>
       </c>
       <c r="N205" t="s" s="2">
-        <v>301</v>
+        <v>294</v>
       </c>
       <c r="O205" t="s" s="2">
-        <v>302</v>
+        <v>295</v>
       </c>
       <c r="P205" t="s" s="2">
         <v>80</v>
@@ -27682,7 +27696,7 @@
         <v>80</v>
       </c>
       <c r="AF205" t="s" s="2">
-        <v>303</v>
+        <v>296</v>
       </c>
       <c r="AG205" t="s" s="2">
         <v>81</v>
@@ -27706,7 +27720,7 @@
         <v>80</v>
       </c>
       <c r="AN205" t="s" s="2">
-        <v>304</v>
+        <v>297</v>
       </c>
       <c r="AO205" t="s" s="2">
         <v>80</v>
@@ -27717,10 +27731,10 @@
     </row>
     <row r="206" hidden="true">
       <c r="A206" t="s" s="2">
-        <v>710</v>
+        <v>713</v>
       </c>
       <c r="B206" t="s" s="2">
-        <v>711</v>
+        <v>714</v>
       </c>
       <c r="C206" s="2"/>
       <c r="D206" t="s" s="2">
@@ -27740,19 +27754,23 @@
         <v>80</v>
       </c>
       <c r="J206" t="s" s="2">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="K206" t="s" s="2">
-        <v>226</v>
+        <v>105</v>
       </c>
       <c r="L206" t="s" s="2">
-        <v>661</v>
+        <v>299</v>
       </c>
       <c r="M206" t="s" s="2">
-        <v>662</v>
-      </c>
-      <c r="N206" s="2"/>
-      <c r="O206" s="2"/>
+        <v>300</v>
+      </c>
+      <c r="N206" t="s" s="2">
+        <v>301</v>
+      </c>
+      <c r="O206" t="s" s="2">
+        <v>302</v>
+      </c>
       <c r="P206" t="s" s="2">
         <v>80</v>
       </c>
@@ -27800,7 +27818,7 @@
         <v>80</v>
       </c>
       <c r="AF206" t="s" s="2">
-        <v>663</v>
+        <v>303</v>
       </c>
       <c r="AG206" t="s" s="2">
         <v>81</v>
@@ -27809,10 +27827,10 @@
         <v>91</v>
       </c>
       <c r="AI206" t="s" s="2">
-        <v>80</v>
+        <v>198</v>
       </c>
       <c r="AJ206" t="s" s="2">
-        <v>80</v>
+        <v>103</v>
       </c>
       <c r="AK206" t="s" s="2">
         <v>80</v>
@@ -27824,7 +27842,7 @@
         <v>80</v>
       </c>
       <c r="AN206" t="s" s="2">
-        <v>80</v>
+        <v>304</v>
       </c>
       <c r="AO206" t="s" s="2">
         <v>80</v>
@@ -27833,16 +27851,14 @@
         <v>80</v>
       </c>
     </row>
-    <row r="207">
+    <row r="207" hidden="true">
       <c r="A207" t="s" s="2">
-        <v>712</v>
+        <v>715</v>
       </c>
       <c r="B207" t="s" s="2">
-        <v>586</v>
-      </c>
-      <c r="C207" t="s" s="2">
-        <v>713</v>
-      </c>
+        <v>716</v>
+      </c>
+      <c r="C207" s="2"/>
       <c r="D207" t="s" s="2">
         <v>80</v>
       </c>
@@ -27854,26 +27870,24 @@
         <v>91</v>
       </c>
       <c r="H207" t="s" s="2">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="I207" t="s" s="2">
         <v>80</v>
       </c>
       <c r="J207" t="s" s="2">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="K207" t="s" s="2">
         <v>226</v>
       </c>
       <c r="L207" t="s" s="2">
-        <v>714</v>
+        <v>666</v>
       </c>
       <c r="M207" t="s" s="2">
-        <v>715</v>
-      </c>
-      <c r="N207" t="s" s="2">
-        <v>590</v>
-      </c>
+        <v>667</v>
+      </c>
+      <c r="N207" s="2"/>
       <c r="O207" s="2"/>
       <c r="P207" t="s" s="2">
         <v>80</v>
@@ -27922,7 +27936,7 @@
         <v>80</v>
       </c>
       <c r="AF207" t="s" s="2">
-        <v>586</v>
+        <v>668</v>
       </c>
       <c r="AG207" t="s" s="2">
         <v>81</v>
@@ -27934,22 +27948,22 @@
         <v>80</v>
       </c>
       <c r="AJ207" t="s" s="2">
-        <v>103</v>
+        <v>80</v>
       </c>
       <c r="AK207" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL207" t="s" s="2">
-        <v>594</v>
+        <v>80</v>
       </c>
       <c r="AM207" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN207" t="s" s="2">
-        <v>595</v>
+        <v>80</v>
       </c>
       <c r="AO207" t="s" s="2">
-        <v>596</v>
+        <v>80</v>
       </c>
       <c r="AP207" t="s" s="2">
         <v>80</v>
@@ -27957,13 +27971,13 @@
     </row>
     <row r="208">
       <c r="A208" t="s" s="2">
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="B208" t="s" s="2">
-        <v>586</v>
+        <v>591</v>
       </c>
       <c r="C208" t="s" s="2">
-        <v>717</v>
+        <v>718</v>
       </c>
       <c r="D208" t="s" s="2">
         <v>80</v>
@@ -27985,7 +27999,7 @@
         <v>92</v>
       </c>
       <c r="K208" t="s" s="2">
-        <v>718</v>
+        <v>226</v>
       </c>
       <c r="L208" t="s" s="2">
         <v>719</v>
@@ -27994,7 +28008,7 @@
         <v>720</v>
       </c>
       <c r="N208" t="s" s="2">
-        <v>590</v>
+        <v>595</v>
       </c>
       <c r="O208" s="2"/>
       <c r="P208" t="s" s="2">
@@ -28044,7 +28058,7 @@
         <v>80</v>
       </c>
       <c r="AF208" t="s" s="2">
-        <v>586</v>
+        <v>591</v>
       </c>
       <c r="AG208" t="s" s="2">
         <v>81</v>
@@ -28062,29 +28076,31 @@
         <v>80</v>
       </c>
       <c r="AL208" t="s" s="2">
-        <v>594</v>
+        <v>599</v>
       </c>
       <c r="AM208" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN208" t="s" s="2">
-        <v>595</v>
+        <v>600</v>
       </c>
       <c r="AO208" t="s" s="2">
-        <v>596</v>
+        <v>601</v>
       </c>
       <c r="AP208" t="s" s="2">
         <v>80</v>
       </c>
     </row>
-    <row r="209" hidden="true">
+    <row r="209">
       <c r="A209" t="s" s="2">
         <v>721</v>
       </c>
       <c r="B209" t="s" s="2">
-        <v>604</v>
-      </c>
-      <c r="C209" s="2"/>
+        <v>591</v>
+      </c>
+      <c r="C209" t="s" s="2">
+        <v>722</v>
+      </c>
       <c r="D209" t="s" s="2">
         <v>80</v>
       </c>
@@ -28096,24 +28112,26 @@
         <v>91</v>
       </c>
       <c r="H209" t="s" s="2">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="I209" t="s" s="2">
         <v>80</v>
       </c>
       <c r="J209" t="s" s="2">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="K209" t="s" s="2">
-        <v>105</v>
+        <v>723</v>
       </c>
       <c r="L209" t="s" s="2">
-        <v>106</v>
+        <v>724</v>
       </c>
       <c r="M209" t="s" s="2">
-        <v>107</v>
-      </c>
-      <c r="N209" s="2"/>
+        <v>725</v>
+      </c>
+      <c r="N209" t="s" s="2">
+        <v>595</v>
+      </c>
       <c r="O209" s="2"/>
       <c r="P209" t="s" s="2">
         <v>80</v>
@@ -28162,7 +28180,7 @@
         <v>80</v>
       </c>
       <c r="AF209" t="s" s="2">
-        <v>108</v>
+        <v>591</v>
       </c>
       <c r="AG209" t="s" s="2">
         <v>81</v>
@@ -28174,22 +28192,22 @@
         <v>80</v>
       </c>
       <c r="AJ209" t="s" s="2">
-        <v>80</v>
+        <v>103</v>
       </c>
       <c r="AK209" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL209" t="s" s="2">
-        <v>80</v>
+        <v>599</v>
       </c>
       <c r="AM209" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN209" t="s" s="2">
-        <v>80</v>
+        <v>600</v>
       </c>
       <c r="AO209" t="s" s="2">
-        <v>80</v>
+        <v>601</v>
       </c>
       <c r="AP209" t="s" s="2">
         <v>80</v>
@@ -28197,21 +28215,21 @@
     </row>
     <row r="210" hidden="true">
       <c r="A210" t="s" s="2">
-        <v>722</v>
+        <v>726</v>
       </c>
       <c r="B210" t="s" s="2">
-        <v>606</v>
+        <v>609</v>
       </c>
       <c r="C210" s="2"/>
       <c r="D210" t="s" s="2">
-        <v>110</v>
+        <v>80</v>
       </c>
       <c r="E210" s="2"/>
       <c r="F210" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G210" t="s" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="H210" t="s" s="2">
         <v>80</v>
@@ -28223,17 +28241,15 @@
         <v>80</v>
       </c>
       <c r="K210" t="s" s="2">
-        <v>111</v>
+        <v>105</v>
       </c>
       <c r="L210" t="s" s="2">
-        <v>112</v>
+        <v>106</v>
       </c>
       <c r="M210" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="N210" t="s" s="2">
-        <v>114</v>
-      </c>
+        <v>107</v>
+      </c>
+      <c r="N210" s="2"/>
       <c r="O210" s="2"/>
       <c r="P210" t="s" s="2">
         <v>80</v>
@@ -28270,31 +28286,31 @@
         <v>80</v>
       </c>
       <c r="AB210" t="s" s="2">
-        <v>115</v>
+        <v>80</v>
       </c>
       <c r="AC210" t="s" s="2">
-        <v>116</v>
+        <v>80</v>
       </c>
       <c r="AD210" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE210" t="s" s="2">
-        <v>117</v>
+        <v>80</v>
       </c>
       <c r="AF210" t="s" s="2">
-        <v>118</v>
+        <v>108</v>
       </c>
       <c r="AG210" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH210" t="s" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="AI210" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ210" t="s" s="2">
-        <v>119</v>
+        <v>80</v>
       </c>
       <c r="AK210" t="s" s="2">
         <v>80</v>
@@ -28317,23 +28333,21 @@
     </row>
     <row r="211" hidden="true">
       <c r="A211" t="s" s="2">
-        <v>723</v>
+        <v>727</v>
       </c>
       <c r="B211" t="s" s="2">
-        <v>606</v>
-      </c>
-      <c r="C211" t="s" s="2">
-        <v>724</v>
-      </c>
+        <v>611</v>
+      </c>
+      <c r="C211" s="2"/>
       <c r="D211" t="s" s="2">
-        <v>80</v>
+        <v>110</v>
       </c>
       <c r="E211" s="2"/>
       <c r="F211" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G211" t="s" s="2">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="H211" t="s" s="2">
         <v>80</v>
@@ -28345,16 +28359,16 @@
         <v>80</v>
       </c>
       <c r="K211" t="s" s="2">
-        <v>624</v>
+        <v>111</v>
       </c>
       <c r="L211" t="s" s="2">
-        <v>725</v>
+        <v>112</v>
       </c>
       <c r="M211" t="s" s="2">
-        <v>381</v>
+        <v>113</v>
       </c>
       <c r="N211" t="s" s="2">
-        <v>726</v>
+        <v>114</v>
       </c>
       <c r="O211" s="2"/>
       <c r="P211" t="s" s="2">
@@ -28392,16 +28406,16 @@
         <v>80</v>
       </c>
       <c r="AB211" t="s" s="2">
-        <v>80</v>
+        <v>115</v>
       </c>
       <c r="AC211" t="s" s="2">
-        <v>80</v>
+        <v>116</v>
       </c>
       <c r="AD211" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE211" t="s" s="2">
-        <v>80</v>
+        <v>117</v>
       </c>
       <c r="AF211" t="s" s="2">
         <v>118</v>
@@ -28439,12 +28453,14 @@
     </row>
     <row r="212" hidden="true">
       <c r="A212" t="s" s="2">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="B212" t="s" s="2">
-        <v>728</v>
-      </c>
-      <c r="C212" s="2"/>
+        <v>611</v>
+      </c>
+      <c r="C212" t="s" s="2">
+        <v>729</v>
+      </c>
       <c r="D212" t="s" s="2">
         <v>80</v>
       </c>
@@ -28465,15 +28481,17 @@
         <v>80</v>
       </c>
       <c r="K212" t="s" s="2">
-        <v>105</v>
+        <v>629</v>
       </c>
       <c r="L212" t="s" s="2">
-        <v>106</v>
+        <v>730</v>
       </c>
       <c r="M212" t="s" s="2">
-        <v>107</v>
-      </c>
-      <c r="N212" s="2"/>
+        <v>381</v>
+      </c>
+      <c r="N212" t="s" s="2">
+        <v>731</v>
+      </c>
       <c r="O212" s="2"/>
       <c r="P212" t="s" s="2">
         <v>80</v>
@@ -28522,19 +28540,19 @@
         <v>80</v>
       </c>
       <c r="AF212" t="s" s="2">
-        <v>108</v>
+        <v>118</v>
       </c>
       <c r="AG212" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH212" t="s" s="2">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="AI212" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ212" t="s" s="2">
-        <v>80</v>
+        <v>119</v>
       </c>
       <c r="AK212" t="s" s="2">
         <v>80</v>
@@ -28557,21 +28575,21 @@
     </row>
     <row r="213" hidden="true">
       <c r="A213" t="s" s="2">
-        <v>729</v>
+        <v>732</v>
       </c>
       <c r="B213" t="s" s="2">
-        <v>730</v>
+        <v>733</v>
       </c>
       <c r="C213" s="2"/>
       <c r="D213" t="s" s="2">
-        <v>110</v>
+        <v>80</v>
       </c>
       <c r="E213" s="2"/>
       <c r="F213" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G213" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H213" t="s" s="2">
         <v>80</v>
@@ -28583,17 +28601,15 @@
         <v>80</v>
       </c>
       <c r="K213" t="s" s="2">
-        <v>111</v>
+        <v>105</v>
       </c>
       <c r="L213" t="s" s="2">
-        <v>112</v>
+        <v>106</v>
       </c>
       <c r="M213" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="N213" t="s" s="2">
-        <v>114</v>
-      </c>
+        <v>107</v>
+      </c>
+      <c r="N213" s="2"/>
       <c r="O213" s="2"/>
       <c r="P213" t="s" s="2">
         <v>80</v>
@@ -28630,31 +28646,31 @@
         <v>80</v>
       </c>
       <c r="AB213" t="s" s="2">
-        <v>115</v>
+        <v>80</v>
       </c>
       <c r="AC213" t="s" s="2">
-        <v>116</v>
+        <v>80</v>
       </c>
       <c r="AD213" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE213" t="s" s="2">
-        <v>117</v>
+        <v>80</v>
       </c>
       <c r="AF213" t="s" s="2">
-        <v>118</v>
+        <v>108</v>
       </c>
       <c r="AG213" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH213" t="s" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="AI213" t="s" s="2">
-        <v>198</v>
+        <v>80</v>
       </c>
       <c r="AJ213" t="s" s="2">
-        <v>119</v>
+        <v>80</v>
       </c>
       <c r="AK213" t="s" s="2">
         <v>80</v>
@@ -28675,26 +28691,26 @@
         <v>80</v>
       </c>
     </row>
-    <row r="214">
+    <row r="214" hidden="true">
       <c r="A214" t="s" s="2">
-        <v>731</v>
+        <v>734</v>
       </c>
       <c r="B214" t="s" s="2">
-        <v>732</v>
+        <v>735</v>
       </c>
       <c r="C214" s="2"/>
       <c r="D214" t="s" s="2">
-        <v>80</v>
+        <v>110</v>
       </c>
       <c r="E214" s="2"/>
       <c r="F214" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="G214" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H214" t="s" s="2">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="I214" t="s" s="2">
         <v>80</v>
@@ -28703,16 +28719,16 @@
         <v>80</v>
       </c>
       <c r="K214" t="s" s="2">
-        <v>132</v>
+        <v>111</v>
       </c>
       <c r="L214" t="s" s="2">
-        <v>205</v>
+        <v>112</v>
       </c>
       <c r="M214" t="s" s="2">
-        <v>206</v>
+        <v>113</v>
       </c>
       <c r="N214" t="s" s="2">
-        <v>207</v>
+        <v>114</v>
       </c>
       <c r="O214" s="2"/>
       <c r="P214" t="s" s="2">
@@ -28720,7 +28736,7 @@
       </c>
       <c r="Q214" s="2"/>
       <c r="R214" t="s" s="2">
-        <v>631</v>
+        <v>80</v>
       </c>
       <c r="S214" t="s" s="2">
         <v>80</v>
@@ -28750,31 +28766,31 @@
         <v>80</v>
       </c>
       <c r="AB214" t="s" s="2">
-        <v>80</v>
+        <v>115</v>
       </c>
       <c r="AC214" t="s" s="2">
-        <v>80</v>
+        <v>116</v>
       </c>
       <c r="AD214" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE214" t="s" s="2">
-        <v>80</v>
+        <v>117</v>
       </c>
       <c r="AF214" t="s" s="2">
-        <v>209</v>
+        <v>118</v>
       </c>
       <c r="AG214" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AH214" t="s" s="2">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="AI214" t="s" s="2">
-        <v>80</v>
+        <v>198</v>
       </c>
       <c r="AJ214" t="s" s="2">
-        <v>80</v>
+        <v>119</v>
       </c>
       <c r="AK214" t="s" s="2">
         <v>80</v>
@@ -28797,10 +28813,10 @@
     </row>
     <row r="215">
       <c r="A215" t="s" s="2">
-        <v>733</v>
+        <v>736</v>
       </c>
       <c r="B215" t="s" s="2">
-        <v>734</v>
+        <v>737</v>
       </c>
       <c r="C215" s="2"/>
       <c r="D215" t="s" s="2">
@@ -28823,22 +28839,24 @@
         <v>80</v>
       </c>
       <c r="K215" t="s" s="2">
-        <v>241</v>
+        <v>132</v>
       </c>
       <c r="L215" t="s" s="2">
-        <v>213</v>
+        <v>205</v>
       </c>
       <c r="M215" t="s" s="2">
-        <v>214</v>
-      </c>
-      <c r="N215" s="2"/>
+        <v>206</v>
+      </c>
+      <c r="N215" t="s" s="2">
+        <v>207</v>
+      </c>
       <c r="O215" s="2"/>
       <c r="P215" t="s" s="2">
         <v>80</v>
       </c>
       <c r="Q215" s="2"/>
       <c r="R215" t="s" s="2">
-        <v>80</v>
+        <v>636</v>
       </c>
       <c r="S215" t="s" s="2">
         <v>80</v>
@@ -28880,19 +28898,19 @@
         <v>80</v>
       </c>
       <c r="AF215" t="s" s="2">
-        <v>215</v>
+        <v>209</v>
       </c>
       <c r="AG215" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AH215" t="s" s="2">
         <v>91</v>
       </c>
       <c r="AI215" t="s" s="2">
-        <v>198</v>
+        <v>80</v>
       </c>
       <c r="AJ215" t="s" s="2">
-        <v>103</v>
+        <v>80</v>
       </c>
       <c r="AK215" t="s" s="2">
         <v>80</v>
@@ -28913,12 +28931,12 @@
         <v>80</v>
       </c>
     </row>
-    <row r="216" hidden="true">
+    <row r="216">
       <c r="A216" t="s" s="2">
-        <v>735</v>
+        <v>738</v>
       </c>
       <c r="B216" t="s" s="2">
-        <v>736</v>
+        <v>739</v>
       </c>
       <c r="C216" s="2"/>
       <c r="D216" t="s" s="2">
@@ -28926,13 +28944,13 @@
       </c>
       <c r="E216" s="2"/>
       <c r="F216" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="G216" t="s" s="2">
         <v>91</v>
       </c>
       <c r="H216" t="s" s="2">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="I216" t="s" s="2">
         <v>80</v>
@@ -28941,13 +28959,13 @@
         <v>80</v>
       </c>
       <c r="K216" t="s" s="2">
-        <v>105</v>
+        <v>241</v>
       </c>
       <c r="L216" t="s" s="2">
-        <v>106</v>
+        <v>213</v>
       </c>
       <c r="M216" t="s" s="2">
-        <v>107</v>
+        <v>214</v>
       </c>
       <c r="N216" s="2"/>
       <c r="O216" s="2"/>
@@ -28998,7 +29016,7 @@
         <v>80</v>
       </c>
       <c r="AF216" t="s" s="2">
-        <v>108</v>
+        <v>215</v>
       </c>
       <c r="AG216" t="s" s="2">
         <v>81</v>
@@ -29007,10 +29025,10 @@
         <v>91</v>
       </c>
       <c r="AI216" t="s" s="2">
-        <v>80</v>
+        <v>198</v>
       </c>
       <c r="AJ216" t="s" s="2">
-        <v>80</v>
+        <v>103</v>
       </c>
       <c r="AK216" t="s" s="2">
         <v>80</v>
@@ -29033,21 +29051,21 @@
     </row>
     <row r="217" hidden="true">
       <c r="A217" t="s" s="2">
-        <v>737</v>
+        <v>740</v>
       </c>
       <c r="B217" t="s" s="2">
-        <v>738</v>
+        <v>741</v>
       </c>
       <c r="C217" s="2"/>
       <c r="D217" t="s" s="2">
-        <v>110</v>
+        <v>80</v>
       </c>
       <c r="E217" s="2"/>
       <c r="F217" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G217" t="s" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="H217" t="s" s="2">
         <v>80</v>
@@ -29059,17 +29077,15 @@
         <v>80</v>
       </c>
       <c r="K217" t="s" s="2">
-        <v>111</v>
+        <v>105</v>
       </c>
       <c r="L217" t="s" s="2">
-        <v>112</v>
+        <v>106</v>
       </c>
       <c r="M217" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="N217" t="s" s="2">
-        <v>114</v>
-      </c>
+        <v>107</v>
+      </c>
+      <c r="N217" s="2"/>
       <c r="O217" s="2"/>
       <c r="P217" t="s" s="2">
         <v>80</v>
@@ -29106,31 +29122,31 @@
         <v>80</v>
       </c>
       <c r="AB217" t="s" s="2">
-        <v>115</v>
+        <v>80</v>
       </c>
       <c r="AC217" t="s" s="2">
-        <v>116</v>
+        <v>80</v>
       </c>
       <c r="AD217" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE217" t="s" s="2">
-        <v>117</v>
+        <v>80</v>
       </c>
       <c r="AF217" t="s" s="2">
-        <v>118</v>
+        <v>108</v>
       </c>
       <c r="AG217" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH217" t="s" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="AI217" t="s" s="2">
-        <v>198</v>
+        <v>80</v>
       </c>
       <c r="AJ217" t="s" s="2">
-        <v>119</v>
+        <v>80</v>
       </c>
       <c r="AK217" t="s" s="2">
         <v>80</v>
@@ -29151,48 +29167,46 @@
         <v>80</v>
       </c>
     </row>
-    <row r="218">
+    <row r="218" hidden="true">
       <c r="A218" t="s" s="2">
-        <v>739</v>
+        <v>742</v>
       </c>
       <c r="B218" t="s" s="2">
-        <v>740</v>
+        <v>743</v>
       </c>
       <c r="C218" s="2"/>
       <c r="D218" t="s" s="2">
-        <v>80</v>
+        <v>110</v>
       </c>
       <c r="E218" s="2"/>
       <c r="F218" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="G218" t="s" s="2">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="H218" t="s" s="2">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="I218" t="s" s="2">
         <v>80</v>
       </c>
       <c r="J218" t="s" s="2">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="K218" t="s" s="2">
-        <v>144</v>
+        <v>111</v>
       </c>
       <c r="L218" t="s" s="2">
-        <v>257</v>
+        <v>112</v>
       </c>
       <c r="M218" t="s" s="2">
-        <v>258</v>
+        <v>113</v>
       </c>
       <c r="N218" t="s" s="2">
-        <v>259</v>
-      </c>
-      <c r="O218" t="s" s="2">
-        <v>260</v>
-      </c>
+        <v>114</v>
+      </c>
+      <c r="O218" s="2"/>
       <c r="P218" t="s" s="2">
         <v>80</v>
       </c>
@@ -29216,31 +29230,31 @@
         <v>80</v>
       </c>
       <c r="X218" t="s" s="2">
-        <v>245</v>
+        <v>80</v>
       </c>
       <c r="Y218" t="s" s="2">
-        <v>641</v>
+        <v>80</v>
       </c>
       <c r="Z218" t="s" s="2">
-        <v>642</v>
+        <v>80</v>
       </c>
       <c r="AA218" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AB218" t="s" s="2">
-        <v>80</v>
+        <v>115</v>
       </c>
       <c r="AC218" t="s" s="2">
-        <v>80</v>
+        <v>116</v>
       </c>
       <c r="AD218" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE218" t="s" s="2">
-        <v>80</v>
+        <v>117</v>
       </c>
       <c r="AF218" t="s" s="2">
-        <v>261</v>
+        <v>118</v>
       </c>
       <c r="AG218" t="s" s="2">
         <v>81</v>
@@ -29252,7 +29266,7 @@
         <v>198</v>
       </c>
       <c r="AJ218" t="s" s="2">
-        <v>103</v>
+        <v>119</v>
       </c>
       <c r="AK218" t="s" s="2">
         <v>80</v>
@@ -29264,7 +29278,7 @@
         <v>80</v>
       </c>
       <c r="AN218" t="s" s="2">
-        <v>262</v>
+        <v>80</v>
       </c>
       <c r="AO218" t="s" s="2">
         <v>80</v>
@@ -29273,12 +29287,12 @@
         <v>80</v>
       </c>
     </row>
-    <row r="219" hidden="true">
+    <row r="219">
       <c r="A219" t="s" s="2">
-        <v>741</v>
+        <v>744</v>
       </c>
       <c r="B219" t="s" s="2">
-        <v>742</v>
+        <v>745</v>
       </c>
       <c r="C219" s="2"/>
       <c r="D219" t="s" s="2">
@@ -29286,31 +29300,35 @@
       </c>
       <c r="E219" s="2"/>
       <c r="F219" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="G219" t="s" s="2">
         <v>91</v>
       </c>
       <c r="H219" t="s" s="2">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="I219" t="s" s="2">
         <v>80</v>
       </c>
       <c r="J219" t="s" s="2">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="K219" t="s" s="2">
-        <v>105</v>
+        <v>144</v>
       </c>
       <c r="L219" t="s" s="2">
-        <v>106</v>
+        <v>257</v>
       </c>
       <c r="M219" t="s" s="2">
-        <v>107</v>
-      </c>
-      <c r="N219" s="2"/>
-      <c r="O219" s="2"/>
+        <v>258</v>
+      </c>
+      <c r="N219" t="s" s="2">
+        <v>259</v>
+      </c>
+      <c r="O219" t="s" s="2">
+        <v>260</v>
+      </c>
       <c r="P219" t="s" s="2">
         <v>80</v>
       </c>
@@ -29334,13 +29352,13 @@
         <v>80</v>
       </c>
       <c r="X219" t="s" s="2">
-        <v>80</v>
+        <v>245</v>
       </c>
       <c r="Y219" t="s" s="2">
-        <v>80</v>
+        <v>646</v>
       </c>
       <c r="Z219" t="s" s="2">
-        <v>80</v>
+        <v>647</v>
       </c>
       <c r="AA219" t="s" s="2">
         <v>80</v>
@@ -29358,19 +29376,19 @@
         <v>80</v>
       </c>
       <c r="AF219" t="s" s="2">
-        <v>108</v>
+        <v>261</v>
       </c>
       <c r="AG219" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH219" t="s" s="2">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="AI219" t="s" s="2">
-        <v>80</v>
+        <v>198</v>
       </c>
       <c r="AJ219" t="s" s="2">
-        <v>80</v>
+        <v>103</v>
       </c>
       <c r="AK219" t="s" s="2">
         <v>80</v>
@@ -29382,7 +29400,7 @@
         <v>80</v>
       </c>
       <c r="AN219" t="s" s="2">
-        <v>80</v>
+        <v>262</v>
       </c>
       <c r="AO219" t="s" s="2">
         <v>80</v>
@@ -29393,21 +29411,21 @@
     </row>
     <row r="220" hidden="true">
       <c r="A220" t="s" s="2">
-        <v>743</v>
+        <v>746</v>
       </c>
       <c r="B220" t="s" s="2">
-        <v>744</v>
+        <v>747</v>
       </c>
       <c r="C220" s="2"/>
       <c r="D220" t="s" s="2">
-        <v>110</v>
+        <v>80</v>
       </c>
       <c r="E220" s="2"/>
       <c r="F220" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G220" t="s" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="H220" t="s" s="2">
         <v>80</v>
@@ -29419,17 +29437,15 @@
         <v>80</v>
       </c>
       <c r="K220" t="s" s="2">
-        <v>111</v>
+        <v>105</v>
       </c>
       <c r="L220" t="s" s="2">
-        <v>112</v>
+        <v>106</v>
       </c>
       <c r="M220" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="N220" t="s" s="2">
-        <v>114</v>
-      </c>
+        <v>107</v>
+      </c>
+      <c r="N220" s="2"/>
       <c r="O220" s="2"/>
       <c r="P220" t="s" s="2">
         <v>80</v>
@@ -29466,31 +29482,31 @@
         <v>80</v>
       </c>
       <c r="AB220" t="s" s="2">
-        <v>115</v>
+        <v>80</v>
       </c>
       <c r="AC220" t="s" s="2">
-        <v>116</v>
+        <v>80</v>
       </c>
       <c r="AD220" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE220" t="s" s="2">
-        <v>117</v>
+        <v>80</v>
       </c>
       <c r="AF220" t="s" s="2">
-        <v>118</v>
+        <v>108</v>
       </c>
       <c r="AG220" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH220" t="s" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="AI220" t="s" s="2">
-        <v>198</v>
+        <v>80</v>
       </c>
       <c r="AJ220" t="s" s="2">
-        <v>119</v>
+        <v>80</v>
       </c>
       <c r="AK220" t="s" s="2">
         <v>80</v>
@@ -29511,48 +29527,46 @@
         <v>80</v>
       </c>
     </row>
-    <row r="221">
+    <row r="221" hidden="true">
       <c r="A221" t="s" s="2">
-        <v>745</v>
+        <v>748</v>
       </c>
       <c r="B221" t="s" s="2">
-        <v>746</v>
+        <v>749</v>
       </c>
       <c r="C221" s="2"/>
       <c r="D221" t="s" s="2">
-        <v>80</v>
+        <v>110</v>
       </c>
       <c r="E221" s="2"/>
       <c r="F221" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="G221" t="s" s="2">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="H221" t="s" s="2">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="I221" t="s" s="2">
         <v>80</v>
       </c>
       <c r="J221" t="s" s="2">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="K221" t="s" s="2">
-        <v>132</v>
+        <v>111</v>
       </c>
       <c r="L221" t="s" s="2">
-        <v>266</v>
+        <v>112</v>
       </c>
       <c r="M221" t="s" s="2">
-        <v>267</v>
+        <v>113</v>
       </c>
       <c r="N221" t="s" s="2">
-        <v>268</v>
-      </c>
-      <c r="O221" t="s" s="2">
-        <v>269</v>
-      </c>
+        <v>114</v>
+      </c>
+      <c r="O221" s="2"/>
       <c r="P221" t="s" s="2">
         <v>80</v>
       </c>
@@ -29588,31 +29602,31 @@
         <v>80</v>
       </c>
       <c r="AB221" t="s" s="2">
-        <v>80</v>
+        <v>115</v>
       </c>
       <c r="AC221" t="s" s="2">
-        <v>80</v>
+        <v>116</v>
       </c>
       <c r="AD221" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE221" t="s" s="2">
-        <v>80</v>
+        <v>117</v>
       </c>
       <c r="AF221" t="s" s="2">
-        <v>270</v>
+        <v>118</v>
       </c>
       <c r="AG221" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH221" t="s" s="2">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="AI221" t="s" s="2">
         <v>198</v>
       </c>
       <c r="AJ221" t="s" s="2">
-        <v>103</v>
+        <v>119</v>
       </c>
       <c r="AK221" t="s" s="2">
         <v>80</v>
@@ -29624,7 +29638,7 @@
         <v>80</v>
       </c>
       <c r="AN221" t="s" s="2">
-        <v>271</v>
+        <v>80</v>
       </c>
       <c r="AO221" t="s" s="2">
         <v>80</v>
@@ -29633,12 +29647,12 @@
         <v>80</v>
       </c>
     </row>
-    <row r="222" hidden="true">
+    <row r="222">
       <c r="A222" t="s" s="2">
-        <v>747</v>
+        <v>750</v>
       </c>
       <c r="B222" t="s" s="2">
-        <v>748</v>
+        <v>751</v>
       </c>
       <c r="C222" s="2"/>
       <c r="D222" t="s" s="2">
@@ -29646,13 +29660,13 @@
       </c>
       <c r="E222" s="2"/>
       <c r="F222" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="G222" t="s" s="2">
         <v>91</v>
       </c>
       <c r="H222" t="s" s="2">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="I222" t="s" s="2">
         <v>80</v>
@@ -29661,18 +29675,20 @@
         <v>92</v>
       </c>
       <c r="K222" t="s" s="2">
-        <v>105</v>
+        <v>132</v>
       </c>
       <c r="L222" t="s" s="2">
-        <v>273</v>
+        <v>266</v>
       </c>
       <c r="M222" t="s" s="2">
-        <v>274</v>
+        <v>267</v>
       </c>
       <c r="N222" t="s" s="2">
-        <v>275</v>
-      </c>
-      <c r="O222" s="2"/>
+        <v>268</v>
+      </c>
+      <c r="O222" t="s" s="2">
+        <v>269</v>
+      </c>
       <c r="P222" t="s" s="2">
         <v>80</v>
       </c>
@@ -29720,7 +29736,7 @@
         <v>80</v>
       </c>
       <c r="AF222" t="s" s="2">
-        <v>276</v>
+        <v>270</v>
       </c>
       <c r="AG222" t="s" s="2">
         <v>81</v>
@@ -29744,7 +29760,7 @@
         <v>80</v>
       </c>
       <c r="AN222" t="s" s="2">
-        <v>277</v>
+        <v>271</v>
       </c>
       <c r="AO222" t="s" s="2">
         <v>80</v>
@@ -29753,12 +29769,12 @@
         <v>80</v>
       </c>
     </row>
-    <row r="223">
+    <row r="223" hidden="true">
       <c r="A223" t="s" s="2">
-        <v>749</v>
+        <v>752</v>
       </c>
       <c r="B223" t="s" s="2">
-        <v>750</v>
+        <v>753</v>
       </c>
       <c r="C223" s="2"/>
       <c r="D223" t="s" s="2">
@@ -29766,13 +29782,13 @@
       </c>
       <c r="E223" s="2"/>
       <c r="F223" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="G223" t="s" s="2">
         <v>91</v>
       </c>
       <c r="H223" t="s" s="2">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="I223" t="s" s="2">
         <v>80</v>
@@ -29781,20 +29797,18 @@
         <v>92</v>
       </c>
       <c r="K223" t="s" s="2">
-        <v>166</v>
+        <v>105</v>
       </c>
       <c r="L223" t="s" s="2">
-        <v>279</v>
+        <v>273</v>
       </c>
       <c r="M223" t="s" s="2">
-        <v>280</v>
+        <v>274</v>
       </c>
       <c r="N223" t="s" s="2">
-        <v>402</v>
-      </c>
-      <c r="O223" t="s" s="2">
-        <v>281</v>
-      </c>
+        <v>275</v>
+      </c>
+      <c r="O223" s="2"/>
       <c r="P223" t="s" s="2">
         <v>80</v>
       </c>
@@ -29842,7 +29856,7 @@
         <v>80</v>
       </c>
       <c r="AF223" t="s" s="2">
-        <v>282</v>
+        <v>276</v>
       </c>
       <c r="AG223" t="s" s="2">
         <v>81</v>
@@ -29866,7 +29880,7 @@
         <v>80</v>
       </c>
       <c r="AN223" t="s" s="2">
-        <v>283</v>
+        <v>277</v>
       </c>
       <c r="AO223" t="s" s="2">
         <v>80</v>
@@ -29875,12 +29889,12 @@
         <v>80</v>
       </c>
     </row>
-    <row r="224" hidden="true">
+    <row r="224">
       <c r="A224" t="s" s="2">
-        <v>751</v>
+        <v>754</v>
       </c>
       <c r="B224" t="s" s="2">
-        <v>752</v>
+        <v>755</v>
       </c>
       <c r="C224" s="2"/>
       <c r="D224" t="s" s="2">
@@ -29888,13 +29902,13 @@
       </c>
       <c r="E224" s="2"/>
       <c r="F224" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="G224" t="s" s="2">
         <v>91</v>
       </c>
       <c r="H224" t="s" s="2">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="I224" t="s" s="2">
         <v>80</v>
@@ -29903,19 +29917,19 @@
         <v>92</v>
       </c>
       <c r="K224" t="s" s="2">
-        <v>105</v>
+        <v>166</v>
       </c>
       <c r="L224" t="s" s="2">
-        <v>285</v>
+        <v>279</v>
       </c>
       <c r="M224" t="s" s="2">
-        <v>286</v>
+        <v>280</v>
       </c>
       <c r="N224" t="s" s="2">
         <v>402</v>
       </c>
       <c r="O224" t="s" s="2">
-        <v>287</v>
+        <v>281</v>
       </c>
       <c r="P224" t="s" s="2">
         <v>80</v>
@@ -29964,7 +29978,7 @@
         <v>80</v>
       </c>
       <c r="AF224" t="s" s="2">
-        <v>288</v>
+        <v>282</v>
       </c>
       <c r="AG224" t="s" s="2">
         <v>81</v>
@@ -29988,7 +30002,7 @@
         <v>80</v>
       </c>
       <c r="AN224" t="s" s="2">
-        <v>289</v>
+        <v>283</v>
       </c>
       <c r="AO224" t="s" s="2">
         <v>80</v>
@@ -29999,10 +30013,10 @@
     </row>
     <row r="225" hidden="true">
       <c r="A225" t="s" s="2">
-        <v>753</v>
+        <v>756</v>
       </c>
       <c r="B225" t="s" s="2">
-        <v>754</v>
+        <v>757</v>
       </c>
       <c r="C225" s="2"/>
       <c r="D225" t="s" s="2">
@@ -30025,19 +30039,19 @@
         <v>92</v>
       </c>
       <c r="K225" t="s" s="2">
-        <v>291</v>
+        <v>105</v>
       </c>
       <c r="L225" t="s" s="2">
-        <v>292</v>
+        <v>285</v>
       </c>
       <c r="M225" t="s" s="2">
-        <v>293</v>
+        <v>286</v>
       </c>
       <c r="N225" t="s" s="2">
-        <v>294</v>
+        <v>402</v>
       </c>
       <c r="O225" t="s" s="2">
-        <v>295</v>
+        <v>287</v>
       </c>
       <c r="P225" t="s" s="2">
         <v>80</v>
@@ -30086,7 +30100,7 @@
         <v>80</v>
       </c>
       <c r="AF225" t="s" s="2">
-        <v>296</v>
+        <v>288</v>
       </c>
       <c r="AG225" t="s" s="2">
         <v>81</v>
@@ -30110,7 +30124,7 @@
         <v>80</v>
       </c>
       <c r="AN225" t="s" s="2">
-        <v>297</v>
+        <v>289</v>
       </c>
       <c r="AO225" t="s" s="2">
         <v>80</v>
@@ -30121,10 +30135,10 @@
     </row>
     <row r="226" hidden="true">
       <c r="A226" t="s" s="2">
-        <v>755</v>
+        <v>758</v>
       </c>
       <c r="B226" t="s" s="2">
-        <v>756</v>
+        <v>759</v>
       </c>
       <c r="C226" s="2"/>
       <c r="D226" t="s" s="2">
@@ -30147,19 +30161,19 @@
         <v>92</v>
       </c>
       <c r="K226" t="s" s="2">
-        <v>105</v>
+        <v>291</v>
       </c>
       <c r="L226" t="s" s="2">
-        <v>299</v>
+        <v>292</v>
       </c>
       <c r="M226" t="s" s="2">
-        <v>300</v>
+        <v>293</v>
       </c>
       <c r="N226" t="s" s="2">
-        <v>301</v>
+        <v>294</v>
       </c>
       <c r="O226" t="s" s="2">
-        <v>302</v>
+        <v>295</v>
       </c>
       <c r="P226" t="s" s="2">
         <v>80</v>
@@ -30208,7 +30222,7 @@
         <v>80</v>
       </c>
       <c r="AF226" t="s" s="2">
-        <v>303</v>
+        <v>296</v>
       </c>
       <c r="AG226" t="s" s="2">
         <v>81</v>
@@ -30232,7 +30246,7 @@
         <v>80</v>
       </c>
       <c r="AN226" t="s" s="2">
-        <v>304</v>
+        <v>297</v>
       </c>
       <c r="AO226" t="s" s="2">
         <v>80</v>
@@ -30243,10 +30257,10 @@
     </row>
     <row r="227" hidden="true">
       <c r="A227" t="s" s="2">
-        <v>757</v>
+        <v>760</v>
       </c>
       <c r="B227" t="s" s="2">
-        <v>758</v>
+        <v>761</v>
       </c>
       <c r="C227" s="2"/>
       <c r="D227" t="s" s="2">
@@ -30269,19 +30283,19 @@
         <v>92</v>
       </c>
       <c r="K227" t="s" s="2">
-        <v>759</v>
+        <v>105</v>
       </c>
       <c r="L227" t="s" s="2">
-        <v>760</v>
+        <v>299</v>
       </c>
       <c r="M227" t="s" s="2">
-        <v>761</v>
+        <v>300</v>
       </c>
       <c r="N227" t="s" s="2">
-        <v>762</v>
+        <v>301</v>
       </c>
       <c r="O227" t="s" s="2">
-        <v>763</v>
+        <v>302</v>
       </c>
       <c r="P227" t="s" s="2">
         <v>80</v>
@@ -30330,7 +30344,7 @@
         <v>80</v>
       </c>
       <c r="AF227" t="s" s="2">
-        <v>764</v>
+        <v>303</v>
       </c>
       <c r="AG227" t="s" s="2">
         <v>81</v>
@@ -30339,7 +30353,7 @@
         <v>91</v>
       </c>
       <c r="AI227" t="s" s="2">
-        <v>80</v>
+        <v>198</v>
       </c>
       <c r="AJ227" t="s" s="2">
         <v>103</v>
@@ -30354,7 +30368,7 @@
         <v>80</v>
       </c>
       <c r="AN227" t="s" s="2">
-        <v>765</v>
+        <v>304</v>
       </c>
       <c r="AO227" t="s" s="2">
         <v>80</v>
@@ -30365,10 +30379,10 @@
     </row>
     <row r="228" hidden="true">
       <c r="A228" t="s" s="2">
-        <v>766</v>
+        <v>762</v>
       </c>
       <c r="B228" t="s" s="2">
-        <v>767</v>
+        <v>763</v>
       </c>
       <c r="C228" s="2"/>
       <c r="D228" t="s" s="2">
@@ -30385,74 +30399,74 @@
         <v>80</v>
       </c>
       <c r="I228" t="s" s="2">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="J228" t="s" s="2">
         <v>92</v>
       </c>
       <c r="K228" t="s" s="2">
-        <v>166</v>
+        <v>764</v>
       </c>
       <c r="L228" t="s" s="2">
+        <v>765</v>
+      </c>
+      <c r="M228" t="s" s="2">
+        <v>766</v>
+      </c>
+      <c r="N228" t="s" s="2">
+        <v>767</v>
+      </c>
+      <c r="O228" t="s" s="2">
         <v>768</v>
       </c>
-      <c r="M228" t="s" s="2">
+      <c r="P228" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q228" s="2"/>
+      <c r="R228" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S228" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T228" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U228" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V228" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W228" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X228" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y228" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z228" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA228" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB228" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC228" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD228" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE228" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF228" t="s" s="2">
         <v>769</v>
-      </c>
-      <c r="N228" s="2"/>
-      <c r="O228" t="s" s="2">
-        <v>770</v>
-      </c>
-      <c r="P228" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Q228" t="s" s="2">
-        <v>771</v>
-      </c>
-      <c r="R228" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="S228" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="T228" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="U228" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="V228" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="W228" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="X228" t="s" s="2">
-        <v>245</v>
-      </c>
-      <c r="Y228" t="s" s="2">
-        <v>772</v>
-      </c>
-      <c r="Z228" t="s" s="2">
-        <v>773</v>
-      </c>
-      <c r="AA228" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB228" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC228" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AD228" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE228" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AF228" t="s" s="2">
-        <v>774</v>
       </c>
       <c r="AG228" t="s" s="2">
         <v>81</v>
@@ -30476,7 +30490,7 @@
         <v>80</v>
       </c>
       <c r="AN228" t="s" s="2">
-        <v>775</v>
+        <v>770</v>
       </c>
       <c r="AO228" t="s" s="2">
         <v>80</v>
@@ -30487,10 +30501,10 @@
     </row>
     <row r="229" hidden="true">
       <c r="A229" t="s" s="2">
-        <v>776</v>
+        <v>771</v>
       </c>
       <c r="B229" t="s" s="2">
-        <v>777</v>
+        <v>772</v>
       </c>
       <c r="C229" s="2"/>
       <c r="D229" t="s" s="2">
@@ -30507,28 +30521,30 @@
         <v>80</v>
       </c>
       <c r="I229" t="s" s="2">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="J229" t="s" s="2">
         <v>92</v>
       </c>
       <c r="K229" t="s" s="2">
-        <v>105</v>
+        <v>166</v>
       </c>
       <c r="L229" t="s" s="2">
-        <v>778</v>
+        <v>773</v>
       </c>
       <c r="M229" t="s" s="2">
-        <v>779</v>
+        <v>774</v>
       </c>
       <c r="N229" s="2"/>
       <c r="O229" t="s" s="2">
-        <v>780</v>
+        <v>775</v>
       </c>
       <c r="P229" t="s" s="2">
         <v>80</v>
       </c>
-      <c r="Q229" s="2"/>
+      <c r="Q229" t="s" s="2">
+        <v>776</v>
+      </c>
       <c r="R229" t="s" s="2">
         <v>80</v>
       </c>
@@ -30548,13 +30564,13 @@
         <v>80</v>
       </c>
       <c r="X229" t="s" s="2">
-        <v>80</v>
+        <v>245</v>
       </c>
       <c r="Y229" t="s" s="2">
-        <v>80</v>
+        <v>777</v>
       </c>
       <c r="Z229" t="s" s="2">
-        <v>80</v>
+        <v>778</v>
       </c>
       <c r="AA229" t="s" s="2">
         <v>80</v>
@@ -30572,7 +30588,7 @@
         <v>80</v>
       </c>
       <c r="AF229" t="s" s="2">
-        <v>781</v>
+        <v>779</v>
       </c>
       <c r="AG229" t="s" s="2">
         <v>81</v>
@@ -30596,7 +30612,7 @@
         <v>80</v>
       </c>
       <c r="AN229" t="s" s="2">
-        <v>782</v>
+        <v>780</v>
       </c>
       <c r="AO229" t="s" s="2">
         <v>80</v>
@@ -30607,10 +30623,10 @@
     </row>
     <row r="230" hidden="true">
       <c r="A230" t="s" s="2">
-        <v>783</v>
+        <v>781</v>
       </c>
       <c r="B230" t="s" s="2">
-        <v>784</v>
+        <v>782</v>
       </c>
       <c r="C230" s="2"/>
       <c r="D230" t="s" s="2">
@@ -30633,17 +30649,17 @@
         <v>92</v>
       </c>
       <c r="K230" t="s" s="2">
-        <v>132</v>
+        <v>105</v>
       </c>
       <c r="L230" t="s" s="2">
-        <v>785</v>
+        <v>783</v>
       </c>
       <c r="M230" t="s" s="2">
-        <v>786</v>
+        <v>784</v>
       </c>
       <c r="N230" s="2"/>
       <c r="O230" t="s" s="2">
-        <v>787</v>
+        <v>785</v>
       </c>
       <c r="P230" t="s" s="2">
         <v>80</v>
@@ -30692,7 +30708,7 @@
         <v>80</v>
       </c>
       <c r="AF230" t="s" s="2">
-        <v>788</v>
+        <v>786</v>
       </c>
       <c r="AG230" t="s" s="2">
         <v>81</v>
@@ -30701,7 +30717,7 @@
         <v>91</v>
       </c>
       <c r="AI230" t="s" s="2">
-        <v>789</v>
+        <v>80</v>
       </c>
       <c r="AJ230" t="s" s="2">
         <v>103</v>
@@ -30716,7 +30732,7 @@
         <v>80</v>
       </c>
       <c r="AN230" t="s" s="2">
-        <v>782</v>
+        <v>787</v>
       </c>
       <c r="AO230" t="s" s="2">
         <v>80</v>
@@ -30727,10 +30743,10 @@
     </row>
     <row r="231" hidden="true">
       <c r="A231" t="s" s="2">
-        <v>790</v>
+        <v>788</v>
       </c>
       <c r="B231" t="s" s="2">
-        <v>791</v>
+        <v>789</v>
       </c>
       <c r="C231" s="2"/>
       <c r="D231" t="s" s="2">
@@ -30753,19 +30769,17 @@
         <v>92</v>
       </c>
       <c r="K231" t="s" s="2">
-        <v>166</v>
+        <v>132</v>
       </c>
       <c r="L231" t="s" s="2">
+        <v>790</v>
+      </c>
+      <c r="M231" t="s" s="2">
+        <v>791</v>
+      </c>
+      <c r="N231" s="2"/>
+      <c r="O231" t="s" s="2">
         <v>792</v>
-      </c>
-      <c r="M231" t="s" s="2">
-        <v>793</v>
-      </c>
-      <c r="N231" t="s" s="2">
-        <v>794</v>
-      </c>
-      <c r="O231" t="s" s="2">
-        <v>795</v>
       </c>
       <c r="P231" t="s" s="2">
         <v>80</v>
@@ -30814,7 +30828,7 @@
         <v>80</v>
       </c>
       <c r="AF231" t="s" s="2">
-        <v>796</v>
+        <v>793</v>
       </c>
       <c r="AG231" t="s" s="2">
         <v>81</v>
@@ -30823,7 +30837,7 @@
         <v>91</v>
       </c>
       <c r="AI231" t="s" s="2">
-        <v>80</v>
+        <v>794</v>
       </c>
       <c r="AJ231" t="s" s="2">
         <v>103</v>
@@ -30838,7 +30852,7 @@
         <v>80</v>
       </c>
       <c r="AN231" t="s" s="2">
-        <v>782</v>
+        <v>787</v>
       </c>
       <c r="AO231" t="s" s="2">
         <v>80</v>
@@ -30849,10 +30863,10 @@
     </row>
     <row r="232" hidden="true">
       <c r="A232" t="s" s="2">
-        <v>797</v>
+        <v>795</v>
       </c>
       <c r="B232" t="s" s="2">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="C232" s="2"/>
       <c r="D232" t="s" s="2">
@@ -30872,21 +30886,23 @@
         <v>80</v>
       </c>
       <c r="J232" t="s" s="2">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="K232" t="s" s="2">
+        <v>166</v>
+      </c>
+      <c r="L232" t="s" s="2">
+        <v>797</v>
+      </c>
+      <c r="M232" t="s" s="2">
         <v>798</v>
       </c>
-      <c r="L232" t="s" s="2">
+      <c r="N232" t="s" s="2">
         <v>799</v>
       </c>
-      <c r="M232" t="s" s="2">
+      <c r="O232" t="s" s="2">
         <v>800</v>
       </c>
-      <c r="N232" t="s" s="2">
-        <v>801</v>
-      </c>
-      <c r="O232" s="2"/>
       <c r="P232" t="s" s="2">
         <v>80</v>
       </c>
@@ -30934,7 +30950,7 @@
         <v>80</v>
       </c>
       <c r="AF232" t="s" s="2">
-        <v>797</v>
+        <v>801</v>
       </c>
       <c r="AG232" t="s" s="2">
         <v>81</v>
@@ -30943,7 +30959,7 @@
         <v>91</v>
       </c>
       <c r="AI232" t="s" s="2">
-        <v>802</v>
+        <v>80</v>
       </c>
       <c r="AJ232" t="s" s="2">
         <v>103</v>
@@ -30958,21 +30974,21 @@
         <v>80</v>
       </c>
       <c r="AN232" t="s" s="2">
-        <v>80</v>
+        <v>787</v>
       </c>
       <c r="AO232" t="s" s="2">
-        <v>803</v>
+        <v>80</v>
       </c>
       <c r="AP232" t="s" s="2">
         <v>80</v>
       </c>
     </row>
-    <row r="233">
+    <row r="233" hidden="true">
       <c r="A233" t="s" s="2">
-        <v>804</v>
+        <v>802</v>
       </c>
       <c r="B233" t="s" s="2">
-        <v>804</v>
+        <v>802</v>
       </c>
       <c r="C233" s="2"/>
       <c r="D233" t="s" s="2">
@@ -30980,30 +30996,32 @@
       </c>
       <c r="E233" s="2"/>
       <c r="F233" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="G233" t="s" s="2">
         <v>91</v>
       </c>
       <c r="H233" t="s" s="2">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="I233" t="s" s="2">
         <v>80</v>
       </c>
       <c r="J233" t="s" s="2">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="K233" t="s" s="2">
-        <v>226</v>
+        <v>803</v>
       </c>
       <c r="L233" t="s" s="2">
+        <v>804</v>
+      </c>
+      <c r="M233" t="s" s="2">
         <v>805</v>
       </c>
-      <c r="M233" t="s" s="2">
+      <c r="N233" t="s" s="2">
         <v>806</v>
       </c>
-      <c r="N233" s="2"/>
       <c r="O233" s="2"/>
       <c r="P233" t="s" s="2">
         <v>80</v>
@@ -31052,7 +31070,7 @@
         <v>80</v>
       </c>
       <c r="AF233" t="s" s="2">
-        <v>804</v>
+        <v>802</v>
       </c>
       <c r="AG233" t="s" s="2">
         <v>81</v>
@@ -31061,13 +31079,13 @@
         <v>91</v>
       </c>
       <c r="AI233" t="s" s="2">
-        <v>80</v>
+        <v>807</v>
       </c>
       <c r="AJ233" t="s" s="2">
         <v>103</v>
       </c>
       <c r="AK233" t="s" s="2">
-        <v>807</v>
+        <v>80</v>
       </c>
       <c r="AL233" t="s" s="2">
         <v>80</v>
@@ -31076,21 +31094,21 @@
         <v>80</v>
       </c>
       <c r="AN233" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AO233" t="s" s="2">
         <v>808</v>
       </c>
-      <c r="AO233" t="s" s="2">
+      <c r="AP233" t="s" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="s" s="2">
         <v>809</v>
       </c>
-      <c r="AP233" t="s" s="2">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="234" hidden="true">
-      <c r="A234" t="s" s="2">
-        <v>810</v>
-      </c>
       <c r="B234" t="s" s="2">
-        <v>810</v>
+        <v>809</v>
       </c>
       <c r="C234" s="2"/>
       <c r="D234" t="s" s="2">
@@ -31098,13 +31116,13 @@
       </c>
       <c r="E234" s="2"/>
       <c r="F234" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="G234" t="s" s="2">
         <v>91</v>
       </c>
       <c r="H234" t="s" s="2">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="I234" t="s" s="2">
         <v>80</v>
@@ -31113,13 +31131,13 @@
         <v>92</v>
       </c>
       <c r="K234" t="s" s="2">
+        <v>226</v>
+      </c>
+      <c r="L234" t="s" s="2">
+        <v>810</v>
+      </c>
+      <c r="M234" t="s" s="2">
         <v>811</v>
-      </c>
-      <c r="L234" t="s" s="2">
-        <v>812</v>
-      </c>
-      <c r="M234" t="s" s="2">
-        <v>813</v>
       </c>
       <c r="N234" s="2"/>
       <c r="O234" s="2"/>
@@ -31170,7 +31188,7 @@
         <v>80</v>
       </c>
       <c r="AF234" t="s" s="2">
-        <v>810</v>
+        <v>809</v>
       </c>
       <c r="AG234" t="s" s="2">
         <v>81</v>
@@ -31185,7 +31203,7 @@
         <v>103</v>
       </c>
       <c r="AK234" t="s" s="2">
-        <v>80</v>
+        <v>812</v>
       </c>
       <c r="AL234" t="s" s="2">
         <v>80</v>
@@ -31194,7 +31212,7 @@
         <v>80</v>
       </c>
       <c r="AN234" t="s" s="2">
-        <v>80</v>
+        <v>813</v>
       </c>
       <c r="AO234" t="s" s="2">
         <v>814</v>
@@ -31231,13 +31249,13 @@
         <v>92</v>
       </c>
       <c r="K235" t="s" s="2">
-        <v>811</v>
+        <v>816</v>
       </c>
       <c r="L235" t="s" s="2">
-        <v>816</v>
+        <v>817</v>
       </c>
       <c r="M235" t="s" s="2">
-        <v>817</v>
+        <v>818</v>
       </c>
       <c r="N235" s="2"/>
       <c r="O235" s="2"/>
@@ -31312,7 +31330,7 @@
         <v>80</v>
       </c>
       <c r="AN235" t="s" s="2">
-        <v>818</v>
+        <v>80</v>
       </c>
       <c r="AO235" t="s" s="2">
         <v>819</v>
@@ -31337,7 +31355,7 @@
         <v>81</v>
       </c>
       <c r="G236" t="s" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="H236" t="s" s="2">
         <v>80</v>
@@ -31346,16 +31364,16 @@
         <v>80</v>
       </c>
       <c r="J236" t="s" s="2">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="K236" t="s" s="2">
+        <v>816</v>
+      </c>
+      <c r="L236" t="s" s="2">
         <v>821</v>
       </c>
-      <c r="L236" t="s" s="2">
+      <c r="M236" t="s" s="2">
         <v>822</v>
-      </c>
-      <c r="M236" t="s" s="2">
-        <v>823</v>
       </c>
       <c r="N236" s="2"/>
       <c r="O236" s="2"/>
@@ -31412,28 +31430,28 @@
         <v>81</v>
       </c>
       <c r="AH236" t="s" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="AI236" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ236" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="AK236" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL236" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM236" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN236" t="s" s="2">
+        <v>823</v>
+      </c>
+      <c r="AO236" t="s" s="2">
         <v>824</v>
-      </c>
-      <c r="AK236" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AL236" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AM236" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN236" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AO236" t="s" s="2">
-        <v>80</v>
       </c>
       <c r="AP236" t="s" s="2">
         <v>80</v>
@@ -31455,7 +31473,7 @@
         <v>81</v>
       </c>
       <c r="G237" t="s" s="2">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="H237" t="s" s="2">
         <v>80</v>
@@ -31467,13 +31485,13 @@
         <v>80</v>
       </c>
       <c r="K237" t="s" s="2">
-        <v>105</v>
+        <v>826</v>
       </c>
       <c r="L237" t="s" s="2">
-        <v>106</v>
+        <v>827</v>
       </c>
       <c r="M237" t="s" s="2">
-        <v>107</v>
+        <v>828</v>
       </c>
       <c r="N237" s="2"/>
       <c r="O237" s="2"/>
@@ -31524,19 +31542,19 @@
         <v>80</v>
       </c>
       <c r="AF237" t="s" s="2">
-        <v>108</v>
+        <v>825</v>
       </c>
       <c r="AG237" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH237" t="s" s="2">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="AI237" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ237" t="s" s="2">
-        <v>80</v>
+        <v>829</v>
       </c>
       <c r="AK237" t="s" s="2">
         <v>80</v>
@@ -31559,21 +31577,21 @@
     </row>
     <row r="238" hidden="true">
       <c r="A238" t="s" s="2">
-        <v>826</v>
+        <v>830</v>
       </c>
       <c r="B238" t="s" s="2">
-        <v>826</v>
+        <v>830</v>
       </c>
       <c r="C238" s="2"/>
       <c r="D238" t="s" s="2">
-        <v>110</v>
+        <v>80</v>
       </c>
       <c r="E238" s="2"/>
       <c r="F238" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G238" t="s" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="H238" t="s" s="2">
         <v>80</v>
@@ -31585,17 +31603,15 @@
         <v>80</v>
       </c>
       <c r="K238" t="s" s="2">
-        <v>111</v>
+        <v>105</v>
       </c>
       <c r="L238" t="s" s="2">
-        <v>112</v>
+        <v>106</v>
       </c>
       <c r="M238" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="N238" t="s" s="2">
-        <v>114</v>
-      </c>
+        <v>107</v>
+      </c>
+      <c r="N238" s="2"/>
       <c r="O238" s="2"/>
       <c r="P238" t="s" s="2">
         <v>80</v>
@@ -31644,19 +31660,19 @@
         <v>80</v>
       </c>
       <c r="AF238" t="s" s="2">
-        <v>118</v>
+        <v>108</v>
       </c>
       <c r="AG238" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH238" t="s" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="AI238" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ238" t="s" s="2">
-        <v>119</v>
+        <v>80</v>
       </c>
       <c r="AK238" t="s" s="2">
         <v>80</v>
@@ -31679,14 +31695,14 @@
     </row>
     <row r="239" hidden="true">
       <c r="A239" t="s" s="2">
-        <v>827</v>
+        <v>831</v>
       </c>
       <c r="B239" t="s" s="2">
-        <v>827</v>
+        <v>831</v>
       </c>
       <c r="C239" s="2"/>
       <c r="D239" t="s" s="2">
-        <v>828</v>
+        <v>110</v>
       </c>
       <c r="E239" s="2"/>
       <c r="F239" t="s" s="2">
@@ -31699,26 +31715,24 @@
         <v>80</v>
       </c>
       <c r="I239" t="s" s="2">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="J239" t="s" s="2">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="K239" t="s" s="2">
         <v>111</v>
       </c>
       <c r="L239" t="s" s="2">
-        <v>829</v>
+        <v>112</v>
       </c>
       <c r="M239" t="s" s="2">
-        <v>830</v>
+        <v>113</v>
       </c>
       <c r="N239" t="s" s="2">
         <v>114</v>
       </c>
-      <c r="O239" t="s" s="2">
-        <v>230</v>
-      </c>
+      <c r="O239" s="2"/>
       <c r="P239" t="s" s="2">
         <v>80</v>
       </c>
@@ -31766,7 +31780,7 @@
         <v>80</v>
       </c>
       <c r="AF239" t="s" s="2">
-        <v>831</v>
+        <v>118</v>
       </c>
       <c r="AG239" t="s" s="2">
         <v>81</v>
@@ -31808,35 +31822,39 @@
       </c>
       <c r="C240" s="2"/>
       <c r="D240" t="s" s="2">
-        <v>80</v>
+        <v>833</v>
       </c>
       <c r="E240" s="2"/>
       <c r="F240" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G240" t="s" s="2">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="H240" t="s" s="2">
         <v>80</v>
       </c>
       <c r="I240" t="s" s="2">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="J240" t="s" s="2">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="K240" t="s" s="2">
-        <v>241</v>
+        <v>111</v>
       </c>
       <c r="L240" t="s" s="2">
-        <v>833</v>
+        <v>834</v>
       </c>
       <c r="M240" t="s" s="2">
-        <v>834</v>
-      </c>
-      <c r="N240" s="2"/>
-      <c r="O240" s="2"/>
+        <v>835</v>
+      </c>
+      <c r="N240" t="s" s="2">
+        <v>114</v>
+      </c>
+      <c r="O240" t="s" s="2">
+        <v>230</v>
+      </c>
       <c r="P240" t="s" s="2">
         <v>80</v>
       </c>
@@ -31860,43 +31878,43 @@
         <v>80</v>
       </c>
       <c r="X240" t="s" s="2">
-        <v>156</v>
+        <v>80</v>
       </c>
       <c r="Y240" t="s" s="2">
-        <v>835</v>
+        <v>80</v>
       </c>
       <c r="Z240" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA240" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB240" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC240" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD240" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE240" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF240" t="s" s="2">
         <v>836</v>
       </c>
-      <c r="AA240" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB240" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC240" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AD240" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE240" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AF240" t="s" s="2">
-        <v>832</v>
-      </c>
       <c r="AG240" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH240" t="s" s="2">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="AI240" t="s" s="2">
-        <v>837</v>
+        <v>80</v>
       </c>
       <c r="AJ240" t="s" s="2">
-        <v>103</v>
+        <v>119</v>
       </c>
       <c r="AK240" t="s" s="2">
         <v>80</v>
@@ -31905,10 +31923,10 @@
         <v>80</v>
       </c>
       <c r="AM240" t="s" s="2">
-        <v>838</v>
+        <v>80</v>
       </c>
       <c r="AN240" t="s" s="2">
-        <v>252</v>
+        <v>80</v>
       </c>
       <c r="AO240" t="s" s="2">
         <v>80</v>
@@ -31919,10 +31937,10 @@
     </row>
     <row r="241" hidden="true">
       <c r="A241" t="s" s="2">
-        <v>839</v>
+        <v>837</v>
       </c>
       <c r="B241" t="s" s="2">
-        <v>839</v>
+        <v>837</v>
       </c>
       <c r="C241" s="2"/>
       <c r="D241" t="s" s="2">
@@ -31933,7 +31951,7 @@
         <v>81</v>
       </c>
       <c r="G241" t="s" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="H241" t="s" s="2">
         <v>80</v>
@@ -31945,13 +31963,13 @@
         <v>80</v>
       </c>
       <c r="K241" t="s" s="2">
-        <v>840</v>
+        <v>241</v>
       </c>
       <c r="L241" t="s" s="2">
-        <v>841</v>
+        <v>838</v>
       </c>
       <c r="M241" t="s" s="2">
-        <v>842</v>
+        <v>839</v>
       </c>
       <c r="N241" s="2"/>
       <c r="O241" s="2"/>
@@ -31978,13 +31996,13 @@
         <v>80</v>
       </c>
       <c r="X241" t="s" s="2">
-        <v>80</v>
+        <v>156</v>
       </c>
       <c r="Y241" t="s" s="2">
-        <v>80</v>
+        <v>840</v>
       </c>
       <c r="Z241" t="s" s="2">
-        <v>80</v>
+        <v>841</v>
       </c>
       <c r="AA241" t="s" s="2">
         <v>80</v>
@@ -32002,16 +32020,16 @@
         <v>80</v>
       </c>
       <c r="AF241" t="s" s="2">
-        <v>839</v>
+        <v>837</v>
       </c>
       <c r="AG241" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH241" t="s" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="AI241" t="s" s="2">
-        <v>837</v>
+        <v>842</v>
       </c>
       <c r="AJ241" t="s" s="2">
         <v>103</v>
@@ -32023,10 +32041,10 @@
         <v>80</v>
       </c>
       <c r="AM241" t="s" s="2">
-        <v>80</v>
+        <v>843</v>
       </c>
       <c r="AN241" t="s" s="2">
-        <v>80</v>
+        <v>252</v>
       </c>
       <c r="AO241" t="s" s="2">
         <v>80</v>
@@ -32037,10 +32055,10 @@
     </row>
     <row r="242" hidden="true">
       <c r="A242" t="s" s="2">
-        <v>843</v>
+        <v>844</v>
       </c>
       <c r="B242" t="s" s="2">
-        <v>843</v>
+        <v>844</v>
       </c>
       <c r="C242" s="2"/>
       <c r="D242" t="s" s="2">
@@ -32051,7 +32069,7 @@
         <v>81</v>
       </c>
       <c r="G242" t="s" s="2">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="H242" t="s" s="2">
         <v>80</v>
@@ -32063,13 +32081,13 @@
         <v>80</v>
       </c>
       <c r="K242" t="s" s="2">
-        <v>241</v>
+        <v>845</v>
       </c>
       <c r="L242" t="s" s="2">
-        <v>844</v>
+        <v>846</v>
       </c>
       <c r="M242" t="s" s="2">
-        <v>845</v>
+        <v>847</v>
       </c>
       <c r="N242" s="2"/>
       <c r="O242" s="2"/>
@@ -32096,13 +32114,13 @@
         <v>80</v>
       </c>
       <c r="X242" t="s" s="2">
-        <v>156</v>
+        <v>80</v>
       </c>
       <c r="Y242" t="s" s="2">
-        <v>846</v>
+        <v>80</v>
       </c>
       <c r="Z242" t="s" s="2">
-        <v>847</v>
+        <v>80</v>
       </c>
       <c r="AA242" t="s" s="2">
         <v>80</v>
@@ -32120,16 +32138,16 @@
         <v>80</v>
       </c>
       <c r="AF242" t="s" s="2">
-        <v>843</v>
+        <v>844</v>
       </c>
       <c r="AG242" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH242" t="s" s="2">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="AI242" t="s" s="2">
-        <v>80</v>
+        <v>842</v>
       </c>
       <c r="AJ242" t="s" s="2">
         <v>103</v>
@@ -32169,7 +32187,7 @@
         <v>81</v>
       </c>
       <c r="G243" t="s" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="H243" t="s" s="2">
         <v>80</v>
@@ -32181,7 +32199,7 @@
         <v>80</v>
       </c>
       <c r="K243" t="s" s="2">
-        <v>821</v>
+        <v>241</v>
       </c>
       <c r="L243" t="s" s="2">
         <v>849</v>
@@ -32189,9 +32207,7 @@
       <c r="M243" t="s" s="2">
         <v>850</v>
       </c>
-      <c r="N243" t="s" s="2">
-        <v>851</v>
-      </c>
+      <c r="N243" s="2"/>
       <c r="O243" s="2"/>
       <c r="P243" t="s" s="2">
         <v>80</v>
@@ -32216,13 +32232,13 @@
         <v>80</v>
       </c>
       <c r="X243" t="s" s="2">
-        <v>80</v>
+        <v>156</v>
       </c>
       <c r="Y243" t="s" s="2">
-        <v>80</v>
+        <v>851</v>
       </c>
       <c r="Z243" t="s" s="2">
-        <v>80</v>
+        <v>852</v>
       </c>
       <c r="AA243" t="s" s="2">
         <v>80</v>
@@ -32246,13 +32262,13 @@
         <v>81</v>
       </c>
       <c r="AH243" t="s" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="AI243" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ243" t="s" s="2">
-        <v>852</v>
+        <v>103</v>
       </c>
       <c r="AK243" t="s" s="2">
         <v>80</v>
@@ -32289,7 +32305,7 @@
         <v>81</v>
       </c>
       <c r="G244" t="s" s="2">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="H244" t="s" s="2">
         <v>80</v>
@@ -32301,15 +32317,17 @@
         <v>80</v>
       </c>
       <c r="K244" t="s" s="2">
-        <v>105</v>
+        <v>826</v>
       </c>
       <c r="L244" t="s" s="2">
-        <v>106</v>
+        <v>854</v>
       </c>
       <c r="M244" t="s" s="2">
-        <v>107</v>
-      </c>
-      <c r="N244" s="2"/>
+        <v>855</v>
+      </c>
+      <c r="N244" t="s" s="2">
+        <v>856</v>
+      </c>
       <c r="O244" s="2"/>
       <c r="P244" t="s" s="2">
         <v>80</v>
@@ -32358,19 +32376,19 @@
         <v>80</v>
       </c>
       <c r="AF244" t="s" s="2">
-        <v>108</v>
+        <v>853</v>
       </c>
       <c r="AG244" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH244" t="s" s="2">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="AI244" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ244" t="s" s="2">
-        <v>80</v>
+        <v>857</v>
       </c>
       <c r="AK244" t="s" s="2">
         <v>80</v>
@@ -32393,21 +32411,21 @@
     </row>
     <row r="245" hidden="true">
       <c r="A245" t="s" s="2">
-        <v>854</v>
+        <v>858</v>
       </c>
       <c r="B245" t="s" s="2">
-        <v>854</v>
+        <v>858</v>
       </c>
       <c r="C245" s="2"/>
       <c r="D245" t="s" s="2">
-        <v>110</v>
+        <v>80</v>
       </c>
       <c r="E245" s="2"/>
       <c r="F245" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G245" t="s" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="H245" t="s" s="2">
         <v>80</v>
@@ -32419,17 +32437,15 @@
         <v>80</v>
       </c>
       <c r="K245" t="s" s="2">
-        <v>111</v>
+        <v>105</v>
       </c>
       <c r="L245" t="s" s="2">
-        <v>112</v>
+        <v>106</v>
       </c>
       <c r="M245" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="N245" t="s" s="2">
-        <v>114</v>
-      </c>
+        <v>107</v>
+      </c>
+      <c r="N245" s="2"/>
       <c r="O245" s="2"/>
       <c r="P245" t="s" s="2">
         <v>80</v>
@@ -32478,19 +32494,19 @@
         <v>80</v>
       </c>
       <c r="AF245" t="s" s="2">
-        <v>118</v>
+        <v>108</v>
       </c>
       <c r="AG245" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH245" t="s" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="AI245" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ245" t="s" s="2">
-        <v>119</v>
+        <v>80</v>
       </c>
       <c r="AK245" t="s" s="2">
         <v>80</v>
@@ -32513,14 +32529,14 @@
     </row>
     <row r="246" hidden="true">
       <c r="A246" t="s" s="2">
-        <v>855</v>
+        <v>859</v>
       </c>
       <c r="B246" t="s" s="2">
-        <v>855</v>
+        <v>859</v>
       </c>
       <c r="C246" s="2"/>
       <c r="D246" t="s" s="2">
-        <v>828</v>
+        <v>110</v>
       </c>
       <c r="E246" s="2"/>
       <c r="F246" t="s" s="2">
@@ -32533,26 +32549,24 @@
         <v>80</v>
       </c>
       <c r="I246" t="s" s="2">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="J246" t="s" s="2">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="K246" t="s" s="2">
         <v>111</v>
       </c>
       <c r="L246" t="s" s="2">
-        <v>829</v>
+        <v>112</v>
       </c>
       <c r="M246" t="s" s="2">
-        <v>830</v>
+        <v>113</v>
       </c>
       <c r="N246" t="s" s="2">
         <v>114</v>
       </c>
-      <c r="O246" t="s" s="2">
-        <v>230</v>
-      </c>
+      <c r="O246" s="2"/>
       <c r="P246" t="s" s="2">
         <v>80</v>
       </c>
@@ -32600,7 +32614,7 @@
         <v>80</v>
       </c>
       <c r="AF246" t="s" s="2">
-        <v>831</v>
+        <v>118</v>
       </c>
       <c r="AG246" t="s" s="2">
         <v>81</v>
@@ -32635,14 +32649,14 @@
     </row>
     <row r="247" hidden="true">
       <c r="A247" t="s" s="2">
-        <v>856</v>
+        <v>860</v>
       </c>
       <c r="B247" t="s" s="2">
-        <v>856</v>
+        <v>860</v>
       </c>
       <c r="C247" s="2"/>
       <c r="D247" t="s" s="2">
-        <v>80</v>
+        <v>833</v>
       </c>
       <c r="E247" s="2"/>
       <c r="F247" t="s" s="2">
@@ -32655,22 +32669,26 @@
         <v>80</v>
       </c>
       <c r="I247" t="s" s="2">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="J247" t="s" s="2">
         <v>92</v>
       </c>
       <c r="K247" t="s" s="2">
-        <v>241</v>
+        <v>111</v>
       </c>
       <c r="L247" t="s" s="2">
-        <v>857</v>
+        <v>834</v>
       </c>
       <c r="M247" t="s" s="2">
-        <v>858</v>
-      </c>
-      <c r="N247" s="2"/>
-      <c r="O247" s="2"/>
+        <v>835</v>
+      </c>
+      <c r="N247" t="s" s="2">
+        <v>114</v>
+      </c>
+      <c r="O247" t="s" s="2">
+        <v>230</v>
+      </c>
       <c r="P247" t="s" s="2">
         <v>80</v>
       </c>
@@ -32694,13 +32712,13 @@
         <v>80</v>
       </c>
       <c r="X247" t="s" s="2">
-        <v>156</v>
+        <v>80</v>
       </c>
       <c r="Y247" t="s" s="2">
-        <v>859</v>
+        <v>80</v>
       </c>
       <c r="Z247" t="s" s="2">
-        <v>860</v>
+        <v>80</v>
       </c>
       <c r="AA247" t="s" s="2">
         <v>80</v>
@@ -32718,7 +32736,7 @@
         <v>80</v>
       </c>
       <c r="AF247" t="s" s="2">
-        <v>856</v>
+        <v>836</v>
       </c>
       <c r="AG247" t="s" s="2">
         <v>81</v>
@@ -32727,25 +32745,25 @@
         <v>82</v>
       </c>
       <c r="AI247" t="s" s="2">
-        <v>861</v>
+        <v>80</v>
       </c>
       <c r="AJ247" t="s" s="2">
-        <v>103</v>
+        <v>119</v>
       </c>
       <c r="AK247" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL247" t="s" s="2">
-        <v>862</v>
+        <v>80</v>
       </c>
       <c r="AM247" t="s" s="2">
-        <v>331</v>
+        <v>80</v>
       </c>
       <c r="AN247" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AO247" t="s" s="2">
-        <v>863</v>
+        <v>80</v>
       </c>
       <c r="AP247" t="s" s="2">
         <v>80</v>
@@ -32753,10 +32771,10 @@
     </row>
     <row r="248" hidden="true">
       <c r="A248" t="s" s="2">
-        <v>864</v>
+        <v>861</v>
       </c>
       <c r="B248" t="s" s="2">
-        <v>864</v>
+        <v>861</v>
       </c>
       <c r="C248" s="2"/>
       <c r="D248" t="s" s="2">
@@ -32779,13 +32797,13 @@
         <v>92</v>
       </c>
       <c r="K248" t="s" s="2">
-        <v>865</v>
+        <v>241</v>
       </c>
       <c r="L248" t="s" s="2">
-        <v>866</v>
+        <v>862</v>
       </c>
       <c r="M248" t="s" s="2">
-        <v>867</v>
+        <v>863</v>
       </c>
       <c r="N248" s="2"/>
       <c r="O248" s="2"/>
@@ -32812,13 +32830,13 @@
         <v>80</v>
       </c>
       <c r="X248" t="s" s="2">
-        <v>80</v>
+        <v>156</v>
       </c>
       <c r="Y248" t="s" s="2">
-        <v>80</v>
+        <v>864</v>
       </c>
       <c r="Z248" t="s" s="2">
-        <v>80</v>
+        <v>865</v>
       </c>
       <c r="AA248" t="s" s="2">
         <v>80</v>
@@ -32836,7 +32854,7 @@
         <v>80</v>
       </c>
       <c r="AF248" t="s" s="2">
-        <v>864</v>
+        <v>861</v>
       </c>
       <c r="AG248" t="s" s="2">
         <v>81</v>
@@ -32845,7 +32863,7 @@
         <v>82</v>
       </c>
       <c r="AI248" t="s" s="2">
-        <v>861</v>
+        <v>866</v>
       </c>
       <c r="AJ248" t="s" s="2">
         <v>103</v>
@@ -32854,27 +32872,27 @@
         <v>80</v>
       </c>
       <c r="AL248" t="s" s="2">
-        <v>80</v>
+        <v>867</v>
       </c>
       <c r="AM248" t="s" s="2">
-        <v>80</v>
+        <v>331</v>
       </c>
       <c r="AN248" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AO248" t="s" s="2">
-        <v>863</v>
+        <v>868</v>
       </c>
       <c r="AP248" t="s" s="2">
         <v>80</v>
       </c>
     </row>
-    <row r="249">
+    <row r="249" hidden="true">
       <c r="A249" t="s" s="2">
-        <v>868</v>
+        <v>869</v>
       </c>
       <c r="B249" t="s" s="2">
-        <v>868</v>
+        <v>869</v>
       </c>
       <c r="C249" s="2"/>
       <c r="D249" t="s" s="2">
@@ -32888,22 +32906,22 @@
         <v>82</v>
       </c>
       <c r="H249" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I249" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J249" t="s" s="2">
         <v>92</v>
       </c>
-      <c r="I249" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="J249" t="s" s="2">
-        <v>80</v>
-      </c>
       <c r="K249" t="s" s="2">
-        <v>869</v>
+        <v>870</v>
       </c>
       <c r="L249" t="s" s="2">
-        <v>870</v>
+        <v>871</v>
       </c>
       <c r="M249" t="s" s="2">
-        <v>871</v>
+        <v>872</v>
       </c>
       <c r="N249" s="2"/>
       <c r="O249" s="2"/>
@@ -32954,7 +32972,7 @@
         <v>80</v>
       </c>
       <c r="AF249" t="s" s="2">
-        <v>868</v>
+        <v>869</v>
       </c>
       <c r="AG249" t="s" s="2">
         <v>81</v>
@@ -32963,32 +32981,150 @@
         <v>82</v>
       </c>
       <c r="AI249" t="s" s="2">
-        <v>80</v>
+        <v>866</v>
       </c>
       <c r="AJ249" t="s" s="2">
         <v>103</v>
       </c>
       <c r="AK249" t="s" s="2">
-        <v>872</v>
+        <v>80</v>
       </c>
       <c r="AL249" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM249" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN249" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AO249" t="s" s="2">
+        <v>868</v>
+      </c>
+      <c r="AP249" t="s" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="s" s="2">
         <v>873</v>
       </c>
-      <c r="AM249" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN249" t="s" s="2">
+      <c r="B250" t="s" s="2">
+        <v>873</v>
+      </c>
+      <c r="C250" s="2"/>
+      <c r="D250" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="E250" s="2"/>
+      <c r="F250" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G250" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="H250" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="I250" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J250" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="K250" t="s" s="2">
         <v>874</v>
       </c>
-      <c r="AO249" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AP249" t="s" s="2">
+      <c r="L250" t="s" s="2">
+        <v>875</v>
+      </c>
+      <c r="M250" t="s" s="2">
+        <v>876</v>
+      </c>
+      <c r="N250" s="2"/>
+      <c r="O250" s="2"/>
+      <c r="P250" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q250" s="2"/>
+      <c r="R250" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S250" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T250" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U250" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V250" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W250" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X250" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y250" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z250" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA250" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB250" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC250" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD250" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE250" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF250" t="s" s="2">
+        <v>873</v>
+      </c>
+      <c r="AG250" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH250" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AI250" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ250" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="AK250" t="s" s="2">
+        <v>877</v>
+      </c>
+      <c r="AL250" t="s" s="2">
+        <v>878</v>
+      </c>
+      <c r="AM250" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN250" t="s" s="2">
+        <v>879</v>
+      </c>
+      <c r="AO250" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AP250" t="s" s="2">
         <v>80</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AP249">
+  <autoFilter ref="A1:AP250">
     <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -32998,7 +33134,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI248">
+  <conditionalFormatting sqref="A2:AI249">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/branches/develop/StructureDefinition-mii-pr-diagnose-condition.xlsx
+++ b/branches/develop/StructureDefinition-mii-pr-diagnose-condition.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2027.0.0-dev</t>
+    <t>2027.0.0-ballot.rc1</t>
   </si>
   <si>
     <t>Name</t>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-15</t>
+    <t>2026-09-01</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/develop/StructureDefinition-mii-pr-diagnose-condition.xlsx
+++ b/branches/develop/StructureDefinition-mii-pr-diagnose-condition.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AP$250</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AP$232</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9544" uniqueCount="880">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8869" uniqueCount="828">
   <si>
     <t>Property</t>
   </si>
@@ -1871,7 +1871,7 @@
     <t>Beginn</t>
   </si>
   <si>
-    <t>Geschätztes oder tatsächliches Datum oder Zeitraum, an dem die Erkrankung begonnen hat, nach Meinung des Klinikers.</t>
+    <t>Geschätztes oder tatsächliches Datum oder Alter, an dem die Erkrankung begonnen hat.</t>
   </si>
   <si>
     <t>Age is generally used when the patient reports an age at which the Condition began to occur.</t>
@@ -1881,9 +1881,6 @@
 </t>
   </si>
   <si>
-    <t>closed</t>
-  </si>
-  <si>
     <t>KlinischRelevanterZeitraum</t>
   </si>
   <si>
@@ -1896,440 +1893,117 @@
     <t>FiveWs.init</t>
   </si>
   <si>
-    <t>Condition.onset[x]:onsetPeriod</t>
-  </si>
-  <si>
-    <t>onsetPeriod</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Period
+    <t>Condition.onset[x]:onsetDateTime</t>
+  </si>
+  <si>
+    <t>onsetDateTime</t>
+  </si>
+  <si>
+    <t>Beginn Datum</t>
+  </si>
+  <si>
+    <t>Das Datum, an dem die Erkrankung begonnen hat, nach Meinung des Klinikers.</t>
+  </si>
+  <si>
+    <t>KlinischRelevanterZeitraum.Zeitraum.von</t>
+  </si>
+  <si>
+    <t>Condition.onset[x]:onsetAge</t>
+  </si>
+  <si>
+    <t>onsetAge</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Age
 </t>
   </si>
   <si>
-    <t>Beginn Zeitraum</t>
-  </si>
-  <si>
-    <t>Der Zeitraum, in dem die Erkrankung begonnen hat, nach Meinung des Klinikers.</t>
-  </si>
-  <si>
-    <t>KlinischRelevanterZeitraum.Zeitraum</t>
-  </si>
-  <si>
-    <t>Condition.onset[x]:onsetPeriod.id</t>
+    <t>Erkrankungsbeginn als Alter</t>
+  </si>
+  <si>
+    <t>Estimated or actual date or date-time  the condition began, in the opinion of the clinician.</t>
+  </si>
+  <si>
+    <t>Condition.onset[x]:onsetAge.id</t>
   </si>
   <si>
     <t>Condition.onset[x].id</t>
   </si>
   <si>
-    <t>Condition.onset[x]:onsetPeriod.extension</t>
+    <t>Condition.onset[x]:onsetAge.extension</t>
   </si>
   <si>
     <t>Condition.onset[x].extension</t>
   </si>
   <si>
-    <t>Condition.onset[x]:onsetPeriod.start</t>
-  </si>
-  <si>
-    <t>Condition.onset[x].start</t>
-  </si>
-  <si>
-    <t>Starting time with inclusive boundary</t>
-  </si>
-  <si>
-    <t>The start of the period. The boundary is inclusive.</t>
-  </si>
-  <si>
-    <t>If the low element is missing, the meaning is that the low boundary is not known.</t>
-  </si>
-  <si>
-    <t>Period.start</t>
-  </si>
-  <si>
-    <t xml:space="preserve">per-1
-</t>
-  </si>
-  <si>
-    <t>KlinischRelevanterZeitraum.Zeitraum.von</t>
-  </si>
-  <si>
-    <t>DR.1</t>
-  </si>
-  <si>
-    <t>Condition.onset[x]:onsetPeriod.start.id</t>
-  </si>
-  <si>
-    <t>Condition.onset[x].start.id</t>
-  </si>
-  <si>
-    <t>xml:id (or equivalent in JSON)</t>
-  </si>
-  <si>
-    <t>unique id for the element within a resource (for internal references)</t>
-  </si>
-  <si>
-    <t>Condition.onset[x]:onsetPeriod.start.extension</t>
-  </si>
-  <si>
-    <t>Condition.onset[x].start.extension</t>
-  </si>
-  <si>
-    <t>Condition.onset[x]:onsetPeriod.start.extension:lebensphase-von</t>
-  </si>
-  <si>
-    <t>lebensphase-von</t>
+    <t>Condition.onset[x]:onsetAge.extension:Lebensphase-Beginn</t>
+  </si>
+  <si>
+    <t>Lebensphase-Beginn</t>
   </si>
   <si>
     <t xml:space="preserve">Extension {http://fhir.de/StructureDefinition/lebensphase}
 </t>
   </si>
   <si>
-    <t>Condition.onset[x]:onsetPeriod.start.extension:lebensphase-von.id</t>
-  </si>
-  <si>
-    <t>Condition.onset[x].start.extension.id</t>
-  </si>
-  <si>
-    <t>Condition.onset[x]:onsetPeriod.start.extension:lebensphase-von.extension</t>
-  </si>
-  <si>
-    <t>Condition.onset[x].start.extension.extension</t>
-  </si>
-  <si>
-    <t>Condition.onset[x]:onsetPeriod.start.extension:lebensphase-von.url</t>
-  </si>
-  <si>
-    <t>Condition.onset[x].start.extension.url</t>
+    <t>Lebensphase des Erkrankungsbeginns</t>
+  </si>
+  <si>
+    <t>Alternative Angabe, wenn genauere Eingrenzungen des Zeitraums nicht möglich sind, insbesondere im Kontext anamnestischer Diagnosen</t>
+  </si>
+  <si>
+    <t>Condition.onset[x]:onsetAge.extension:Lebensphase-Beginn.id</t>
+  </si>
+  <si>
+    <t>Condition.onset[x].extension.id</t>
+  </si>
+  <si>
+    <t>Condition.onset[x]:onsetAge.extension:Lebensphase-Beginn.extension</t>
+  </si>
+  <si>
+    <t>Condition.onset[x].extension.extension</t>
+  </si>
+  <si>
+    <t>Condition.onset[x]:onsetAge.extension:Lebensphase-Beginn.url</t>
+  </si>
+  <si>
+    <t>Condition.onset[x].extension.url</t>
   </si>
   <si>
     <t>http://fhir.de/StructureDefinition/lebensphase</t>
   </si>
   <si>
-    <t>Condition.onset[x]:onsetPeriod.start.extension:lebensphase-von.value[x]</t>
-  </si>
-  <si>
-    <t>Condition.onset[x].start.extension.value[x]</t>
+    <t>Condition.onset[x]:onsetAge.extension:Lebensphase-Beginn.value[x]</t>
+  </si>
+  <si>
+    <t>Condition.onset[x].extension.value[x]</t>
   </si>
   <si>
     <t>KlinischRelevanterZeitraum.Lebensphase.von</t>
   </si>
   <si>
-    <t>Condition.onset[x]:onsetPeriod.start.extension:lebensphase-von.value[x].id</t>
-  </si>
-  <si>
-    <t>Condition.onset[x].start.extension.value[x].id</t>
-  </si>
-  <si>
-    <t>Condition.onset[x]:onsetPeriod.start.extension:lebensphase-von.value[x].extension</t>
-  </si>
-  <si>
-    <t>Condition.onset[x].start.extension.value[x].extension</t>
-  </si>
-  <si>
-    <t>Condition.onset[x]:onsetPeriod.start.extension:lebensphase-von.value[x].coding</t>
-  </si>
-  <si>
-    <t>Condition.onset[x].start.extension.value[x].coding</t>
+    <t>Condition.onset[x]:onsetAge.extension:Lebensphase-Beginn.value[x].id</t>
+  </si>
+  <si>
+    <t>Condition.onset[x].extension.value[x].id</t>
+  </si>
+  <si>
+    <t>Condition.onset[x]:onsetAge.extension:Lebensphase-Beginn.value[x].extension</t>
+  </si>
+  <si>
+    <t>Condition.onset[x].extension.value[x].extension</t>
+  </si>
+  <si>
+    <t>Condition.onset[x]:onsetAge.extension:Lebensphase-Beginn.value[x].coding</t>
+  </si>
+  <si>
+    <t>Condition.onset[x].extension.value[x].coding</t>
   </si>
   <si>
     <t>Lebensphase</t>
   </si>
   <si>
     <t>http://fhir.de/ValueSet/lebensphase-de</t>
-  </si>
-  <si>
-    <t>Condition.onset[x]:onsetPeriod.start.extension:lebensphase-von.value[x].coding.id</t>
-  </si>
-  <si>
-    <t>Condition.onset[x].start.extension.value[x].coding.id</t>
-  </si>
-  <si>
-    <t>Condition.onset[x]:onsetPeriod.start.extension:lebensphase-von.value[x].coding.extension</t>
-  </si>
-  <si>
-    <t>Condition.onset[x].start.extension.value[x].coding.extension</t>
-  </si>
-  <si>
-    <t>Condition.onset[x]:onsetPeriod.start.extension:lebensphase-von.value[x].coding.system</t>
-  </si>
-  <si>
-    <t>Condition.onset[x].start.extension.value[x].coding.system</t>
-  </si>
-  <si>
-    <t>Condition.onset[x]:onsetPeriod.start.extension:lebensphase-von.value[x].coding.version</t>
-  </si>
-  <si>
-    <t>Condition.onset[x].start.extension.value[x].coding.version</t>
-  </si>
-  <si>
-    <t>Condition.onset[x]:onsetPeriod.start.extension:lebensphase-von.value[x].coding.code</t>
-  </si>
-  <si>
-    <t>Condition.onset[x].start.extension.value[x].coding.code</t>
-  </si>
-  <si>
-    <t>Condition.onset[x]:onsetPeriod.start.extension:lebensphase-von.value[x].coding.display</t>
-  </si>
-  <si>
-    <t>Condition.onset[x].start.extension.value[x].coding.display</t>
-  </si>
-  <si>
-    <t>Condition.onset[x]:onsetPeriod.start.extension:lebensphase-von.value[x].coding.userSelected</t>
-  </si>
-  <si>
-    <t>Condition.onset[x].start.extension.value[x].coding.userSelected</t>
-  </si>
-  <si>
-    <t>Condition.onset[x]:onsetPeriod.start.extension:lebensphase-von.value[x].text</t>
-  </si>
-  <si>
-    <t>Condition.onset[x].start.extension.value[x].text</t>
-  </si>
-  <si>
-    <t>Condition.onset[x]:onsetPeriod.start.value</t>
-  </si>
-  <si>
-    <t>Condition.onset[x].start.value</t>
-  </si>
-  <si>
-    <t>Primitive value for dateTime</t>
-  </si>
-  <si>
-    <t>The actual value</t>
-  </si>
-  <si>
-    <t>dateTime.value</t>
-  </si>
-  <si>
-    <t>Condition.onset[x]:onsetPeriod.end</t>
-  </si>
-  <si>
-    <t>Condition.onset[x].end</t>
-  </si>
-  <si>
-    <t>End time with inclusive boundary, if not ongoing</t>
-  </si>
-  <si>
-    <t>The end of the period. If the end of the period is missing, it means no end was known or planned at the time the instance was created. The start may be in the past, and the end date in the future, which means that period is expected/planned to end at that time.</t>
-  </si>
-  <si>
-    <t>The high value includes any matching date/time. i.e. 2012-02-03T10:00:00 is in a period that has an end value of 2012-02-03.</t>
-  </si>
-  <si>
-    <t>If the end of the period is missing, it means that the period is ongoing</t>
-  </si>
-  <si>
-    <t>Period.end</t>
-  </si>
-  <si>
-    <t>KlinischRelevanterZeitraum.Zeitraum.bis</t>
-  </si>
-  <si>
-    <t>DR.2</t>
-  </si>
-  <si>
-    <t>Condition.onset[x]:onsetPeriod.end.id</t>
-  </si>
-  <si>
-    <t>Condition.onset[x].end.id</t>
-  </si>
-  <si>
-    <t>Condition.onset[x]:onsetPeriod.end.extension</t>
-  </si>
-  <si>
-    <t>Condition.onset[x].end.extension</t>
-  </si>
-  <si>
-    <t>Condition.onset[x]:onsetPeriod.end.extension:lebensphase-bis</t>
-  </si>
-  <si>
-    <t>lebensphase-bis</t>
-  </si>
-  <si>
-    <t>Condition.onset[x]:onsetPeriod.end.extension:lebensphase-bis.id</t>
-  </si>
-  <si>
-    <t>Condition.onset[x].end.extension.id</t>
-  </si>
-  <si>
-    <t>Condition.onset[x]:onsetPeriod.end.extension:lebensphase-bis.extension</t>
-  </si>
-  <si>
-    <t>Condition.onset[x].end.extension.extension</t>
-  </si>
-  <si>
-    <t>Condition.onset[x]:onsetPeriod.end.extension:lebensphase-bis.url</t>
-  </si>
-  <si>
-    <t>Condition.onset[x].end.extension.url</t>
-  </si>
-  <si>
-    <t>Condition.onset[x]:onsetPeriod.end.extension:lebensphase-bis.value[x]</t>
-  </si>
-  <si>
-    <t>Condition.onset[x].end.extension.value[x]</t>
-  </si>
-  <si>
-    <t>KlinischRelevanterZeitraum.Lebensphase.bis</t>
-  </si>
-  <si>
-    <t>Condition.onset[x]:onsetPeriod.end.extension:lebensphase-bis.value[x].id</t>
-  </si>
-  <si>
-    <t>Condition.onset[x].end.extension.value[x].id</t>
-  </si>
-  <si>
-    <t>Condition.onset[x]:onsetPeriod.end.extension:lebensphase-bis.value[x].extension</t>
-  </si>
-  <si>
-    <t>Condition.onset[x].end.extension.value[x].extension</t>
-  </si>
-  <si>
-    <t>Condition.onset[x]:onsetPeriod.end.extension:lebensphase-bis.value[x].coding</t>
-  </si>
-  <si>
-    <t>Condition.onset[x].end.extension.value[x].coding</t>
-  </si>
-  <si>
-    <t>Condition.onset[x]:onsetPeriod.end.extension:lebensphase-bis.value[x].coding.id</t>
-  </si>
-  <si>
-    <t>Condition.onset[x].end.extension.value[x].coding.id</t>
-  </si>
-  <si>
-    <t>Condition.onset[x]:onsetPeriod.end.extension:lebensphase-bis.value[x].coding.extension</t>
-  </si>
-  <si>
-    <t>Condition.onset[x].end.extension.value[x].coding.extension</t>
-  </si>
-  <si>
-    <t>Condition.onset[x]:onsetPeriod.end.extension:lebensphase-bis.value[x].coding.system</t>
-  </si>
-  <si>
-    <t>Condition.onset[x].end.extension.value[x].coding.system</t>
-  </si>
-  <si>
-    <t>Condition.onset[x]:onsetPeriod.end.extension:lebensphase-bis.value[x].coding.version</t>
-  </si>
-  <si>
-    <t>Condition.onset[x].end.extension.value[x].coding.version</t>
-  </si>
-  <si>
-    <t>Condition.onset[x]:onsetPeriod.end.extension:lebensphase-bis.value[x].coding.code</t>
-  </si>
-  <si>
-    <t>Condition.onset[x].end.extension.value[x].coding.code</t>
-  </si>
-  <si>
-    <t>Condition.onset[x]:onsetPeriod.end.extension:lebensphase-bis.value[x].coding.display</t>
-  </si>
-  <si>
-    <t>Condition.onset[x].end.extension.value[x].coding.display</t>
-  </si>
-  <si>
-    <t>Condition.onset[x]:onsetPeriod.end.extension:lebensphase-bis.value[x].coding.userSelected</t>
-  </si>
-  <si>
-    <t>Condition.onset[x].end.extension.value[x].coding.userSelected</t>
-  </si>
-  <si>
-    <t>Condition.onset[x]:onsetPeriod.end.extension:lebensphase-bis.value[x].text</t>
-  </si>
-  <si>
-    <t>Condition.onset[x].end.extension.value[x].text</t>
-  </si>
-  <si>
-    <t>Condition.onset[x]:onsetPeriod.end.value</t>
-  </si>
-  <si>
-    <t>Condition.onset[x].end.value</t>
-  </si>
-  <si>
-    <t>Condition.onset[x]:onsetDateTime</t>
-  </si>
-  <si>
-    <t>onsetDateTime</t>
-  </si>
-  <si>
-    <t>Beginn Datum</t>
-  </si>
-  <si>
-    <t>Das Datum, an dem die Erkrankung begonnen hat, nach Meinung des Klinikers.</t>
-  </si>
-  <si>
-    <t>Condition.onset[x]:onsetAge</t>
-  </si>
-  <si>
-    <t>onsetAge</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Age
-</t>
-  </si>
-  <si>
-    <t>Erkrankungsbeginn als Alter</t>
-  </si>
-  <si>
-    <t>Estimated or actual date or date-time  the condition began, in the opinion of the clinician.</t>
-  </si>
-  <si>
-    <t>Condition.onset[x]:onsetAge.id</t>
-  </si>
-  <si>
-    <t>Condition.onset[x]:onsetAge.extension</t>
-  </si>
-  <si>
-    <t>Condition.onset[x]:onsetAge.extension:Lebensphase-Beginn</t>
-  </si>
-  <si>
-    <t>Lebensphase-Beginn</t>
-  </si>
-  <si>
-    <t>Lebensphase des Erkrankungsbeginns</t>
-  </si>
-  <si>
-    <t>Alternative Angabe, wenn genauere Eingrenzungen des Zeitraums nicht möglich sind, insbesondere im Kontext anamnestischer Diagnosen</t>
-  </si>
-  <si>
-    <t>Condition.onset[x]:onsetAge.extension:Lebensphase-Beginn.id</t>
-  </si>
-  <si>
-    <t>Condition.onset[x].extension.id</t>
-  </si>
-  <si>
-    <t>Condition.onset[x]:onsetAge.extension:Lebensphase-Beginn.extension</t>
-  </si>
-  <si>
-    <t>Condition.onset[x].extension.extension</t>
-  </si>
-  <si>
-    <t>Condition.onset[x]:onsetAge.extension:Lebensphase-Beginn.url</t>
-  </si>
-  <si>
-    <t>Condition.onset[x].extension.url</t>
-  </si>
-  <si>
-    <t>Condition.onset[x]:onsetAge.extension:Lebensphase-Beginn.value[x]</t>
-  </si>
-  <si>
-    <t>Condition.onset[x].extension.value[x]</t>
-  </si>
-  <si>
-    <t>Condition.onset[x]:onsetAge.extension:Lebensphase-Beginn.value[x].id</t>
-  </si>
-  <si>
-    <t>Condition.onset[x].extension.value[x].id</t>
-  </si>
-  <si>
-    <t>Condition.onset[x]:onsetAge.extension:Lebensphase-Beginn.value[x].extension</t>
-  </si>
-  <si>
-    <t>Condition.onset[x].extension.value[x].extension</t>
-  </si>
-  <si>
-    <t>Condition.onset[x]:onsetAge.extension:Lebensphase-Beginn.value[x].coding</t>
-  </si>
-  <si>
-    <t>Condition.onset[x].extension.value[x].coding</t>
   </si>
   <si>
     <t>Condition.onset[x]:onsetAge.extension:Lebensphase-Beginn.value[x].coding.id</t>
@@ -2505,14 +2179,10 @@
     <t>Condition.abatement[x]</t>
   </si>
   <si>
-    <t>dateTime
-AgePeriodRangestring</t>
-  </si>
-  <si>
-    <t>When in resolution/remission</t>
-  </si>
-  <si>
-    <t>The date or estimated date that the condition resolved or went into remission. This is called "abatement" because of the many overloaded connotations associated with "remission" or "resolution" - Conditions are never really resolved, but they can abate.</t>
+    <t>Ende</t>
+  </si>
+  <si>
+    <t>Geschätztes oder tatsächliches Datum oder Alter, an dem die Erkrankung beendet wurde.</t>
   </si>
   <si>
     <t>There is no explicit distinction between resolution and remission because in many cases the distinction is not clear. Age is generally used when the patient reports an age at which the Condition abated.  If there is no abatement element, it is unknown whether the condition has resolved or entered remission; applications and users should generally assume that the condition is still valid.  When abatementString exists, it implies the condition is abated.</t>
@@ -2523,6 +2193,177 @@
   </si>
   <si>
     <t>FiveWs.done[x]</t>
+  </si>
+  <si>
+    <t>Condition.abatement[x]:abatementDateTime</t>
+  </si>
+  <si>
+    <t>abatementDateTime</t>
+  </si>
+  <si>
+    <t>Ende Datum</t>
+  </si>
+  <si>
+    <t>Das Datum, an dem die Erkrankung beendet wurde.</t>
+  </si>
+  <si>
+    <t>KlinischRelevanterZeitraum.Zeitraum.bis</t>
+  </si>
+  <si>
+    <t>Condition.abatement[x]:abatementAge</t>
+  </si>
+  <si>
+    <t>abatementAge</t>
+  </si>
+  <si>
+    <t>Erkrankungsende als Alter</t>
+  </si>
+  <si>
+    <t>The date or estimated date that the condition resolved or went into remission. This is called "abatement" because of the many overloaded connotations associated with "remission" or "resolution" - Conditions are never really resolved, but they can abate.</t>
+  </si>
+  <si>
+    <t>Condition.abatement[x]:abatementAge.id</t>
+  </si>
+  <si>
+    <t>Condition.abatement[x].id</t>
+  </si>
+  <si>
+    <t>Condition.abatement[x]:abatementAge.extension</t>
+  </si>
+  <si>
+    <t>Condition.abatement[x].extension</t>
+  </si>
+  <si>
+    <t>Condition.abatement[x]:abatementAge.extension:Lebensphase-Ende</t>
+  </si>
+  <si>
+    <t>Lebensphase-Ende</t>
+  </si>
+  <si>
+    <t>Lebensphase des Erkrankungsendes</t>
+  </si>
+  <si>
+    <t>Condition.abatement[x]:abatementAge.extension:Lebensphase-Ende.id</t>
+  </si>
+  <si>
+    <t>Condition.abatement[x].extension.id</t>
+  </si>
+  <si>
+    <t>Condition.abatement[x]:abatementAge.extension:Lebensphase-Ende.extension</t>
+  </si>
+  <si>
+    <t>Condition.abatement[x].extension.extension</t>
+  </si>
+  <si>
+    <t>Condition.abatement[x]:abatementAge.extension:Lebensphase-Ende.url</t>
+  </si>
+  <si>
+    <t>Condition.abatement[x].extension.url</t>
+  </si>
+  <si>
+    <t>Condition.abatement[x]:abatementAge.extension:Lebensphase-Ende.value[x]</t>
+  </si>
+  <si>
+    <t>Condition.abatement[x].extension.value[x]</t>
+  </si>
+  <si>
+    <t>KlinischRelevanterZeitraum.Lebensphase.bis</t>
+  </si>
+  <si>
+    <t>Condition.abatement[x]:abatementAge.extension:Lebensphase-Ende.value[x].id</t>
+  </si>
+  <si>
+    <t>Condition.abatement[x].extension.value[x].id</t>
+  </si>
+  <si>
+    <t>Condition.abatement[x]:abatementAge.extension:Lebensphase-Ende.value[x].extension</t>
+  </si>
+  <si>
+    <t>Condition.abatement[x].extension.value[x].extension</t>
+  </si>
+  <si>
+    <t>Condition.abatement[x]:abatementAge.extension:Lebensphase-Ende.value[x].coding</t>
+  </si>
+  <si>
+    <t>Condition.abatement[x].extension.value[x].coding</t>
+  </si>
+  <si>
+    <t>Condition.abatement[x]:abatementAge.extension:Lebensphase-Ende.value[x].coding.id</t>
+  </si>
+  <si>
+    <t>Condition.abatement[x].extension.value[x].coding.id</t>
+  </si>
+  <si>
+    <t>Condition.abatement[x]:abatementAge.extension:Lebensphase-Ende.value[x].coding.extension</t>
+  </si>
+  <si>
+    <t>Condition.abatement[x].extension.value[x].coding.extension</t>
+  </si>
+  <si>
+    <t>Condition.abatement[x]:abatementAge.extension:Lebensphase-Ende.value[x].coding.system</t>
+  </si>
+  <si>
+    <t>Condition.abatement[x].extension.value[x].coding.system</t>
+  </si>
+  <si>
+    <t>Condition.abatement[x]:abatementAge.extension:Lebensphase-Ende.value[x].coding.version</t>
+  </si>
+  <si>
+    <t>Condition.abatement[x].extension.value[x].coding.version</t>
+  </si>
+  <si>
+    <t>Condition.abatement[x]:abatementAge.extension:Lebensphase-Ende.value[x].coding.code</t>
+  </si>
+  <si>
+    <t>Condition.abatement[x].extension.value[x].coding.code</t>
+  </si>
+  <si>
+    <t>Condition.abatement[x]:abatementAge.extension:Lebensphase-Ende.value[x].coding.display</t>
+  </si>
+  <si>
+    <t>Condition.abatement[x].extension.value[x].coding.display</t>
+  </si>
+  <si>
+    <t>Condition.abatement[x]:abatementAge.extension:Lebensphase-Ende.value[x].coding.userSelected</t>
+  </si>
+  <si>
+    <t>Condition.abatement[x].extension.value[x].coding.userSelected</t>
+  </si>
+  <si>
+    <t>Condition.abatement[x]:abatementAge.extension:Lebensphase-Ende.value[x].text</t>
+  </si>
+  <si>
+    <t>Condition.abatement[x].extension.value[x].text</t>
+  </si>
+  <si>
+    <t>Condition.abatement[x]:abatementAge.value</t>
+  </si>
+  <si>
+    <t>Condition.abatement[x].value</t>
+  </si>
+  <si>
+    <t>Condition.abatement[x]:abatementAge.comparator</t>
+  </si>
+  <si>
+    <t>Condition.abatement[x].comparator</t>
+  </si>
+  <si>
+    <t>Condition.abatement[x]:abatementAge.unit</t>
+  </si>
+  <si>
+    <t>Condition.abatement[x].unit</t>
+  </si>
+  <si>
+    <t>Condition.abatement[x]:abatementAge.system</t>
+  </si>
+  <si>
+    <t>Condition.abatement[x].system</t>
+  </si>
+  <si>
+    <t>Condition.abatement[x]:abatementAge.code</t>
+  </si>
+  <si>
+    <t>Condition.abatement[x].code</t>
   </si>
   <si>
     <t>Condition.recordedDate</t>
@@ -3067,11 +2908,11 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AP250"/>
+  <dimension ref="A1:AP232"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="79.40625" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="51.20703125" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="51.3046875" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="27.52734375" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="34.21875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="5.80859375" customWidth="true" bestFit="true"/>
@@ -22779,7 +22620,7 @@
         <v>80</v>
       </c>
       <c r="AE164" t="s" s="2">
-        <v>597</v>
+        <v>117</v>
       </c>
       <c r="AF164" t="s" s="2">
         <v>591</v>
@@ -22797,19 +22638,19 @@
         <v>103</v>
       </c>
       <c r="AK164" t="s" s="2">
+        <v>597</v>
+      </c>
+      <c r="AL164" t="s" s="2">
         <v>598</v>
       </c>
-      <c r="AL164" t="s" s="2">
+      <c r="AM164" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN164" t="s" s="2">
         <v>599</v>
       </c>
-      <c r="AM164" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN164" t="s" s="2">
+      <c r="AO164" t="s" s="2">
         <v>600</v>
-      </c>
-      <c r="AO164" t="s" s="2">
-        <v>601</v>
       </c>
       <c r="AP164" t="s" s="2">
         <v>80</v>
@@ -22817,13 +22658,13 @@
     </row>
     <row r="165">
       <c r="A165" t="s" s="2">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="B165" t="s" s="2">
         <v>591</v>
       </c>
       <c r="C165" t="s" s="2">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="D165" t="s" s="2">
         <v>80</v>
@@ -22845,13 +22686,13 @@
         <v>92</v>
       </c>
       <c r="K165" t="s" s="2">
+        <v>226</v>
+      </c>
+      <c r="L165" t="s" s="2">
+        <v>603</v>
+      </c>
+      <c r="M165" t="s" s="2">
         <v>604</v>
-      </c>
-      <c r="L165" t="s" s="2">
-        <v>605</v>
-      </c>
-      <c r="M165" t="s" s="2">
-        <v>606</v>
       </c>
       <c r="N165" t="s" s="2">
         <v>595</v>
@@ -22919,32 +22760,34 @@
         <v>103</v>
       </c>
       <c r="AK165" t="s" s="2">
+        <v>605</v>
+      </c>
+      <c r="AL165" t="s" s="2">
+        <v>598</v>
+      </c>
+      <c r="AM165" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN165" t="s" s="2">
+        <v>599</v>
+      </c>
+      <c r="AO165" t="s" s="2">
+        <v>600</v>
+      </c>
+      <c r="AP165" t="s" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="s" s="2">
+        <v>606</v>
+      </c>
+      <c r="B166" t="s" s="2">
+        <v>591</v>
+      </c>
+      <c r="C166" t="s" s="2">
         <v>607</v>
       </c>
-      <c r="AL165" t="s" s="2">
-        <v>599</v>
-      </c>
-      <c r="AM165" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN165" t="s" s="2">
-        <v>600</v>
-      </c>
-      <c r="AO165" t="s" s="2">
-        <v>601</v>
-      </c>
-      <c r="AP165" t="s" s="2">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="166" hidden="true">
-      <c r="A166" t="s" s="2">
-        <v>608</v>
-      </c>
-      <c r="B166" t="s" s="2">
-        <v>609</v>
-      </c>
-      <c r="C166" s="2"/>
       <c r="D166" t="s" s="2">
         <v>80</v>
       </c>
@@ -22956,24 +22799,26 @@
         <v>91</v>
       </c>
       <c r="H166" t="s" s="2">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="I166" t="s" s="2">
         <v>80</v>
       </c>
       <c r="J166" t="s" s="2">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="K166" t="s" s="2">
-        <v>105</v>
+        <v>608</v>
       </c>
       <c r="L166" t="s" s="2">
-        <v>106</v>
+        <v>609</v>
       </c>
       <c r="M166" t="s" s="2">
-        <v>107</v>
-      </c>
-      <c r="N166" s="2"/>
+        <v>610</v>
+      </c>
+      <c r="N166" t="s" s="2">
+        <v>595</v>
+      </c>
       <c r="O166" s="2"/>
       <c r="P166" t="s" s="2">
         <v>80</v>
@@ -23022,7 +22867,7 @@
         <v>80</v>
       </c>
       <c r="AF166" t="s" s="2">
-        <v>108</v>
+        <v>591</v>
       </c>
       <c r="AG166" t="s" s="2">
         <v>81</v>
@@ -23034,22 +22879,22 @@
         <v>80</v>
       </c>
       <c r="AJ166" t="s" s="2">
-        <v>80</v>
+        <v>103</v>
       </c>
       <c r="AK166" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL166" t="s" s="2">
-        <v>80</v>
+        <v>598</v>
       </c>
       <c r="AM166" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN166" t="s" s="2">
-        <v>80</v>
+        <v>599</v>
       </c>
       <c r="AO166" t="s" s="2">
-        <v>80</v>
+        <v>600</v>
       </c>
       <c r="AP166" t="s" s="2">
         <v>80</v>
@@ -23057,21 +22902,21 @@
     </row>
     <row r="167" hidden="true">
       <c r="A167" t="s" s="2">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="B167" t="s" s="2">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="C167" s="2"/>
       <c r="D167" t="s" s="2">
-        <v>110</v>
+        <v>80</v>
       </c>
       <c r="E167" s="2"/>
       <c r="F167" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G167" t="s" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="H167" t="s" s="2">
         <v>80</v>
@@ -23083,17 +22928,15 @@
         <v>80</v>
       </c>
       <c r="K167" t="s" s="2">
-        <v>111</v>
+        <v>105</v>
       </c>
       <c r="L167" t="s" s="2">
-        <v>112</v>
+        <v>106</v>
       </c>
       <c r="M167" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="N167" t="s" s="2">
-        <v>114</v>
-      </c>
+        <v>107</v>
+      </c>
+      <c r="N167" s="2"/>
       <c r="O167" s="2"/>
       <c r="P167" t="s" s="2">
         <v>80</v>
@@ -23130,31 +22973,31 @@
         <v>80</v>
       </c>
       <c r="AB167" t="s" s="2">
-        <v>115</v>
+        <v>80</v>
       </c>
       <c r="AC167" t="s" s="2">
-        <v>116</v>
+        <v>80</v>
       </c>
       <c r="AD167" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE167" t="s" s="2">
-        <v>117</v>
+        <v>80</v>
       </c>
       <c r="AF167" t="s" s="2">
-        <v>118</v>
+        <v>108</v>
       </c>
       <c r="AG167" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH167" t="s" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="AI167" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ167" t="s" s="2">
-        <v>119</v>
+        <v>80</v>
       </c>
       <c r="AK167" t="s" s="2">
         <v>80</v>
@@ -23175,44 +23018,44 @@
         <v>80</v>
       </c>
     </row>
-    <row r="168">
+    <row r="168" hidden="true">
       <c r="A168" t="s" s="2">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="B168" t="s" s="2">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="C168" s="2"/>
       <c r="D168" t="s" s="2">
-        <v>80</v>
+        <v>110</v>
       </c>
       <c r="E168" s="2"/>
       <c r="F168" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G168" t="s" s="2">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="H168" t="s" s="2">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="I168" t="s" s="2">
         <v>80</v>
       </c>
       <c r="J168" t="s" s="2">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="K168" t="s" s="2">
-        <v>226</v>
+        <v>111</v>
       </c>
       <c r="L168" t="s" s="2">
-        <v>614</v>
+        <v>112</v>
       </c>
       <c r="M168" t="s" s="2">
-        <v>615</v>
+        <v>113</v>
       </c>
       <c r="N168" t="s" s="2">
-        <v>616</v>
+        <v>114</v>
       </c>
       <c r="O168" s="2"/>
       <c r="P168" t="s" s="2">
@@ -23250,34 +23093,34 @@
         <v>80</v>
       </c>
       <c r="AB168" t="s" s="2">
-        <v>80</v>
+        <v>115</v>
       </c>
       <c r="AC168" t="s" s="2">
-        <v>80</v>
+        <v>116</v>
       </c>
       <c r="AD168" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE168" t="s" s="2">
-        <v>80</v>
+        <v>117</v>
       </c>
       <c r="AF168" t="s" s="2">
-        <v>617</v>
+        <v>118</v>
       </c>
       <c r="AG168" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH168" t="s" s="2">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="AI168" t="s" s="2">
-        <v>618</v>
+        <v>80</v>
       </c>
       <c r="AJ168" t="s" s="2">
-        <v>103</v>
+        <v>119</v>
       </c>
       <c r="AK168" t="s" s="2">
-        <v>619</v>
+        <v>80</v>
       </c>
       <c r="AL168" t="s" s="2">
         <v>80</v>
@@ -23286,7 +23129,7 @@
         <v>80</v>
       </c>
       <c r="AN168" t="s" s="2">
-        <v>620</v>
+        <v>80</v>
       </c>
       <c r="AO168" t="s" s="2">
         <v>80</v>
@@ -23297,12 +23140,14 @@
     </row>
     <row r="169" hidden="true">
       <c r="A169" t="s" s="2">
-        <v>621</v>
+        <v>615</v>
       </c>
       <c r="B169" t="s" s="2">
-        <v>622</v>
-      </c>
-      <c r="C169" s="2"/>
+        <v>614</v>
+      </c>
+      <c r="C169" t="s" s="2">
+        <v>616</v>
+      </c>
       <c r="D169" t="s" s="2">
         <v>80</v>
       </c>
@@ -23323,15 +23168,17 @@
         <v>80</v>
       </c>
       <c r="K169" t="s" s="2">
-        <v>105</v>
+        <v>617</v>
       </c>
       <c r="L169" t="s" s="2">
-        <v>623</v>
+        <v>618</v>
       </c>
       <c r="M169" t="s" s="2">
-        <v>624</v>
-      </c>
-      <c r="N169" s="2"/>
+        <v>381</v>
+      </c>
+      <c r="N169" t="s" s="2">
+        <v>619</v>
+      </c>
       <c r="O169" s="2"/>
       <c r="P169" t="s" s="2">
         <v>80</v>
@@ -23380,19 +23227,19 @@
         <v>80</v>
       </c>
       <c r="AF169" t="s" s="2">
-        <v>108</v>
+        <v>118</v>
       </c>
       <c r="AG169" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH169" t="s" s="2">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="AI169" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ169" t="s" s="2">
-        <v>80</v>
+        <v>119</v>
       </c>
       <c r="AK169" t="s" s="2">
         <v>80</v>
@@ -23415,10 +23262,10 @@
     </row>
     <row r="170" hidden="true">
       <c r="A170" t="s" s="2">
-        <v>625</v>
+        <v>620</v>
       </c>
       <c r="B170" t="s" s="2">
-        <v>626</v>
+        <v>621</v>
       </c>
       <c r="C170" s="2"/>
       <c r="D170" t="s" s="2">
@@ -23429,7 +23276,7 @@
         <v>81</v>
       </c>
       <c r="G170" t="s" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="H170" t="s" s="2">
         <v>80</v>
@@ -23441,13 +23288,13 @@
         <v>80</v>
       </c>
       <c r="K170" t="s" s="2">
-        <v>111</v>
+        <v>105</v>
       </c>
       <c r="L170" t="s" s="2">
-        <v>189</v>
+        <v>106</v>
       </c>
       <c r="M170" t="s" s="2">
-        <v>190</v>
+        <v>107</v>
       </c>
       <c r="N170" s="2"/>
       <c r="O170" s="2"/>
@@ -23486,29 +23333,31 @@
         <v>80</v>
       </c>
       <c r="AB170" t="s" s="2">
-        <v>115</v>
-      </c>
-      <c r="AC170" s="2"/>
+        <v>80</v>
+      </c>
+      <c r="AC170" t="s" s="2">
+        <v>80</v>
+      </c>
       <c r="AD170" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE170" t="s" s="2">
-        <v>117</v>
+        <v>80</v>
       </c>
       <c r="AF170" t="s" s="2">
-        <v>118</v>
+        <v>108</v>
       </c>
       <c r="AG170" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH170" t="s" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="AI170" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ170" t="s" s="2">
-        <v>119</v>
+        <v>80</v>
       </c>
       <c r="AK170" t="s" s="2">
         <v>80</v>
@@ -23529,28 +23378,26 @@
         <v>80</v>
       </c>
     </row>
-    <row r="171">
+    <row r="171" hidden="true">
       <c r="A171" t="s" s="2">
-        <v>627</v>
+        <v>622</v>
       </c>
       <c r="B171" t="s" s="2">
-        <v>626</v>
-      </c>
-      <c r="C171" t="s" s="2">
-        <v>628</v>
-      </c>
+        <v>623</v>
+      </c>
+      <c r="C171" s="2"/>
       <c r="D171" t="s" s="2">
-        <v>80</v>
+        <v>110</v>
       </c>
       <c r="E171" s="2"/>
       <c r="F171" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G171" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H171" t="s" s="2">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="I171" t="s" s="2">
         <v>80</v>
@@ -23559,15 +23406,17 @@
         <v>80</v>
       </c>
       <c r="K171" t="s" s="2">
-        <v>629</v>
+        <v>111</v>
       </c>
       <c r="L171" t="s" s="2">
-        <v>380</v>
+        <v>112</v>
       </c>
       <c r="M171" t="s" s="2">
-        <v>381</v>
-      </c>
-      <c r="N171" s="2"/>
+        <v>113</v>
+      </c>
+      <c r="N171" t="s" s="2">
+        <v>114</v>
+      </c>
       <c r="O171" s="2"/>
       <c r="P171" t="s" s="2">
         <v>80</v>
@@ -23604,16 +23453,16 @@
         <v>80</v>
       </c>
       <c r="AB171" t="s" s="2">
-        <v>80</v>
+        <v>115</v>
       </c>
       <c r="AC171" t="s" s="2">
-        <v>80</v>
+        <v>116</v>
       </c>
       <c r="AD171" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE171" t="s" s="2">
-        <v>80</v>
+        <v>117</v>
       </c>
       <c r="AF171" t="s" s="2">
         <v>118</v>
@@ -23649,12 +23498,12 @@
         <v>80</v>
       </c>
     </row>
-    <row r="172" hidden="true">
+    <row r="172">
       <c r="A172" t="s" s="2">
-        <v>630</v>
+        <v>624</v>
       </c>
       <c r="B172" t="s" s="2">
-        <v>631</v>
+        <v>625</v>
       </c>
       <c r="C172" s="2"/>
       <c r="D172" t="s" s="2">
@@ -23662,13 +23511,13 @@
       </c>
       <c r="E172" s="2"/>
       <c r="F172" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="G172" t="s" s="2">
         <v>91</v>
       </c>
       <c r="H172" t="s" s="2">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="I172" t="s" s="2">
         <v>80</v>
@@ -23677,22 +23526,24 @@
         <v>80</v>
       </c>
       <c r="K172" t="s" s="2">
-        <v>105</v>
+        <v>132</v>
       </c>
       <c r="L172" t="s" s="2">
-        <v>106</v>
+        <v>205</v>
       </c>
       <c r="M172" t="s" s="2">
-        <v>107</v>
-      </c>
-      <c r="N172" s="2"/>
+        <v>206</v>
+      </c>
+      <c r="N172" t="s" s="2">
+        <v>207</v>
+      </c>
       <c r="O172" s="2"/>
       <c r="P172" t="s" s="2">
         <v>80</v>
       </c>
       <c r="Q172" s="2"/>
       <c r="R172" t="s" s="2">
-        <v>80</v>
+        <v>626</v>
       </c>
       <c r="S172" t="s" s="2">
         <v>80</v>
@@ -23734,10 +23585,10 @@
         <v>80</v>
       </c>
       <c r="AF172" t="s" s="2">
-        <v>108</v>
+        <v>209</v>
       </c>
       <c r="AG172" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AH172" t="s" s="2">
         <v>91</v>
@@ -23767,26 +23618,26 @@
         <v>80</v>
       </c>
     </row>
-    <row r="173" hidden="true">
+    <row r="173">
       <c r="A173" t="s" s="2">
-        <v>632</v>
+        <v>627</v>
       </c>
       <c r="B173" t="s" s="2">
-        <v>633</v>
+        <v>628</v>
       </c>
       <c r="C173" s="2"/>
       <c r="D173" t="s" s="2">
-        <v>110</v>
+        <v>80</v>
       </c>
       <c r="E173" s="2"/>
       <c r="F173" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="G173" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H173" t="s" s="2">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="I173" t="s" s="2">
         <v>80</v>
@@ -23795,17 +23646,15 @@
         <v>80</v>
       </c>
       <c r="K173" t="s" s="2">
-        <v>111</v>
+        <v>241</v>
       </c>
       <c r="L173" t="s" s="2">
-        <v>112</v>
+        <v>213</v>
       </c>
       <c r="M173" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="N173" t="s" s="2">
-        <v>114</v>
-      </c>
+        <v>214</v>
+      </c>
+      <c r="N173" s="2"/>
       <c r="O173" s="2"/>
       <c r="P173" t="s" s="2">
         <v>80</v>
@@ -23842,34 +23691,34 @@
         <v>80</v>
       </c>
       <c r="AB173" t="s" s="2">
-        <v>115</v>
+        <v>80</v>
       </c>
       <c r="AC173" t="s" s="2">
-        <v>116</v>
+        <v>80</v>
       </c>
       <c r="AD173" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE173" t="s" s="2">
-        <v>117</v>
+        <v>80</v>
       </c>
       <c r="AF173" t="s" s="2">
-        <v>118</v>
+        <v>215</v>
       </c>
       <c r="AG173" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH173" t="s" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="AI173" t="s" s="2">
         <v>198</v>
       </c>
       <c r="AJ173" t="s" s="2">
-        <v>119</v>
+        <v>103</v>
       </c>
       <c r="AK173" t="s" s="2">
-        <v>80</v>
+        <v>629</v>
       </c>
       <c r="AL173" t="s" s="2">
         <v>80</v>
@@ -23887,12 +23736,12 @@
         <v>80</v>
       </c>
     </row>
-    <row r="174">
+    <row r="174" hidden="true">
       <c r="A174" t="s" s="2">
-        <v>634</v>
+        <v>630</v>
       </c>
       <c r="B174" t="s" s="2">
-        <v>635</v>
+        <v>631</v>
       </c>
       <c r="C174" s="2"/>
       <c r="D174" t="s" s="2">
@@ -23900,13 +23749,13 @@
       </c>
       <c r="E174" s="2"/>
       <c r="F174" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="G174" t="s" s="2">
         <v>91</v>
       </c>
       <c r="H174" t="s" s="2">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="I174" t="s" s="2">
         <v>80</v>
@@ -23915,24 +23764,22 @@
         <v>80</v>
       </c>
       <c r="K174" t="s" s="2">
-        <v>132</v>
+        <v>105</v>
       </c>
       <c r="L174" t="s" s="2">
-        <v>205</v>
+        <v>106</v>
       </c>
       <c r="M174" t="s" s="2">
-        <v>206</v>
-      </c>
-      <c r="N174" t="s" s="2">
-        <v>207</v>
-      </c>
+        <v>107</v>
+      </c>
+      <c r="N174" s="2"/>
       <c r="O174" s="2"/>
       <c r="P174" t="s" s="2">
         <v>80</v>
       </c>
       <c r="Q174" s="2"/>
       <c r="R174" t="s" s="2">
-        <v>636</v>
+        <v>80</v>
       </c>
       <c r="S174" t="s" s="2">
         <v>80</v>
@@ -23974,10 +23821,10 @@
         <v>80</v>
       </c>
       <c r="AF174" t="s" s="2">
-        <v>209</v>
+        <v>108</v>
       </c>
       <c r="AG174" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AH174" t="s" s="2">
         <v>91</v>
@@ -24007,26 +23854,26 @@
         <v>80</v>
       </c>
     </row>
-    <row r="175">
+    <row r="175" hidden="true">
       <c r="A175" t="s" s="2">
-        <v>637</v>
+        <v>632</v>
       </c>
       <c r="B175" t="s" s="2">
-        <v>638</v>
+        <v>633</v>
       </c>
       <c r="C175" s="2"/>
       <c r="D175" t="s" s="2">
-        <v>80</v>
+        <v>110</v>
       </c>
       <c r="E175" s="2"/>
       <c r="F175" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="G175" t="s" s="2">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="H175" t="s" s="2">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="I175" t="s" s="2">
         <v>80</v>
@@ -24035,15 +23882,17 @@
         <v>80</v>
       </c>
       <c r="K175" t="s" s="2">
-        <v>241</v>
+        <v>111</v>
       </c>
       <c r="L175" t="s" s="2">
-        <v>213</v>
+        <v>112</v>
       </c>
       <c r="M175" t="s" s="2">
-        <v>214</v>
-      </c>
-      <c r="N175" s="2"/>
+        <v>113</v>
+      </c>
+      <c r="N175" t="s" s="2">
+        <v>114</v>
+      </c>
       <c r="O175" s="2"/>
       <c r="P175" t="s" s="2">
         <v>80</v>
@@ -24080,34 +23929,34 @@
         <v>80</v>
       </c>
       <c r="AB175" t="s" s="2">
-        <v>80</v>
+        <v>115</v>
       </c>
       <c r="AC175" t="s" s="2">
-        <v>80</v>
+        <v>116</v>
       </c>
       <c r="AD175" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE175" t="s" s="2">
-        <v>80</v>
+        <v>117</v>
       </c>
       <c r="AF175" t="s" s="2">
-        <v>215</v>
+        <v>118</v>
       </c>
       <c r="AG175" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH175" t="s" s="2">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="AI175" t="s" s="2">
         <v>198</v>
       </c>
       <c r="AJ175" t="s" s="2">
-        <v>103</v>
+        <v>119</v>
       </c>
       <c r="AK175" t="s" s="2">
-        <v>639</v>
+        <v>80</v>
       </c>
       <c r="AL175" t="s" s="2">
         <v>80</v>
@@ -24125,12 +23974,12 @@
         <v>80</v>
       </c>
     </row>
-    <row r="176" hidden="true">
+    <row r="176">
       <c r="A176" t="s" s="2">
-        <v>640</v>
+        <v>634</v>
       </c>
       <c r="B176" t="s" s="2">
-        <v>641</v>
+        <v>635</v>
       </c>
       <c r="C176" s="2"/>
       <c r="D176" t="s" s="2">
@@ -24138,31 +23987,35 @@
       </c>
       <c r="E176" s="2"/>
       <c r="F176" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="G176" t="s" s="2">
         <v>91</v>
       </c>
       <c r="H176" t="s" s="2">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="I176" t="s" s="2">
         <v>80</v>
       </c>
       <c r="J176" t="s" s="2">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="K176" t="s" s="2">
-        <v>105</v>
+        <v>144</v>
       </c>
       <c r="L176" t="s" s="2">
-        <v>106</v>
+        <v>257</v>
       </c>
       <c r="M176" t="s" s="2">
-        <v>107</v>
-      </c>
-      <c r="N176" s="2"/>
-      <c r="O176" s="2"/>
+        <v>258</v>
+      </c>
+      <c r="N176" t="s" s="2">
+        <v>259</v>
+      </c>
+      <c r="O176" t="s" s="2">
+        <v>260</v>
+      </c>
       <c r="P176" t="s" s="2">
         <v>80</v>
       </c>
@@ -24186,13 +24039,13 @@
         <v>80</v>
       </c>
       <c r="X176" t="s" s="2">
-        <v>80</v>
+        <v>245</v>
       </c>
       <c r="Y176" t="s" s="2">
-        <v>80</v>
+        <v>636</v>
       </c>
       <c r="Z176" t="s" s="2">
-        <v>80</v>
+        <v>637</v>
       </c>
       <c r="AA176" t="s" s="2">
         <v>80</v>
@@ -24210,19 +24063,19 @@
         <v>80</v>
       </c>
       <c r="AF176" t="s" s="2">
-        <v>108</v>
+        <v>261</v>
       </c>
       <c r="AG176" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH176" t="s" s="2">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="AI176" t="s" s="2">
-        <v>80</v>
+        <v>198</v>
       </c>
       <c r="AJ176" t="s" s="2">
-        <v>80</v>
+        <v>103</v>
       </c>
       <c r="AK176" t="s" s="2">
         <v>80</v>
@@ -24234,7 +24087,7 @@
         <v>80</v>
       </c>
       <c r="AN176" t="s" s="2">
-        <v>80</v>
+        <v>262</v>
       </c>
       <c r="AO176" t="s" s="2">
         <v>80</v>
@@ -24245,21 +24098,21 @@
     </row>
     <row r="177" hidden="true">
       <c r="A177" t="s" s="2">
-        <v>642</v>
+        <v>638</v>
       </c>
       <c r="B177" t="s" s="2">
-        <v>643</v>
+        <v>639</v>
       </c>
       <c r="C177" s="2"/>
       <c r="D177" t="s" s="2">
-        <v>110</v>
+        <v>80</v>
       </c>
       <c r="E177" s="2"/>
       <c r="F177" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G177" t="s" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="H177" t="s" s="2">
         <v>80</v>
@@ -24271,17 +24124,15 @@
         <v>80</v>
       </c>
       <c r="K177" t="s" s="2">
-        <v>111</v>
+        <v>105</v>
       </c>
       <c r="L177" t="s" s="2">
-        <v>112</v>
+        <v>106</v>
       </c>
       <c r="M177" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="N177" t="s" s="2">
-        <v>114</v>
-      </c>
+        <v>107</v>
+      </c>
+      <c r="N177" s="2"/>
       <c r="O177" s="2"/>
       <c r="P177" t="s" s="2">
         <v>80</v>
@@ -24318,31 +24169,31 @@
         <v>80</v>
       </c>
       <c r="AB177" t="s" s="2">
-        <v>115</v>
+        <v>80</v>
       </c>
       <c r="AC177" t="s" s="2">
-        <v>116</v>
+        <v>80</v>
       </c>
       <c r="AD177" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE177" t="s" s="2">
-        <v>117</v>
+        <v>80</v>
       </c>
       <c r="AF177" t="s" s="2">
-        <v>118</v>
+        <v>108</v>
       </c>
       <c r="AG177" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH177" t="s" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="AI177" t="s" s="2">
-        <v>198</v>
+        <v>80</v>
       </c>
       <c r="AJ177" t="s" s="2">
-        <v>119</v>
+        <v>80</v>
       </c>
       <c r="AK177" t="s" s="2">
         <v>80</v>
@@ -24363,48 +24214,46 @@
         <v>80</v>
       </c>
     </row>
-    <row r="178">
+    <row r="178" hidden="true">
       <c r="A178" t="s" s="2">
-        <v>644</v>
+        <v>640</v>
       </c>
       <c r="B178" t="s" s="2">
-        <v>645</v>
+        <v>641</v>
       </c>
       <c r="C178" s="2"/>
       <c r="D178" t="s" s="2">
-        <v>80</v>
+        <v>110</v>
       </c>
       <c r="E178" s="2"/>
       <c r="F178" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="G178" t="s" s="2">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="H178" t="s" s="2">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="I178" t="s" s="2">
         <v>80</v>
       </c>
       <c r="J178" t="s" s="2">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="K178" t="s" s="2">
-        <v>144</v>
+        <v>111</v>
       </c>
       <c r="L178" t="s" s="2">
-        <v>257</v>
+        <v>112</v>
       </c>
       <c r="M178" t="s" s="2">
-        <v>258</v>
+        <v>113</v>
       </c>
       <c r="N178" t="s" s="2">
-        <v>259</v>
-      </c>
-      <c r="O178" t="s" s="2">
-        <v>260</v>
-      </c>
+        <v>114</v>
+      </c>
+      <c r="O178" s="2"/>
       <c r="P178" t="s" s="2">
         <v>80</v>
       </c>
@@ -24428,31 +24277,31 @@
         <v>80</v>
       </c>
       <c r="X178" t="s" s="2">
-        <v>245</v>
+        <v>80</v>
       </c>
       <c r="Y178" t="s" s="2">
-        <v>646</v>
+        <v>80</v>
       </c>
       <c r="Z178" t="s" s="2">
-        <v>647</v>
+        <v>80</v>
       </c>
       <c r="AA178" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AB178" t="s" s="2">
-        <v>80</v>
+        <v>115</v>
       </c>
       <c r="AC178" t="s" s="2">
-        <v>80</v>
+        <v>116</v>
       </c>
       <c r="AD178" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE178" t="s" s="2">
-        <v>80</v>
+        <v>117</v>
       </c>
       <c r="AF178" t="s" s="2">
-        <v>261</v>
+        <v>118</v>
       </c>
       <c r="AG178" t="s" s="2">
         <v>81</v>
@@ -24464,7 +24313,7 @@
         <v>198</v>
       </c>
       <c r="AJ178" t="s" s="2">
-        <v>103</v>
+        <v>119</v>
       </c>
       <c r="AK178" t="s" s="2">
         <v>80</v>
@@ -24476,7 +24325,7 @@
         <v>80</v>
       </c>
       <c r="AN178" t="s" s="2">
-        <v>262</v>
+        <v>80</v>
       </c>
       <c r="AO178" t="s" s="2">
         <v>80</v>
@@ -24485,12 +24334,12 @@
         <v>80</v>
       </c>
     </row>
-    <row r="179" hidden="true">
+    <row r="179">
       <c r="A179" t="s" s="2">
-        <v>648</v>
+        <v>642</v>
       </c>
       <c r="B179" t="s" s="2">
-        <v>649</v>
+        <v>643</v>
       </c>
       <c r="C179" s="2"/>
       <c r="D179" t="s" s="2">
@@ -24498,31 +24347,35 @@
       </c>
       <c r="E179" s="2"/>
       <c r="F179" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="G179" t="s" s="2">
         <v>91</v>
       </c>
       <c r="H179" t="s" s="2">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="I179" t="s" s="2">
         <v>80</v>
       </c>
       <c r="J179" t="s" s="2">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="K179" t="s" s="2">
-        <v>105</v>
+        <v>132</v>
       </c>
       <c r="L179" t="s" s="2">
-        <v>106</v>
+        <v>266</v>
       </c>
       <c r="M179" t="s" s="2">
-        <v>107</v>
-      </c>
-      <c r="N179" s="2"/>
-      <c r="O179" s="2"/>
+        <v>267</v>
+      </c>
+      <c r="N179" t="s" s="2">
+        <v>268</v>
+      </c>
+      <c r="O179" t="s" s="2">
+        <v>269</v>
+      </c>
       <c r="P179" t="s" s="2">
         <v>80</v>
       </c>
@@ -24570,7 +24423,7 @@
         <v>80</v>
       </c>
       <c r="AF179" t="s" s="2">
-        <v>108</v>
+        <v>270</v>
       </c>
       <c r="AG179" t="s" s="2">
         <v>81</v>
@@ -24579,10 +24432,10 @@
         <v>91</v>
       </c>
       <c r="AI179" t="s" s="2">
-        <v>80</v>
+        <v>198</v>
       </c>
       <c r="AJ179" t="s" s="2">
-        <v>80</v>
+        <v>103</v>
       </c>
       <c r="AK179" t="s" s="2">
         <v>80</v>
@@ -24594,7 +24447,7 @@
         <v>80</v>
       </c>
       <c r="AN179" t="s" s="2">
-        <v>80</v>
+        <v>271</v>
       </c>
       <c r="AO179" t="s" s="2">
         <v>80</v>
@@ -24605,21 +24458,21 @@
     </row>
     <row r="180" hidden="true">
       <c r="A180" t="s" s="2">
-        <v>650</v>
+        <v>644</v>
       </c>
       <c r="B180" t="s" s="2">
-        <v>651</v>
+        <v>645</v>
       </c>
       <c r="C180" s="2"/>
       <c r="D180" t="s" s="2">
-        <v>110</v>
+        <v>80</v>
       </c>
       <c r="E180" s="2"/>
       <c r="F180" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G180" t="s" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="H180" t="s" s="2">
         <v>80</v>
@@ -24628,19 +24481,19 @@
         <v>80</v>
       </c>
       <c r="J180" t="s" s="2">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="K180" t="s" s="2">
-        <v>111</v>
+        <v>105</v>
       </c>
       <c r="L180" t="s" s="2">
-        <v>112</v>
+        <v>273</v>
       </c>
       <c r="M180" t="s" s="2">
-        <v>113</v>
+        <v>274</v>
       </c>
       <c r="N180" t="s" s="2">
-        <v>114</v>
+        <v>275</v>
       </c>
       <c r="O180" s="2"/>
       <c r="P180" t="s" s="2">
@@ -24678,31 +24531,31 @@
         <v>80</v>
       </c>
       <c r="AB180" t="s" s="2">
-        <v>115</v>
+        <v>80</v>
       </c>
       <c r="AC180" t="s" s="2">
-        <v>116</v>
+        <v>80</v>
       </c>
       <c r="AD180" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE180" t="s" s="2">
-        <v>117</v>
+        <v>80</v>
       </c>
       <c r="AF180" t="s" s="2">
-        <v>118</v>
+        <v>276</v>
       </c>
       <c r="AG180" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH180" t="s" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="AI180" t="s" s="2">
         <v>198</v>
       </c>
       <c r="AJ180" t="s" s="2">
-        <v>119</v>
+        <v>103</v>
       </c>
       <c r="AK180" t="s" s="2">
         <v>80</v>
@@ -24714,7 +24567,7 @@
         <v>80</v>
       </c>
       <c r="AN180" t="s" s="2">
-        <v>80</v>
+        <v>277</v>
       </c>
       <c r="AO180" t="s" s="2">
         <v>80</v>
@@ -24725,10 +24578,10 @@
     </row>
     <row r="181">
       <c r="A181" t="s" s="2">
-        <v>652</v>
+        <v>646</v>
       </c>
       <c r="B181" t="s" s="2">
-        <v>653</v>
+        <v>647</v>
       </c>
       <c r="C181" s="2"/>
       <c r="D181" t="s" s="2">
@@ -24751,19 +24604,19 @@
         <v>92</v>
       </c>
       <c r="K181" t="s" s="2">
-        <v>132</v>
+        <v>166</v>
       </c>
       <c r="L181" t="s" s="2">
-        <v>266</v>
+        <v>279</v>
       </c>
       <c r="M181" t="s" s="2">
-        <v>267</v>
+        <v>280</v>
       </c>
       <c r="N181" t="s" s="2">
-        <v>268</v>
+        <v>402</v>
       </c>
       <c r="O181" t="s" s="2">
-        <v>269</v>
+        <v>281</v>
       </c>
       <c r="P181" t="s" s="2">
         <v>80</v>
@@ -24812,7 +24665,7 @@
         <v>80</v>
       </c>
       <c r="AF181" t="s" s="2">
-        <v>270</v>
+        <v>282</v>
       </c>
       <c r="AG181" t="s" s="2">
         <v>81</v>
@@ -24836,7 +24689,7 @@
         <v>80</v>
       </c>
       <c r="AN181" t="s" s="2">
-        <v>271</v>
+        <v>283</v>
       </c>
       <c r="AO181" t="s" s="2">
         <v>80</v>
@@ -24847,10 +24700,10 @@
     </row>
     <row r="182" hidden="true">
       <c r="A182" t="s" s="2">
-        <v>654</v>
+        <v>648</v>
       </c>
       <c r="B182" t="s" s="2">
-        <v>655</v>
+        <v>649</v>
       </c>
       <c r="C182" s="2"/>
       <c r="D182" t="s" s="2">
@@ -24876,15 +24729,17 @@
         <v>105</v>
       </c>
       <c r="L182" t="s" s="2">
-        <v>273</v>
+        <v>285</v>
       </c>
       <c r="M182" t="s" s="2">
-        <v>274</v>
+        <v>286</v>
       </c>
       <c r="N182" t="s" s="2">
-        <v>275</v>
-      </c>
-      <c r="O182" s="2"/>
+        <v>402</v>
+      </c>
+      <c r="O182" t="s" s="2">
+        <v>287</v>
+      </c>
       <c r="P182" t="s" s="2">
         <v>80</v>
       </c>
@@ -24932,7 +24787,7 @@
         <v>80</v>
       </c>
       <c r="AF182" t="s" s="2">
-        <v>276</v>
+        <v>288</v>
       </c>
       <c r="AG182" t="s" s="2">
         <v>81</v>
@@ -24956,7 +24811,7 @@
         <v>80</v>
       </c>
       <c r="AN182" t="s" s="2">
-        <v>277</v>
+        <v>289</v>
       </c>
       <c r="AO182" t="s" s="2">
         <v>80</v>
@@ -24965,12 +24820,12 @@
         <v>80</v>
       </c>
     </row>
-    <row r="183">
+    <row r="183" hidden="true">
       <c r="A183" t="s" s="2">
-        <v>656</v>
+        <v>650</v>
       </c>
       <c r="B183" t="s" s="2">
-        <v>657</v>
+        <v>651</v>
       </c>
       <c r="C183" s="2"/>
       <c r="D183" t="s" s="2">
@@ -24978,13 +24833,13 @@
       </c>
       <c r="E183" s="2"/>
       <c r="F183" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="G183" t="s" s="2">
         <v>91</v>
       </c>
       <c r="H183" t="s" s="2">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="I183" t="s" s="2">
         <v>80</v>
@@ -24993,19 +24848,19 @@
         <v>92</v>
       </c>
       <c r="K183" t="s" s="2">
-        <v>166</v>
+        <v>291</v>
       </c>
       <c r="L183" t="s" s="2">
-        <v>279</v>
+        <v>292</v>
       </c>
       <c r="M183" t="s" s="2">
-        <v>280</v>
+        <v>293</v>
       </c>
       <c r="N183" t="s" s="2">
-        <v>402</v>
+        <v>294</v>
       </c>
       <c r="O183" t="s" s="2">
-        <v>281</v>
+        <v>295</v>
       </c>
       <c r="P183" t="s" s="2">
         <v>80</v>
@@ -25054,7 +24909,7 @@
         <v>80</v>
       </c>
       <c r="AF183" t="s" s="2">
-        <v>282</v>
+        <v>296</v>
       </c>
       <c r="AG183" t="s" s="2">
         <v>81</v>
@@ -25078,7 +24933,7 @@
         <v>80</v>
       </c>
       <c r="AN183" t="s" s="2">
-        <v>283</v>
+        <v>297</v>
       </c>
       <c r="AO183" t="s" s="2">
         <v>80</v>
@@ -25089,10 +24944,10 @@
     </row>
     <row r="184" hidden="true">
       <c r="A184" t="s" s="2">
-        <v>658</v>
+        <v>652</v>
       </c>
       <c r="B184" t="s" s="2">
-        <v>659</v>
+        <v>653</v>
       </c>
       <c r="C184" s="2"/>
       <c r="D184" t="s" s="2">
@@ -25118,16 +24973,16 @@
         <v>105</v>
       </c>
       <c r="L184" t="s" s="2">
-        <v>285</v>
+        <v>299</v>
       </c>
       <c r="M184" t="s" s="2">
-        <v>286</v>
+        <v>300</v>
       </c>
       <c r="N184" t="s" s="2">
-        <v>402</v>
+        <v>301</v>
       </c>
       <c r="O184" t="s" s="2">
-        <v>287</v>
+        <v>302</v>
       </c>
       <c r="P184" t="s" s="2">
         <v>80</v>
@@ -25176,7 +25031,7 @@
         <v>80</v>
       </c>
       <c r="AF184" t="s" s="2">
-        <v>288</v>
+        <v>303</v>
       </c>
       <c r="AG184" t="s" s="2">
         <v>81</v>
@@ -25200,7 +25055,7 @@
         <v>80</v>
       </c>
       <c r="AN184" t="s" s="2">
-        <v>289</v>
+        <v>304</v>
       </c>
       <c r="AO184" t="s" s="2">
         <v>80</v>
@@ -25211,10 +25066,10 @@
     </row>
     <row r="185" hidden="true">
       <c r="A185" t="s" s="2">
-        <v>660</v>
+        <v>654</v>
       </c>
       <c r="B185" t="s" s="2">
-        <v>661</v>
+        <v>655</v>
       </c>
       <c r="C185" s="2"/>
       <c r="D185" t="s" s="2">
@@ -25237,19 +25092,19 @@
         <v>92</v>
       </c>
       <c r="K185" t="s" s="2">
-        <v>291</v>
+        <v>656</v>
       </c>
       <c r="L185" t="s" s="2">
-        <v>292</v>
+        <v>657</v>
       </c>
       <c r="M185" t="s" s="2">
-        <v>293</v>
+        <v>658</v>
       </c>
       <c r="N185" t="s" s="2">
-        <v>294</v>
+        <v>659</v>
       </c>
       <c r="O185" t="s" s="2">
-        <v>295</v>
+        <v>660</v>
       </c>
       <c r="P185" t="s" s="2">
         <v>80</v>
@@ -25298,7 +25153,7 @@
         <v>80</v>
       </c>
       <c r="AF185" t="s" s="2">
-        <v>296</v>
+        <v>661</v>
       </c>
       <c r="AG185" t="s" s="2">
         <v>81</v>
@@ -25307,7 +25162,7 @@
         <v>91</v>
       </c>
       <c r="AI185" t="s" s="2">
-        <v>198</v>
+        <v>80</v>
       </c>
       <c r="AJ185" t="s" s="2">
         <v>103</v>
@@ -25322,7 +25177,7 @@
         <v>80</v>
       </c>
       <c r="AN185" t="s" s="2">
-        <v>297</v>
+        <v>662</v>
       </c>
       <c r="AO185" t="s" s="2">
         <v>80</v>
@@ -25333,10 +25188,10 @@
     </row>
     <row r="186" hidden="true">
       <c r="A186" t="s" s="2">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="B186" t="s" s="2">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="C186" s="2"/>
       <c r="D186" t="s" s="2">
@@ -25353,30 +25208,30 @@
         <v>80</v>
       </c>
       <c r="I186" t="s" s="2">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="J186" t="s" s="2">
         <v>92</v>
       </c>
       <c r="K186" t="s" s="2">
-        <v>105</v>
+        <v>166</v>
       </c>
       <c r="L186" t="s" s="2">
-        <v>299</v>
+        <v>665</v>
       </c>
       <c r="M186" t="s" s="2">
-        <v>300</v>
-      </c>
-      <c r="N186" t="s" s="2">
-        <v>301</v>
-      </c>
+        <v>666</v>
+      </c>
+      <c r="N186" s="2"/>
       <c r="O186" t="s" s="2">
-        <v>302</v>
+        <v>667</v>
       </c>
       <c r="P186" t="s" s="2">
         <v>80</v>
       </c>
-      <c r="Q186" s="2"/>
+      <c r="Q186" t="s" s="2">
+        <v>668</v>
+      </c>
       <c r="R186" t="s" s="2">
         <v>80</v>
       </c>
@@ -25396,13 +25251,13 @@
         <v>80</v>
       </c>
       <c r="X186" t="s" s="2">
-        <v>80</v>
+        <v>245</v>
       </c>
       <c r="Y186" t="s" s="2">
-        <v>80</v>
+        <v>669</v>
       </c>
       <c r="Z186" t="s" s="2">
-        <v>80</v>
+        <v>670</v>
       </c>
       <c r="AA186" t="s" s="2">
         <v>80</v>
@@ -25420,7 +25275,7 @@
         <v>80</v>
       </c>
       <c r="AF186" t="s" s="2">
-        <v>303</v>
+        <v>671</v>
       </c>
       <c r="AG186" t="s" s="2">
         <v>81</v>
@@ -25429,7 +25284,7 @@
         <v>91</v>
       </c>
       <c r="AI186" t="s" s="2">
-        <v>198</v>
+        <v>80</v>
       </c>
       <c r="AJ186" t="s" s="2">
         <v>103</v>
@@ -25444,7 +25299,7 @@
         <v>80</v>
       </c>
       <c r="AN186" t="s" s="2">
-        <v>304</v>
+        <v>672</v>
       </c>
       <c r="AO186" t="s" s="2">
         <v>80</v>
@@ -25455,10 +25310,10 @@
     </row>
     <row r="187" hidden="true">
       <c r="A187" t="s" s="2">
-        <v>664</v>
+        <v>673</v>
       </c>
       <c r="B187" t="s" s="2">
-        <v>665</v>
+        <v>674</v>
       </c>
       <c r="C187" s="2"/>
       <c r="D187" t="s" s="2">
@@ -25478,19 +25333,21 @@
         <v>80</v>
       </c>
       <c r="J187" t="s" s="2">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="K187" t="s" s="2">
-        <v>226</v>
+        <v>105</v>
       </c>
       <c r="L187" t="s" s="2">
-        <v>666</v>
+        <v>675</v>
       </c>
       <c r="M187" t="s" s="2">
-        <v>667</v>
+        <v>676</v>
       </c>
       <c r="N187" s="2"/>
-      <c r="O187" s="2"/>
+      <c r="O187" t="s" s="2">
+        <v>677</v>
+      </c>
       <c r="P187" t="s" s="2">
         <v>80</v>
       </c>
@@ -25538,7 +25395,7 @@
         <v>80</v>
       </c>
       <c r="AF187" t="s" s="2">
-        <v>668</v>
+        <v>678</v>
       </c>
       <c r="AG187" t="s" s="2">
         <v>81</v>
@@ -25550,7 +25407,7 @@
         <v>80</v>
       </c>
       <c r="AJ187" t="s" s="2">
-        <v>80</v>
+        <v>103</v>
       </c>
       <c r="AK187" t="s" s="2">
         <v>80</v>
@@ -25562,7 +25419,7 @@
         <v>80</v>
       </c>
       <c r="AN187" t="s" s="2">
-        <v>80</v>
+        <v>679</v>
       </c>
       <c r="AO187" t="s" s="2">
         <v>80</v>
@@ -25571,12 +25428,12 @@
         <v>80</v>
       </c>
     </row>
-    <row r="188">
+    <row r="188" hidden="true">
       <c r="A188" t="s" s="2">
-        <v>669</v>
+        <v>680</v>
       </c>
       <c r="B188" t="s" s="2">
-        <v>670</v>
+        <v>681</v>
       </c>
       <c r="C188" s="2"/>
       <c r="D188" t="s" s="2">
@@ -25590,7 +25447,7 @@
         <v>91</v>
       </c>
       <c r="H188" t="s" s="2">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="I188" t="s" s="2">
         <v>80</v>
@@ -25599,24 +25456,22 @@
         <v>92</v>
       </c>
       <c r="K188" t="s" s="2">
-        <v>226</v>
+        <v>132</v>
       </c>
       <c r="L188" t="s" s="2">
-        <v>671</v>
+        <v>682</v>
       </c>
       <c r="M188" t="s" s="2">
-        <v>672</v>
-      </c>
-      <c r="N188" t="s" s="2">
-        <v>673</v>
-      </c>
-      <c r="O188" s="2"/>
+        <v>683</v>
+      </c>
+      <c r="N188" s="2"/>
+      <c r="O188" t="s" s="2">
+        <v>684</v>
+      </c>
       <c r="P188" t="s" s="2">
         <v>80</v>
       </c>
-      <c r="Q188" t="s" s="2">
-        <v>674</v>
-      </c>
+      <c r="Q188" s="2"/>
       <c r="R188" t="s" s="2">
         <v>80</v>
       </c>
@@ -25660,7 +25515,7 @@
         <v>80</v>
       </c>
       <c r="AF188" t="s" s="2">
-        <v>675</v>
+        <v>685</v>
       </c>
       <c r="AG188" t="s" s="2">
         <v>81</v>
@@ -25669,13 +25524,13 @@
         <v>91</v>
       </c>
       <c r="AI188" t="s" s="2">
-        <v>618</v>
+        <v>686</v>
       </c>
       <c r="AJ188" t="s" s="2">
         <v>103</v>
       </c>
       <c r="AK188" t="s" s="2">
-        <v>676</v>
+        <v>80</v>
       </c>
       <c r="AL188" t="s" s="2">
         <v>80</v>
@@ -25684,7 +25539,7 @@
         <v>80</v>
       </c>
       <c r="AN188" t="s" s="2">
-        <v>677</v>
+        <v>679</v>
       </c>
       <c r="AO188" t="s" s="2">
         <v>80</v>
@@ -25695,10 +25550,10 @@
     </row>
     <row r="189" hidden="true">
       <c r="A189" t="s" s="2">
-        <v>678</v>
+        <v>687</v>
       </c>
       <c r="B189" t="s" s="2">
-        <v>679</v>
+        <v>688</v>
       </c>
       <c r="C189" s="2"/>
       <c r="D189" t="s" s="2">
@@ -25718,19 +25573,23 @@
         <v>80</v>
       </c>
       <c r="J189" t="s" s="2">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="K189" t="s" s="2">
-        <v>105</v>
+        <v>166</v>
       </c>
       <c r="L189" t="s" s="2">
-        <v>623</v>
+        <v>689</v>
       </c>
       <c r="M189" t="s" s="2">
-        <v>624</v>
-      </c>
-      <c r="N189" s="2"/>
-      <c r="O189" s="2"/>
+        <v>690</v>
+      </c>
+      <c r="N189" t="s" s="2">
+        <v>691</v>
+      </c>
+      <c r="O189" t="s" s="2">
+        <v>692</v>
+      </c>
       <c r="P189" t="s" s="2">
         <v>80</v>
       </c>
@@ -25778,7 +25637,7 @@
         <v>80</v>
       </c>
       <c r="AF189" t="s" s="2">
-        <v>108</v>
+        <v>693</v>
       </c>
       <c r="AG189" t="s" s="2">
         <v>81</v>
@@ -25790,7 +25649,7 @@
         <v>80</v>
       </c>
       <c r="AJ189" t="s" s="2">
-        <v>80</v>
+        <v>103</v>
       </c>
       <c r="AK189" t="s" s="2">
         <v>80</v>
@@ -25802,7 +25661,7 @@
         <v>80</v>
       </c>
       <c r="AN189" t="s" s="2">
-        <v>80</v>
+        <v>679</v>
       </c>
       <c r="AO189" t="s" s="2">
         <v>80</v>
@@ -25813,10 +25672,10 @@
     </row>
     <row r="190" hidden="true">
       <c r="A190" t="s" s="2">
-        <v>680</v>
+        <v>694</v>
       </c>
       <c r="B190" t="s" s="2">
-        <v>681</v>
+        <v>694</v>
       </c>
       <c r="C190" s="2"/>
       <c r="D190" t="s" s="2">
@@ -25827,10 +25686,10 @@
         <v>81</v>
       </c>
       <c r="G190" t="s" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="H190" t="s" s="2">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="I190" t="s" s="2">
         <v>80</v>
@@ -25839,15 +25698,17 @@
         <v>80</v>
       </c>
       <c r="K190" t="s" s="2">
-        <v>111</v>
+        <v>592</v>
       </c>
       <c r="L190" t="s" s="2">
-        <v>189</v>
+        <v>695</v>
       </c>
       <c r="M190" t="s" s="2">
-        <v>190</v>
-      </c>
-      <c r="N190" s="2"/>
+        <v>696</v>
+      </c>
+      <c r="N190" t="s" s="2">
+        <v>697</v>
+      </c>
       <c r="O190" s="2"/>
       <c r="P190" t="s" s="2">
         <v>80</v>
@@ -25884,7 +25745,7 @@
         <v>80</v>
       </c>
       <c r="AB190" t="s" s="2">
-        <v>115</v>
+        <v>596</v>
       </c>
       <c r="AC190" s="2"/>
       <c r="AD190" t="s" s="2">
@@ -25894,22 +25755,22 @@
         <v>117</v>
       </c>
       <c r="AF190" t="s" s="2">
-        <v>118</v>
+        <v>694</v>
       </c>
       <c r="AG190" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH190" t="s" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="AI190" t="s" s="2">
-        <v>80</v>
+        <v>698</v>
       </c>
       <c r="AJ190" t="s" s="2">
-        <v>119</v>
+        <v>103</v>
       </c>
       <c r="AK190" t="s" s="2">
-        <v>80</v>
+        <v>597</v>
       </c>
       <c r="AL190" t="s" s="2">
         <v>80</v>
@@ -25921,7 +25782,7 @@
         <v>80</v>
       </c>
       <c r="AO190" t="s" s="2">
-        <v>80</v>
+        <v>699</v>
       </c>
       <c r="AP190" t="s" s="2">
         <v>80</v>
@@ -25929,13 +25790,13 @@
     </row>
     <row r="191">
       <c r="A191" t="s" s="2">
-        <v>682</v>
+        <v>700</v>
       </c>
       <c r="B191" t="s" s="2">
-        <v>681</v>
+        <v>694</v>
       </c>
       <c r="C191" t="s" s="2">
-        <v>683</v>
+        <v>701</v>
       </c>
       <c r="D191" t="s" s="2">
         <v>80</v>
@@ -25957,15 +25818,17 @@
         <v>80</v>
       </c>
       <c r="K191" t="s" s="2">
-        <v>629</v>
+        <v>226</v>
       </c>
       <c r="L191" t="s" s="2">
-        <v>380</v>
+        <v>702</v>
       </c>
       <c r="M191" t="s" s="2">
-        <v>381</v>
-      </c>
-      <c r="N191" s="2"/>
+        <v>703</v>
+      </c>
+      <c r="N191" t="s" s="2">
+        <v>697</v>
+      </c>
       <c r="O191" s="2"/>
       <c r="P191" t="s" s="2">
         <v>80</v>
@@ -26014,22 +25877,22 @@
         <v>80</v>
       </c>
       <c r="AF191" t="s" s="2">
-        <v>118</v>
+        <v>694</v>
       </c>
       <c r="AG191" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH191" t="s" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="AI191" t="s" s="2">
-        <v>198</v>
+        <v>698</v>
       </c>
       <c r="AJ191" t="s" s="2">
-        <v>119</v>
+        <v>103</v>
       </c>
       <c r="AK191" t="s" s="2">
-        <v>80</v>
+        <v>704</v>
       </c>
       <c r="AL191" t="s" s="2">
         <v>80</v>
@@ -26041,20 +25904,22 @@
         <v>80</v>
       </c>
       <c r="AO191" t="s" s="2">
-        <v>80</v>
+        <v>699</v>
       </c>
       <c r="AP191" t="s" s="2">
         <v>80</v>
       </c>
     </row>
-    <row r="192" hidden="true">
+    <row r="192">
       <c r="A192" t="s" s="2">
-        <v>684</v>
+        <v>705</v>
       </c>
       <c r="B192" t="s" s="2">
-        <v>685</v>
-      </c>
-      <c r="C192" s="2"/>
+        <v>694</v>
+      </c>
+      <c r="C192" t="s" s="2">
+        <v>706</v>
+      </c>
       <c r="D192" t="s" s="2">
         <v>80</v>
       </c>
@@ -26066,7 +25931,7 @@
         <v>91</v>
       </c>
       <c r="H192" t="s" s="2">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="I192" t="s" s="2">
         <v>80</v>
@@ -26075,15 +25940,17 @@
         <v>80</v>
       </c>
       <c r="K192" t="s" s="2">
-        <v>105</v>
+        <v>608</v>
       </c>
       <c r="L192" t="s" s="2">
-        <v>106</v>
+        <v>707</v>
       </c>
       <c r="M192" t="s" s="2">
-        <v>107</v>
-      </c>
-      <c r="N192" s="2"/>
+        <v>708</v>
+      </c>
+      <c r="N192" t="s" s="2">
+        <v>697</v>
+      </c>
       <c r="O192" s="2"/>
       <c r="P192" t="s" s="2">
         <v>80</v>
@@ -26132,7 +25999,7 @@
         <v>80</v>
       </c>
       <c r="AF192" t="s" s="2">
-        <v>108</v>
+        <v>694</v>
       </c>
       <c r="AG192" t="s" s="2">
         <v>81</v>
@@ -26141,10 +26008,10 @@
         <v>91</v>
       </c>
       <c r="AI192" t="s" s="2">
-        <v>80</v>
+        <v>698</v>
       </c>
       <c r="AJ192" t="s" s="2">
-        <v>80</v>
+        <v>103</v>
       </c>
       <c r="AK192" t="s" s="2">
         <v>80</v>
@@ -26159,7 +26026,7 @@
         <v>80</v>
       </c>
       <c r="AO192" t="s" s="2">
-        <v>80</v>
+        <v>699</v>
       </c>
       <c r="AP192" t="s" s="2">
         <v>80</v>
@@ -26167,21 +26034,21 @@
     </row>
     <row r="193" hidden="true">
       <c r="A193" t="s" s="2">
-        <v>686</v>
+        <v>709</v>
       </c>
       <c r="B193" t="s" s="2">
-        <v>687</v>
+        <v>710</v>
       </c>
       <c r="C193" s="2"/>
       <c r="D193" t="s" s="2">
-        <v>110</v>
+        <v>80</v>
       </c>
       <c r="E193" s="2"/>
       <c r="F193" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G193" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H193" t="s" s="2">
         <v>80</v>
@@ -26193,17 +26060,15 @@
         <v>80</v>
       </c>
       <c r="K193" t="s" s="2">
-        <v>111</v>
+        <v>105</v>
       </c>
       <c r="L193" t="s" s="2">
-        <v>112</v>
+        <v>106</v>
       </c>
       <c r="M193" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="N193" t="s" s="2">
-        <v>114</v>
-      </c>
+        <v>107</v>
+      </c>
+      <c r="N193" s="2"/>
       <c r="O193" s="2"/>
       <c r="P193" t="s" s="2">
         <v>80</v>
@@ -26240,31 +26105,31 @@
         <v>80</v>
       </c>
       <c r="AB193" t="s" s="2">
-        <v>115</v>
+        <v>80</v>
       </c>
       <c r="AC193" t="s" s="2">
-        <v>116</v>
+        <v>80</v>
       </c>
       <c r="AD193" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE193" t="s" s="2">
-        <v>117</v>
+        <v>80</v>
       </c>
       <c r="AF193" t="s" s="2">
-        <v>118</v>
+        <v>108</v>
       </c>
       <c r="AG193" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH193" t="s" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="AI193" t="s" s="2">
-        <v>198</v>
+        <v>80</v>
       </c>
       <c r="AJ193" t="s" s="2">
-        <v>119</v>
+        <v>80</v>
       </c>
       <c r="AK193" t="s" s="2">
         <v>80</v>
@@ -26285,26 +26150,26 @@
         <v>80</v>
       </c>
     </row>
-    <row r="194">
+    <row r="194" hidden="true">
       <c r="A194" t="s" s="2">
-        <v>688</v>
+        <v>711</v>
       </c>
       <c r="B194" t="s" s="2">
-        <v>689</v>
+        <v>712</v>
       </c>
       <c r="C194" s="2"/>
       <c r="D194" t="s" s="2">
-        <v>80</v>
+        <v>110</v>
       </c>
       <c r="E194" s="2"/>
       <c r="F194" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="G194" t="s" s="2">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="H194" t="s" s="2">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="I194" t="s" s="2">
         <v>80</v>
@@ -26313,16 +26178,16 @@
         <v>80</v>
       </c>
       <c r="K194" t="s" s="2">
-        <v>132</v>
+        <v>111</v>
       </c>
       <c r="L194" t="s" s="2">
-        <v>205</v>
+        <v>112</v>
       </c>
       <c r="M194" t="s" s="2">
-        <v>206</v>
+        <v>113</v>
       </c>
       <c r="N194" t="s" s="2">
-        <v>207</v>
+        <v>114</v>
       </c>
       <c r="O194" s="2"/>
       <c r="P194" t="s" s="2">
@@ -26330,7 +26195,7 @@
       </c>
       <c r="Q194" s="2"/>
       <c r="R194" t="s" s="2">
-        <v>636</v>
+        <v>80</v>
       </c>
       <c r="S194" t="s" s="2">
         <v>80</v>
@@ -26360,31 +26225,31 @@
         <v>80</v>
       </c>
       <c r="AB194" t="s" s="2">
-        <v>80</v>
+        <v>115</v>
       </c>
       <c r="AC194" t="s" s="2">
-        <v>80</v>
+        <v>116</v>
       </c>
       <c r="AD194" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE194" t="s" s="2">
-        <v>80</v>
+        <v>117</v>
       </c>
       <c r="AF194" t="s" s="2">
-        <v>209</v>
+        <v>118</v>
       </c>
       <c r="AG194" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AH194" t="s" s="2">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="AI194" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ194" t="s" s="2">
-        <v>80</v>
+        <v>119</v>
       </c>
       <c r="AK194" t="s" s="2">
         <v>80</v>
@@ -26405,26 +26270,28 @@
         <v>80</v>
       </c>
     </row>
-    <row r="195">
+    <row r="195" hidden="true">
       <c r="A195" t="s" s="2">
-        <v>690</v>
+        <v>713</v>
       </c>
       <c r="B195" t="s" s="2">
-        <v>691</v>
-      </c>
-      <c r="C195" s="2"/>
+        <v>712</v>
+      </c>
+      <c r="C195" t="s" s="2">
+        <v>714</v>
+      </c>
       <c r="D195" t="s" s="2">
         <v>80</v>
       </c>
       <c r="E195" s="2"/>
       <c r="F195" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="G195" t="s" s="2">
         <v>91</v>
       </c>
       <c r="H195" t="s" s="2">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="I195" t="s" s="2">
         <v>80</v>
@@ -26433,15 +26300,17 @@
         <v>80</v>
       </c>
       <c r="K195" t="s" s="2">
-        <v>241</v>
+        <v>617</v>
       </c>
       <c r="L195" t="s" s="2">
-        <v>213</v>
+        <v>715</v>
       </c>
       <c r="M195" t="s" s="2">
-        <v>214</v>
-      </c>
-      <c r="N195" s="2"/>
+        <v>381</v>
+      </c>
+      <c r="N195" t="s" s="2">
+        <v>619</v>
+      </c>
       <c r="O195" s="2"/>
       <c r="P195" t="s" s="2">
         <v>80</v>
@@ -26490,22 +26359,22 @@
         <v>80</v>
       </c>
       <c r="AF195" t="s" s="2">
-        <v>215</v>
+        <v>118</v>
       </c>
       <c r="AG195" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH195" t="s" s="2">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="AI195" t="s" s="2">
-        <v>198</v>
+        <v>80</v>
       </c>
       <c r="AJ195" t="s" s="2">
-        <v>103</v>
+        <v>119</v>
       </c>
       <c r="AK195" t="s" s="2">
-        <v>692</v>
+        <v>80</v>
       </c>
       <c r="AL195" t="s" s="2">
         <v>80</v>
@@ -26525,10 +26394,10 @@
     </row>
     <row r="196" hidden="true">
       <c r="A196" t="s" s="2">
-        <v>693</v>
+        <v>716</v>
       </c>
       <c r="B196" t="s" s="2">
-        <v>694</v>
+        <v>717</v>
       </c>
       <c r="C196" s="2"/>
       <c r="D196" t="s" s="2">
@@ -26643,10 +26512,10 @@
     </row>
     <row r="197" hidden="true">
       <c r="A197" t="s" s="2">
-        <v>695</v>
+        <v>718</v>
       </c>
       <c r="B197" t="s" s="2">
-        <v>696</v>
+        <v>719</v>
       </c>
       <c r="C197" s="2"/>
       <c r="D197" t="s" s="2">
@@ -26657,7 +26526,7 @@
         <v>81</v>
       </c>
       <c r="G197" t="s" s="2">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="H197" t="s" s="2">
         <v>80</v>
@@ -26763,10 +26632,10 @@
     </row>
     <row r="198">
       <c r="A198" t="s" s="2">
-        <v>697</v>
+        <v>720</v>
       </c>
       <c r="B198" t="s" s="2">
-        <v>698</v>
+        <v>721</v>
       </c>
       <c r="C198" s="2"/>
       <c r="D198" t="s" s="2">
@@ -26786,29 +26655,27 @@
         <v>80</v>
       </c>
       <c r="J198" t="s" s="2">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="K198" t="s" s="2">
-        <v>144</v>
+        <v>132</v>
       </c>
       <c r="L198" t="s" s="2">
-        <v>257</v>
+        <v>205</v>
       </c>
       <c r="M198" t="s" s="2">
-        <v>258</v>
+        <v>206</v>
       </c>
       <c r="N198" t="s" s="2">
-        <v>259</v>
-      </c>
-      <c r="O198" t="s" s="2">
-        <v>260</v>
-      </c>
+        <v>207</v>
+      </c>
+      <c r="O198" s="2"/>
       <c r="P198" t="s" s="2">
         <v>80</v>
       </c>
       <c r="Q198" s="2"/>
       <c r="R198" t="s" s="2">
-        <v>80</v>
+        <v>626</v>
       </c>
       <c r="S198" t="s" s="2">
         <v>80</v>
@@ -26826,13 +26693,13 @@
         <v>80</v>
       </c>
       <c r="X198" t="s" s="2">
-        <v>245</v>
+        <v>80</v>
       </c>
       <c r="Y198" t="s" s="2">
-        <v>646</v>
+        <v>80</v>
       </c>
       <c r="Z198" t="s" s="2">
-        <v>647</v>
+        <v>80</v>
       </c>
       <c r="AA198" t="s" s="2">
         <v>80</v>
@@ -26850,19 +26717,19 @@
         <v>80</v>
       </c>
       <c r="AF198" t="s" s="2">
-        <v>261</v>
+        <v>209</v>
       </c>
       <c r="AG198" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AH198" t="s" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="AI198" t="s" s="2">
-        <v>198</v>
+        <v>80</v>
       </c>
       <c r="AJ198" t="s" s="2">
-        <v>103</v>
+        <v>80</v>
       </c>
       <c r="AK198" t="s" s="2">
         <v>80</v>
@@ -26874,7 +26741,7 @@
         <v>80</v>
       </c>
       <c r="AN198" t="s" s="2">
-        <v>262</v>
+        <v>80</v>
       </c>
       <c r="AO198" t="s" s="2">
         <v>80</v>
@@ -26883,12 +26750,12 @@
         <v>80</v>
       </c>
     </row>
-    <row r="199" hidden="true">
+    <row r="199">
       <c r="A199" t="s" s="2">
-        <v>699</v>
+        <v>722</v>
       </c>
       <c r="B199" t="s" s="2">
-        <v>700</v>
+        <v>723</v>
       </c>
       <c r="C199" s="2"/>
       <c r="D199" t="s" s="2">
@@ -26896,13 +26763,13 @@
       </c>
       <c r="E199" s="2"/>
       <c r="F199" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="G199" t="s" s="2">
         <v>91</v>
       </c>
       <c r="H199" t="s" s="2">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="I199" t="s" s="2">
         <v>80</v>
@@ -26911,13 +26778,13 @@
         <v>80</v>
       </c>
       <c r="K199" t="s" s="2">
-        <v>105</v>
+        <v>241</v>
       </c>
       <c r="L199" t="s" s="2">
-        <v>106</v>
+        <v>213</v>
       </c>
       <c r="M199" t="s" s="2">
-        <v>107</v>
+        <v>214</v>
       </c>
       <c r="N199" s="2"/>
       <c r="O199" s="2"/>
@@ -26968,7 +26835,7 @@
         <v>80</v>
       </c>
       <c r="AF199" t="s" s="2">
-        <v>108</v>
+        <v>215</v>
       </c>
       <c r="AG199" t="s" s="2">
         <v>81</v>
@@ -26977,13 +26844,13 @@
         <v>91</v>
       </c>
       <c r="AI199" t="s" s="2">
-        <v>80</v>
+        <v>198</v>
       </c>
       <c r="AJ199" t="s" s="2">
-        <v>80</v>
+        <v>103</v>
       </c>
       <c r="AK199" t="s" s="2">
-        <v>80</v>
+        <v>724</v>
       </c>
       <c r="AL199" t="s" s="2">
         <v>80</v>
@@ -27003,21 +26870,21 @@
     </row>
     <row r="200" hidden="true">
       <c r="A200" t="s" s="2">
-        <v>701</v>
+        <v>725</v>
       </c>
       <c r="B200" t="s" s="2">
-        <v>702</v>
+        <v>726</v>
       </c>
       <c r="C200" s="2"/>
       <c r="D200" t="s" s="2">
-        <v>110</v>
+        <v>80</v>
       </c>
       <c r="E200" s="2"/>
       <c r="F200" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G200" t="s" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="H200" t="s" s="2">
         <v>80</v>
@@ -27029,17 +26896,15 @@
         <v>80</v>
       </c>
       <c r="K200" t="s" s="2">
-        <v>111</v>
+        <v>105</v>
       </c>
       <c r="L200" t="s" s="2">
-        <v>112</v>
+        <v>106</v>
       </c>
       <c r="M200" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="N200" t="s" s="2">
-        <v>114</v>
-      </c>
+        <v>107</v>
+      </c>
+      <c r="N200" s="2"/>
       <c r="O200" s="2"/>
       <c r="P200" t="s" s="2">
         <v>80</v>
@@ -27076,31 +26941,31 @@
         <v>80</v>
       </c>
       <c r="AB200" t="s" s="2">
-        <v>115</v>
+        <v>80</v>
       </c>
       <c r="AC200" t="s" s="2">
-        <v>116</v>
+        <v>80</v>
       </c>
       <c r="AD200" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE200" t="s" s="2">
-        <v>117</v>
+        <v>80</v>
       </c>
       <c r="AF200" t="s" s="2">
-        <v>118</v>
+        <v>108</v>
       </c>
       <c r="AG200" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH200" t="s" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="AI200" t="s" s="2">
-        <v>198</v>
+        <v>80</v>
       </c>
       <c r="AJ200" t="s" s="2">
-        <v>119</v>
+        <v>80</v>
       </c>
       <c r="AK200" t="s" s="2">
         <v>80</v>
@@ -27121,48 +26986,46 @@
         <v>80</v>
       </c>
     </row>
-    <row r="201">
+    <row r="201" hidden="true">
       <c r="A201" t="s" s="2">
-        <v>703</v>
+        <v>727</v>
       </c>
       <c r="B201" t="s" s="2">
-        <v>704</v>
+        <v>728</v>
       </c>
       <c r="C201" s="2"/>
       <c r="D201" t="s" s="2">
-        <v>80</v>
+        <v>110</v>
       </c>
       <c r="E201" s="2"/>
       <c r="F201" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="G201" t="s" s="2">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="H201" t="s" s="2">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="I201" t="s" s="2">
         <v>80</v>
       </c>
       <c r="J201" t="s" s="2">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="K201" t="s" s="2">
-        <v>132</v>
+        <v>111</v>
       </c>
       <c r="L201" t="s" s="2">
-        <v>266</v>
+        <v>112</v>
       </c>
       <c r="M201" t="s" s="2">
-        <v>267</v>
+        <v>113</v>
       </c>
       <c r="N201" t="s" s="2">
-        <v>268</v>
-      </c>
-      <c r="O201" t="s" s="2">
-        <v>269</v>
-      </c>
+        <v>114</v>
+      </c>
+      <c r="O201" s="2"/>
       <c r="P201" t="s" s="2">
         <v>80</v>
       </c>
@@ -27198,31 +27061,31 @@
         <v>80</v>
       </c>
       <c r="AB201" t="s" s="2">
-        <v>80</v>
+        <v>115</v>
       </c>
       <c r="AC201" t="s" s="2">
-        <v>80</v>
+        <v>116</v>
       </c>
       <c r="AD201" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE201" t="s" s="2">
-        <v>80</v>
+        <v>117</v>
       </c>
       <c r="AF201" t="s" s="2">
-        <v>270</v>
+        <v>118</v>
       </c>
       <c r="AG201" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH201" t="s" s="2">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="AI201" t="s" s="2">
         <v>198</v>
       </c>
       <c r="AJ201" t="s" s="2">
-        <v>103</v>
+        <v>119</v>
       </c>
       <c r="AK201" t="s" s="2">
         <v>80</v>
@@ -27234,7 +27097,7 @@
         <v>80</v>
       </c>
       <c r="AN201" t="s" s="2">
-        <v>271</v>
+        <v>80</v>
       </c>
       <c r="AO201" t="s" s="2">
         <v>80</v>
@@ -27243,12 +27106,12 @@
         <v>80</v>
       </c>
     </row>
-    <row r="202" hidden="true">
+    <row r="202">
       <c r="A202" t="s" s="2">
-        <v>705</v>
+        <v>729</v>
       </c>
       <c r="B202" t="s" s="2">
-        <v>706</v>
+        <v>730</v>
       </c>
       <c r="C202" s="2"/>
       <c r="D202" t="s" s="2">
@@ -27256,13 +27119,13 @@
       </c>
       <c r="E202" s="2"/>
       <c r="F202" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="G202" t="s" s="2">
         <v>91</v>
       </c>
       <c r="H202" t="s" s="2">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="I202" t="s" s="2">
         <v>80</v>
@@ -27271,18 +27134,20 @@
         <v>92</v>
       </c>
       <c r="K202" t="s" s="2">
-        <v>105</v>
+        <v>144</v>
       </c>
       <c r="L202" t="s" s="2">
-        <v>273</v>
+        <v>257</v>
       </c>
       <c r="M202" t="s" s="2">
-        <v>274</v>
+        <v>258</v>
       </c>
       <c r="N202" t="s" s="2">
-        <v>275</v>
-      </c>
-      <c r="O202" s="2"/>
+        <v>259</v>
+      </c>
+      <c r="O202" t="s" s="2">
+        <v>260</v>
+      </c>
       <c r="P202" t="s" s="2">
         <v>80</v>
       </c>
@@ -27306,13 +27171,13 @@
         <v>80</v>
       </c>
       <c r="X202" t="s" s="2">
-        <v>80</v>
+        <v>245</v>
       </c>
       <c r="Y202" t="s" s="2">
-        <v>80</v>
+        <v>636</v>
       </c>
       <c r="Z202" t="s" s="2">
-        <v>80</v>
+        <v>637</v>
       </c>
       <c r="AA202" t="s" s="2">
         <v>80</v>
@@ -27330,13 +27195,13 @@
         <v>80</v>
       </c>
       <c r="AF202" t="s" s="2">
-        <v>276</v>
+        <v>261</v>
       </c>
       <c r="AG202" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH202" t="s" s="2">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="AI202" t="s" s="2">
         <v>198</v>
@@ -27354,7 +27219,7 @@
         <v>80</v>
       </c>
       <c r="AN202" t="s" s="2">
-        <v>277</v>
+        <v>262</v>
       </c>
       <c r="AO202" t="s" s="2">
         <v>80</v>
@@ -27363,12 +27228,12 @@
         <v>80</v>
       </c>
     </row>
-    <row r="203">
+    <row r="203" hidden="true">
       <c r="A203" t="s" s="2">
-        <v>707</v>
+        <v>731</v>
       </c>
       <c r="B203" t="s" s="2">
-        <v>708</v>
+        <v>732</v>
       </c>
       <c r="C203" s="2"/>
       <c r="D203" t="s" s="2">
@@ -27376,35 +27241,31 @@
       </c>
       <c r="E203" s="2"/>
       <c r="F203" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="G203" t="s" s="2">
         <v>91</v>
       </c>
       <c r="H203" t="s" s="2">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="I203" t="s" s="2">
         <v>80</v>
       </c>
       <c r="J203" t="s" s="2">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="K203" t="s" s="2">
-        <v>166</v>
+        <v>105</v>
       </c>
       <c r="L203" t="s" s="2">
-        <v>279</v>
+        <v>106</v>
       </c>
       <c r="M203" t="s" s="2">
-        <v>280</v>
-      </c>
-      <c r="N203" t="s" s="2">
-        <v>402</v>
-      </c>
-      <c r="O203" t="s" s="2">
-        <v>281</v>
-      </c>
+        <v>107</v>
+      </c>
+      <c r="N203" s="2"/>
+      <c r="O203" s="2"/>
       <c r="P203" t="s" s="2">
         <v>80</v>
       </c>
@@ -27452,7 +27313,7 @@
         <v>80</v>
       </c>
       <c r="AF203" t="s" s="2">
-        <v>282</v>
+        <v>108</v>
       </c>
       <c r="AG203" t="s" s="2">
         <v>81</v>
@@ -27461,10 +27322,10 @@
         <v>91</v>
       </c>
       <c r="AI203" t="s" s="2">
-        <v>198</v>
+        <v>80</v>
       </c>
       <c r="AJ203" t="s" s="2">
-        <v>103</v>
+        <v>80</v>
       </c>
       <c r="AK203" t="s" s="2">
         <v>80</v>
@@ -27476,7 +27337,7 @@
         <v>80</v>
       </c>
       <c r="AN203" t="s" s="2">
-        <v>283</v>
+        <v>80</v>
       </c>
       <c r="AO203" t="s" s="2">
         <v>80</v>
@@ -27487,21 +27348,21 @@
     </row>
     <row r="204" hidden="true">
       <c r="A204" t="s" s="2">
-        <v>709</v>
+        <v>733</v>
       </c>
       <c r="B204" t="s" s="2">
-        <v>710</v>
+        <v>734</v>
       </c>
       <c r="C204" s="2"/>
       <c r="D204" t="s" s="2">
-        <v>80</v>
+        <v>110</v>
       </c>
       <c r="E204" s="2"/>
       <c r="F204" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G204" t="s" s="2">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="H204" t="s" s="2">
         <v>80</v>
@@ -27510,23 +27371,21 @@
         <v>80</v>
       </c>
       <c r="J204" t="s" s="2">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="K204" t="s" s="2">
-        <v>105</v>
+        <v>111</v>
       </c>
       <c r="L204" t="s" s="2">
-        <v>285</v>
+        <v>112</v>
       </c>
       <c r="M204" t="s" s="2">
-        <v>286</v>
+        <v>113</v>
       </c>
       <c r="N204" t="s" s="2">
-        <v>402</v>
-      </c>
-      <c r="O204" t="s" s="2">
-        <v>287</v>
-      </c>
+        <v>114</v>
+      </c>
+      <c r="O204" s="2"/>
       <c r="P204" t="s" s="2">
         <v>80</v>
       </c>
@@ -27562,31 +27421,31 @@
         <v>80</v>
       </c>
       <c r="AB204" t="s" s="2">
-        <v>80</v>
+        <v>115</v>
       </c>
       <c r="AC204" t="s" s="2">
-        <v>80</v>
+        <v>116</v>
       </c>
       <c r="AD204" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE204" t="s" s="2">
-        <v>80</v>
+        <v>117</v>
       </c>
       <c r="AF204" t="s" s="2">
-        <v>288</v>
+        <v>118</v>
       </c>
       <c r="AG204" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH204" t="s" s="2">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="AI204" t="s" s="2">
         <v>198</v>
       </c>
       <c r="AJ204" t="s" s="2">
-        <v>103</v>
+        <v>119</v>
       </c>
       <c r="AK204" t="s" s="2">
         <v>80</v>
@@ -27598,7 +27457,7 @@
         <v>80</v>
       </c>
       <c r="AN204" t="s" s="2">
-        <v>289</v>
+        <v>80</v>
       </c>
       <c r="AO204" t="s" s="2">
         <v>80</v>
@@ -27607,12 +27466,12 @@
         <v>80</v>
       </c>
     </row>
-    <row r="205" hidden="true">
+    <row r="205">
       <c r="A205" t="s" s="2">
-        <v>711</v>
+        <v>735</v>
       </c>
       <c r="B205" t="s" s="2">
-        <v>712</v>
+        <v>736</v>
       </c>
       <c r="C205" s="2"/>
       <c r="D205" t="s" s="2">
@@ -27620,13 +27479,13 @@
       </c>
       <c r="E205" s="2"/>
       <c r="F205" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="G205" t="s" s="2">
         <v>91</v>
       </c>
       <c r="H205" t="s" s="2">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="I205" t="s" s="2">
         <v>80</v>
@@ -27635,19 +27494,19 @@
         <v>92</v>
       </c>
       <c r="K205" t="s" s="2">
-        <v>291</v>
+        <v>132</v>
       </c>
       <c r="L205" t="s" s="2">
-        <v>292</v>
+        <v>266</v>
       </c>
       <c r="M205" t="s" s="2">
-        <v>293</v>
+        <v>267</v>
       </c>
       <c r="N205" t="s" s="2">
-        <v>294</v>
+        <v>268</v>
       </c>
       <c r="O205" t="s" s="2">
-        <v>295</v>
+        <v>269</v>
       </c>
       <c r="P205" t="s" s="2">
         <v>80</v>
@@ -27696,7 +27555,7 @@
         <v>80</v>
       </c>
       <c r="AF205" t="s" s="2">
-        <v>296</v>
+        <v>270</v>
       </c>
       <c r="AG205" t="s" s="2">
         <v>81</v>
@@ -27720,7 +27579,7 @@
         <v>80</v>
       </c>
       <c r="AN205" t="s" s="2">
-        <v>297</v>
+        <v>271</v>
       </c>
       <c r="AO205" t="s" s="2">
         <v>80</v>
@@ -27731,10 +27590,10 @@
     </row>
     <row r="206" hidden="true">
       <c r="A206" t="s" s="2">
-        <v>713</v>
+        <v>737</v>
       </c>
       <c r="B206" t="s" s="2">
-        <v>714</v>
+        <v>738</v>
       </c>
       <c r="C206" s="2"/>
       <c r="D206" t="s" s="2">
@@ -27760,17 +27619,15 @@
         <v>105</v>
       </c>
       <c r="L206" t="s" s="2">
-        <v>299</v>
+        <v>273</v>
       </c>
       <c r="M206" t="s" s="2">
-        <v>300</v>
+        <v>274</v>
       </c>
       <c r="N206" t="s" s="2">
-        <v>301</v>
-      </c>
-      <c r="O206" t="s" s="2">
-        <v>302</v>
-      </c>
+        <v>275</v>
+      </c>
+      <c r="O206" s="2"/>
       <c r="P206" t="s" s="2">
         <v>80</v>
       </c>
@@ -27818,7 +27675,7 @@
         <v>80</v>
       </c>
       <c r="AF206" t="s" s="2">
-        <v>303</v>
+        <v>276</v>
       </c>
       <c r="AG206" t="s" s="2">
         <v>81</v>
@@ -27842,7 +27699,7 @@
         <v>80</v>
       </c>
       <c r="AN206" t="s" s="2">
-        <v>304</v>
+        <v>277</v>
       </c>
       <c r="AO206" t="s" s="2">
         <v>80</v>
@@ -27851,12 +27708,12 @@
         <v>80</v>
       </c>
     </row>
-    <row r="207" hidden="true">
+    <row r="207">
       <c r="A207" t="s" s="2">
-        <v>715</v>
+        <v>739</v>
       </c>
       <c r="B207" t="s" s="2">
-        <v>716</v>
+        <v>740</v>
       </c>
       <c r="C207" s="2"/>
       <c r="D207" t="s" s="2">
@@ -27864,31 +27721,35 @@
       </c>
       <c r="E207" s="2"/>
       <c r="F207" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="G207" t="s" s="2">
         <v>91</v>
       </c>
       <c r="H207" t="s" s="2">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="I207" t="s" s="2">
         <v>80</v>
       </c>
       <c r="J207" t="s" s="2">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="K207" t="s" s="2">
-        <v>226</v>
+        <v>166</v>
       </c>
       <c r="L207" t="s" s="2">
-        <v>666</v>
+        <v>279</v>
       </c>
       <c r="M207" t="s" s="2">
-        <v>667</v>
-      </c>
-      <c r="N207" s="2"/>
-      <c r="O207" s="2"/>
+        <v>280</v>
+      </c>
+      <c r="N207" t="s" s="2">
+        <v>402</v>
+      </c>
+      <c r="O207" t="s" s="2">
+        <v>281</v>
+      </c>
       <c r="P207" t="s" s="2">
         <v>80</v>
       </c>
@@ -27936,7 +27797,7 @@
         <v>80</v>
       </c>
       <c r="AF207" t="s" s="2">
-        <v>668</v>
+        <v>282</v>
       </c>
       <c r="AG207" t="s" s="2">
         <v>81</v>
@@ -27945,10 +27806,10 @@
         <v>91</v>
       </c>
       <c r="AI207" t="s" s="2">
-        <v>80</v>
+        <v>198</v>
       </c>
       <c r="AJ207" t="s" s="2">
-        <v>80</v>
+        <v>103</v>
       </c>
       <c r="AK207" t="s" s="2">
         <v>80</v>
@@ -27960,7 +27821,7 @@
         <v>80</v>
       </c>
       <c r="AN207" t="s" s="2">
-        <v>80</v>
+        <v>283</v>
       </c>
       <c r="AO207" t="s" s="2">
         <v>80</v>
@@ -27969,16 +27830,14 @@
         <v>80</v>
       </c>
     </row>
-    <row r="208">
+    <row r="208" hidden="true">
       <c r="A208" t="s" s="2">
-        <v>717</v>
+        <v>741</v>
       </c>
       <c r="B208" t="s" s="2">
-        <v>591</v>
-      </c>
-      <c r="C208" t="s" s="2">
-        <v>718</v>
-      </c>
+        <v>742</v>
+      </c>
+      <c r="C208" s="2"/>
       <c r="D208" t="s" s="2">
         <v>80</v>
       </c>
@@ -27990,7 +27849,7 @@
         <v>91</v>
       </c>
       <c r="H208" t="s" s="2">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="I208" t="s" s="2">
         <v>80</v>
@@ -27999,18 +27858,20 @@
         <v>92</v>
       </c>
       <c r="K208" t="s" s="2">
-        <v>226</v>
+        <v>105</v>
       </c>
       <c r="L208" t="s" s="2">
-        <v>719</v>
+        <v>285</v>
       </c>
       <c r="M208" t="s" s="2">
-        <v>720</v>
+        <v>286</v>
       </c>
       <c r="N208" t="s" s="2">
-        <v>595</v>
-      </c>
-      <c r="O208" s="2"/>
+        <v>402</v>
+      </c>
+      <c r="O208" t="s" s="2">
+        <v>287</v>
+      </c>
       <c r="P208" t="s" s="2">
         <v>80</v>
       </c>
@@ -28058,7 +27919,7 @@
         <v>80</v>
       </c>
       <c r="AF208" t="s" s="2">
-        <v>591</v>
+        <v>288</v>
       </c>
       <c r="AG208" t="s" s="2">
         <v>81</v>
@@ -28067,7 +27928,7 @@
         <v>91</v>
       </c>
       <c r="AI208" t="s" s="2">
-        <v>80</v>
+        <v>198</v>
       </c>
       <c r="AJ208" t="s" s="2">
         <v>103</v>
@@ -28076,31 +27937,29 @@
         <v>80</v>
       </c>
       <c r="AL208" t="s" s="2">
-        <v>599</v>
+        <v>80</v>
       </c>
       <c r="AM208" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN208" t="s" s="2">
-        <v>600</v>
+        <v>289</v>
       </c>
       <c r="AO208" t="s" s="2">
-        <v>601</v>
+        <v>80</v>
       </c>
       <c r="AP208" t="s" s="2">
         <v>80</v>
       </c>
     </row>
-    <row r="209">
+    <row r="209" hidden="true">
       <c r="A209" t="s" s="2">
-        <v>721</v>
+        <v>743</v>
       </c>
       <c r="B209" t="s" s="2">
-        <v>591</v>
-      </c>
-      <c r="C209" t="s" s="2">
-        <v>722</v>
-      </c>
+        <v>744</v>
+      </c>
+      <c r="C209" s="2"/>
       <c r="D209" t="s" s="2">
         <v>80</v>
       </c>
@@ -28112,7 +27971,7 @@
         <v>91</v>
       </c>
       <c r="H209" t="s" s="2">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="I209" t="s" s="2">
         <v>80</v>
@@ -28121,18 +27980,20 @@
         <v>92</v>
       </c>
       <c r="K209" t="s" s="2">
-        <v>723</v>
+        <v>291</v>
       </c>
       <c r="L209" t="s" s="2">
-        <v>724</v>
+        <v>292</v>
       </c>
       <c r="M209" t="s" s="2">
-        <v>725</v>
+        <v>293</v>
       </c>
       <c r="N209" t="s" s="2">
-        <v>595</v>
-      </c>
-      <c r="O209" s="2"/>
+        <v>294</v>
+      </c>
+      <c r="O209" t="s" s="2">
+        <v>295</v>
+      </c>
       <c r="P209" t="s" s="2">
         <v>80</v>
       </c>
@@ -28180,7 +28041,7 @@
         <v>80</v>
       </c>
       <c r="AF209" t="s" s="2">
-        <v>591</v>
+        <v>296</v>
       </c>
       <c r="AG209" t="s" s="2">
         <v>81</v>
@@ -28189,7 +28050,7 @@
         <v>91</v>
       </c>
       <c r="AI209" t="s" s="2">
-        <v>80</v>
+        <v>198</v>
       </c>
       <c r="AJ209" t="s" s="2">
         <v>103</v>
@@ -28198,16 +28059,16 @@
         <v>80</v>
       </c>
       <c r="AL209" t="s" s="2">
-        <v>599</v>
+        <v>80</v>
       </c>
       <c r="AM209" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN209" t="s" s="2">
-        <v>600</v>
+        <v>297</v>
       </c>
       <c r="AO209" t="s" s="2">
-        <v>601</v>
+        <v>80</v>
       </c>
       <c r="AP209" t="s" s="2">
         <v>80</v>
@@ -28215,10 +28076,10 @@
     </row>
     <row r="210" hidden="true">
       <c r="A210" t="s" s="2">
-        <v>726</v>
+        <v>745</v>
       </c>
       <c r="B210" t="s" s="2">
-        <v>609</v>
+        <v>746</v>
       </c>
       <c r="C210" s="2"/>
       <c r="D210" t="s" s="2">
@@ -28238,19 +28099,23 @@
         <v>80</v>
       </c>
       <c r="J210" t="s" s="2">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="K210" t="s" s="2">
         <v>105</v>
       </c>
       <c r="L210" t="s" s="2">
-        <v>106</v>
+        <v>299</v>
       </c>
       <c r="M210" t="s" s="2">
-        <v>107</v>
-      </c>
-      <c r="N210" s="2"/>
-      <c r="O210" s="2"/>
+        <v>300</v>
+      </c>
+      <c r="N210" t="s" s="2">
+        <v>301</v>
+      </c>
+      <c r="O210" t="s" s="2">
+        <v>302</v>
+      </c>
       <c r="P210" t="s" s="2">
         <v>80</v>
       </c>
@@ -28298,7 +28163,7 @@
         <v>80</v>
       </c>
       <c r="AF210" t="s" s="2">
-        <v>108</v>
+        <v>303</v>
       </c>
       <c r="AG210" t="s" s="2">
         <v>81</v>
@@ -28307,10 +28172,10 @@
         <v>91</v>
       </c>
       <c r="AI210" t="s" s="2">
-        <v>80</v>
+        <v>198</v>
       </c>
       <c r="AJ210" t="s" s="2">
-        <v>80</v>
+        <v>103</v>
       </c>
       <c r="AK210" t="s" s="2">
         <v>80</v>
@@ -28322,7 +28187,7 @@
         <v>80</v>
       </c>
       <c r="AN210" t="s" s="2">
-        <v>80</v>
+        <v>304</v>
       </c>
       <c r="AO210" t="s" s="2">
         <v>80</v>
@@ -28333,21 +28198,21 @@
     </row>
     <row r="211" hidden="true">
       <c r="A211" t="s" s="2">
-        <v>727</v>
+        <v>747</v>
       </c>
       <c r="B211" t="s" s="2">
-        <v>611</v>
+        <v>748</v>
       </c>
       <c r="C211" s="2"/>
       <c r="D211" t="s" s="2">
-        <v>110</v>
+        <v>80</v>
       </c>
       <c r="E211" s="2"/>
       <c r="F211" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G211" t="s" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="H211" t="s" s="2">
         <v>80</v>
@@ -28356,21 +28221,23 @@
         <v>80</v>
       </c>
       <c r="J211" t="s" s="2">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="K211" t="s" s="2">
-        <v>111</v>
+        <v>656</v>
       </c>
       <c r="L211" t="s" s="2">
-        <v>112</v>
+        <v>657</v>
       </c>
       <c r="M211" t="s" s="2">
-        <v>113</v>
+        <v>658</v>
       </c>
       <c r="N211" t="s" s="2">
-        <v>114</v>
-      </c>
-      <c r="O211" s="2"/>
+        <v>659</v>
+      </c>
+      <c r="O211" t="s" s="2">
+        <v>660</v>
+      </c>
       <c r="P211" t="s" s="2">
         <v>80</v>
       </c>
@@ -28406,31 +28273,31 @@
         <v>80</v>
       </c>
       <c r="AB211" t="s" s="2">
-        <v>115</v>
+        <v>80</v>
       </c>
       <c r="AC211" t="s" s="2">
-        <v>116</v>
+        <v>80</v>
       </c>
       <c r="AD211" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE211" t="s" s="2">
-        <v>117</v>
+        <v>80</v>
       </c>
       <c r="AF211" t="s" s="2">
-        <v>118</v>
+        <v>661</v>
       </c>
       <c r="AG211" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH211" t="s" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="AI211" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ211" t="s" s="2">
-        <v>119</v>
+        <v>103</v>
       </c>
       <c r="AK211" t="s" s="2">
         <v>80</v>
@@ -28442,7 +28309,7 @@
         <v>80</v>
       </c>
       <c r="AN211" t="s" s="2">
-        <v>80</v>
+        <v>662</v>
       </c>
       <c r="AO211" t="s" s="2">
         <v>80</v>
@@ -28453,14 +28320,12 @@
     </row>
     <row r="212" hidden="true">
       <c r="A212" t="s" s="2">
-        <v>728</v>
+        <v>749</v>
       </c>
       <c r="B212" t="s" s="2">
-        <v>611</v>
-      </c>
-      <c r="C212" t="s" s="2">
-        <v>729</v>
-      </c>
+        <v>750</v>
+      </c>
+      <c r="C212" s="2"/>
       <c r="D212" t="s" s="2">
         <v>80</v>
       </c>
@@ -28475,28 +28340,30 @@
         <v>80</v>
       </c>
       <c r="I212" t="s" s="2">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="J212" t="s" s="2">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="K212" t="s" s="2">
-        <v>629</v>
+        <v>166</v>
       </c>
       <c r="L212" t="s" s="2">
-        <v>730</v>
+        <v>665</v>
       </c>
       <c r="M212" t="s" s="2">
-        <v>381</v>
-      </c>
-      <c r="N212" t="s" s="2">
-        <v>731</v>
-      </c>
-      <c r="O212" s="2"/>
+        <v>666</v>
+      </c>
+      <c r="N212" s="2"/>
+      <c r="O212" t="s" s="2">
+        <v>667</v>
+      </c>
       <c r="P212" t="s" s="2">
         <v>80</v>
       </c>
-      <c r="Q212" s="2"/>
+      <c r="Q212" t="s" s="2">
+        <v>668</v>
+      </c>
       <c r="R212" t="s" s="2">
         <v>80</v>
       </c>
@@ -28516,13 +28383,13 @@
         <v>80</v>
       </c>
       <c r="X212" t="s" s="2">
-        <v>80</v>
+        <v>245</v>
       </c>
       <c r="Y212" t="s" s="2">
-        <v>80</v>
+        <v>669</v>
       </c>
       <c r="Z212" t="s" s="2">
-        <v>80</v>
+        <v>670</v>
       </c>
       <c r="AA212" t="s" s="2">
         <v>80</v>
@@ -28540,19 +28407,19 @@
         <v>80</v>
       </c>
       <c r="AF212" t="s" s="2">
-        <v>118</v>
+        <v>671</v>
       </c>
       <c r="AG212" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH212" t="s" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="AI212" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ212" t="s" s="2">
-        <v>119</v>
+        <v>103</v>
       </c>
       <c r="AK212" t="s" s="2">
         <v>80</v>
@@ -28564,7 +28431,7 @@
         <v>80</v>
       </c>
       <c r="AN212" t="s" s="2">
-        <v>80</v>
+        <v>672</v>
       </c>
       <c r="AO212" t="s" s="2">
         <v>80</v>
@@ -28575,10 +28442,10 @@
     </row>
     <row r="213" hidden="true">
       <c r="A213" t="s" s="2">
-        <v>732</v>
+        <v>751</v>
       </c>
       <c r="B213" t="s" s="2">
-        <v>733</v>
+        <v>752</v>
       </c>
       <c r="C213" s="2"/>
       <c r="D213" t="s" s="2">
@@ -28598,19 +28465,21 @@
         <v>80</v>
       </c>
       <c r="J213" t="s" s="2">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="K213" t="s" s="2">
         <v>105</v>
       </c>
       <c r="L213" t="s" s="2">
-        <v>106</v>
+        <v>675</v>
       </c>
       <c r="M213" t="s" s="2">
-        <v>107</v>
+        <v>676</v>
       </c>
       <c r="N213" s="2"/>
-      <c r="O213" s="2"/>
+      <c r="O213" t="s" s="2">
+        <v>677</v>
+      </c>
       <c r="P213" t="s" s="2">
         <v>80</v>
       </c>
@@ -28658,7 +28527,7 @@
         <v>80</v>
       </c>
       <c r="AF213" t="s" s="2">
-        <v>108</v>
+        <v>678</v>
       </c>
       <c r="AG213" t="s" s="2">
         <v>81</v>
@@ -28670,7 +28539,7 @@
         <v>80</v>
       </c>
       <c r="AJ213" t="s" s="2">
-        <v>80</v>
+        <v>103</v>
       </c>
       <c r="AK213" t="s" s="2">
         <v>80</v>
@@ -28682,7 +28551,7 @@
         <v>80</v>
       </c>
       <c r="AN213" t="s" s="2">
-        <v>80</v>
+        <v>679</v>
       </c>
       <c r="AO213" t="s" s="2">
         <v>80</v>
@@ -28693,21 +28562,21 @@
     </row>
     <row r="214" hidden="true">
       <c r="A214" t="s" s="2">
-        <v>734</v>
+        <v>753</v>
       </c>
       <c r="B214" t="s" s="2">
-        <v>735</v>
+        <v>754</v>
       </c>
       <c r="C214" s="2"/>
       <c r="D214" t="s" s="2">
-        <v>110</v>
+        <v>80</v>
       </c>
       <c r="E214" s="2"/>
       <c r="F214" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G214" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H214" t="s" s="2">
         <v>80</v>
@@ -28716,21 +28585,21 @@
         <v>80</v>
       </c>
       <c r="J214" t="s" s="2">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="K214" t="s" s="2">
-        <v>111</v>
+        <v>132</v>
       </c>
       <c r="L214" t="s" s="2">
-        <v>112</v>
+        <v>682</v>
       </c>
       <c r="M214" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="N214" t="s" s="2">
-        <v>114</v>
-      </c>
-      <c r="O214" s="2"/>
+        <v>683</v>
+      </c>
+      <c r="N214" s="2"/>
+      <c r="O214" t="s" s="2">
+        <v>684</v>
+      </c>
       <c r="P214" t="s" s="2">
         <v>80</v>
       </c>
@@ -28766,31 +28635,31 @@
         <v>80</v>
       </c>
       <c r="AB214" t="s" s="2">
-        <v>115</v>
+        <v>80</v>
       </c>
       <c r="AC214" t="s" s="2">
-        <v>116</v>
+        <v>80</v>
       </c>
       <c r="AD214" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE214" t="s" s="2">
-        <v>117</v>
+        <v>80</v>
       </c>
       <c r="AF214" t="s" s="2">
-        <v>118</v>
+        <v>685</v>
       </c>
       <c r="AG214" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH214" t="s" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="AI214" t="s" s="2">
-        <v>198</v>
+        <v>686</v>
       </c>
       <c r="AJ214" t="s" s="2">
-        <v>119</v>
+        <v>103</v>
       </c>
       <c r="AK214" t="s" s="2">
         <v>80</v>
@@ -28802,7 +28671,7 @@
         <v>80</v>
       </c>
       <c r="AN214" t="s" s="2">
-        <v>80</v>
+        <v>679</v>
       </c>
       <c r="AO214" t="s" s="2">
         <v>80</v>
@@ -28811,12 +28680,12 @@
         <v>80</v>
       </c>
     </row>
-    <row r="215">
+    <row r="215" hidden="true">
       <c r="A215" t="s" s="2">
-        <v>736</v>
+        <v>755</v>
       </c>
       <c r="B215" t="s" s="2">
-        <v>737</v>
+        <v>756</v>
       </c>
       <c r="C215" s="2"/>
       <c r="D215" t="s" s="2">
@@ -28824,39 +28693,41 @@
       </c>
       <c r="E215" s="2"/>
       <c r="F215" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="G215" t="s" s="2">
         <v>91</v>
       </c>
       <c r="H215" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I215" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J215" t="s" s="2">
         <v>92</v>
       </c>
-      <c r="I215" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="J215" t="s" s="2">
-        <v>80</v>
-      </c>
       <c r="K215" t="s" s="2">
-        <v>132</v>
+        <v>166</v>
       </c>
       <c r="L215" t="s" s="2">
-        <v>205</v>
+        <v>689</v>
       </c>
       <c r="M215" t="s" s="2">
-        <v>206</v>
+        <v>690</v>
       </c>
       <c r="N215" t="s" s="2">
-        <v>207</v>
-      </c>
-      <c r="O215" s="2"/>
+        <v>691</v>
+      </c>
+      <c r="O215" t="s" s="2">
+        <v>692</v>
+      </c>
       <c r="P215" t="s" s="2">
         <v>80</v>
       </c>
       <c r="Q215" s="2"/>
       <c r="R215" t="s" s="2">
-        <v>636</v>
+        <v>80</v>
       </c>
       <c r="S215" t="s" s="2">
         <v>80</v>
@@ -28898,10 +28769,10 @@
         <v>80</v>
       </c>
       <c r="AF215" t="s" s="2">
-        <v>209</v>
+        <v>693</v>
       </c>
       <c r="AG215" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AH215" t="s" s="2">
         <v>91</v>
@@ -28910,7 +28781,7 @@
         <v>80</v>
       </c>
       <c r="AJ215" t="s" s="2">
-        <v>80</v>
+        <v>103</v>
       </c>
       <c r="AK215" t="s" s="2">
         <v>80</v>
@@ -28922,7 +28793,7 @@
         <v>80</v>
       </c>
       <c r="AN215" t="s" s="2">
-        <v>80</v>
+        <v>679</v>
       </c>
       <c r="AO215" t="s" s="2">
         <v>80</v>
@@ -28933,10 +28804,10 @@
     </row>
     <row r="216">
       <c r="A216" t="s" s="2">
-        <v>738</v>
+        <v>757</v>
       </c>
       <c r="B216" t="s" s="2">
-        <v>739</v>
+        <v>757</v>
       </c>
       <c r="C216" s="2"/>
       <c r="D216" t="s" s="2">
@@ -28956,16 +28827,16 @@
         <v>80</v>
       </c>
       <c r="J216" t="s" s="2">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="K216" t="s" s="2">
-        <v>241</v>
+        <v>226</v>
       </c>
       <c r="L216" t="s" s="2">
-        <v>213</v>
+        <v>758</v>
       </c>
       <c r="M216" t="s" s="2">
-        <v>214</v>
+        <v>759</v>
       </c>
       <c r="N216" s="2"/>
       <c r="O216" s="2"/>
@@ -29016,7 +28887,7 @@
         <v>80</v>
       </c>
       <c r="AF216" t="s" s="2">
-        <v>215</v>
+        <v>757</v>
       </c>
       <c r="AG216" t="s" s="2">
         <v>81</v>
@@ -29025,13 +28896,13 @@
         <v>91</v>
       </c>
       <c r="AI216" t="s" s="2">
-        <v>198</v>
+        <v>80</v>
       </c>
       <c r="AJ216" t="s" s="2">
         <v>103</v>
       </c>
       <c r="AK216" t="s" s="2">
-        <v>80</v>
+        <v>760</v>
       </c>
       <c r="AL216" t="s" s="2">
         <v>80</v>
@@ -29040,10 +28911,10 @@
         <v>80</v>
       </c>
       <c r="AN216" t="s" s="2">
-        <v>80</v>
+        <v>761</v>
       </c>
       <c r="AO216" t="s" s="2">
-        <v>80</v>
+        <v>762</v>
       </c>
       <c r="AP216" t="s" s="2">
         <v>80</v>
@@ -29051,10 +28922,10 @@
     </row>
     <row r="217" hidden="true">
       <c r="A217" t="s" s="2">
-        <v>740</v>
+        <v>763</v>
       </c>
       <c r="B217" t="s" s="2">
-        <v>741</v>
+        <v>763</v>
       </c>
       <c r="C217" s="2"/>
       <c r="D217" t="s" s="2">
@@ -29074,16 +28945,16 @@
         <v>80</v>
       </c>
       <c r="J217" t="s" s="2">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="K217" t="s" s="2">
-        <v>105</v>
+        <v>764</v>
       </c>
       <c r="L217" t="s" s="2">
-        <v>106</v>
+        <v>765</v>
       </c>
       <c r="M217" t="s" s="2">
-        <v>107</v>
+        <v>766</v>
       </c>
       <c r="N217" s="2"/>
       <c r="O217" s="2"/>
@@ -29134,7 +29005,7 @@
         <v>80</v>
       </c>
       <c r="AF217" t="s" s="2">
-        <v>108</v>
+        <v>763</v>
       </c>
       <c r="AG217" t="s" s="2">
         <v>81</v>
@@ -29146,7 +29017,7 @@
         <v>80</v>
       </c>
       <c r="AJ217" t="s" s="2">
-        <v>80</v>
+        <v>103</v>
       </c>
       <c r="AK217" t="s" s="2">
         <v>80</v>
@@ -29161,7 +29032,7 @@
         <v>80</v>
       </c>
       <c r="AO217" t="s" s="2">
-        <v>80</v>
+        <v>767</v>
       </c>
       <c r="AP217" t="s" s="2">
         <v>80</v>
@@ -29169,21 +29040,21 @@
     </row>
     <row r="218" hidden="true">
       <c r="A218" t="s" s="2">
-        <v>742</v>
+        <v>768</v>
       </c>
       <c r="B218" t="s" s="2">
-        <v>743</v>
+        <v>768</v>
       </c>
       <c r="C218" s="2"/>
       <c r="D218" t="s" s="2">
-        <v>110</v>
+        <v>80</v>
       </c>
       <c r="E218" s="2"/>
       <c r="F218" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G218" t="s" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="H218" t="s" s="2">
         <v>80</v>
@@ -29192,20 +29063,18 @@
         <v>80</v>
       </c>
       <c r="J218" t="s" s="2">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="K218" t="s" s="2">
-        <v>111</v>
+        <v>764</v>
       </c>
       <c r="L218" t="s" s="2">
-        <v>112</v>
+        <v>769</v>
       </c>
       <c r="M218" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="N218" t="s" s="2">
-        <v>114</v>
-      </c>
+        <v>770</v>
+      </c>
+      <c r="N218" s="2"/>
       <c r="O218" s="2"/>
       <c r="P218" t="s" s="2">
         <v>80</v>
@@ -29242,31 +29111,31 @@
         <v>80</v>
       </c>
       <c r="AB218" t="s" s="2">
-        <v>115</v>
+        <v>80</v>
       </c>
       <c r="AC218" t="s" s="2">
-        <v>116</v>
+        <v>80</v>
       </c>
       <c r="AD218" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE218" t="s" s="2">
-        <v>117</v>
+        <v>80</v>
       </c>
       <c r="AF218" t="s" s="2">
-        <v>118</v>
+        <v>768</v>
       </c>
       <c r="AG218" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH218" t="s" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="AI218" t="s" s="2">
-        <v>198</v>
+        <v>80</v>
       </c>
       <c r="AJ218" t="s" s="2">
-        <v>119</v>
+        <v>103</v>
       </c>
       <c r="AK218" t="s" s="2">
         <v>80</v>
@@ -29278,21 +29147,21 @@
         <v>80</v>
       </c>
       <c r="AN218" t="s" s="2">
-        <v>80</v>
+        <v>771</v>
       </c>
       <c r="AO218" t="s" s="2">
-        <v>80</v>
+        <v>772</v>
       </c>
       <c r="AP218" t="s" s="2">
         <v>80</v>
       </c>
     </row>
-    <row r="219">
+    <row r="219" hidden="true">
       <c r="A219" t="s" s="2">
-        <v>744</v>
+        <v>773</v>
       </c>
       <c r="B219" t="s" s="2">
-        <v>745</v>
+        <v>773</v>
       </c>
       <c r="C219" s="2"/>
       <c r="D219" t="s" s="2">
@@ -29300,35 +29169,31 @@
       </c>
       <c r="E219" s="2"/>
       <c r="F219" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="G219" t="s" s="2">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="H219" t="s" s="2">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="I219" t="s" s="2">
         <v>80</v>
       </c>
       <c r="J219" t="s" s="2">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="K219" t="s" s="2">
-        <v>144</v>
+        <v>774</v>
       </c>
       <c r="L219" t="s" s="2">
-        <v>257</v>
+        <v>775</v>
       </c>
       <c r="M219" t="s" s="2">
-        <v>258</v>
-      </c>
-      <c r="N219" t="s" s="2">
-        <v>259</v>
-      </c>
-      <c r="O219" t="s" s="2">
-        <v>260</v>
-      </c>
+        <v>776</v>
+      </c>
+      <c r="N219" s="2"/>
+      <c r="O219" s="2"/>
       <c r="P219" t="s" s="2">
         <v>80</v>
       </c>
@@ -29352,13 +29217,13 @@
         <v>80</v>
       </c>
       <c r="X219" t="s" s="2">
-        <v>245</v>
+        <v>80</v>
       </c>
       <c r="Y219" t="s" s="2">
-        <v>646</v>
+        <v>80</v>
       </c>
       <c r="Z219" t="s" s="2">
-        <v>647</v>
+        <v>80</v>
       </c>
       <c r="AA219" t="s" s="2">
         <v>80</v>
@@ -29376,7 +29241,7 @@
         <v>80</v>
       </c>
       <c r="AF219" t="s" s="2">
-        <v>261</v>
+        <v>773</v>
       </c>
       <c r="AG219" t="s" s="2">
         <v>81</v>
@@ -29385,10 +29250,10 @@
         <v>82</v>
       </c>
       <c r="AI219" t="s" s="2">
-        <v>198</v>
+        <v>80</v>
       </c>
       <c r="AJ219" t="s" s="2">
-        <v>103</v>
+        <v>777</v>
       </c>
       <c r="AK219" t="s" s="2">
         <v>80</v>
@@ -29400,7 +29265,7 @@
         <v>80</v>
       </c>
       <c r="AN219" t="s" s="2">
-        <v>262</v>
+        <v>80</v>
       </c>
       <c r="AO219" t="s" s="2">
         <v>80</v>
@@ -29411,10 +29276,10 @@
     </row>
     <row r="220" hidden="true">
       <c r="A220" t="s" s="2">
-        <v>746</v>
+        <v>778</v>
       </c>
       <c r="B220" t="s" s="2">
-        <v>747</v>
+        <v>778</v>
       </c>
       <c r="C220" s="2"/>
       <c r="D220" t="s" s="2">
@@ -29529,10 +29394,10 @@
     </row>
     <row r="221" hidden="true">
       <c r="A221" t="s" s="2">
-        <v>748</v>
+        <v>779</v>
       </c>
       <c r="B221" t="s" s="2">
-        <v>749</v>
+        <v>779</v>
       </c>
       <c r="C221" s="2"/>
       <c r="D221" t="s" s="2">
@@ -29602,16 +29467,16 @@
         <v>80</v>
       </c>
       <c r="AB221" t="s" s="2">
-        <v>115</v>
+        <v>80</v>
       </c>
       <c r="AC221" t="s" s="2">
-        <v>116</v>
+        <v>80</v>
       </c>
       <c r="AD221" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE221" t="s" s="2">
-        <v>117</v>
+        <v>80</v>
       </c>
       <c r="AF221" t="s" s="2">
         <v>118</v>
@@ -29623,7 +29488,7 @@
         <v>82</v>
       </c>
       <c r="AI221" t="s" s="2">
-        <v>198</v>
+        <v>80</v>
       </c>
       <c r="AJ221" t="s" s="2">
         <v>119</v>
@@ -29647,47 +29512,47 @@
         <v>80</v>
       </c>
     </row>
-    <row r="222">
+    <row r="222" hidden="true">
       <c r="A222" t="s" s="2">
-        <v>750</v>
+        <v>780</v>
       </c>
       <c r="B222" t="s" s="2">
-        <v>751</v>
+        <v>780</v>
       </c>
       <c r="C222" s="2"/>
       <c r="D222" t="s" s="2">
-        <v>80</v>
+        <v>781</v>
       </c>
       <c r="E222" s="2"/>
       <c r="F222" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="G222" t="s" s="2">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="H222" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I222" t="s" s="2">
         <v>92</v>
-      </c>
-      <c r="I222" t="s" s="2">
-        <v>80</v>
       </c>
       <c r="J222" t="s" s="2">
         <v>92</v>
       </c>
       <c r="K222" t="s" s="2">
-        <v>132</v>
+        <v>111</v>
       </c>
       <c r="L222" t="s" s="2">
-        <v>266</v>
+        <v>782</v>
       </c>
       <c r="M222" t="s" s="2">
-        <v>267</v>
+        <v>783</v>
       </c>
       <c r="N222" t="s" s="2">
-        <v>268</v>
+        <v>114</v>
       </c>
       <c r="O222" t="s" s="2">
-        <v>269</v>
+        <v>230</v>
       </c>
       <c r="P222" t="s" s="2">
         <v>80</v>
@@ -29736,19 +29601,19 @@
         <v>80</v>
       </c>
       <c r="AF222" t="s" s="2">
-        <v>270</v>
+        <v>784</v>
       </c>
       <c r="AG222" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH222" t="s" s="2">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="AI222" t="s" s="2">
-        <v>198</v>
+        <v>80</v>
       </c>
       <c r="AJ222" t="s" s="2">
-        <v>103</v>
+        <v>119</v>
       </c>
       <c r="AK222" t="s" s="2">
         <v>80</v>
@@ -29760,7 +29625,7 @@
         <v>80</v>
       </c>
       <c r="AN222" t="s" s="2">
-        <v>271</v>
+        <v>80</v>
       </c>
       <c r="AO222" t="s" s="2">
         <v>80</v>
@@ -29771,10 +29636,10 @@
     </row>
     <row r="223" hidden="true">
       <c r="A223" t="s" s="2">
-        <v>752</v>
+        <v>785</v>
       </c>
       <c r="B223" t="s" s="2">
-        <v>753</v>
+        <v>785</v>
       </c>
       <c r="C223" s="2"/>
       <c r="D223" t="s" s="2">
@@ -29794,20 +29659,18 @@
         <v>80</v>
       </c>
       <c r="J223" t="s" s="2">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="K223" t="s" s="2">
-        <v>105</v>
+        <v>241</v>
       </c>
       <c r="L223" t="s" s="2">
-        <v>273</v>
+        <v>786</v>
       </c>
       <c r="M223" t="s" s="2">
-        <v>274</v>
-      </c>
-      <c r="N223" t="s" s="2">
-        <v>275</v>
-      </c>
+        <v>787</v>
+      </c>
+      <c r="N223" s="2"/>
       <c r="O223" s="2"/>
       <c r="P223" t="s" s="2">
         <v>80</v>
@@ -29832,13 +29695,13 @@
         <v>80</v>
       </c>
       <c r="X223" t="s" s="2">
-        <v>80</v>
+        <v>156</v>
       </c>
       <c r="Y223" t="s" s="2">
-        <v>80</v>
+        <v>788</v>
       </c>
       <c r="Z223" t="s" s="2">
-        <v>80</v>
+        <v>789</v>
       </c>
       <c r="AA223" t="s" s="2">
         <v>80</v>
@@ -29856,7 +29719,7 @@
         <v>80</v>
       </c>
       <c r="AF223" t="s" s="2">
-        <v>276</v>
+        <v>785</v>
       </c>
       <c r="AG223" t="s" s="2">
         <v>81</v>
@@ -29865,7 +29728,7 @@
         <v>91</v>
       </c>
       <c r="AI223" t="s" s="2">
-        <v>198</v>
+        <v>790</v>
       </c>
       <c r="AJ223" t="s" s="2">
         <v>103</v>
@@ -29877,10 +29740,10 @@
         <v>80</v>
       </c>
       <c r="AM223" t="s" s="2">
-        <v>80</v>
+        <v>791</v>
       </c>
       <c r="AN223" t="s" s="2">
-        <v>277</v>
+        <v>252</v>
       </c>
       <c r="AO223" t="s" s="2">
         <v>80</v>
@@ -29889,12 +29752,12 @@
         <v>80</v>
       </c>
     </row>
-    <row r="224">
+    <row r="224" hidden="true">
       <c r="A224" t="s" s="2">
-        <v>754</v>
+        <v>792</v>
       </c>
       <c r="B224" t="s" s="2">
-        <v>755</v>
+        <v>792</v>
       </c>
       <c r="C224" s="2"/>
       <c r="D224" t="s" s="2">
@@ -29902,35 +29765,31 @@
       </c>
       <c r="E224" s="2"/>
       <c r="F224" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="G224" t="s" s="2">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="H224" t="s" s="2">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="I224" t="s" s="2">
         <v>80</v>
       </c>
       <c r="J224" t="s" s="2">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="K224" t="s" s="2">
-        <v>166</v>
+        <v>793</v>
       </c>
       <c r="L224" t="s" s="2">
-        <v>279</v>
+        <v>794</v>
       </c>
       <c r="M224" t="s" s="2">
-        <v>280</v>
-      </c>
-      <c r="N224" t="s" s="2">
-        <v>402</v>
-      </c>
-      <c r="O224" t="s" s="2">
-        <v>281</v>
-      </c>
+        <v>795</v>
+      </c>
+      <c r="N224" s="2"/>
+      <c r="O224" s="2"/>
       <c r="P224" t="s" s="2">
         <v>80</v>
       </c>
@@ -29978,16 +29837,16 @@
         <v>80</v>
       </c>
       <c r="AF224" t="s" s="2">
-        <v>282</v>
+        <v>792</v>
       </c>
       <c r="AG224" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH224" t="s" s="2">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="AI224" t="s" s="2">
-        <v>198</v>
+        <v>790</v>
       </c>
       <c r="AJ224" t="s" s="2">
         <v>103</v>
@@ -30002,7 +29861,7 @@
         <v>80</v>
       </c>
       <c r="AN224" t="s" s="2">
-        <v>283</v>
+        <v>80</v>
       </c>
       <c r="AO224" t="s" s="2">
         <v>80</v>
@@ -30013,10 +29872,10 @@
     </row>
     <row r="225" hidden="true">
       <c r="A225" t="s" s="2">
-        <v>756</v>
+        <v>796</v>
       </c>
       <c r="B225" t="s" s="2">
-        <v>757</v>
+        <v>796</v>
       </c>
       <c r="C225" s="2"/>
       <c r="D225" t="s" s="2">
@@ -30036,23 +29895,19 @@
         <v>80</v>
       </c>
       <c r="J225" t="s" s="2">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="K225" t="s" s="2">
-        <v>105</v>
+        <v>241</v>
       </c>
       <c r="L225" t="s" s="2">
-        <v>285</v>
+        <v>797</v>
       </c>
       <c r="M225" t="s" s="2">
-        <v>286</v>
-      </c>
-      <c r="N225" t="s" s="2">
-        <v>402</v>
-      </c>
-      <c r="O225" t="s" s="2">
-        <v>287</v>
-      </c>
+        <v>798</v>
+      </c>
+      <c r="N225" s="2"/>
+      <c r="O225" s="2"/>
       <c r="P225" t="s" s="2">
         <v>80</v>
       </c>
@@ -30076,13 +29931,13 @@
         <v>80</v>
       </c>
       <c r="X225" t="s" s="2">
-        <v>80</v>
+        <v>156</v>
       </c>
       <c r="Y225" t="s" s="2">
-        <v>80</v>
+        <v>799</v>
       </c>
       <c r="Z225" t="s" s="2">
-        <v>80</v>
+        <v>800</v>
       </c>
       <c r="AA225" t="s" s="2">
         <v>80</v>
@@ -30100,7 +29955,7 @@
         <v>80</v>
       </c>
       <c r="AF225" t="s" s="2">
-        <v>288</v>
+        <v>796</v>
       </c>
       <c r="AG225" t="s" s="2">
         <v>81</v>
@@ -30109,7 +29964,7 @@
         <v>91</v>
       </c>
       <c r="AI225" t="s" s="2">
-        <v>198</v>
+        <v>80</v>
       </c>
       <c r="AJ225" t="s" s="2">
         <v>103</v>
@@ -30124,7 +29979,7 @@
         <v>80</v>
       </c>
       <c r="AN225" t="s" s="2">
-        <v>289</v>
+        <v>80</v>
       </c>
       <c r="AO225" t="s" s="2">
         <v>80</v>
@@ -30135,10 +29990,10 @@
     </row>
     <row r="226" hidden="true">
       <c r="A226" t="s" s="2">
-        <v>758</v>
+        <v>801</v>
       </c>
       <c r="B226" t="s" s="2">
-        <v>759</v>
+        <v>801</v>
       </c>
       <c r="C226" s="2"/>
       <c r="D226" t="s" s="2">
@@ -30149,7 +30004,7 @@
         <v>81</v>
       </c>
       <c r="G226" t="s" s="2">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="H226" t="s" s="2">
         <v>80</v>
@@ -30158,23 +30013,21 @@
         <v>80</v>
       </c>
       <c r="J226" t="s" s="2">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="K226" t="s" s="2">
-        <v>291</v>
+        <v>774</v>
       </c>
       <c r="L226" t="s" s="2">
-        <v>292</v>
+        <v>802</v>
       </c>
       <c r="M226" t="s" s="2">
-        <v>293</v>
+        <v>803</v>
       </c>
       <c r="N226" t="s" s="2">
-        <v>294</v>
-      </c>
-      <c r="O226" t="s" s="2">
-        <v>295</v>
-      </c>
+        <v>804</v>
+      </c>
+      <c r="O226" s="2"/>
       <c r="P226" t="s" s="2">
         <v>80</v>
       </c>
@@ -30222,19 +30075,19 @@
         <v>80</v>
       </c>
       <c r="AF226" t="s" s="2">
-        <v>296</v>
+        <v>801</v>
       </c>
       <c r="AG226" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH226" t="s" s="2">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="AI226" t="s" s="2">
-        <v>198</v>
+        <v>80</v>
       </c>
       <c r="AJ226" t="s" s="2">
-        <v>103</v>
+        <v>805</v>
       </c>
       <c r="AK226" t="s" s="2">
         <v>80</v>
@@ -30246,7 +30099,7 @@
         <v>80</v>
       </c>
       <c r="AN226" t="s" s="2">
-        <v>297</v>
+        <v>80</v>
       </c>
       <c r="AO226" t="s" s="2">
         <v>80</v>
@@ -30257,10 +30110,10 @@
     </row>
     <row r="227" hidden="true">
       <c r="A227" t="s" s="2">
-        <v>760</v>
+        <v>806</v>
       </c>
       <c r="B227" t="s" s="2">
-        <v>761</v>
+        <v>806</v>
       </c>
       <c r="C227" s="2"/>
       <c r="D227" t="s" s="2">
@@ -30280,23 +30133,19 @@
         <v>80</v>
       </c>
       <c r="J227" t="s" s="2">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="K227" t="s" s="2">
         <v>105</v>
       </c>
       <c r="L227" t="s" s="2">
-        <v>299</v>
+        <v>106</v>
       </c>
       <c r="M227" t="s" s="2">
-        <v>300</v>
-      </c>
-      <c r="N227" t="s" s="2">
-        <v>301</v>
-      </c>
-      <c r="O227" t="s" s="2">
-        <v>302</v>
-      </c>
+        <v>107</v>
+      </c>
+      <c r="N227" s="2"/>
+      <c r="O227" s="2"/>
       <c r="P227" t="s" s="2">
         <v>80</v>
       </c>
@@ -30344,7 +30193,7 @@
         <v>80</v>
       </c>
       <c r="AF227" t="s" s="2">
-        <v>303</v>
+        <v>108</v>
       </c>
       <c r="AG227" t="s" s="2">
         <v>81</v>
@@ -30353,10 +30202,10 @@
         <v>91</v>
       </c>
       <c r="AI227" t="s" s="2">
-        <v>198</v>
+        <v>80</v>
       </c>
       <c r="AJ227" t="s" s="2">
-        <v>103</v>
+        <v>80</v>
       </c>
       <c r="AK227" t="s" s="2">
         <v>80</v>
@@ -30368,7 +30217,7 @@
         <v>80</v>
       </c>
       <c r="AN227" t="s" s="2">
-        <v>304</v>
+        <v>80</v>
       </c>
       <c r="AO227" t="s" s="2">
         <v>80</v>
@@ -30379,21 +30228,21 @@
     </row>
     <row r="228" hidden="true">
       <c r="A228" t="s" s="2">
-        <v>762</v>
+        <v>807</v>
       </c>
       <c r="B228" t="s" s="2">
-        <v>763</v>
+        <v>807</v>
       </c>
       <c r="C228" s="2"/>
       <c r="D228" t="s" s="2">
-        <v>80</v>
+        <v>110</v>
       </c>
       <c r="E228" s="2"/>
       <c r="F228" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G228" t="s" s="2">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="H228" t="s" s="2">
         <v>80</v>
@@ -30402,23 +30251,21 @@
         <v>80</v>
       </c>
       <c r="J228" t="s" s="2">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="K228" t="s" s="2">
-        <v>764</v>
+        <v>111</v>
       </c>
       <c r="L228" t="s" s="2">
-        <v>765</v>
+        <v>112</v>
       </c>
       <c r="M228" t="s" s="2">
-        <v>766</v>
+        <v>113</v>
       </c>
       <c r="N228" t="s" s="2">
-        <v>767</v>
-      </c>
-      <c r="O228" t="s" s="2">
-        <v>768</v>
-      </c>
+        <v>114</v>
+      </c>
+      <c r="O228" s="2"/>
       <c r="P228" t="s" s="2">
         <v>80</v>
       </c>
@@ -30466,19 +30313,19 @@
         <v>80</v>
       </c>
       <c r="AF228" t="s" s="2">
-        <v>769</v>
+        <v>118</v>
       </c>
       <c r="AG228" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH228" t="s" s="2">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="AI228" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ228" t="s" s="2">
-        <v>103</v>
+        <v>119</v>
       </c>
       <c r="AK228" t="s" s="2">
         <v>80</v>
@@ -30490,7 +30337,7 @@
         <v>80</v>
       </c>
       <c r="AN228" t="s" s="2">
-        <v>770</v>
+        <v>80</v>
       </c>
       <c r="AO228" t="s" s="2">
         <v>80</v>
@@ -30501,21 +30348,21 @@
     </row>
     <row r="229" hidden="true">
       <c r="A229" t="s" s="2">
-        <v>771</v>
+        <v>808</v>
       </c>
       <c r="B229" t="s" s="2">
-        <v>772</v>
+        <v>808</v>
       </c>
       <c r="C229" s="2"/>
       <c r="D229" t="s" s="2">
-        <v>80</v>
+        <v>781</v>
       </c>
       <c r="E229" s="2"/>
       <c r="F229" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G229" t="s" s="2">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="H229" t="s" s="2">
         <v>80</v>
@@ -30527,24 +30374,24 @@
         <v>92</v>
       </c>
       <c r="K229" t="s" s="2">
-        <v>166</v>
+        <v>111</v>
       </c>
       <c r="L229" t="s" s="2">
-        <v>773</v>
+        <v>782</v>
       </c>
       <c r="M229" t="s" s="2">
-        <v>774</v>
-      </c>
-      <c r="N229" s="2"/>
+        <v>783</v>
+      </c>
+      <c r="N229" t="s" s="2">
+        <v>114</v>
+      </c>
       <c r="O229" t="s" s="2">
-        <v>775</v>
+        <v>230</v>
       </c>
       <c r="P229" t="s" s="2">
         <v>80</v>
       </c>
-      <c r="Q229" t="s" s="2">
-        <v>776</v>
-      </c>
+      <c r="Q229" s="2"/>
       <c r="R229" t="s" s="2">
         <v>80</v>
       </c>
@@ -30564,13 +30411,13 @@
         <v>80</v>
       </c>
       <c r="X229" t="s" s="2">
-        <v>245</v>
+        <v>80</v>
       </c>
       <c r="Y229" t="s" s="2">
-        <v>777</v>
+        <v>80</v>
       </c>
       <c r="Z229" t="s" s="2">
-        <v>778</v>
+        <v>80</v>
       </c>
       <c r="AA229" t="s" s="2">
         <v>80</v>
@@ -30588,19 +30435,19 @@
         <v>80</v>
       </c>
       <c r="AF229" t="s" s="2">
-        <v>779</v>
+        <v>784</v>
       </c>
       <c r="AG229" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH229" t="s" s="2">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="AI229" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ229" t="s" s="2">
-        <v>103</v>
+        <v>119</v>
       </c>
       <c r="AK229" t="s" s="2">
         <v>80</v>
@@ -30612,7 +30459,7 @@
         <v>80</v>
       </c>
       <c r="AN229" t="s" s="2">
-        <v>780</v>
+        <v>80</v>
       </c>
       <c r="AO229" t="s" s="2">
         <v>80</v>
@@ -30623,10 +30470,10 @@
     </row>
     <row r="230" hidden="true">
       <c r="A230" t="s" s="2">
-        <v>781</v>
+        <v>809</v>
       </c>
       <c r="B230" t="s" s="2">
-        <v>782</v>
+        <v>809</v>
       </c>
       <c r="C230" s="2"/>
       <c r="D230" t="s" s="2">
@@ -30637,7 +30484,7 @@
         <v>81</v>
       </c>
       <c r="G230" t="s" s="2">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="H230" t="s" s="2">
         <v>80</v>
@@ -30649,18 +30496,16 @@
         <v>92</v>
       </c>
       <c r="K230" t="s" s="2">
-        <v>105</v>
+        <v>241</v>
       </c>
       <c r="L230" t="s" s="2">
-        <v>783</v>
+        <v>810</v>
       </c>
       <c r="M230" t="s" s="2">
-        <v>784</v>
+        <v>811</v>
       </c>
       <c r="N230" s="2"/>
-      <c r="O230" t="s" s="2">
-        <v>785</v>
-      </c>
+      <c r="O230" s="2"/>
       <c r="P230" t="s" s="2">
         <v>80</v>
       </c>
@@ -30684,13 +30529,13 @@
         <v>80</v>
       </c>
       <c r="X230" t="s" s="2">
-        <v>80</v>
+        <v>156</v>
       </c>
       <c r="Y230" t="s" s="2">
-        <v>80</v>
+        <v>812</v>
       </c>
       <c r="Z230" t="s" s="2">
-        <v>80</v>
+        <v>813</v>
       </c>
       <c r="AA230" t="s" s="2">
         <v>80</v>
@@ -30708,16 +30553,16 @@
         <v>80</v>
       </c>
       <c r="AF230" t="s" s="2">
-        <v>786</v>
+        <v>809</v>
       </c>
       <c r="AG230" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH230" t="s" s="2">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="AI230" t="s" s="2">
-        <v>80</v>
+        <v>814</v>
       </c>
       <c r="AJ230" t="s" s="2">
         <v>103</v>
@@ -30726,16 +30571,16 @@
         <v>80</v>
       </c>
       <c r="AL230" t="s" s="2">
-        <v>80</v>
+        <v>815</v>
       </c>
       <c r="AM230" t="s" s="2">
-        <v>80</v>
+        <v>331</v>
       </c>
       <c r="AN230" t="s" s="2">
-        <v>787</v>
+        <v>80</v>
       </c>
       <c r="AO230" t="s" s="2">
-        <v>80</v>
+        <v>816</v>
       </c>
       <c r="AP230" t="s" s="2">
         <v>80</v>
@@ -30743,10 +30588,10 @@
     </row>
     <row r="231" hidden="true">
       <c r="A231" t="s" s="2">
-        <v>788</v>
+        <v>817</v>
       </c>
       <c r="B231" t="s" s="2">
-        <v>789</v>
+        <v>817</v>
       </c>
       <c r="C231" s="2"/>
       <c r="D231" t="s" s="2">
@@ -30757,7 +30602,7 @@
         <v>81</v>
       </c>
       <c r="G231" t="s" s="2">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="H231" t="s" s="2">
         <v>80</v>
@@ -30769,18 +30614,16 @@
         <v>92</v>
       </c>
       <c r="K231" t="s" s="2">
-        <v>132</v>
+        <v>818</v>
       </c>
       <c r="L231" t="s" s="2">
-        <v>790</v>
+        <v>819</v>
       </c>
       <c r="M231" t="s" s="2">
-        <v>791</v>
+        <v>820</v>
       </c>
       <c r="N231" s="2"/>
-      <c r="O231" t="s" s="2">
-        <v>792</v>
-      </c>
+      <c r="O231" s="2"/>
       <c r="P231" t="s" s="2">
         <v>80</v>
       </c>
@@ -30828,16 +30671,16 @@
         <v>80</v>
       </c>
       <c r="AF231" t="s" s="2">
-        <v>793</v>
+        <v>817</v>
       </c>
       <c r="AG231" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH231" t="s" s="2">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="AI231" t="s" s="2">
-        <v>794</v>
+        <v>814</v>
       </c>
       <c r="AJ231" t="s" s="2">
         <v>103</v>
@@ -30852,21 +30695,21 @@
         <v>80</v>
       </c>
       <c r="AN231" t="s" s="2">
-        <v>787</v>
+        <v>80</v>
       </c>
       <c r="AO231" t="s" s="2">
-        <v>80</v>
+        <v>816</v>
       </c>
       <c r="AP231" t="s" s="2">
         <v>80</v>
       </c>
     </row>
-    <row r="232" hidden="true">
+    <row r="232">
       <c r="A232" t="s" s="2">
-        <v>795</v>
+        <v>821</v>
       </c>
       <c r="B232" t="s" s="2">
-        <v>796</v>
+        <v>821</v>
       </c>
       <c r="C232" s="2"/>
       <c r="D232" t="s" s="2">
@@ -30877,32 +30720,28 @@
         <v>81</v>
       </c>
       <c r="G232" t="s" s="2">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="H232" t="s" s="2">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="I232" t="s" s="2">
         <v>80</v>
       </c>
       <c r="J232" t="s" s="2">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="K232" t="s" s="2">
-        <v>166</v>
+        <v>822</v>
       </c>
       <c r="L232" t="s" s="2">
-        <v>797</v>
+        <v>823</v>
       </c>
       <c r="M232" t="s" s="2">
-        <v>798</v>
-      </c>
-      <c r="N232" t="s" s="2">
-        <v>799</v>
-      </c>
-      <c r="O232" t="s" s="2">
-        <v>800</v>
-      </c>
+        <v>824</v>
+      </c>
+      <c r="N232" s="2"/>
+      <c r="O232" s="2"/>
       <c r="P232" t="s" s="2">
         <v>80</v>
       </c>
@@ -30950,13 +30789,13 @@
         <v>80</v>
       </c>
       <c r="AF232" t="s" s="2">
-        <v>801</v>
+        <v>821</v>
       </c>
       <c r="AG232" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH232" t="s" s="2">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="AI232" t="s" s="2">
         <v>80</v>
@@ -30965,2166 +30804,26 @@
         <v>103</v>
       </c>
       <c r="AK232" t="s" s="2">
-        <v>80</v>
+        <v>825</v>
       </c>
       <c r="AL232" t="s" s="2">
-        <v>80</v>
+        <v>826</v>
       </c>
       <c r="AM232" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN232" t="s" s="2">
-        <v>787</v>
+        <v>827</v>
       </c>
       <c r="AO232" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AP232" t="s" s="2">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="233" hidden="true">
-      <c r="A233" t="s" s="2">
-        <v>802</v>
-      </c>
-      <c r="B233" t="s" s="2">
-        <v>802</v>
-      </c>
-      <c r="C233" s="2"/>
-      <c r="D233" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="E233" s="2"/>
-      <c r="F233" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="G233" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="H233" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="I233" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="J233" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="K233" t="s" s="2">
-        <v>803</v>
-      </c>
-      <c r="L233" t="s" s="2">
-        <v>804</v>
-      </c>
-      <c r="M233" t="s" s="2">
-        <v>805</v>
-      </c>
-      <c r="N233" t="s" s="2">
-        <v>806</v>
-      </c>
-      <c r="O233" s="2"/>
-      <c r="P233" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Q233" s="2"/>
-      <c r="R233" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="S233" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="T233" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="U233" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="V233" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="W233" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="X233" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Y233" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Z233" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AA233" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB233" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC233" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AD233" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE233" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AF233" t="s" s="2">
-        <v>802</v>
-      </c>
-      <c r="AG233" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH233" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="AI233" t="s" s="2">
-        <v>807</v>
-      </c>
-      <c r="AJ233" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="AK233" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AL233" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AM233" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN233" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AO233" t="s" s="2">
-        <v>808</v>
-      </c>
-      <c r="AP233" t="s" s="2">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="234">
-      <c r="A234" t="s" s="2">
-        <v>809</v>
-      </c>
-      <c r="B234" t="s" s="2">
-        <v>809</v>
-      </c>
-      <c r="C234" s="2"/>
-      <c r="D234" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="E234" s="2"/>
-      <c r="F234" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="G234" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="H234" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="I234" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="J234" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="K234" t="s" s="2">
-        <v>226</v>
-      </c>
-      <c r="L234" t="s" s="2">
-        <v>810</v>
-      </c>
-      <c r="M234" t="s" s="2">
-        <v>811</v>
-      </c>
-      <c r="N234" s="2"/>
-      <c r="O234" s="2"/>
-      <c r="P234" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Q234" s="2"/>
-      <c r="R234" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="S234" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="T234" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="U234" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="V234" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="W234" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="X234" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Y234" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Z234" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AA234" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB234" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC234" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AD234" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE234" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AF234" t="s" s="2">
-        <v>809</v>
-      </c>
-      <c r="AG234" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH234" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="AI234" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AJ234" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="AK234" t="s" s="2">
-        <v>812</v>
-      </c>
-      <c r="AL234" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AM234" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN234" t="s" s="2">
-        <v>813</v>
-      </c>
-      <c r="AO234" t="s" s="2">
-        <v>814</v>
-      </c>
-      <c r="AP234" t="s" s="2">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="235" hidden="true">
-      <c r="A235" t="s" s="2">
-        <v>815</v>
-      </c>
-      <c r="B235" t="s" s="2">
-        <v>815</v>
-      </c>
-      <c r="C235" s="2"/>
-      <c r="D235" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="E235" s="2"/>
-      <c r="F235" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="G235" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="H235" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="I235" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="J235" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="K235" t="s" s="2">
-        <v>816</v>
-      </c>
-      <c r="L235" t="s" s="2">
-        <v>817</v>
-      </c>
-      <c r="M235" t="s" s="2">
-        <v>818</v>
-      </c>
-      <c r="N235" s="2"/>
-      <c r="O235" s="2"/>
-      <c r="P235" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Q235" s="2"/>
-      <c r="R235" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="S235" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="T235" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="U235" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="V235" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="W235" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="X235" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Y235" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Z235" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AA235" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB235" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC235" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AD235" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE235" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AF235" t="s" s="2">
-        <v>815</v>
-      </c>
-      <c r="AG235" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH235" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="AI235" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AJ235" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="AK235" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AL235" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AM235" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN235" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AO235" t="s" s="2">
-        <v>819</v>
-      </c>
-      <c r="AP235" t="s" s="2">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="236" hidden="true">
-      <c r="A236" t="s" s="2">
-        <v>820</v>
-      </c>
-      <c r="B236" t="s" s="2">
-        <v>820</v>
-      </c>
-      <c r="C236" s="2"/>
-      <c r="D236" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="E236" s="2"/>
-      <c r="F236" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="G236" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="H236" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="I236" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="J236" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="K236" t="s" s="2">
-        <v>816</v>
-      </c>
-      <c r="L236" t="s" s="2">
-        <v>821</v>
-      </c>
-      <c r="M236" t="s" s="2">
-        <v>822</v>
-      </c>
-      <c r="N236" s="2"/>
-      <c r="O236" s="2"/>
-      <c r="P236" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Q236" s="2"/>
-      <c r="R236" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="S236" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="T236" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="U236" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="V236" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="W236" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="X236" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Y236" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Z236" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AA236" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB236" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC236" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AD236" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE236" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AF236" t="s" s="2">
-        <v>820</v>
-      </c>
-      <c r="AG236" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH236" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="AI236" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AJ236" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="AK236" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AL236" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AM236" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN236" t="s" s="2">
-        <v>823</v>
-      </c>
-      <c r="AO236" t="s" s="2">
-        <v>824</v>
-      </c>
-      <c r="AP236" t="s" s="2">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="237" hidden="true">
-      <c r="A237" t="s" s="2">
-        <v>825</v>
-      </c>
-      <c r="B237" t="s" s="2">
-        <v>825</v>
-      </c>
-      <c r="C237" s="2"/>
-      <c r="D237" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="E237" s="2"/>
-      <c r="F237" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="G237" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="H237" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="I237" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="J237" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="K237" t="s" s="2">
-        <v>826</v>
-      </c>
-      <c r="L237" t="s" s="2">
-        <v>827</v>
-      </c>
-      <c r="M237" t="s" s="2">
-        <v>828</v>
-      </c>
-      <c r="N237" s="2"/>
-      <c r="O237" s="2"/>
-      <c r="P237" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Q237" s="2"/>
-      <c r="R237" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="S237" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="T237" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="U237" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="V237" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="W237" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="X237" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Y237" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Z237" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AA237" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB237" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC237" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AD237" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE237" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AF237" t="s" s="2">
-        <v>825</v>
-      </c>
-      <c r="AG237" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH237" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AI237" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AJ237" t="s" s="2">
-        <v>829</v>
-      </c>
-      <c r="AK237" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AL237" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AM237" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN237" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AO237" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AP237" t="s" s="2">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="238" hidden="true">
-      <c r="A238" t="s" s="2">
-        <v>830</v>
-      </c>
-      <c r="B238" t="s" s="2">
-        <v>830</v>
-      </c>
-      <c r="C238" s="2"/>
-      <c r="D238" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="E238" s="2"/>
-      <c r="F238" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="G238" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="H238" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="I238" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="J238" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="K238" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="L238" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="M238" t="s" s="2">
-        <v>107</v>
-      </c>
-      <c r="N238" s="2"/>
-      <c r="O238" s="2"/>
-      <c r="P238" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Q238" s="2"/>
-      <c r="R238" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="S238" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="T238" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="U238" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="V238" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="W238" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="X238" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Y238" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Z238" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AA238" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB238" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC238" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AD238" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE238" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AF238" t="s" s="2">
-        <v>108</v>
-      </c>
-      <c r="AG238" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH238" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="AI238" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AJ238" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AK238" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AL238" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AM238" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN238" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AO238" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AP238" t="s" s="2">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="239" hidden="true">
-      <c r="A239" t="s" s="2">
-        <v>831</v>
-      </c>
-      <c r="B239" t="s" s="2">
-        <v>831</v>
-      </c>
-      <c r="C239" s="2"/>
-      <c r="D239" t="s" s="2">
-        <v>110</v>
-      </c>
-      <c r="E239" s="2"/>
-      <c r="F239" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="G239" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="H239" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="I239" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="J239" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="K239" t="s" s="2">
-        <v>111</v>
-      </c>
-      <c r="L239" t="s" s="2">
-        <v>112</v>
-      </c>
-      <c r="M239" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="N239" t="s" s="2">
-        <v>114</v>
-      </c>
-      <c r="O239" s="2"/>
-      <c r="P239" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Q239" s="2"/>
-      <c r="R239" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="S239" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="T239" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="U239" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="V239" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="W239" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="X239" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Y239" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Z239" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AA239" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB239" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC239" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AD239" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE239" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AF239" t="s" s="2">
-        <v>118</v>
-      </c>
-      <c r="AG239" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH239" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AI239" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AJ239" t="s" s="2">
-        <v>119</v>
-      </c>
-      <c r="AK239" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AL239" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AM239" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN239" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AO239" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AP239" t="s" s="2">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="240" hidden="true">
-      <c r="A240" t="s" s="2">
-        <v>832</v>
-      </c>
-      <c r="B240" t="s" s="2">
-        <v>832</v>
-      </c>
-      <c r="C240" s="2"/>
-      <c r="D240" t="s" s="2">
-        <v>833</v>
-      </c>
-      <c r="E240" s="2"/>
-      <c r="F240" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="G240" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="H240" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="I240" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="J240" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="K240" t="s" s="2">
-        <v>111</v>
-      </c>
-      <c r="L240" t="s" s="2">
-        <v>834</v>
-      </c>
-      <c r="M240" t="s" s="2">
-        <v>835</v>
-      </c>
-      <c r="N240" t="s" s="2">
-        <v>114</v>
-      </c>
-      <c r="O240" t="s" s="2">
-        <v>230</v>
-      </c>
-      <c r="P240" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Q240" s="2"/>
-      <c r="R240" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="S240" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="T240" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="U240" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="V240" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="W240" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="X240" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Y240" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Z240" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AA240" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB240" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC240" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AD240" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE240" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AF240" t="s" s="2">
-        <v>836</v>
-      </c>
-      <c r="AG240" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH240" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AI240" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AJ240" t="s" s="2">
-        <v>119</v>
-      </c>
-      <c r="AK240" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AL240" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AM240" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN240" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AO240" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AP240" t="s" s="2">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="241" hidden="true">
-      <c r="A241" t="s" s="2">
-        <v>837</v>
-      </c>
-      <c r="B241" t="s" s="2">
-        <v>837</v>
-      </c>
-      <c r="C241" s="2"/>
-      <c r="D241" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="E241" s="2"/>
-      <c r="F241" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="G241" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="H241" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="I241" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="J241" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="K241" t="s" s="2">
-        <v>241</v>
-      </c>
-      <c r="L241" t="s" s="2">
-        <v>838</v>
-      </c>
-      <c r="M241" t="s" s="2">
-        <v>839</v>
-      </c>
-      <c r="N241" s="2"/>
-      <c r="O241" s="2"/>
-      <c r="P241" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Q241" s="2"/>
-      <c r="R241" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="S241" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="T241" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="U241" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="V241" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="W241" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="X241" t="s" s="2">
-        <v>156</v>
-      </c>
-      <c r="Y241" t="s" s="2">
-        <v>840</v>
-      </c>
-      <c r="Z241" t="s" s="2">
-        <v>841</v>
-      </c>
-      <c r="AA241" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB241" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC241" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AD241" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE241" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AF241" t="s" s="2">
-        <v>837</v>
-      </c>
-      <c r="AG241" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH241" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="AI241" t="s" s="2">
-        <v>842</v>
-      </c>
-      <c r="AJ241" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="AK241" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AL241" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AM241" t="s" s="2">
-        <v>843</v>
-      </c>
-      <c r="AN241" t="s" s="2">
-        <v>252</v>
-      </c>
-      <c r="AO241" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AP241" t="s" s="2">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="242" hidden="true">
-      <c r="A242" t="s" s="2">
-        <v>844</v>
-      </c>
-      <c r="B242" t="s" s="2">
-        <v>844</v>
-      </c>
-      <c r="C242" s="2"/>
-      <c r="D242" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="E242" s="2"/>
-      <c r="F242" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="G242" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="H242" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="I242" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="J242" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="K242" t="s" s="2">
-        <v>845</v>
-      </c>
-      <c r="L242" t="s" s="2">
-        <v>846</v>
-      </c>
-      <c r="M242" t="s" s="2">
-        <v>847</v>
-      </c>
-      <c r="N242" s="2"/>
-      <c r="O242" s="2"/>
-      <c r="P242" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Q242" s="2"/>
-      <c r="R242" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="S242" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="T242" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="U242" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="V242" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="W242" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="X242" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Y242" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Z242" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AA242" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB242" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC242" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AD242" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE242" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AF242" t="s" s="2">
-        <v>844</v>
-      </c>
-      <c r="AG242" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH242" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AI242" t="s" s="2">
-        <v>842</v>
-      </c>
-      <c r="AJ242" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="AK242" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AL242" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AM242" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN242" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AO242" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AP242" t="s" s="2">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="243" hidden="true">
-      <c r="A243" t="s" s="2">
-        <v>848</v>
-      </c>
-      <c r="B243" t="s" s="2">
-        <v>848</v>
-      </c>
-      <c r="C243" s="2"/>
-      <c r="D243" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="E243" s="2"/>
-      <c r="F243" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="G243" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="H243" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="I243" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="J243" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="K243" t="s" s="2">
-        <v>241</v>
-      </c>
-      <c r="L243" t="s" s="2">
-        <v>849</v>
-      </c>
-      <c r="M243" t="s" s="2">
-        <v>850</v>
-      </c>
-      <c r="N243" s="2"/>
-      <c r="O243" s="2"/>
-      <c r="P243" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Q243" s="2"/>
-      <c r="R243" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="S243" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="T243" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="U243" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="V243" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="W243" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="X243" t="s" s="2">
-        <v>156</v>
-      </c>
-      <c r="Y243" t="s" s="2">
-        <v>851</v>
-      </c>
-      <c r="Z243" t="s" s="2">
-        <v>852</v>
-      </c>
-      <c r="AA243" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB243" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC243" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AD243" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE243" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AF243" t="s" s="2">
-        <v>848</v>
-      </c>
-      <c r="AG243" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH243" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="AI243" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AJ243" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="AK243" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AL243" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AM243" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN243" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AO243" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AP243" t="s" s="2">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="244" hidden="true">
-      <c r="A244" t="s" s="2">
-        <v>853</v>
-      </c>
-      <c r="B244" t="s" s="2">
-        <v>853</v>
-      </c>
-      <c r="C244" s="2"/>
-      <c r="D244" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="E244" s="2"/>
-      <c r="F244" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="G244" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="H244" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="I244" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="J244" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="K244" t="s" s="2">
-        <v>826</v>
-      </c>
-      <c r="L244" t="s" s="2">
-        <v>854</v>
-      </c>
-      <c r="M244" t="s" s="2">
-        <v>855</v>
-      </c>
-      <c r="N244" t="s" s="2">
-        <v>856</v>
-      </c>
-      <c r="O244" s="2"/>
-      <c r="P244" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Q244" s="2"/>
-      <c r="R244" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="S244" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="T244" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="U244" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="V244" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="W244" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="X244" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Y244" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Z244" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AA244" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB244" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC244" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AD244" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE244" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AF244" t="s" s="2">
-        <v>853</v>
-      </c>
-      <c r="AG244" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH244" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AI244" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AJ244" t="s" s="2">
-        <v>857</v>
-      </c>
-      <c r="AK244" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AL244" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AM244" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN244" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AO244" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AP244" t="s" s="2">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="245" hidden="true">
-      <c r="A245" t="s" s="2">
-        <v>858</v>
-      </c>
-      <c r="B245" t="s" s="2">
-        <v>858</v>
-      </c>
-      <c r="C245" s="2"/>
-      <c r="D245" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="E245" s="2"/>
-      <c r="F245" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="G245" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="H245" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="I245" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="J245" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="K245" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="L245" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="M245" t="s" s="2">
-        <v>107</v>
-      </c>
-      <c r="N245" s="2"/>
-      <c r="O245" s="2"/>
-      <c r="P245" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Q245" s="2"/>
-      <c r="R245" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="S245" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="T245" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="U245" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="V245" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="W245" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="X245" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Y245" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Z245" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AA245" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB245" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC245" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AD245" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE245" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AF245" t="s" s="2">
-        <v>108</v>
-      </c>
-      <c r="AG245" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH245" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="AI245" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AJ245" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AK245" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AL245" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AM245" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN245" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AO245" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AP245" t="s" s="2">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="246" hidden="true">
-      <c r="A246" t="s" s="2">
-        <v>859</v>
-      </c>
-      <c r="B246" t="s" s="2">
-        <v>859</v>
-      </c>
-      <c r="C246" s="2"/>
-      <c r="D246" t="s" s="2">
-        <v>110</v>
-      </c>
-      <c r="E246" s="2"/>
-      <c r="F246" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="G246" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="H246" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="I246" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="J246" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="K246" t="s" s="2">
-        <v>111</v>
-      </c>
-      <c r="L246" t="s" s="2">
-        <v>112</v>
-      </c>
-      <c r="M246" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="N246" t="s" s="2">
-        <v>114</v>
-      </c>
-      <c r="O246" s="2"/>
-      <c r="P246" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Q246" s="2"/>
-      <c r="R246" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="S246" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="T246" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="U246" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="V246" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="W246" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="X246" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Y246" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Z246" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AA246" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB246" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC246" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AD246" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE246" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AF246" t="s" s="2">
-        <v>118</v>
-      </c>
-      <c r="AG246" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH246" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AI246" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AJ246" t="s" s="2">
-        <v>119</v>
-      </c>
-      <c r="AK246" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AL246" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AM246" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN246" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AO246" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AP246" t="s" s="2">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="247" hidden="true">
-      <c r="A247" t="s" s="2">
-        <v>860</v>
-      </c>
-      <c r="B247" t="s" s="2">
-        <v>860</v>
-      </c>
-      <c r="C247" s="2"/>
-      <c r="D247" t="s" s="2">
-        <v>833</v>
-      </c>
-      <c r="E247" s="2"/>
-      <c r="F247" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="G247" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="H247" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="I247" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="J247" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="K247" t="s" s="2">
-        <v>111</v>
-      </c>
-      <c r="L247" t="s" s="2">
-        <v>834</v>
-      </c>
-      <c r="M247" t="s" s="2">
-        <v>835</v>
-      </c>
-      <c r="N247" t="s" s="2">
-        <v>114</v>
-      </c>
-      <c r="O247" t="s" s="2">
-        <v>230</v>
-      </c>
-      <c r="P247" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Q247" s="2"/>
-      <c r="R247" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="S247" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="T247" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="U247" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="V247" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="W247" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="X247" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Y247" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Z247" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AA247" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB247" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC247" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AD247" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE247" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AF247" t="s" s="2">
-        <v>836</v>
-      </c>
-      <c r="AG247" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH247" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AI247" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AJ247" t="s" s="2">
-        <v>119</v>
-      </c>
-      <c r="AK247" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AL247" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AM247" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN247" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AO247" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AP247" t="s" s="2">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="248" hidden="true">
-      <c r="A248" t="s" s="2">
-        <v>861</v>
-      </c>
-      <c r="B248" t="s" s="2">
-        <v>861</v>
-      </c>
-      <c r="C248" s="2"/>
-      <c r="D248" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="E248" s="2"/>
-      <c r="F248" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="G248" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="H248" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="I248" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="J248" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="K248" t="s" s="2">
-        <v>241</v>
-      </c>
-      <c r="L248" t="s" s="2">
-        <v>862</v>
-      </c>
-      <c r="M248" t="s" s="2">
-        <v>863</v>
-      </c>
-      <c r="N248" s="2"/>
-      <c r="O248" s="2"/>
-      <c r="P248" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Q248" s="2"/>
-      <c r="R248" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="S248" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="T248" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="U248" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="V248" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="W248" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="X248" t="s" s="2">
-        <v>156</v>
-      </c>
-      <c r="Y248" t="s" s="2">
-        <v>864</v>
-      </c>
-      <c r="Z248" t="s" s="2">
-        <v>865</v>
-      </c>
-      <c r="AA248" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB248" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC248" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AD248" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE248" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AF248" t="s" s="2">
-        <v>861</v>
-      </c>
-      <c r="AG248" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH248" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AI248" t="s" s="2">
-        <v>866</v>
-      </c>
-      <c r="AJ248" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="AK248" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AL248" t="s" s="2">
-        <v>867</v>
-      </c>
-      <c r="AM248" t="s" s="2">
-        <v>331</v>
-      </c>
-      <c r="AN248" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AO248" t="s" s="2">
-        <v>868</v>
-      </c>
-      <c r="AP248" t="s" s="2">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="249" hidden="true">
-      <c r="A249" t="s" s="2">
-        <v>869</v>
-      </c>
-      <c r="B249" t="s" s="2">
-        <v>869</v>
-      </c>
-      <c r="C249" s="2"/>
-      <c r="D249" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="E249" s="2"/>
-      <c r="F249" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="G249" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="H249" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="I249" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="J249" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="K249" t="s" s="2">
-        <v>870</v>
-      </c>
-      <c r="L249" t="s" s="2">
-        <v>871</v>
-      </c>
-      <c r="M249" t="s" s="2">
-        <v>872</v>
-      </c>
-      <c r="N249" s="2"/>
-      <c r="O249" s="2"/>
-      <c r="P249" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Q249" s="2"/>
-      <c r="R249" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="S249" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="T249" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="U249" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="V249" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="W249" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="X249" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Y249" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Z249" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AA249" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB249" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC249" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AD249" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE249" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AF249" t="s" s="2">
-        <v>869</v>
-      </c>
-      <c r="AG249" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH249" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AI249" t="s" s="2">
-        <v>866</v>
-      </c>
-      <c r="AJ249" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="AK249" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AL249" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AM249" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN249" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AO249" t="s" s="2">
-        <v>868</v>
-      </c>
-      <c r="AP249" t="s" s="2">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="250">
-      <c r="A250" t="s" s="2">
-        <v>873</v>
-      </c>
-      <c r="B250" t="s" s="2">
-        <v>873</v>
-      </c>
-      <c r="C250" s="2"/>
-      <c r="D250" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="E250" s="2"/>
-      <c r="F250" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="G250" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="H250" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="I250" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="J250" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="K250" t="s" s="2">
-        <v>874</v>
-      </c>
-      <c r="L250" t="s" s="2">
-        <v>875</v>
-      </c>
-      <c r="M250" t="s" s="2">
-        <v>876</v>
-      </c>
-      <c r="N250" s="2"/>
-      <c r="O250" s="2"/>
-      <c r="P250" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Q250" s="2"/>
-      <c r="R250" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="S250" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="T250" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="U250" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="V250" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="W250" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="X250" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Y250" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Z250" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AA250" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB250" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC250" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AD250" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE250" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AF250" t="s" s="2">
-        <v>873</v>
-      </c>
-      <c r="AG250" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH250" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AI250" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AJ250" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="AK250" t="s" s="2">
-        <v>877</v>
-      </c>
-      <c r="AL250" t="s" s="2">
-        <v>878</v>
-      </c>
-      <c r="AM250" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN250" t="s" s="2">
-        <v>879</v>
-      </c>
-      <c r="AO250" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AP250" t="s" s="2">
         <v>80</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AP250">
+  <autoFilter ref="A1:AP232">
     <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -33134,7 +30833,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI249">
+  <conditionalFormatting sqref="A2:AI231">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/branches/develop/StructureDefinition-mii-pr-diagnose-condition.xlsx
+++ b/branches/develop/StructureDefinition-mii-pr-diagnose-condition.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2027.0.0-ballot.rc1</t>
+    <t>2027.0.0-ballot</t>
   </si>
   <si>
     <t>Name</t>
